--- a/Data/FairCarboN_Datas_Contacts.xlsx
+++ b/Data/FairCarboN_Datas_Contacts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01697B8B-4B4E-496F-A3BD-C4CC9A2749B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122DAB6C-F776-4063-B01B-0089419CD2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Liste" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Liste!$A$1:$Q$416</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Liste!$A$1:$R$416</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4868" uniqueCount="1781">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5284" uniqueCount="1783">
   <si>
     <t>Titre : Liste des unités du PEPR FairCarboN</t>
   </si>
@@ -5394,6 +5394,12 @@
   </si>
   <si>
     <t>Michelle</t>
+  </si>
+  <si>
+    <t>Sollicitation</t>
+  </si>
+  <si>
+    <t>NON</t>
   </si>
 </sst>
 </file>
@@ -5616,7 +5622,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5639,6 +5645,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -5684,7 +5696,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5840,6 +5852,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6199,8 +6214,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:Q416"/>
+  <dimension ref="A1:R416"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.54296875" style="8" bestFit="1" customWidth="1"/>
@@ -6213,16 +6227,16 @@
     <col min="9" max="9" width="27.81640625" style="36" customWidth="1"/>
     <col min="10" max="10" width="12" style="8" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.90625" style="8" customWidth="1"/>
-    <col min="13" max="13" width="17.36328125" style="8" customWidth="1"/>
-    <col min="14" max="14" width="15" style="8" customWidth="1"/>
-    <col min="15" max="15" width="10.90625" style="8" customWidth="1"/>
-    <col min="16" max="16" width="14.6328125" style="8" customWidth="1"/>
-    <col min="17" max="17" width="68.7265625" style="8" customWidth="1"/>
-    <col min="18" max="16384" width="8.7265625" style="8"/>
+    <col min="12" max="13" width="22.90625" style="8" customWidth="1"/>
+    <col min="14" max="14" width="17.36328125" style="8" customWidth="1"/>
+    <col min="15" max="15" width="15" style="8" customWidth="1"/>
+    <col min="16" max="16" width="10.90625" style="8" customWidth="1"/>
+    <col min="17" max="17" width="14.6328125" style="8" customWidth="1"/>
+    <col min="18" max="18" width="68.7265625" style="8" customWidth="1"/>
+    <col min="19" max="16384" width="8.7265625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="47" t="s">
         <v>3</v>
       </c>
@@ -6259,23 +6273,26 @@
       <c r="L1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="M1" s="57" t="s">
+        <v>1781</v>
+      </c>
+      <c r="N1" s="46" t="s">
         <v>1758</v>
       </c>
-      <c r="N1" s="46" t="s">
+      <c r="O1" s="46" t="s">
         <v>1761</v>
       </c>
-      <c r="O1" s="46" t="s">
+      <c r="P1" s="46" t="s">
         <v>1763</v>
       </c>
-      <c r="P1" s="46" t="s">
+      <c r="Q1" s="46" t="s">
         <v>1764</v>
       </c>
-      <c r="Q1" s="46" t="s">
+      <c r="R1" s="46" t="s">
         <v>1765</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="3" customFormat="1" ht="188.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -6312,13 +6329,16 @@
       <c r="L2" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="M2" s="2"/>
+      <c r="M2" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
-    </row>
-    <row r="3" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R2" s="2"/>
+    </row>
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -6355,13 +6375,16 @@
       <c r="L3" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="M3" s="2"/>
+      <c r="M3" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
-    </row>
-    <row r="4" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R3" s="2"/>
+    </row>
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -6398,13 +6421,16 @@
       <c r="L4" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="M4" s="2"/>
+      <c r="M4" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
-    </row>
-    <row r="5" spans="1:17" s="3" customFormat="1" ht="188.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R4" s="2"/>
+    </row>
+    <row r="5" spans="1:18" s="3" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -6441,13 +6467,16 @@
       <c r="L5" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="M5" s="2"/>
+      <c r="M5" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
-    </row>
-    <row r="6" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R5" s="2"/>
+    </row>
+    <row r="6" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -6484,13 +6513,16 @@
       <c r="L6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M6" s="2"/>
+      <c r="M6" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
-    </row>
-    <row r="7" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R6" s="2"/>
+    </row>
+    <row r="7" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
@@ -6527,13 +6559,16 @@
       <c r="L7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="2"/>
+      <c r="M7" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -6570,13 +6605,16 @@
       <c r="L8" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M8" s="2"/>
+      <c r="M8" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
-    </row>
-    <row r="9" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R8" s="2"/>
+    </row>
+    <row r="9" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
@@ -6613,13 +6651,16 @@
       <c r="L9" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M9" s="2"/>
+      <c r="M9" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
-    </row>
-    <row r="10" spans="1:17" s="3" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R9" s="2"/>
+    </row>
+    <row r="10" spans="1:18" s="3" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -6656,13 +6697,16 @@
       <c r="L10" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="M10" s="2"/>
+      <c r="M10" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
-    </row>
-    <row r="11" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R10" s="2"/>
+    </row>
+    <row r="11" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -6699,13 +6743,16 @@
       <c r="L11" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="M11" s="2"/>
+      <c r="M11" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
-    </row>
-    <row r="12" spans="1:17" s="3" customFormat="1" ht="188.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R11" s="2"/>
+    </row>
+    <row r="12" spans="1:18" s="3" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -6742,13 +6789,16 @@
       <c r="L12" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="M12" s="2"/>
+      <c r="M12" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
-    </row>
-    <row r="13" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R12" s="2"/>
+    </row>
+    <row r="13" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
@@ -6785,13 +6835,16 @@
       <c r="L13" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="M13" s="2"/>
+      <c r="M13" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
-    </row>
-    <row r="14" spans="1:17" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="R13" s="2"/>
+    </row>
+    <row r="14" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
@@ -6828,13 +6881,16 @@
       <c r="L14" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="M14" s="2"/>
+      <c r="M14" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
-    </row>
-    <row r="15" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R14" s="2"/>
+    </row>
+    <row r="15" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
@@ -6871,13 +6927,16 @@
       <c r="L15" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="M15" s="2"/>
+      <c r="M15" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
-    </row>
-    <row r="16" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R15" s="2"/>
+    </row>
+    <row r="16" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
@@ -6914,13 +6973,16 @@
       <c r="L16" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="M16" s="2"/>
+      <c r="M16" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
-    </row>
-    <row r="17" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R16" s="2"/>
+    </row>
+    <row r="17" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>9</v>
       </c>
@@ -6957,13 +7019,16 @@
       <c r="L17" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="M17" s="2"/>
+      <c r="M17" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
-    </row>
-    <row r="18" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R17" s="2"/>
+    </row>
+    <row r="18" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>9</v>
       </c>
@@ -7000,13 +7065,16 @@
       <c r="L18" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="M18" s="2"/>
+      <c r="M18" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
-    </row>
-    <row r="19" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R18" s="2"/>
+    </row>
+    <row r="19" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
@@ -7043,13 +7111,16 @@
       <c r="L19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M19" s="2"/>
+      <c r="M19" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
-    </row>
-    <row r="20" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R19" s="2"/>
+    </row>
+    <row r="20" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
@@ -7086,13 +7157,16 @@
       <c r="L20" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="M20" s="2"/>
+      <c r="M20" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
-    </row>
-    <row r="21" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R20" s="2"/>
+    </row>
+    <row r="21" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
@@ -7129,13 +7203,16 @@
       <c r="L21" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M21" s="2"/>
+      <c r="M21" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
-    </row>
-    <row r="22" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R21" s="2"/>
+    </row>
+    <row r="22" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
@@ -7172,13 +7249,16 @@
       <c r="L22" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M22" s="2"/>
+      <c r="M22" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
-    </row>
-    <row r="23" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R22" s="2"/>
+    </row>
+    <row r="23" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
@@ -7215,13 +7295,16 @@
       <c r="L23" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M23" s="2"/>
+      <c r="M23" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
       <c r="Q23" s="2"/>
-    </row>
-    <row r="24" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R23" s="2"/>
+    </row>
+    <row r="24" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>9</v>
       </c>
@@ -7258,13 +7341,16 @@
       <c r="L24" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M24" s="2"/>
+      <c r="M24" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
       <c r="Q24" s="2"/>
-    </row>
-    <row r="25" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R24" s="2"/>
+    </row>
+    <row r="25" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>9</v>
       </c>
@@ -7301,13 +7387,16 @@
       <c r="L25" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M25" s="2"/>
+      <c r="M25" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
-    </row>
-    <row r="26" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R25" s="2"/>
+    </row>
+    <row r="26" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>9</v>
       </c>
@@ -7344,13 +7433,16 @@
       <c r="L26" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="M26" s="2"/>
+      <c r="M26" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
-    </row>
-    <row r="27" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R26" s="2"/>
+    </row>
+    <row r="27" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>9</v>
       </c>
@@ -7387,13 +7479,16 @@
       <c r="L27" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="M27" s="2"/>
+      <c r="M27" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
-    </row>
-    <row r="28" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R27" s="2"/>
+    </row>
+    <row r="28" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>9</v>
       </c>
@@ -7430,13 +7525,16 @@
       <c r="L28" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="M28" s="2"/>
+      <c r="M28" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
       <c r="Q28" s="2"/>
-    </row>
-    <row r="29" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R28" s="2"/>
+    </row>
+    <row r="29" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>9</v>
       </c>
@@ -7473,13 +7571,16 @@
       <c r="L29" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="M29" s="2"/>
+      <c r="M29" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
-    </row>
-    <row r="30" spans="1:17" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R29" s="2"/>
+    </row>
+    <row r="30" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>9</v>
       </c>
@@ -7516,13 +7617,16 @@
       <c r="L30" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="M30" s="2"/>
+      <c r="M30" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
-    </row>
-    <row r="31" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R30" s="2"/>
+    </row>
+    <row r="31" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>9</v>
       </c>
@@ -7559,13 +7663,16 @@
       <c r="L31" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M31" s="2"/>
+      <c r="M31" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
       <c r="Q31" s="2"/>
-    </row>
-    <row r="32" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R31" s="2"/>
+    </row>
+    <row r="32" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>9</v>
       </c>
@@ -7602,13 +7709,16 @@
       <c r="L32" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="M32" s="2"/>
+      <c r="M32" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
       <c r="Q32" s="2"/>
-    </row>
-    <row r="33" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R32" s="2"/>
+    </row>
+    <row r="33" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>9</v>
       </c>
@@ -7645,13 +7755,16 @@
       <c r="L33" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M33" s="2"/>
+      <c r="M33" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
       <c r="Q33" s="2"/>
-    </row>
-    <row r="34" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R33" s="2"/>
+    </row>
+    <row r="34" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>9</v>
       </c>
@@ -7688,13 +7801,16 @@
       <c r="L34" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M34" s="2"/>
+      <c r="M34" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
-    </row>
-    <row r="35" spans="1:17" s="3" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R34" s="2"/>
+    </row>
+    <row r="35" spans="1:18" s="3" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>9</v>
       </c>
@@ -7731,13 +7847,16 @@
       <c r="L35" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="M35" s="2"/>
+      <c r="M35" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
-    </row>
-    <row r="36" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R35" s="2"/>
+    </row>
+    <row r="36" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>9</v>
       </c>
@@ -7774,13 +7893,16 @@
       <c r="L36" s="11" t="s">
         <v>366</v>
       </c>
-      <c r="M36" s="2"/>
+      <c r="M36" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
       <c r="Q36" s="2"/>
-    </row>
-    <row r="37" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R36" s="2"/>
+    </row>
+    <row r="37" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>9</v>
       </c>
@@ -7817,13 +7939,16 @@
       <c r="L37" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="M37" s="2"/>
+      <c r="M37" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
-    </row>
-    <row r="38" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R37" s="2"/>
+    </row>
+    <row r="38" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>9</v>
       </c>
@@ -7860,13 +7985,16 @@
       <c r="L38" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M38" s="2"/>
+      <c r="M38" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
       <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="1:17" s="3" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="1:18" s="3" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>9</v>
       </c>
@@ -7903,13 +8031,16 @@
       <c r="L39" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="M39" s="2"/>
+      <c r="M39" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
       <c r="Q39" s="2"/>
-    </row>
-    <row r="40" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R39" s="2"/>
+    </row>
+    <row r="40" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>9</v>
       </c>
@@ -7946,13 +8077,16 @@
       <c r="L40" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="M40" s="2"/>
+      <c r="M40" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
-    </row>
-    <row r="41" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R40" s="2"/>
+    </row>
+    <row r="41" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>9</v>
       </c>
@@ -7989,13 +8123,16 @@
       <c r="L41" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="M41" s="2"/>
+      <c r="M41" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" s="2"/>
       <c r="Q41" s="2"/>
-    </row>
-    <row r="42" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R41" s="2"/>
+    </row>
+    <row r="42" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>9</v>
       </c>
@@ -8032,13 +8169,16 @@
       <c r="L42" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="M42" s="2"/>
+      <c r="M42" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" s="2"/>
       <c r="Q42" s="2"/>
-    </row>
-    <row r="43" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R42" s="2"/>
+    </row>
+    <row r="43" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>9</v>
       </c>
@@ -8075,13 +8215,16 @@
       <c r="L43" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="M43" s="2"/>
+      <c r="M43" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" s="2"/>
       <c r="Q43" s="2"/>
-    </row>
-    <row r="44" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R43" s="2"/>
+    </row>
+    <row r="44" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>9</v>
       </c>
@@ -8118,13 +8261,16 @@
       <c r="L44" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="M44" s="2"/>
+      <c r="M44" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" s="2"/>
       <c r="Q44" s="2"/>
-    </row>
-    <row r="45" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R44" s="2"/>
+    </row>
+    <row r="45" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>9</v>
       </c>
@@ -8161,13 +8307,16 @@
       <c r="L45" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="M45" s="2"/>
+      <c r="M45" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" s="2"/>
       <c r="Q45" s="2"/>
-    </row>
-    <row r="46" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R45" s="2"/>
+    </row>
+    <row r="46" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>9</v>
       </c>
@@ -8204,13 +8353,16 @@
       <c r="L46" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="M46" s="2"/>
+      <c r="M46" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" s="2"/>
       <c r="Q46" s="2"/>
-    </row>
-    <row r="47" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R46" s="2"/>
+    </row>
+    <row r="47" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>9</v>
       </c>
@@ -8247,13 +8399,16 @@
       <c r="L47" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M47" s="2"/>
+      <c r="M47" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
       <c r="Q47" s="2"/>
-    </row>
-    <row r="48" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R47" s="2"/>
+    </row>
+    <row r="48" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>9</v>
       </c>
@@ -8290,13 +8445,16 @@
       <c r="L48" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="M48" s="2"/>
+      <c r="M48" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" s="2"/>
       <c r="Q48" s="2"/>
-    </row>
-    <row r="49" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R48" s="2"/>
+    </row>
+    <row r="49" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>9</v>
       </c>
@@ -8333,13 +8491,16 @@
       <c r="L49" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="M49" s="2"/>
+      <c r="M49" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
       <c r="Q49" s="2"/>
-    </row>
-    <row r="50" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R49" s="2"/>
+    </row>
+    <row r="50" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>9</v>
       </c>
@@ -8376,13 +8537,16 @@
       <c r="L50" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="M50" s="2"/>
+      <c r="M50" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" s="2"/>
       <c r="Q50" s="2"/>
-    </row>
-    <row r="51" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R50" s="2"/>
+    </row>
+    <row r="51" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>9</v>
       </c>
@@ -8419,13 +8583,16 @@
       <c r="L51" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="M51" s="2"/>
+      <c r="M51" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" s="2"/>
       <c r="Q51" s="2"/>
-    </row>
-    <row r="52" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R51" s="2"/>
+    </row>
+    <row r="52" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>9</v>
       </c>
@@ -8462,13 +8629,16 @@
       <c r="L52" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="M52" s="2"/>
+      <c r="M52" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" s="2"/>
       <c r="Q52" s="2"/>
-    </row>
-    <row r="53" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R52" s="2"/>
+    </row>
+    <row r="53" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>9</v>
       </c>
@@ -8505,13 +8675,16 @@
       <c r="L53" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="M53" s="2"/>
+      <c r="M53" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" s="2"/>
       <c r="Q53" s="2"/>
-    </row>
-    <row r="54" spans="1:17" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R53" s="2"/>
+    </row>
+    <row r="54" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>9</v>
       </c>
@@ -8548,13 +8721,16 @@
       <c r="L54" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="M54" s="2"/>
+      <c r="M54" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" s="2"/>
       <c r="Q54" s="2"/>
-    </row>
-    <row r="55" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R54" s="2"/>
+    </row>
+    <row r="55" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>9</v>
       </c>
@@ -8591,13 +8767,16 @@
       <c r="L55" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="M55" s="2"/>
+      <c r="M55" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" s="2"/>
       <c r="Q55" s="2"/>
-    </row>
-    <row r="56" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R55" s="2"/>
+    </row>
+    <row r="56" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>9</v>
       </c>
@@ -8634,13 +8813,16 @@
       <c r="L56" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="M56" s="2"/>
+      <c r="M56" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" s="2"/>
       <c r="Q56" s="2"/>
-    </row>
-    <row r="57" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R56" s="2"/>
+    </row>
+    <row r="57" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>9</v>
       </c>
@@ -8677,13 +8859,16 @@
       <c r="L57" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="M57" s="2"/>
+      <c r="M57" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
       <c r="Q57" s="2"/>
-    </row>
-    <row r="58" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R57" s="2"/>
+    </row>
+    <row r="58" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>9</v>
       </c>
@@ -8720,13 +8905,16 @@
       <c r="L58" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="M58" s="2"/>
+      <c r="M58" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" s="2"/>
       <c r="Q58" s="2"/>
-    </row>
-    <row r="59" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R58" s="2"/>
+    </row>
+    <row r="59" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>9</v>
       </c>
@@ -8763,13 +8951,16 @@
       <c r="L59" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="M59" s="2"/>
+      <c r="M59" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" s="2"/>
       <c r="Q59" s="2"/>
-    </row>
-    <row r="60" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R59" s="2"/>
+    </row>
+    <row r="60" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>9</v>
       </c>
@@ -8806,13 +8997,16 @@
       <c r="L60" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="M60" s="2"/>
+      <c r="M60" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" s="2"/>
       <c r="Q60" s="2"/>
-    </row>
-    <row r="61" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R60" s="2"/>
+    </row>
+    <row r="61" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>9</v>
       </c>
@@ -8849,13 +9043,16 @@
       <c r="L61" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="M61" s="2"/>
+      <c r="M61" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" s="2"/>
       <c r="Q61" s="2"/>
-    </row>
-    <row r="62" spans="1:17" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R61" s="2"/>
+    </row>
+    <row r="62" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>9</v>
       </c>
@@ -8892,13 +9089,16 @@
       <c r="L62" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="M62" s="2"/>
+      <c r="M62" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" s="2"/>
       <c r="Q62" s="2"/>
-    </row>
-    <row r="63" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R62" s="2"/>
+    </row>
+    <row r="63" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>9</v>
       </c>
@@ -8935,13 +9135,16 @@
       <c r="L63" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="M63" s="2"/>
+      <c r="M63" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" s="2"/>
       <c r="Q63" s="2"/>
-    </row>
-    <row r="64" spans="1:17" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R63" s="2"/>
+    </row>
+    <row r="64" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>9</v>
       </c>
@@ -8978,13 +9181,16 @@
       <c r="L64" s="2" t="s">
         <v>748</v>
       </c>
-      <c r="M64" s="2"/>
+      <c r="M64" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" s="2"/>
       <c r="Q64" s="2"/>
-    </row>
-    <row r="65" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R64" s="2"/>
+    </row>
+    <row r="65" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>9</v>
       </c>
@@ -9021,13 +9227,16 @@
       <c r="L65" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="M65" s="2"/>
+      <c r="M65" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" s="2"/>
       <c r="Q65" s="2"/>
-    </row>
-    <row r="66" spans="1:17" s="3" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R65" s="2"/>
+    </row>
+    <row r="66" spans="1:18" s="3" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>9</v>
       </c>
@@ -9064,13 +9273,16 @@
       <c r="L66" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="M66" s="2"/>
+      <c r="M66" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" s="2"/>
       <c r="Q66" s="2"/>
-    </row>
-    <row r="67" spans="1:17" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R66" s="2"/>
+    </row>
+    <row r="67" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>9</v>
       </c>
@@ -9107,13 +9319,16 @@
       <c r="L67" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="M67" s="2"/>
+      <c r="M67" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" s="2"/>
       <c r="Q67" s="2"/>
-    </row>
-    <row r="68" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R67" s="2"/>
+    </row>
+    <row r="68" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>9</v>
       </c>
@@ -9150,13 +9365,16 @@
       <c r="L68" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="M68" s="2"/>
+      <c r="M68" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" s="2"/>
       <c r="Q68" s="2"/>
-    </row>
-    <row r="69" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R68" s="2"/>
+    </row>
+    <row r="69" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>9</v>
       </c>
@@ -9193,13 +9411,16 @@
       <c r="L69" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="M69" s="2"/>
+      <c r="M69" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" s="2"/>
       <c r="Q69" s="2"/>
-    </row>
-    <row r="70" spans="1:17" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R69" s="2"/>
+    </row>
+    <row r="70" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>9</v>
       </c>
@@ -9236,13 +9457,16 @@
       <c r="L70" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="M70" s="2"/>
+      <c r="M70" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" s="2"/>
       <c r="Q70" s="2"/>
-    </row>
-    <row r="71" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R70" s="2"/>
+    </row>
+    <row r="71" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>9</v>
       </c>
@@ -9279,13 +9503,16 @@
       <c r="L71" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="M71" s="2"/>
+      <c r="M71" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" s="2"/>
       <c r="Q71" s="2"/>
-    </row>
-    <row r="72" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R71" s="2"/>
+    </row>
+    <row r="72" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>9</v>
       </c>
@@ -9322,13 +9549,16 @@
       <c r="L72" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="M72" s="2"/>
+      <c r="M72" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" s="2"/>
       <c r="Q72" s="2"/>
-    </row>
-    <row r="73" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R72" s="2"/>
+    </row>
+    <row r="73" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>9</v>
       </c>
@@ -9365,13 +9595,16 @@
       <c r="L73" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="M73" s="2"/>
+      <c r="M73" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" s="2"/>
       <c r="Q73" s="2"/>
-    </row>
-    <row r="74" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R73" s="2"/>
+    </row>
+    <row r="74" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>9</v>
       </c>
@@ -9408,13 +9641,16 @@
       <c r="L74" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="M74" s="2"/>
+      <c r="M74" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" s="2"/>
       <c r="Q74" s="2"/>
-    </row>
-    <row r="75" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R74" s="2"/>
+    </row>
+    <row r="75" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>9</v>
       </c>
@@ -9451,13 +9687,16 @@
       <c r="L75" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="M75" s="2"/>
+      <c r="M75" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" s="2"/>
       <c r="Q75" s="2"/>
-    </row>
-    <row r="76" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R75" s="2"/>
+    </row>
+    <row r="76" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>9</v>
       </c>
@@ -9494,13 +9733,16 @@
       <c r="L76" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="M76" s="2"/>
+      <c r="M76" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" s="2"/>
       <c r="Q76" s="2"/>
-    </row>
-    <row r="77" spans="1:17" s="3" customFormat="1" ht="27.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R76" s="2"/>
+    </row>
+    <row r="77" spans="1:18" s="3" customFormat="1" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>9</v>
       </c>
@@ -9537,13 +9779,16 @@
       <c r="L77" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="M77" s="2"/>
+      <c r="M77" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" s="2"/>
       <c r="Q77" s="2"/>
-    </row>
-    <row r="78" spans="1:17" s="3" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R77" s="2"/>
+    </row>
+    <row r="78" spans="1:18" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>9</v>
       </c>
@@ -9580,13 +9825,16 @@
       <c r="L78" s="21" t="s">
         <v>734</v>
       </c>
-      <c r="M78" s="2"/>
+      <c r="M78" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" s="2"/>
       <c r="Q78" s="2"/>
-    </row>
-    <row r="79" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R78" s="2"/>
+    </row>
+    <row r="79" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>9</v>
       </c>
@@ -9623,13 +9871,16 @@
       <c r="L79" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="M79" s="2"/>
+      <c r="M79" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" s="2"/>
       <c r="Q79" s="2"/>
-    </row>
-    <row r="80" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R79" s="2"/>
+    </row>
+    <row r="80" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>9</v>
       </c>
@@ -9666,13 +9917,16 @@
       <c r="L80" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="M80" s="2"/>
+      <c r="M80" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" s="2"/>
       <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>9</v>
       </c>
@@ -9709,13 +9963,16 @@
       <c r="L81" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="M81" s="2"/>
+      <c r="M81" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" s="2"/>
       <c r="Q81" s="2"/>
-    </row>
-    <row r="82" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R81" s="2"/>
+    </row>
+    <row r="82" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>9</v>
       </c>
@@ -9752,13 +10009,16 @@
       <c r="L82" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="M82" s="2"/>
+      <c r="M82" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" s="2"/>
       <c r="Q82" s="2"/>
-    </row>
-    <row r="83" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R82" s="2"/>
+    </row>
+    <row r="83" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>9</v>
       </c>
@@ -9795,13 +10055,16 @@
       <c r="L83" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="M83" s="2"/>
+      <c r="M83" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" s="2"/>
       <c r="Q83" s="2"/>
-    </row>
-    <row r="84" spans="1:17" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R83" s="2"/>
+    </row>
+    <row r="84" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>9</v>
       </c>
@@ -9838,13 +10101,16 @@
       <c r="L84" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="M84" s="2"/>
+      <c r="M84" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" s="2"/>
       <c r="Q84" s="2"/>
-    </row>
-    <row r="85" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R84" s="2"/>
+    </row>
+    <row r="85" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>9</v>
       </c>
@@ -9881,13 +10147,16 @@
       <c r="L85" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="M85" s="2"/>
+      <c r="M85" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" s="2"/>
       <c r="Q85" s="2"/>
-    </row>
-    <row r="86" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R85" s="2"/>
+    </row>
+    <row r="86" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>9</v>
       </c>
@@ -9924,13 +10193,16 @@
       <c r="L86" s="43" t="s">
         <v>1738</v>
       </c>
-      <c r="M86" s="2"/>
+      <c r="M86" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" s="2"/>
       <c r="Q86" s="2"/>
-    </row>
-    <row r="87" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R86" s="2"/>
+    </row>
+    <row r="87" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>9</v>
       </c>
@@ -9967,13 +10239,16 @@
       <c r="L87" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="M87" s="2"/>
+      <c r="M87" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" s="2"/>
       <c r="Q87" s="2"/>
-    </row>
-    <row r="88" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R87" s="2"/>
+    </row>
+    <row r="88" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>9</v>
       </c>
@@ -10010,13 +10285,16 @@
       <c r="L88" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="M88" s="2"/>
+      <c r="M88" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" s="2"/>
       <c r="Q88" s="2"/>
-    </row>
-    <row r="89" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R88" s="2"/>
+    </row>
+    <row r="89" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>9</v>
       </c>
@@ -10051,13 +10329,16 @@
       <c r="L89" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="M89" s="2"/>
+      <c r="M89" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" s="2"/>
       <c r="Q89" s="2"/>
-    </row>
-    <row r="90" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R89" s="2"/>
+    </row>
+    <row r="90" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>9</v>
       </c>
@@ -10094,13 +10375,16 @@
       <c r="L90" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="M90" s="2"/>
+      <c r="M90" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" s="2"/>
       <c r="Q90" s="2"/>
-    </row>
-    <row r="91" spans="1:17" s="3" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R90" s="2"/>
+    </row>
+    <row r="91" spans="1:18" s="3" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>9</v>
       </c>
@@ -10137,13 +10421,16 @@
       <c r="L91" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="M91" s="2"/>
+      <c r="M91" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
       <c r="Q91" s="2"/>
-    </row>
-    <row r="92" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R91" s="2"/>
+    </row>
+    <row r="92" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>9</v>
       </c>
@@ -10180,13 +10467,16 @@
       <c r="L92" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="M92" s="2"/>
+      <c r="M92" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
       <c r="Q92" s="2"/>
-    </row>
-    <row r="93" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R92" s="2"/>
+    </row>
+    <row r="93" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>9</v>
       </c>
@@ -10223,13 +10513,16 @@
       <c r="L93" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="M93" s="2"/>
+      <c r="M93" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" s="2"/>
       <c r="Q93" s="2"/>
-    </row>
-    <row r="94" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R93" s="2"/>
+    </row>
+    <row r="94" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>9</v>
       </c>
@@ -10266,13 +10559,16 @@
       <c r="L94" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="M94" s="2"/>
+      <c r="M94" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" s="2"/>
       <c r="Q94" s="2"/>
-    </row>
-    <row r="95" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R94" s="2"/>
+    </row>
+    <row r="95" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>9</v>
       </c>
@@ -10309,13 +10605,16 @@
       <c r="L95" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="M95" s="2"/>
+      <c r="M95" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" s="2"/>
       <c r="Q95" s="2"/>
-    </row>
-    <row r="96" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R95" s="2"/>
+    </row>
+    <row r="96" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>9</v>
       </c>
@@ -10352,13 +10651,16 @@
       <c r="L96" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M96" s="2"/>
+      <c r="M96" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" s="2"/>
       <c r="Q96" s="2"/>
-    </row>
-    <row r="97" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R96" s="2"/>
+    </row>
+    <row r="97" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>9</v>
       </c>
@@ -10395,13 +10697,16 @@
       <c r="L97" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="M97" s="2"/>
+      <c r="M97" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" s="2"/>
       <c r="Q97" s="2"/>
-    </row>
-    <row r="98" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R97" s="2"/>
+    </row>
+    <row r="98" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>9</v>
       </c>
@@ -10438,13 +10743,16 @@
       <c r="L98" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="M98" s="2"/>
+      <c r="M98" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" s="2"/>
       <c r="Q98" s="2"/>
-    </row>
-    <row r="99" spans="1:17" s="3" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R98" s="2"/>
+    </row>
+    <row r="99" spans="1:18" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>9</v>
       </c>
@@ -10481,13 +10789,16 @@
       <c r="L99" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="M99" s="2"/>
+      <c r="M99" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" s="2"/>
       <c r="Q99" s="2"/>
-    </row>
-    <row r="100" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R99" s="2"/>
+    </row>
+    <row r="100" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>9</v>
       </c>
@@ -10524,13 +10835,16 @@
       <c r="L100" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="M100" s="2"/>
+      <c r="M100" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" s="2"/>
       <c r="Q100" s="2"/>
-    </row>
-    <row r="101" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R100" s="2"/>
+    </row>
+    <row r="101" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>9</v>
       </c>
@@ -10565,13 +10879,16 @@
       <c r="L101" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="M101" s="2"/>
+      <c r="M101" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" s="2"/>
       <c r="Q101" s="2"/>
-    </row>
-    <row r="102" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R101" s="2"/>
+    </row>
+    <row r="102" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>9</v>
       </c>
@@ -10608,13 +10925,16 @@
       <c r="L102" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="M102" s="2"/>
+      <c r="M102" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" s="2"/>
       <c r="Q102" s="2"/>
-    </row>
-    <row r="103" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R102" s="2"/>
+    </row>
+    <row r="103" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>9</v>
       </c>
@@ -10651,13 +10971,16 @@
       <c r="L103" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="M103" s="2"/>
+      <c r="M103" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" s="2"/>
       <c r="Q103" s="2"/>
-    </row>
-    <row r="104" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R103" s="2"/>
+    </row>
+    <row r="104" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>9</v>
       </c>
@@ -10692,13 +11015,16 @@
       <c r="L104" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="M104" s="2"/>
+      <c r="M104" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" s="2"/>
       <c r="Q104" s="2"/>
-    </row>
-    <row r="105" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R104" s="2"/>
+    </row>
+    <row r="105" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>9</v>
       </c>
@@ -10735,13 +11061,16 @@
       <c r="L105" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="M105" s="2"/>
+      <c r="M105" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" s="2"/>
       <c r="Q105" s="2"/>
-    </row>
-    <row r="106" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R105" s="2"/>
+    </row>
+    <row r="106" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>9</v>
       </c>
@@ -10778,13 +11107,16 @@
       <c r="L106" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="M106" s="2"/>
+      <c r="M106" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" s="2"/>
       <c r="Q106" s="2"/>
-    </row>
-    <row r="107" spans="1:17" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R106" s="2"/>
+    </row>
+    <row r="107" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>9</v>
       </c>
@@ -10821,13 +11153,16 @@
       <c r="L107" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="M107" s="2"/>
+      <c r="M107" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" s="2"/>
       <c r="Q107" s="2"/>
-    </row>
-    <row r="108" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R107" s="2"/>
+    </row>
+    <row r="108" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>9</v>
       </c>
@@ -10864,13 +11199,16 @@
       <c r="L108" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="M108" s="2"/>
+      <c r="M108" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" s="2"/>
       <c r="Q108" s="2"/>
-    </row>
-    <row r="109" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R108" s="2"/>
+    </row>
+    <row r="109" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>9</v>
       </c>
@@ -10905,13 +11243,16 @@
       <c r="L109" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="M109" s="2"/>
+      <c r="M109" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" s="2"/>
       <c r="Q109" s="2"/>
-    </row>
-    <row r="110" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R109" s="2"/>
+    </row>
+    <row r="110" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>9</v>
       </c>
@@ -10948,13 +11289,16 @@
       <c r="L110" s="43" t="s">
         <v>1738</v>
       </c>
-      <c r="M110" s="2"/>
+      <c r="M110" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" s="2"/>
       <c r="Q110" s="2"/>
-    </row>
-    <row r="111" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R110" s="2"/>
+    </row>
+    <row r="111" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>9</v>
       </c>
@@ -10991,13 +11335,16 @@
       <c r="L111" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="M111" s="2"/>
+      <c r="M111" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" s="2"/>
       <c r="Q111" s="2"/>
-    </row>
-    <row r="112" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R111" s="2"/>
+    </row>
+    <row r="112" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>9</v>
       </c>
@@ -11034,13 +11381,16 @@
       <c r="L112" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M112" s="2"/>
+      <c r="M112" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" s="2"/>
       <c r="Q112" s="2"/>
-    </row>
-    <row r="113" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R112" s="2"/>
+    </row>
+    <row r="113" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>9</v>
       </c>
@@ -11077,13 +11427,16 @@
       <c r="L113" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="M113" s="2"/>
+      <c r="M113" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" s="2"/>
       <c r="Q113" s="2"/>
-    </row>
-    <row r="114" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R113" s="2"/>
+    </row>
+    <row r="114" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>9</v>
       </c>
@@ -11120,13 +11473,16 @@
       <c r="L114" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="M114" s="2"/>
+      <c r="M114" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" s="2"/>
       <c r="Q114" s="2"/>
-    </row>
-    <row r="115" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R114" s="2"/>
+    </row>
+    <row r="115" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>9</v>
       </c>
@@ -11163,13 +11519,16 @@
       <c r="L115" s="43" t="s">
         <v>1738</v>
       </c>
-      <c r="M115" s="2"/>
+      <c r="M115" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" s="2"/>
       <c r="Q115" s="2"/>
-    </row>
-    <row r="116" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R115" s="2"/>
+    </row>
+    <row r="116" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>9</v>
       </c>
@@ -11206,13 +11565,16 @@
       <c r="L116" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="M116" s="2"/>
+      <c r="M116" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" s="2"/>
       <c r="Q116" s="2"/>
-    </row>
-    <row r="117" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R116" s="2"/>
+    </row>
+    <row r="117" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>9</v>
       </c>
@@ -11249,13 +11611,16 @@
       <c r="L117" s="43" t="s">
         <v>1738</v>
       </c>
-      <c r="M117" s="2"/>
+      <c r="M117" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" s="2"/>
       <c r="Q117" s="2"/>
-    </row>
-    <row r="118" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R117" s="2"/>
+    </row>
+    <row r="118" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>9</v>
       </c>
@@ -11292,13 +11657,16 @@
       <c r="L118" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="M118" s="2"/>
+      <c r="M118" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" s="2"/>
       <c r="Q118" s="2"/>
-    </row>
-    <row r="119" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R118" s="2"/>
+    </row>
+    <row r="119" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>9</v>
       </c>
@@ -11335,13 +11703,16 @@
       <c r="L119" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="M119" s="2"/>
+      <c r="M119" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" s="2"/>
       <c r="Q119" s="2"/>
-    </row>
-    <row r="120" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R119" s="2"/>
+    </row>
+    <row r="120" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>9</v>
       </c>
@@ -11378,13 +11749,16 @@
       <c r="L120" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="M120" s="2"/>
+      <c r="M120" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
       <c r="P120" s="2"/>
       <c r="Q120" s="2"/>
-    </row>
-    <row r="121" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R120" s="2"/>
+    </row>
+    <row r="121" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>9</v>
       </c>
@@ -11421,13 +11795,16 @@
       <c r="L121" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="M121" s="2"/>
+      <c r="M121" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
       <c r="P121" s="2"/>
       <c r="Q121" s="2"/>
-    </row>
-    <row r="122" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R121" s="2"/>
+    </row>
+    <row r="122" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>9</v>
       </c>
@@ -11464,13 +11841,16 @@
       <c r="L122" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="M122" s="2"/>
+      <c r="M122" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
       <c r="P122" s="2"/>
       <c r="Q122" s="2"/>
-    </row>
-    <row r="123" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R122" s="2"/>
+    </row>
+    <row r="123" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>9</v>
       </c>
@@ -11507,13 +11887,16 @@
       <c r="L123" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M123" s="2"/>
+      <c r="M123" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" s="2"/>
       <c r="Q123" s="2"/>
-    </row>
-    <row r="124" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R123" s="2"/>
+    </row>
+    <row r="124" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>9</v>
       </c>
@@ -11550,13 +11933,16 @@
       <c r="L124" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M124" s="2"/>
+      <c r="M124" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" s="2"/>
       <c r="Q124" s="2"/>
-    </row>
-    <row r="125" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R124" s="2"/>
+    </row>
+    <row r="125" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>9</v>
       </c>
@@ -11593,13 +11979,16 @@
       <c r="L125" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="M125" s="2"/>
+      <c r="M125" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
       <c r="P125" s="2"/>
       <c r="Q125" s="2"/>
-    </row>
-    <row r="126" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R125" s="2"/>
+    </row>
+    <row r="126" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>9</v>
       </c>
@@ -11636,13 +12025,16 @@
       <c r="L126" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="M126" s="2"/>
+      <c r="M126" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
       <c r="P126" s="2"/>
       <c r="Q126" s="2"/>
-    </row>
-    <row r="127" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R126" s="2"/>
+    </row>
+    <row r="127" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>9</v>
       </c>
@@ -11679,13 +12071,16 @@
       <c r="L127" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M127" s="2"/>
+      <c r="M127" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" s="2"/>
       <c r="Q127" s="2"/>
-    </row>
-    <row r="128" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R127" s="2"/>
+    </row>
+    <row r="128" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>9</v>
       </c>
@@ -11722,13 +12117,16 @@
       <c r="L128" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="M128" s="2"/>
+      <c r="M128" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
       <c r="P128" s="2"/>
       <c r="Q128" s="2"/>
-    </row>
-    <row r="129" spans="1:17" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R128" s="2"/>
+    </row>
+    <row r="129" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>9</v>
       </c>
@@ -11765,13 +12163,16 @@
       <c r="L129" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M129" s="2"/>
+      <c r="M129" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
       <c r="P129" s="2"/>
       <c r="Q129" s="2"/>
-    </row>
-    <row r="130" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R129" s="2"/>
+    </row>
+    <row r="130" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>9</v>
       </c>
@@ -11808,13 +12209,16 @@
       <c r="L130" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="M130" s="2"/>
+      <c r="M130" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" s="2"/>
       <c r="Q130" s="2"/>
-    </row>
-    <row r="131" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R130" s="2"/>
+    </row>
+    <row r="131" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>9</v>
       </c>
@@ -11851,13 +12255,16 @@
       <c r="L131" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M131" s="2"/>
+      <c r="M131" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
       <c r="P131" s="2"/>
       <c r="Q131" s="2"/>
-    </row>
-    <row r="132" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R131" s="2"/>
+    </row>
+    <row r="132" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>9</v>
       </c>
@@ -11894,13 +12301,16 @@
       <c r="L132" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="M132" s="2"/>
+      <c r="M132" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
       <c r="P132" s="2"/>
       <c r="Q132" s="2"/>
-    </row>
-    <row r="133" spans="1:17" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R132" s="2"/>
+    </row>
+    <row r="133" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>9</v>
       </c>
@@ -11937,13 +12347,16 @@
       <c r="L133" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="M133" s="2"/>
+      <c r="M133" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
       <c r="P133" s="2"/>
       <c r="Q133" s="2"/>
-    </row>
-    <row r="134" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R133" s="2"/>
+    </row>
+    <row r="134" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>9</v>
       </c>
@@ -11980,13 +12393,16 @@
       <c r="L134" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="M134" s="2"/>
+      <c r="M134" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" s="2"/>
       <c r="Q134" s="2"/>
-    </row>
-    <row r="135" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R134" s="2"/>
+    </row>
+    <row r="135" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>9</v>
       </c>
@@ -12023,13 +12439,16 @@
       <c r="L135" s="43" t="s">
         <v>1738</v>
       </c>
-      <c r="M135" s="2"/>
+      <c r="M135" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
       <c r="P135" s="2"/>
       <c r="Q135" s="2"/>
-    </row>
-    <row r="136" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R135" s="2"/>
+    </row>
+    <row r="136" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>9</v>
       </c>
@@ -12066,13 +12485,16 @@
       <c r="L136" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M136" s="2"/>
+      <c r="M136" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
       <c r="P136" s="2"/>
       <c r="Q136" s="2"/>
-    </row>
-    <row r="137" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R136" s="2"/>
+    </row>
+    <row r="137" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>9</v>
       </c>
@@ -12109,13 +12531,16 @@
       <c r="L137" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="M137" s="2"/>
+      <c r="M137" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
       <c r="P137" s="2"/>
       <c r="Q137" s="2"/>
-    </row>
-    <row r="138" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R137" s="2"/>
+    </row>
+    <row r="138" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>9</v>
       </c>
@@ -12152,13 +12577,16 @@
       <c r="L138" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="M138" s="2"/>
+      <c r="M138" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
       <c r="P138" s="2"/>
       <c r="Q138" s="2"/>
-    </row>
-    <row r="139" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R138" s="2"/>
+    </row>
+    <row r="139" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>9</v>
       </c>
@@ -12195,13 +12623,16 @@
       <c r="L139" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="M139" s="2"/>
+      <c r="M139" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
       <c r="P139" s="2"/>
       <c r="Q139" s="2"/>
-    </row>
-    <row r="140" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R139" s="2"/>
+    </row>
+    <row r="140" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>9</v>
       </c>
@@ -12238,13 +12669,16 @@
       <c r="L140" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M140" s="2"/>
+      <c r="M140" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
       <c r="P140" s="2"/>
       <c r="Q140" s="2"/>
-    </row>
-    <row r="141" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R140" s="2"/>
+    </row>
+    <row r="141" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>9</v>
       </c>
@@ -12281,13 +12715,16 @@
       <c r="L141" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M141" s="2"/>
+      <c r="M141" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
       <c r="P141" s="2"/>
       <c r="Q141" s="2"/>
-    </row>
-    <row r="142" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R141" s="2"/>
+    </row>
+    <row r="142" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>9</v>
       </c>
@@ -12324,13 +12761,16 @@
       <c r="L142" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="M142" s="2"/>
+      <c r="M142" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
       <c r="P142" s="2"/>
       <c r="Q142" s="2"/>
-    </row>
-    <row r="143" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R142" s="2"/>
+    </row>
+    <row r="143" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>9</v>
       </c>
@@ -12367,13 +12807,16 @@
       <c r="L143" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="M143" s="2"/>
+      <c r="M143" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
       <c r="P143" s="2"/>
       <c r="Q143" s="2"/>
-    </row>
-    <row r="144" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R143" s="2"/>
+    </row>
+    <row r="144" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>9</v>
       </c>
@@ -12410,13 +12853,16 @@
       <c r="L144" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="M144" s="2"/>
+      <c r="M144" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
       <c r="P144" s="2"/>
       <c r="Q144" s="2"/>
-    </row>
-    <row r="145" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R144" s="2"/>
+    </row>
+    <row r="145" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>9</v>
       </c>
@@ -12453,13 +12899,16 @@
       <c r="L145" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="M145" s="2"/>
+      <c r="M145" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
       <c r="P145" s="2"/>
       <c r="Q145" s="2"/>
-    </row>
-    <row r="146" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R145" s="2"/>
+    </row>
+    <row r="146" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>9</v>
       </c>
@@ -12496,13 +12945,16 @@
       <c r="L146" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M146" s="2"/>
+      <c r="M146" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
       <c r="P146" s="2"/>
       <c r="Q146" s="2"/>
-    </row>
-    <row r="147" spans="1:17" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R146" s="2"/>
+    </row>
+    <row r="147" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>9</v>
       </c>
@@ -12539,13 +12991,16 @@
       <c r="L147" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="M147" s="2"/>
+      <c r="M147" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
       <c r="P147" s="2"/>
       <c r="Q147" s="2"/>
-    </row>
-    <row r="148" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R147" s="2"/>
+    </row>
+    <row r="148" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>9</v>
       </c>
@@ -12582,13 +13037,16 @@
       <c r="L148" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="M148" s="2"/>
+      <c r="M148" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
       <c r="P148" s="2"/>
       <c r="Q148" s="2"/>
-    </row>
-    <row r="149" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R148" s="2"/>
+    </row>
+    <row r="149" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>9</v>
       </c>
@@ -12625,13 +13083,16 @@
       <c r="L149" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M149" s="2"/>
+      <c r="M149" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
       <c r="P149" s="2"/>
       <c r="Q149" s="2"/>
-    </row>
-    <row r="150" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R149" s="2"/>
+    </row>
+    <row r="150" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>9</v>
       </c>
@@ -12668,13 +13129,16 @@
       <c r="L150" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M150" s="2"/>
+      <c r="M150" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
       <c r="P150" s="2"/>
       <c r="Q150" s="2"/>
-    </row>
-    <row r="151" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R150" s="2"/>
+    </row>
+    <row r="151" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>9</v>
       </c>
@@ -12711,13 +13175,16 @@
       <c r="L151" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="M151" s="2"/>
+      <c r="M151" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
       <c r="P151" s="2"/>
       <c r="Q151" s="2"/>
-    </row>
-    <row r="152" spans="1:17" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R151" s="2"/>
+    </row>
+    <row r="152" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>9</v>
       </c>
@@ -12754,13 +13221,16 @@
       <c r="L152" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M152" s="2"/>
+      <c r="M152" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
       <c r="P152" s="2"/>
       <c r="Q152" s="2"/>
-    </row>
-    <row r="153" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R152" s="2"/>
+    </row>
+    <row r="153" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>9</v>
       </c>
@@ -12797,13 +13267,16 @@
       <c r="L153" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="M153" s="2"/>
+      <c r="M153" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
       <c r="P153" s="2"/>
       <c r="Q153" s="2"/>
-    </row>
-    <row r="154" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R153" s="2"/>
+    </row>
+    <row r="154" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>9</v>
       </c>
@@ -12840,13 +13313,16 @@
       <c r="L154" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M154" s="2"/>
+      <c r="M154" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
       <c r="P154" s="2"/>
       <c r="Q154" s="2"/>
-    </row>
-    <row r="155" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R154" s="2"/>
+    </row>
+    <row r="155" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>9</v>
       </c>
@@ -12883,13 +13359,16 @@
       <c r="L155" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M155" s="2"/>
+      <c r="M155" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
       <c r="P155" s="2"/>
       <c r="Q155" s="2"/>
-    </row>
-    <row r="156" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R155" s="2"/>
+    </row>
+    <row r="156" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>9</v>
       </c>
@@ -12926,13 +13405,16 @@
       <c r="L156" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M156" s="2"/>
+      <c r="M156" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
       <c r="P156" s="2"/>
       <c r="Q156" s="2"/>
-    </row>
-    <row r="157" spans="1:17" s="3" customFormat="1" ht="65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R156" s="2"/>
+    </row>
+    <row r="157" spans="1:18" s="3" customFormat="1" ht="65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>9</v>
       </c>
@@ -12970,22 +13452,25 @@
         <v>395</v>
       </c>
       <c r="M157" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="N157" s="2" t="s">
         <v>1759</v>
       </c>
-      <c r="N157" s="2" t="s">
+      <c r="O157" s="2" t="s">
         <v>1762</v>
       </c>
-      <c r="O157" s="2" t="s">
+      <c r="P157" s="2" t="s">
         <v>1766</v>
       </c>
-      <c r="P157" s="2" t="s">
+      <c r="Q157" s="2" t="s">
         <v>1767</v>
       </c>
-      <c r="Q157" s="2" t="s">
+      <c r="R157" s="2" t="s">
         <v>1768</v>
       </c>
     </row>
-    <row r="158" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>9</v>
       </c>
@@ -13023,14 +13508,17 @@
         <v>397</v>
       </c>
       <c r="M158" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="N158" s="2" t="s">
         <v>1759</v>
       </c>
-      <c r="N158" s="2"/>
       <c r="O158" s="2"/>
       <c r="P158" s="2"/>
       <c r="Q158" s="2"/>
-    </row>
-    <row r="159" spans="1:17" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R158" s="2"/>
+    </row>
+    <row r="159" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>9</v>
       </c>
@@ -13068,14 +13556,17 @@
         <v>1039</v>
       </c>
       <c r="M159" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="N159" s="2" t="s">
         <v>1759</v>
       </c>
-      <c r="N159" s="2"/>
       <c r="O159" s="2"/>
       <c r="P159" s="2"/>
       <c r="Q159" s="2"/>
-    </row>
-    <row r="160" spans="1:17" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R159" s="2"/>
+    </row>
+    <row r="160" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>9</v>
       </c>
@@ -13113,14 +13604,17 @@
         <v>1039</v>
       </c>
       <c r="M160" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="N160" s="2" t="s">
         <v>1759</v>
       </c>
-      <c r="N160" s="2"/>
       <c r="O160" s="2"/>
       <c r="P160" s="2"/>
       <c r="Q160" s="2"/>
-    </row>
-    <row r="161" spans="1:17" s="3" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R160" s="2"/>
+    </row>
+    <row r="161" spans="1:18" s="3" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>9</v>
       </c>
@@ -13158,14 +13652,17 @@
         <v>192</v>
       </c>
       <c r="M161" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="N161" s="2" t="s">
         <v>1759</v>
       </c>
-      <c r="N161" s="2"/>
       <c r="O161" s="2"/>
       <c r="P161" s="2"/>
       <c r="Q161" s="2"/>
-    </row>
-    <row r="162" spans="1:17" s="3" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R161" s="2"/>
+    </row>
+    <row r="162" spans="1:18" s="3" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>9</v>
       </c>
@@ -13203,14 +13700,17 @@
         <v>192</v>
       </c>
       <c r="M162" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="N162" s="2" t="s">
         <v>1759</v>
       </c>
-      <c r="N162" s="2"/>
       <c r="O162" s="2"/>
       <c r="P162" s="2"/>
       <c r="Q162" s="2"/>
-    </row>
-    <row r="163" spans="1:17" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R162" s="2"/>
+    </row>
+    <row r="163" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>9</v>
       </c>
@@ -13248,14 +13748,17 @@
         <v>395</v>
       </c>
       <c r="M163" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="N163" s="2" t="s">
         <v>1759</v>
       </c>
-      <c r="N163" s="2"/>
       <c r="O163" s="2"/>
       <c r="P163" s="2"/>
       <c r="Q163" s="2"/>
-    </row>
-    <row r="164" spans="1:17" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R163" s="2"/>
+    </row>
+    <row r="164" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>9</v>
       </c>
@@ -13293,14 +13796,17 @@
         <v>395</v>
       </c>
       <c r="M164" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="N164" s="2" t="s">
         <v>1760</v>
       </c>
-      <c r="N164" s="2"/>
       <c r="O164" s="2"/>
       <c r="P164" s="2"/>
       <c r="Q164" s="2"/>
-    </row>
-    <row r="165" spans="1:17" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R164" s="2"/>
+    </row>
+    <row r="165" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>9</v>
       </c>
@@ -13338,14 +13844,17 @@
         <v>395</v>
       </c>
       <c r="M165" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="N165" s="2" t="s">
         <v>1760</v>
       </c>
-      <c r="N165" s="2"/>
       <c r="O165" s="2"/>
       <c r="P165" s="2"/>
       <c r="Q165" s="2"/>
-    </row>
-    <row r="166" spans="1:17" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R165" s="2"/>
+    </row>
+    <row r="166" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>9</v>
       </c>
@@ -13383,14 +13892,17 @@
         <v>395</v>
       </c>
       <c r="M166" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="N166" s="2" t="s">
         <v>1760</v>
       </c>
-      <c r="N166" s="2"/>
       <c r="O166" s="2"/>
       <c r="P166" s="2"/>
       <c r="Q166" s="2"/>
-    </row>
-    <row r="167" spans="1:17" s="3" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R166" s="2"/>
+    </row>
+    <row r="167" spans="1:18" s="3" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>9</v>
       </c>
@@ -13428,14 +13940,17 @@
         <v>192</v>
       </c>
       <c r="M167" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="N167" s="2" t="s">
         <v>1760</v>
       </c>
-      <c r="N167" s="2"/>
       <c r="O167" s="2"/>
       <c r="P167" s="2"/>
       <c r="Q167" s="2"/>
-    </row>
-    <row r="168" spans="1:17" s="3" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R167" s="2"/>
+    </row>
+    <row r="168" spans="1:18" s="3" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>9</v>
       </c>
@@ -13473,14 +13988,17 @@
         <v>192</v>
       </c>
       <c r="M168" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="N168" s="2" t="s">
         <v>1760</v>
       </c>
-      <c r="N168" s="2"/>
       <c r="O168" s="2"/>
       <c r="P168" s="2"/>
       <c r="Q168" s="2"/>
-    </row>
-    <row r="169" spans="1:17" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R168" s="2"/>
+    </row>
+    <row r="169" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>9</v>
       </c>
@@ -13518,14 +14036,17 @@
         <v>1039</v>
       </c>
       <c r="M169" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="N169" s="2" t="s">
         <v>1760</v>
       </c>
-      <c r="N169" s="2"/>
       <c r="O169" s="2"/>
       <c r="P169" s="2"/>
       <c r="Q169" s="2"/>
-    </row>
-    <row r="170" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R169" s="2"/>
+    </row>
+    <row r="170" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>9</v>
       </c>
@@ -13563,14 +14084,17 @@
         <v>397</v>
       </c>
       <c r="M170" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="N170" s="2" t="s">
         <v>1760</v>
       </c>
-      <c r="N170" s="2"/>
       <c r="O170" s="2"/>
       <c r="P170" s="2"/>
       <c r="Q170" s="2"/>
-    </row>
-    <row r="171" spans="1:17" s="3" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R170" s="2"/>
+    </row>
+    <row r="171" spans="1:18" s="3" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>9</v>
       </c>
@@ -13608,14 +14132,17 @@
         <v>192</v>
       </c>
       <c r="M171" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="N171" s="2" t="s">
         <v>1760</v>
       </c>
-      <c r="N171" s="2"/>
       <c r="O171" s="2"/>
       <c r="P171" s="2"/>
       <c r="Q171" s="2"/>
-    </row>
-    <row r="172" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R171" s="2"/>
+    </row>
+    <row r="172" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>9</v>
       </c>
@@ -13653,14 +14180,17 @@
         <v>397</v>
       </c>
       <c r="M172" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="N172" s="2" t="s">
         <v>1760</v>
       </c>
-      <c r="N172" s="2"/>
       <c r="O172" s="2"/>
       <c r="P172" s="2"/>
       <c r="Q172" s="2"/>
-    </row>
-    <row r="173" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R172" s="2"/>
+    </row>
+    <row r="173" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>9</v>
       </c>
@@ -13697,13 +14227,16 @@
       <c r="L173" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="M173" s="2"/>
+      <c r="M173" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
       <c r="P173" s="2"/>
       <c r="Q173" s="2"/>
-    </row>
-    <row r="174" spans="1:17" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R173" s="2"/>
+    </row>
+    <row r="174" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>9</v>
       </c>
@@ -13740,13 +14273,16 @@
       <c r="L174" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="M174" s="2"/>
+      <c r="M174" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
       <c r="P174" s="2"/>
       <c r="Q174" s="2"/>
-    </row>
-    <row r="175" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R174" s="2"/>
+    </row>
+    <row r="175" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>9</v>
       </c>
@@ -13783,13 +14319,16 @@
       <c r="L175" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="M175" s="2"/>
+      <c r="M175" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
       <c r="P175" s="2"/>
       <c r="Q175" s="2"/>
-    </row>
-    <row r="176" spans="1:17" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R175" s="2"/>
+    </row>
+    <row r="176" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>9</v>
       </c>
@@ -13826,13 +14365,16 @@
       <c r="L176" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="M176" s="2"/>
+      <c r="M176" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
       <c r="P176" s="2"/>
       <c r="Q176" s="2"/>
-    </row>
-    <row r="177" spans="1:17" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R176" s="2"/>
+    </row>
+    <row r="177" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>9</v>
       </c>
@@ -13869,13 +14411,16 @@
       <c r="L177" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="M177" s="2"/>
+      <c r="M177" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
       <c r="P177" s="2"/>
       <c r="Q177" s="2"/>
-    </row>
-    <row r="178" spans="1:17" s="3" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R177" s="2"/>
+    </row>
+    <row r="178" spans="1:18" s="3" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>9</v>
       </c>
@@ -13912,13 +14457,16 @@
       <c r="L178" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="M178" s="2"/>
+      <c r="M178" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
       <c r="P178" s="2"/>
       <c r="Q178" s="2"/>
-    </row>
-    <row r="179" spans="1:17" s="3" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R178" s="2"/>
+    </row>
+    <row r="179" spans="1:18" s="3" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>9</v>
       </c>
@@ -13955,13 +14503,16 @@
       <c r="L179" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="M179" s="2"/>
+      <c r="M179" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
       <c r="P179" s="2"/>
       <c r="Q179" s="2"/>
-    </row>
-    <row r="180" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R179" s="2"/>
+    </row>
+    <row r="180" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>9</v>
       </c>
@@ -13998,13 +14549,16 @@
       <c r="L180" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="M180" s="2"/>
+      <c r="M180" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
       <c r="P180" s="2"/>
       <c r="Q180" s="2"/>
-    </row>
-    <row r="181" spans="1:17" s="3" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R180" s="2"/>
+    </row>
+    <row r="181" spans="1:18" s="3" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>9</v>
       </c>
@@ -14041,13 +14595,16 @@
       <c r="L181" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="M181" s="2"/>
+      <c r="M181" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
       <c r="P181" s="2"/>
       <c r="Q181" s="2"/>
-    </row>
-    <row r="182" spans="1:17" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R181" s="2"/>
+    </row>
+    <row r="182" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>9</v>
       </c>
@@ -14084,13 +14641,16 @@
       <c r="L182" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="M182" s="2"/>
+      <c r="M182" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
       <c r="P182" s="2"/>
       <c r="Q182" s="2"/>
-    </row>
-    <row r="183" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R182" s="2"/>
+    </row>
+    <row r="183" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>9</v>
       </c>
@@ -14127,13 +14687,16 @@
       <c r="L183" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="M183" s="2"/>
+      <c r="M183" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
       <c r="P183" s="2"/>
       <c r="Q183" s="2"/>
-    </row>
-    <row r="184" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R183" s="2"/>
+    </row>
+    <row r="184" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>9</v>
       </c>
@@ -14170,13 +14733,16 @@
       <c r="L184" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="M184" s="2"/>
+      <c r="M184" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
       <c r="P184" s="2"/>
       <c r="Q184" s="2"/>
-    </row>
-    <row r="185" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R184" s="2"/>
+    </row>
+    <row r="185" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>9</v>
       </c>
@@ -14213,13 +14779,16 @@
       <c r="L185" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M185" s="2"/>
+      <c r="M185" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
       <c r="P185" s="2"/>
       <c r="Q185" s="2"/>
-    </row>
-    <row r="186" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R185" s="2"/>
+    </row>
+    <row r="186" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>9</v>
       </c>
@@ -14256,13 +14825,16 @@
       <c r="L186" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M186" s="2"/>
+      <c r="M186" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
       <c r="P186" s="2"/>
       <c r="Q186" s="2"/>
-    </row>
-    <row r="187" spans="1:17" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R186" s="2"/>
+    </row>
+    <row r="187" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>9</v>
       </c>
@@ -14299,13 +14871,16 @@
       <c r="L187" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="M187" s="2"/>
+      <c r="M187" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
       <c r="P187" s="2"/>
       <c r="Q187" s="2"/>
-    </row>
-    <row r="188" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R187" s="2"/>
+    </row>
+    <row r="188" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>9</v>
       </c>
@@ -14342,13 +14917,16 @@
       <c r="L188" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="M188" s="2"/>
+      <c r="M188" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N188" s="2"/>
       <c r="O188" s="2"/>
       <c r="P188" s="2"/>
       <c r="Q188" s="2"/>
-    </row>
-    <row r="189" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R188" s="2"/>
+    </row>
+    <row r="189" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>9</v>
       </c>
@@ -14385,13 +14963,16 @@
       <c r="L189" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M189" s="2"/>
+      <c r="M189" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
       <c r="P189" s="2"/>
       <c r="Q189" s="2"/>
-    </row>
-    <row r="190" spans="1:17" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R189" s="2"/>
+    </row>
+    <row r="190" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>9</v>
       </c>
@@ -14428,13 +15009,16 @@
       <c r="L190" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="M190" s="2"/>
+      <c r="M190" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
       <c r="P190" s="2"/>
       <c r="Q190" s="2"/>
-    </row>
-    <row r="191" spans="1:17" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R190" s="2"/>
+    </row>
+    <row r="191" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>9</v>
       </c>
@@ -14471,13 +15055,16 @@
       <c r="L191" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="M191" s="2"/>
+      <c r="M191" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
       <c r="P191" s="2"/>
       <c r="Q191" s="2"/>
-    </row>
-    <row r="192" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R191" s="2"/>
+    </row>
+    <row r="192" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>9</v>
       </c>
@@ -14514,13 +15101,16 @@
       <c r="L192" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M192" s="2"/>
+      <c r="M192" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
       <c r="P192" s="2"/>
       <c r="Q192" s="2"/>
-    </row>
-    <row r="193" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R192" s="2"/>
+    </row>
+    <row r="193" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>9</v>
       </c>
@@ -14557,13 +15147,16 @@
       <c r="L193" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M193" s="2"/>
+      <c r="M193" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
       <c r="P193" s="2"/>
       <c r="Q193" s="2"/>
-    </row>
-    <row r="194" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R193" s="2"/>
+    </row>
+    <row r="194" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>9</v>
       </c>
@@ -14600,13 +15193,16 @@
       <c r="L194" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="M194" s="2"/>
+      <c r="M194" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
       <c r="P194" s="2"/>
       <c r="Q194" s="2"/>
-    </row>
-    <row r="195" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R194" s="2"/>
+    </row>
+    <row r="195" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>9</v>
       </c>
@@ -14643,13 +15239,16 @@
       <c r="L195" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="M195" s="2"/>
+      <c r="M195" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
       <c r="P195" s="2"/>
       <c r="Q195" s="2"/>
-    </row>
-    <row r="196" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R195" s="2"/>
+    </row>
+    <row r="196" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>9</v>
       </c>
@@ -14686,13 +15285,16 @@
       <c r="L196" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="M196" s="2"/>
+      <c r="M196" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
       <c r="P196" s="2"/>
       <c r="Q196" s="2"/>
-    </row>
-    <row r="197" spans="1:17" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R196" s="2"/>
+    </row>
+    <row r="197" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>9</v>
       </c>
@@ -14729,13 +15331,16 @@
       <c r="L197" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="M197" s="2"/>
+      <c r="M197" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
       <c r="P197" s="2"/>
       <c r="Q197" s="2"/>
-    </row>
-    <row r="198" spans="1:17" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R197" s="2"/>
+    </row>
+    <row r="198" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>9</v>
       </c>
@@ -14772,13 +15377,16 @@
       <c r="L198" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="M198" s="2"/>
+      <c r="M198" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
       <c r="P198" s="2"/>
       <c r="Q198" s="2"/>
-    </row>
-    <row r="199" spans="1:17" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R198" s="2"/>
+    </row>
+    <row r="199" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>9</v>
       </c>
@@ -14815,13 +15423,16 @@
       <c r="L199" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="M199" s="2"/>
+      <c r="M199" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
       <c r="P199" s="2"/>
       <c r="Q199" s="2"/>
-    </row>
-    <row r="200" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R199" s="2"/>
+    </row>
+    <row r="200" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>9</v>
       </c>
@@ -14858,13 +15469,16 @@
       <c r="L200" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="M200" s="2"/>
+      <c r="M200" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N200" s="2"/>
       <c r="O200" s="2"/>
       <c r="P200" s="2"/>
       <c r="Q200" s="2"/>
-    </row>
-    <row r="201" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R200" s="2"/>
+    </row>
+    <row r="201" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>9</v>
       </c>
@@ -14901,13 +15515,16 @@
       <c r="L201" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="M201" s="2"/>
+      <c r="M201" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N201" s="2"/>
       <c r="O201" s="2"/>
       <c r="P201" s="2"/>
       <c r="Q201" s="2"/>
-    </row>
-    <row r="202" spans="1:17" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R201" s="2"/>
+    </row>
+    <row r="202" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>9</v>
       </c>
@@ -14944,13 +15561,16 @@
       <c r="L202" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="M202" s="2"/>
+      <c r="M202" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
       <c r="P202" s="2"/>
       <c r="Q202" s="2"/>
-    </row>
-    <row r="203" spans="1:17" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R202" s="2"/>
+    </row>
+    <row r="203" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>9</v>
       </c>
@@ -14987,13 +15607,16 @@
       <c r="L203" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="M203" s="2"/>
+      <c r="M203" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
       <c r="P203" s="2"/>
       <c r="Q203" s="2"/>
-    </row>
-    <row r="204" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R203" s="2"/>
+    </row>
+    <row r="204" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>9</v>
       </c>
@@ -15030,13 +15653,16 @@
       <c r="L204" s="2">
         <v>5.4070900000000002</v>
       </c>
-      <c r="M204" s="2"/>
+      <c r="M204" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
       <c r="P204" s="2"/>
       <c r="Q204" s="2"/>
-    </row>
-    <row r="205" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R204" s="2"/>
+    </row>
+    <row r="205" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>9</v>
       </c>
@@ -15073,13 +15699,16 @@
       <c r="L205" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="M205" s="2"/>
+      <c r="M205" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
       <c r="P205" s="2"/>
       <c r="Q205" s="2"/>
-    </row>
-    <row r="206" spans="1:17" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R205" s="2"/>
+    </row>
+    <row r="206" spans="1:18" ht="87" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>9</v>
       </c>
@@ -15116,13 +15745,16 @@
       <c r="L206" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="M206" s="2"/>
+      <c r="M206" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
       <c r="P206" s="2"/>
       <c r="Q206" s="2"/>
-    </row>
-    <row r="207" spans="1:17" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R206" s="2"/>
+    </row>
+    <row r="207" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>9</v>
       </c>
@@ -15159,13 +15791,16 @@
       <c r="L207" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="M207" s="2"/>
+      <c r="M207" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>
       <c r="P207" s="2"/>
       <c r="Q207" s="2"/>
-    </row>
-    <row r="208" spans="1:17" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R207" s="2"/>
+    </row>
+    <row r="208" spans="1:18" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>9</v>
       </c>
@@ -15202,13 +15837,16 @@
       <c r="L208" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="M208" s="2"/>
+      <c r="M208" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N208" s="2"/>
       <c r="O208" s="2"/>
       <c r="P208" s="2"/>
       <c r="Q208" s="2"/>
-    </row>
-    <row r="209" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R208" s="2"/>
+    </row>
+    <row r="209" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>9</v>
       </c>
@@ -15245,13 +15883,16 @@
       <c r="L209" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="M209" s="2"/>
+      <c r="M209" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
       <c r="P209" s="2"/>
       <c r="Q209" s="2"/>
-    </row>
-    <row r="210" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R209" s="2"/>
+    </row>
+    <row r="210" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>9</v>
       </c>
@@ -15288,13 +15929,16 @@
       <c r="L210" s="2">
         <v>5.4070900000000002</v>
       </c>
-      <c r="M210" s="2"/>
+      <c r="M210" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N210" s="2"/>
       <c r="O210" s="2"/>
       <c r="P210" s="2"/>
       <c r="Q210" s="2"/>
-    </row>
-    <row r="211" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R210" s="2"/>
+    </row>
+    <row r="211" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>9</v>
       </c>
@@ -15329,13 +15973,16 @@
       <c r="L211" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M211" s="2"/>
+      <c r="M211" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N211" s="2"/>
       <c r="O211" s="2"/>
       <c r="P211" s="2"/>
       <c r="Q211" s="2"/>
-    </row>
-    <row r="212" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R211" s="2"/>
+    </row>
+    <row r="212" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>9</v>
       </c>
@@ -15370,13 +16017,16 @@
       <c r="L212" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M212" s="2"/>
+      <c r="M212" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
       <c r="P212" s="2"/>
       <c r="Q212" s="2"/>
-    </row>
-    <row r="213" spans="1:17" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R212" s="2"/>
+    </row>
+    <row r="213" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>9</v>
       </c>
@@ -15411,13 +16061,16 @@
       <c r="L213" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="M213" s="2"/>
+      <c r="M213" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
       <c r="P213" s="2"/>
       <c r="Q213" s="2"/>
-    </row>
-    <row r="214" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R213" s="2"/>
+    </row>
+    <row r="214" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>9</v>
       </c>
@@ -15452,13 +16105,16 @@
       <c r="L214" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M214" s="2"/>
+      <c r="M214" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N214" s="2"/>
       <c r="O214" s="2"/>
       <c r="P214" s="2"/>
       <c r="Q214" s="2"/>
-    </row>
-    <row r="215" spans="1:17" s="3" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R214" s="2"/>
+    </row>
+    <row r="215" spans="1:18" s="3" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>9</v>
       </c>
@@ -15493,13 +16149,16 @@
       <c r="L215" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="M215" s="2"/>
+      <c r="M215" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N215" s="2"/>
       <c r="O215" s="2"/>
       <c r="P215" s="2"/>
       <c r="Q215" s="2"/>
-    </row>
-    <row r="216" spans="1:17" s="3" customFormat="1" ht="188.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R215" s="2"/>
+    </row>
+    <row r="216" spans="1:18" s="3" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>9</v>
       </c>
@@ -15534,13 +16193,16 @@
       <c r="L216" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="M216" s="2"/>
+      <c r="M216" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
       <c r="P216" s="2"/>
       <c r="Q216" s="2"/>
-    </row>
-    <row r="217" spans="1:17" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R216" s="2"/>
+    </row>
+    <row r="217" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>9</v>
       </c>
@@ -15575,13 +16237,16 @@
       <c r="L217" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="M217" s="2"/>
+      <c r="M217" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N217" s="2"/>
       <c r="O217" s="2"/>
       <c r="P217" s="2"/>
       <c r="Q217" s="2"/>
-    </row>
-    <row r="218" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R217" s="2"/>
+    </row>
+    <row r="218" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>9</v>
       </c>
@@ -15618,13 +16283,16 @@
       <c r="L218" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="M218" s="2"/>
+      <c r="M218" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
       <c r="P218" s="2"/>
       <c r="Q218" s="2"/>
-    </row>
-    <row r="219" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R218" s="2"/>
+    </row>
+    <row r="219" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>9</v>
       </c>
@@ -15661,13 +16329,16 @@
       <c r="L219" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="M219" s="2"/>
+      <c r="M219" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N219" s="2"/>
       <c r="O219" s="2"/>
       <c r="P219" s="2"/>
       <c r="Q219" s="2"/>
-    </row>
-    <row r="220" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R219" s="2"/>
+    </row>
+    <row r="220" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>9</v>
       </c>
@@ -15704,13 +16375,16 @@
       <c r="L220" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="M220" s="2"/>
+      <c r="M220" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N220" s="2"/>
       <c r="O220" s="2"/>
       <c r="P220" s="2"/>
       <c r="Q220" s="2"/>
-    </row>
-    <row r="221" spans="1:17" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R220" s="2"/>
+    </row>
+    <row r="221" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>9</v>
       </c>
@@ -15747,13 +16421,16 @@
       <c r="L221" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="M221" s="2"/>
+      <c r="M221" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N221" s="2"/>
       <c r="O221" s="2"/>
       <c r="P221" s="2"/>
       <c r="Q221" s="2"/>
-    </row>
-    <row r="222" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R221" s="2"/>
+    </row>
+    <row r="222" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>9</v>
       </c>
@@ -15788,13 +16465,16 @@
       <c r="L222" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="M222" s="2"/>
+      <c r="M222" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N222" s="2"/>
       <c r="O222" s="2"/>
       <c r="P222" s="2"/>
       <c r="Q222" s="2"/>
-    </row>
-    <row r="223" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R222" s="2"/>
+    </row>
+    <row r="223" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>9</v>
       </c>
@@ -15831,13 +16511,16 @@
       <c r="L223" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="M223" s="2"/>
+      <c r="M223" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>
       <c r="P223" s="2"/>
       <c r="Q223" s="2"/>
-    </row>
-    <row r="224" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R223" s="2"/>
+    </row>
+    <row r="224" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>9</v>
       </c>
@@ -15874,13 +16557,16 @@
       <c r="L224" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="M224" s="2"/>
+      <c r="M224" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N224" s="2"/>
       <c r="O224" s="2"/>
       <c r="P224" s="2"/>
       <c r="Q224" s="2"/>
-    </row>
-    <row r="225" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R224" s="2"/>
+    </row>
+    <row r="225" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>9</v>
       </c>
@@ -15917,13 +16603,16 @@
       <c r="L225" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="M225" s="2"/>
+      <c r="M225" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
       <c r="P225" s="2"/>
       <c r="Q225" s="2"/>
-    </row>
-    <row r="226" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R225" s="2"/>
+    </row>
+    <row r="226" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
         <v>9</v>
       </c>
@@ -15958,13 +16647,16 @@
       <c r="L226" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="M226" s="2"/>
+      <c r="M226" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
       <c r="P226" s="2"/>
       <c r="Q226" s="2"/>
-    </row>
-    <row r="227" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R226" s="2"/>
+    </row>
+    <row r="227" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>9</v>
       </c>
@@ -15999,13 +16691,16 @@
       <c r="L227" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="M227" s="2"/>
+      <c r="M227" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N227" s="2"/>
       <c r="O227" s="2"/>
       <c r="P227" s="2"/>
       <c r="Q227" s="2"/>
-    </row>
-    <row r="228" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R227" s="2"/>
+    </row>
+    <row r="228" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
         <v>9</v>
       </c>
@@ -16040,13 +16735,16 @@
       <c r="L228" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="M228" s="2"/>
+      <c r="M228" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N228" s="2"/>
       <c r="O228" s="2"/>
       <c r="P228" s="2"/>
       <c r="Q228" s="2"/>
-    </row>
-    <row r="229" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R228" s="2"/>
+    </row>
+    <row r="229" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
         <v>9</v>
       </c>
@@ -16083,13 +16781,16 @@
       <c r="L229" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="M229" s="2"/>
+      <c r="M229" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
       <c r="P229" s="2"/>
       <c r="Q229" s="2"/>
-    </row>
-    <row r="230" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R229" s="2"/>
+    </row>
+    <row r="230" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
         <v>9</v>
       </c>
@@ -16124,13 +16825,16 @@
       <c r="L230" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="M230" s="2"/>
+      <c r="M230" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N230" s="2"/>
       <c r="O230" s="2"/>
       <c r="P230" s="2"/>
       <c r="Q230" s="2"/>
-    </row>
-    <row r="231" spans="1:17" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R230" s="2"/>
+    </row>
+    <row r="231" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
         <v>9</v>
       </c>
@@ -16165,13 +16869,16 @@
       <c r="L231" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="M231" s="2"/>
+      <c r="M231" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N231" s="2"/>
       <c r="O231" s="2"/>
       <c r="P231" s="2"/>
       <c r="Q231" s="2"/>
-    </row>
-    <row r="232" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R231" s="2"/>
+    </row>
+    <row r="232" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>9</v>
       </c>
@@ -16206,13 +16913,16 @@
       <c r="L232" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="M232" s="2"/>
+      <c r="M232" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N232" s="2"/>
       <c r="O232" s="2"/>
       <c r="P232" s="2"/>
       <c r="Q232" s="2"/>
-    </row>
-    <row r="233" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R232" s="2"/>
+    </row>
+    <row r="233" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>9</v>
       </c>
@@ -16247,13 +16957,16 @@
       <c r="L233" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="M233" s="2"/>
+      <c r="M233" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N233" s="2"/>
       <c r="O233" s="2"/>
       <c r="P233" s="2"/>
       <c r="Q233" s="2"/>
-    </row>
-    <row r="234" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R233" s="2"/>
+    </row>
+    <row r="234" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>9</v>
       </c>
@@ -16288,13 +17001,16 @@
       <c r="L234" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="M234" s="2"/>
+      <c r="M234" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N234" s="2"/>
       <c r="O234" s="2"/>
       <c r="P234" s="2"/>
       <c r="Q234" s="2"/>
-    </row>
-    <row r="235" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R234" s="2"/>
+    </row>
+    <row r="235" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
         <v>9</v>
       </c>
@@ -16329,13 +17045,16 @@
       <c r="L235" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="M235" s="2"/>
+      <c r="M235" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N235" s="2"/>
       <c r="O235" s="2"/>
       <c r="P235" s="2"/>
       <c r="Q235" s="2"/>
-    </row>
-    <row r="236" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R235" s="2"/>
+    </row>
+    <row r="236" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A236" s="2" t="s">
         <v>9</v>
       </c>
@@ -16370,13 +17089,16 @@
       <c r="L236" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="M236" s="2"/>
+      <c r="M236" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N236" s="2"/>
       <c r="O236" s="2"/>
       <c r="P236" s="2"/>
       <c r="Q236" s="2"/>
-    </row>
-    <row r="237" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R236" s="2"/>
+    </row>
+    <row r="237" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>9</v>
       </c>
@@ -16411,13 +17133,16 @@
       <c r="L237" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="M237" s="2"/>
+      <c r="M237" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N237" s="2"/>
       <c r="O237" s="2"/>
       <c r="P237" s="2"/>
       <c r="Q237" s="2"/>
-    </row>
-    <row r="238" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R237" s="2"/>
+    </row>
+    <row r="238" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A238" s="2" t="s">
         <v>9</v>
       </c>
@@ -16452,13 +17177,16 @@
       <c r="L238" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="M238" s="2"/>
+      <c r="M238" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N238" s="2"/>
       <c r="O238" s="2"/>
       <c r="P238" s="2"/>
       <c r="Q238" s="2"/>
-    </row>
-    <row r="239" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R238" s="2"/>
+    </row>
+    <row r="239" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>9</v>
       </c>
@@ -16493,13 +17221,16 @@
       <c r="L239" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="M239" s="2"/>
+      <c r="M239" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N239" s="2"/>
       <c r="O239" s="2"/>
       <c r="P239" s="2"/>
       <c r="Q239" s="2"/>
-    </row>
-    <row r="240" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R239" s="2"/>
+    </row>
+    <row r="240" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>9</v>
       </c>
@@ -16534,13 +17265,16 @@
       <c r="L240" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="M240" s="2"/>
+      <c r="M240" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N240" s="2"/>
       <c r="O240" s="2"/>
       <c r="P240" s="2"/>
       <c r="Q240" s="2"/>
-    </row>
-    <row r="241" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R240" s="2"/>
+    </row>
+    <row r="241" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>9</v>
       </c>
@@ -16575,13 +17309,16 @@
       <c r="L241" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="M241" s="2"/>
+      <c r="M241" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N241" s="2"/>
       <c r="O241" s="2"/>
       <c r="P241" s="2"/>
       <c r="Q241" s="2"/>
-    </row>
-    <row r="242" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R241" s="2"/>
+    </row>
+    <row r="242" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A242" s="2" t="s">
         <v>9</v>
       </c>
@@ -16616,13 +17353,16 @@
       <c r="L242" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="M242" s="2"/>
+      <c r="M242" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N242" s="2"/>
       <c r="O242" s="2"/>
       <c r="P242" s="2"/>
       <c r="Q242" s="2"/>
-    </row>
-    <row r="243" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R242" s="2"/>
+    </row>
+    <row r="243" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A243" s="2" t="s">
         <v>9</v>
       </c>
@@ -16657,13 +17397,16 @@
       <c r="L243" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="M243" s="2"/>
+      <c r="M243" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N243" s="2"/>
       <c r="O243" s="2"/>
       <c r="P243" s="2"/>
       <c r="Q243" s="2"/>
-    </row>
-    <row r="244" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R243" s="2"/>
+    </row>
+    <row r="244" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
         <v>9</v>
       </c>
@@ -16698,13 +17441,16 @@
       <c r="L244" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="M244" s="2"/>
+      <c r="M244" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N244" s="2"/>
       <c r="O244" s="2"/>
       <c r="P244" s="2"/>
       <c r="Q244" s="2"/>
-    </row>
-    <row r="245" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R244" s="2"/>
+    </row>
+    <row r="245" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A245" s="2" t="s">
         <v>9</v>
       </c>
@@ -16739,13 +17485,16 @@
       <c r="L245" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="M245" s="2"/>
+      <c r="M245" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N245" s="2"/>
       <c r="O245" s="2"/>
       <c r="P245" s="2"/>
       <c r="Q245" s="2"/>
-    </row>
-    <row r="246" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R245" s="2"/>
+    </row>
+    <row r="246" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>9</v>
       </c>
@@ -16780,13 +17529,16 @@
       <c r="L246" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="M246" s="2"/>
+      <c r="M246" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N246" s="2"/>
       <c r="O246" s="2"/>
       <c r="P246" s="2"/>
       <c r="Q246" s="2"/>
-    </row>
-    <row r="247" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R246" s="2"/>
+    </row>
+    <row r="247" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>9</v>
       </c>
@@ -16821,13 +17573,16 @@
       <c r="L247" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="M247" s="2"/>
+      <c r="M247" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N247" s="2"/>
       <c r="O247" s="2"/>
       <c r="P247" s="2"/>
       <c r="Q247" s="2"/>
-    </row>
-    <row r="248" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R247" s="2"/>
+    </row>
+    <row r="248" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A248" s="2" t="s">
         <v>9</v>
       </c>
@@ -16862,13 +17617,16 @@
       <c r="L248" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="M248" s="2"/>
+      <c r="M248" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N248" s="2"/>
       <c r="O248" s="2"/>
       <c r="P248" s="2"/>
       <c r="Q248" s="2"/>
-    </row>
-    <row r="249" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R248" s="2"/>
+    </row>
+    <row r="249" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A249" s="2" t="s">
         <v>9</v>
       </c>
@@ -16903,13 +17661,16 @@
       <c r="L249" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="M249" s="2"/>
+      <c r="M249" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N249" s="2"/>
       <c r="O249" s="2"/>
       <c r="P249" s="2"/>
       <c r="Q249" s="2"/>
-    </row>
-    <row r="250" spans="1:17" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R249" s="2"/>
+    </row>
+    <row r="250" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A250" s="2" t="s">
         <v>9</v>
       </c>
@@ -16944,13 +17705,16 @@
       <c r="L250" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="M250" s="2"/>
+      <c r="M250" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N250" s="2"/>
       <c r="O250" s="2"/>
       <c r="P250" s="2"/>
       <c r="Q250" s="2"/>
-    </row>
-    <row r="251" spans="1:17" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R250" s="2"/>
+    </row>
+    <row r="251" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A251" s="2" t="s">
         <v>9</v>
       </c>
@@ -16985,13 +17749,16 @@
       <c r="L251" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="M251" s="2"/>
+      <c r="M251" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N251" s="2"/>
       <c r="O251" s="2"/>
       <c r="P251" s="2"/>
       <c r="Q251" s="2"/>
-    </row>
-    <row r="252" spans="1:17" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R251" s="2"/>
+    </row>
+    <row r="252" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
         <v>9</v>
       </c>
@@ -17026,13 +17793,16 @@
       <c r="L252" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="M252" s="2"/>
+      <c r="M252" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N252" s="2"/>
       <c r="O252" s="2"/>
       <c r="P252" s="2"/>
       <c r="Q252" s="2"/>
-    </row>
-    <row r="253" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R252" s="2"/>
+    </row>
+    <row r="253" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A253" s="2" t="s">
         <v>9</v>
       </c>
@@ -17069,13 +17839,16 @@
       <c r="L253" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="M253" s="2"/>
+      <c r="M253" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N253" s="2"/>
       <c r="O253" s="2"/>
       <c r="P253" s="2"/>
       <c r="Q253" s="2"/>
-    </row>
-    <row r="254" spans="1:17" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R253" s="2"/>
+    </row>
+    <row r="254" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
         <v>9</v>
       </c>
@@ -17110,13 +17883,16 @@
       <c r="L254" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="M254" s="2"/>
+      <c r="M254" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N254" s="2"/>
       <c r="O254" s="2"/>
       <c r="P254" s="2"/>
       <c r="Q254" s="2"/>
-    </row>
-    <row r="255" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R254" s="2"/>
+    </row>
+    <row r="255" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A255" s="2" t="s">
         <v>9</v>
       </c>
@@ -17153,13 +17929,16 @@
       <c r="L255" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="M255" s="2"/>
+      <c r="M255" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N255" s="2"/>
       <c r="O255" s="2"/>
       <c r="P255" s="2"/>
       <c r="Q255" s="2"/>
-    </row>
-    <row r="256" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R255" s="2"/>
+    </row>
+    <row r="256" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A256" s="2" t="s">
         <v>9</v>
       </c>
@@ -17194,13 +17973,16 @@
       <c r="L256" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="M256" s="2"/>
+      <c r="M256" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N256" s="2"/>
       <c r="O256" s="2"/>
       <c r="P256" s="2"/>
       <c r="Q256" s="2"/>
-    </row>
-    <row r="257" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R256" s="2"/>
+    </row>
+    <row r="257" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A257" s="2" t="s">
         <v>9</v>
       </c>
@@ -17235,13 +18017,16 @@
       <c r="L257" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M257" s="2"/>
+      <c r="M257" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N257" s="2"/>
       <c r="O257" s="2"/>
       <c r="P257" s="2"/>
       <c r="Q257" s="2"/>
-    </row>
-    <row r="258" spans="1:17" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R257" s="2"/>
+    </row>
+    <row r="258" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A258" s="2" t="s">
         <v>9</v>
       </c>
@@ -17276,13 +18061,16 @@
       <c r="L258" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="M258" s="2"/>
+      <c r="M258" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N258" s="2"/>
       <c r="O258" s="2"/>
       <c r="P258" s="2"/>
       <c r="Q258" s="2"/>
-    </row>
-    <row r="259" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R258" s="2"/>
+    </row>
+    <row r="259" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
         <v>9</v>
       </c>
@@ -17317,13 +18105,16 @@
       <c r="L259" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M259" s="2"/>
+      <c r="M259" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N259" s="2"/>
       <c r="O259" s="2"/>
       <c r="P259" s="2"/>
       <c r="Q259" s="2"/>
-    </row>
-    <row r="260" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R259" s="2"/>
+    </row>
+    <row r="260" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>9</v>
       </c>
@@ -17358,13 +18149,16 @@
       <c r="L260" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="M260" s="2"/>
+      <c r="M260" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N260" s="2"/>
       <c r="O260" s="2"/>
       <c r="P260" s="2"/>
       <c r="Q260" s="2"/>
-    </row>
-    <row r="261" spans="1:17" s="3" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R260" s="2"/>
+    </row>
+    <row r="261" spans="1:18" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A261" s="2" t="s">
         <v>9</v>
       </c>
@@ -17399,13 +18193,16 @@
       <c r="L261" s="2" t="s">
         <v>1317</v>
       </c>
-      <c r="M261" s="2"/>
+      <c r="M261" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N261" s="2"/>
       <c r="O261" s="2"/>
       <c r="P261" s="2"/>
       <c r="Q261" s="2"/>
-    </row>
-    <row r="262" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R261" s="2"/>
+    </row>
+    <row r="262" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A262" s="2" t="s">
         <v>9</v>
       </c>
@@ -17440,13 +18237,16 @@
       <c r="L262" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="M262" s="2"/>
+      <c r="M262" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N262" s="2"/>
       <c r="O262" s="2"/>
       <c r="P262" s="2"/>
       <c r="Q262" s="2"/>
-    </row>
-    <row r="263" spans="1:17" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R262" s="2"/>
+    </row>
+    <row r="263" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A263" s="2" t="s">
         <v>9</v>
       </c>
@@ -17481,13 +18281,16 @@
       <c r="L263" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="M263" s="2"/>
+      <c r="M263" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N263" s="2"/>
       <c r="O263" s="2"/>
       <c r="P263" s="2"/>
       <c r="Q263" s="2"/>
-    </row>
-    <row r="264" spans="1:17" s="3" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R263" s="2"/>
+    </row>
+    <row r="264" spans="1:18" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A264" s="2" t="s">
         <v>9</v>
       </c>
@@ -17522,13 +18325,16 @@
       <c r="L264" s="2" t="s">
         <v>1317</v>
       </c>
-      <c r="M264" s="2"/>
+      <c r="M264" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N264" s="2"/>
       <c r="O264" s="2"/>
       <c r="P264" s="2"/>
       <c r="Q264" s="2"/>
-    </row>
-    <row r="265" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R264" s="2"/>
+    </row>
+    <row r="265" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A265" s="2" t="s">
         <v>9</v>
       </c>
@@ -17563,13 +18369,16 @@
       <c r="L265" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="M265" s="2"/>
+      <c r="M265" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N265" s="2"/>
       <c r="O265" s="2"/>
       <c r="P265" s="2"/>
       <c r="Q265" s="2"/>
-    </row>
-    <row r="266" spans="1:17" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R265" s="2"/>
+    </row>
+    <row r="266" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A266" s="2" t="s">
         <v>9</v>
       </c>
@@ -17604,13 +18413,16 @@
       <c r="L266" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="M266" s="2"/>
+      <c r="M266" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N266" s="2"/>
       <c r="O266" s="2"/>
       <c r="P266" s="2"/>
       <c r="Q266" s="2"/>
-    </row>
-    <row r="267" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R266" s="2"/>
+    </row>
+    <row r="267" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>9</v>
       </c>
@@ -17645,13 +18457,16 @@
       <c r="L267" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M267" s="2"/>
+      <c r="M267" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N267" s="2"/>
       <c r="O267" s="2"/>
       <c r="P267" s="2"/>
       <c r="Q267" s="2"/>
-    </row>
-    <row r="268" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R267" s="2"/>
+    </row>
+    <row r="268" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>9</v>
       </c>
@@ -17686,13 +18501,16 @@
       <c r="L268" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M268" s="2"/>
+      <c r="M268" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N268" s="2"/>
       <c r="O268" s="2"/>
       <c r="P268" s="2"/>
       <c r="Q268" s="2"/>
-    </row>
-    <row r="269" spans="1:17" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R268" s="2"/>
+    </row>
+    <row r="269" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
         <v>9</v>
       </c>
@@ -17727,13 +18545,16 @@
       <c r="L269" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="M269" s="2"/>
+      <c r="M269" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N269" s="2"/>
       <c r="O269" s="2"/>
       <c r="P269" s="2"/>
       <c r="Q269" s="2"/>
-    </row>
-    <row r="270" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R269" s="2"/>
+    </row>
+    <row r="270" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A270" s="2" t="s">
         <v>9</v>
       </c>
@@ -17768,13 +18589,16 @@
       <c r="L270" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M270" s="2"/>
+      <c r="M270" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N270" s="2"/>
       <c r="O270" s="2"/>
       <c r="P270" s="2"/>
       <c r="Q270" s="2"/>
-    </row>
-    <row r="271" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R270" s="2"/>
+    </row>
+    <row r="271" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A271" s="2" t="s">
         <v>9</v>
       </c>
@@ -17809,13 +18633,16 @@
       <c r="L271" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M271" s="2"/>
+      <c r="M271" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N271" s="2"/>
       <c r="O271" s="2"/>
       <c r="P271" s="2"/>
       <c r="Q271" s="2"/>
-    </row>
-    <row r="272" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R271" s="2"/>
+    </row>
+    <row r="272" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
         <v>9</v>
       </c>
@@ -17852,13 +18679,16 @@
       <c r="L272" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="M272" s="2"/>
+      <c r="M272" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N272" s="2"/>
       <c r="O272" s="2"/>
       <c r="P272" s="2"/>
       <c r="Q272" s="2"/>
-    </row>
-    <row r="273" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R272" s="2"/>
+    </row>
+    <row r="273" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
         <v>9</v>
       </c>
@@ -17895,13 +18725,16 @@
       <c r="L273" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="M273" s="2"/>
+      <c r="M273" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N273" s="2"/>
       <c r="O273" s="2"/>
       <c r="P273" s="2"/>
       <c r="Q273" s="2"/>
-    </row>
-    <row r="274" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R273" s="2"/>
+    </row>
+    <row r="274" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>9</v>
       </c>
@@ -17938,13 +18771,16 @@
       <c r="L274" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="M274" s="2"/>
+      <c r="M274" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N274" s="2"/>
       <c r="O274" s="2"/>
       <c r="P274" s="2"/>
       <c r="Q274" s="2"/>
-    </row>
-    <row r="275" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R274" s="2"/>
+    </row>
+    <row r="275" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>9</v>
       </c>
@@ -17981,13 +18817,16 @@
       <c r="L275" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="M275" s="2"/>
+      <c r="M275" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N275" s="2"/>
       <c r="O275" s="2"/>
       <c r="P275" s="2"/>
       <c r="Q275" s="2"/>
-    </row>
-    <row r="276" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R275" s="2"/>
+    </row>
+    <row r="276" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>9</v>
       </c>
@@ -18024,13 +18863,16 @@
       <c r="L276" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="M276" s="2"/>
+      <c r="M276" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N276" s="2"/>
       <c r="O276" s="2"/>
       <c r="P276" s="2"/>
       <c r="Q276" s="2"/>
-    </row>
-    <row r="277" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R276" s="2"/>
+    </row>
+    <row r="277" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
         <v>9</v>
       </c>
@@ -18067,13 +18909,16 @@
       <c r="L277" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="M277" s="2"/>
+      <c r="M277" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N277" s="2"/>
       <c r="O277" s="2"/>
       <c r="P277" s="2"/>
       <c r="Q277" s="2"/>
-    </row>
-    <row r="278" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R277" s="2"/>
+    </row>
+    <row r="278" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>9</v>
       </c>
@@ -18110,13 +18955,16 @@
       <c r="L278" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="M278" s="2"/>
+      <c r="M278" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N278" s="2"/>
       <c r="O278" s="2"/>
       <c r="P278" s="2"/>
       <c r="Q278" s="2"/>
-    </row>
-    <row r="279" spans="1:17" s="3" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R278" s="2"/>
+    </row>
+    <row r="279" spans="1:18" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>9</v>
       </c>
@@ -18153,13 +19001,16 @@
       <c r="L279" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="M279" s="2"/>
+      <c r="M279" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N279" s="2"/>
       <c r="O279" s="2"/>
       <c r="P279" s="2"/>
       <c r="Q279" s="2"/>
-    </row>
-    <row r="280" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R279" s="2"/>
+    </row>
+    <row r="280" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>9</v>
       </c>
@@ -18196,13 +19047,16 @@
       <c r="L280" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M280" s="2"/>
+      <c r="M280" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N280" s="2"/>
       <c r="O280" s="2"/>
       <c r="P280" s="2"/>
       <c r="Q280" s="2"/>
-    </row>
-    <row r="281" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R280" s="2"/>
+    </row>
+    <row r="281" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>9</v>
       </c>
@@ -18239,13 +19093,16 @@
       <c r="L281" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="M281" s="2"/>
+      <c r="M281" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N281" s="2"/>
       <c r="O281" s="2"/>
       <c r="P281" s="2"/>
       <c r="Q281" s="2"/>
-    </row>
-    <row r="282" spans="1:17" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R281" s="2"/>
+    </row>
+    <row r="282" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>9</v>
       </c>
@@ -18282,13 +19139,16 @@
       <c r="L282" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="M282" s="2"/>
+      <c r="M282" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N282" s="2"/>
       <c r="O282" s="2"/>
       <c r="P282" s="2"/>
       <c r="Q282" s="2"/>
-    </row>
-    <row r="283" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R282" s="2"/>
+    </row>
+    <row r="283" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>9</v>
       </c>
@@ -18325,13 +19185,16 @@
       <c r="L283" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="M283" s="2"/>
+      <c r="M283" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N283" s="2"/>
       <c r="O283" s="2"/>
       <c r="P283" s="2"/>
       <c r="Q283" s="2"/>
-    </row>
-    <row r="284" spans="1:17" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R283" s="2"/>
+    </row>
+    <row r="284" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A284" s="2" t="s">
         <v>9</v>
       </c>
@@ -18368,13 +19231,16 @@
       <c r="L284" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="M284" s="2"/>
+      <c r="M284" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N284" s="2"/>
       <c r="O284" s="2"/>
       <c r="P284" s="2"/>
       <c r="Q284" s="2"/>
-    </row>
-    <row r="285" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R284" s="2"/>
+    </row>
+    <row r="285" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
         <v>9</v>
       </c>
@@ -18409,13 +19275,16 @@
       <c r="L285" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="M285" s="2"/>
+      <c r="M285" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N285" s="2"/>
       <c r="O285" s="2"/>
       <c r="P285" s="2"/>
       <c r="Q285" s="2"/>
-    </row>
-    <row r="286" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R285" s="2"/>
+    </row>
+    <row r="286" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A286" s="2" t="s">
         <v>9</v>
       </c>
@@ -18450,13 +19319,16 @@
       <c r="L286" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M286" s="2"/>
+      <c r="M286" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N286" s="2"/>
       <c r="O286" s="2"/>
       <c r="P286" s="2"/>
       <c r="Q286" s="2"/>
-    </row>
-    <row r="287" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R286" s="2"/>
+    </row>
+    <row r="287" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A287" s="2" t="s">
         <v>9</v>
       </c>
@@ -18491,13 +19363,16 @@
       <c r="L287" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="M287" s="2"/>
+      <c r="M287" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N287" s="2"/>
       <c r="O287" s="2"/>
       <c r="P287" s="2"/>
       <c r="Q287" s="2"/>
-    </row>
-    <row r="288" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R287" s="2"/>
+    </row>
+    <row r="288" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A288" s="2" t="s">
         <v>9</v>
       </c>
@@ -18532,13 +19407,16 @@
       <c r="L288" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="M288" s="2"/>
+      <c r="M288" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N288" s="2"/>
       <c r="O288" s="2"/>
       <c r="P288" s="2"/>
       <c r="Q288" s="2"/>
-    </row>
-    <row r="289" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R288" s="2"/>
+    </row>
+    <row r="289" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
         <v>9</v>
       </c>
@@ -18573,13 +19451,16 @@
       <c r="L289" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M289" s="2"/>
+      <c r="M289" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N289" s="2"/>
       <c r="O289" s="2"/>
       <c r="P289" s="2"/>
       <c r="Q289" s="2"/>
-    </row>
-    <row r="290" spans="1:17" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R289" s="2"/>
+    </row>
+    <row r="290" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A290" s="2" t="s">
         <v>9</v>
       </c>
@@ -18614,13 +19495,16 @@
       <c r="L290" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="M290" s="2"/>
+      <c r="M290" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N290" s="2"/>
       <c r="O290" s="2"/>
       <c r="P290" s="2"/>
       <c r="Q290" s="2"/>
-    </row>
-    <row r="291" spans="1:17" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R290" s="2"/>
+    </row>
+    <row r="291" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A291" s="2" t="s">
         <v>9</v>
       </c>
@@ -18655,13 +19539,16 @@
       <c r="L291" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="M291" s="2"/>
+      <c r="M291" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N291" s="2"/>
       <c r="O291" s="2"/>
       <c r="P291" s="2"/>
       <c r="Q291" s="2"/>
-    </row>
-    <row r="292" spans="1:17" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R291" s="2"/>
+    </row>
+    <row r="292" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
         <v>9</v>
       </c>
@@ -18696,13 +19583,16 @@
       <c r="L292" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="M292" s="2"/>
+      <c r="M292" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N292" s="2"/>
       <c r="O292" s="2"/>
       <c r="P292" s="2"/>
       <c r="Q292" s="2"/>
-    </row>
-    <row r="293" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R292" s="2"/>
+    </row>
+    <row r="293" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A293" s="2" t="s">
         <v>9</v>
       </c>
@@ -18737,13 +19627,16 @@
       <c r="L293" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M293" s="2"/>
+      <c r="M293" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N293" s="2"/>
       <c r="O293" s="2"/>
       <c r="P293" s="2"/>
       <c r="Q293" s="2"/>
-    </row>
-    <row r="294" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R293" s="2"/>
+    </row>
+    <row r="294" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A294" s="2" t="s">
         <v>9</v>
       </c>
@@ -18778,13 +19671,16 @@
       <c r="L294" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M294" s="2"/>
+      <c r="M294" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N294" s="2"/>
       <c r="O294" s="2"/>
       <c r="P294" s="2"/>
       <c r="Q294" s="2"/>
-    </row>
-    <row r="295" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R294" s="2"/>
+    </row>
+    <row r="295" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A295" s="2" t="s">
         <v>9</v>
       </c>
@@ -18819,13 +19715,16 @@
       <c r="L295" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="M295" s="2"/>
+      <c r="M295" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N295" s="2"/>
       <c r="O295" s="2"/>
       <c r="P295" s="2"/>
       <c r="Q295" s="2"/>
-    </row>
-    <row r="296" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R295" s="2"/>
+    </row>
+    <row r="296" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A296" s="2" t="s">
         <v>9</v>
       </c>
@@ -18860,13 +19759,16 @@
       <c r="L296" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="M296" s="2"/>
+      <c r="M296" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N296" s="2"/>
       <c r="O296" s="2"/>
       <c r="P296" s="2"/>
       <c r="Q296" s="2"/>
-    </row>
-    <row r="297" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R296" s="2"/>
+    </row>
+    <row r="297" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>9</v>
       </c>
@@ -18901,13 +19803,16 @@
       <c r="L297" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="M297" s="2"/>
+      <c r="M297" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N297" s="2"/>
       <c r="O297" s="2"/>
       <c r="P297" s="2"/>
       <c r="Q297" s="2"/>
-    </row>
-    <row r="298" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R297" s="2"/>
+    </row>
+    <row r="298" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
         <v>9</v>
       </c>
@@ -18942,13 +19847,16 @@
       <c r="L298" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="M298" s="2"/>
+      <c r="M298" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N298" s="2"/>
       <c r="O298" s="2"/>
       <c r="P298" s="2"/>
       <c r="Q298" s="2"/>
-    </row>
-    <row r="299" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R298" s="2"/>
+    </row>
+    <row r="299" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
         <v>9</v>
       </c>
@@ -18983,13 +19891,16 @@
       <c r="L299" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="M299" s="2"/>
+      <c r="M299" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N299" s="2"/>
       <c r="O299" s="2"/>
       <c r="P299" s="2"/>
       <c r="Q299" s="2"/>
-    </row>
-    <row r="300" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R299" s="2"/>
+    </row>
+    <row r="300" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A300" s="2" t="s">
         <v>9</v>
       </c>
@@ -19024,13 +19935,16 @@
       <c r="L300" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="M300" s="2"/>
+      <c r="M300" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N300" s="2"/>
       <c r="O300" s="2"/>
       <c r="P300" s="2"/>
       <c r="Q300" s="2"/>
-    </row>
-    <row r="301" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R300" s="2"/>
+    </row>
+    <row r="301" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A301" s="2" t="s">
         <v>9</v>
       </c>
@@ -19065,13 +19979,16 @@
       <c r="L301" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="M301" s="2"/>
+      <c r="M301" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N301" s="2"/>
       <c r="O301" s="2"/>
       <c r="P301" s="2"/>
       <c r="Q301" s="2"/>
-    </row>
-    <row r="302" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R301" s="2"/>
+    </row>
+    <row r="302" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A302" s="2" t="s">
         <v>9</v>
       </c>
@@ -19106,13 +20023,16 @@
       <c r="L302" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="M302" s="2"/>
+      <c r="M302" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N302" s="2"/>
       <c r="O302" s="2"/>
       <c r="P302" s="2"/>
       <c r="Q302" s="2"/>
-    </row>
-    <row r="303" spans="1:17" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R302" s="2"/>
+    </row>
+    <row r="303" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A303" s="2" t="s">
         <v>9</v>
       </c>
@@ -19149,13 +20069,16 @@
       <c r="L303" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="M303" s="2"/>
+      <c r="M303" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N303" s="2"/>
       <c r="O303" s="2"/>
       <c r="P303" s="2"/>
       <c r="Q303" s="2"/>
-    </row>
-    <row r="304" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R303" s="2"/>
+    </row>
+    <row r="304" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A304" s="2" t="s">
         <v>9</v>
       </c>
@@ -19190,13 +20113,16 @@
       <c r="L304" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="M304" s="2"/>
+      <c r="M304" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N304" s="2"/>
       <c r="O304" s="2"/>
       <c r="P304" s="2"/>
       <c r="Q304" s="2"/>
-    </row>
-    <row r="305" spans="1:17" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R304" s="2"/>
+    </row>
+    <row r="305" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A305" s="2" t="s">
         <v>9</v>
       </c>
@@ -19231,13 +20157,16 @@
       <c r="L305" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="M305" s="2"/>
+      <c r="M305" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N305" s="2"/>
       <c r="O305" s="2"/>
       <c r="P305" s="2"/>
       <c r="Q305" s="2"/>
-    </row>
-    <row r="306" spans="1:17" s="3" customFormat="1" ht="76.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R305" s="2"/>
+    </row>
+    <row r="306" spans="1:18" s="3" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="2" t="s">
         <v>9</v>
       </c>
@@ -19272,13 +20201,16 @@
       <c r="L306" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="M306" s="2"/>
+      <c r="M306" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N306" s="2"/>
       <c r="O306" s="2"/>
       <c r="P306" s="2"/>
       <c r="Q306" s="2"/>
-    </row>
-    <row r="307" spans="1:17" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R306" s="2"/>
+    </row>
+    <row r="307" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A307" s="2" t="s">
         <v>9</v>
       </c>
@@ -19313,13 +20245,16 @@
       <c r="L307" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="M307" s="2"/>
+      <c r="M307" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N307" s="2"/>
       <c r="O307" s="2"/>
       <c r="P307" s="2"/>
       <c r="Q307" s="2"/>
-    </row>
-    <row r="308" spans="1:17" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R307" s="2"/>
+    </row>
+    <row r="308" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A308" s="2" t="s">
         <v>9</v>
       </c>
@@ -19354,13 +20289,16 @@
       <c r="L308" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="M308" s="2"/>
+      <c r="M308" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N308" s="2"/>
       <c r="O308" s="2"/>
       <c r="P308" s="2"/>
       <c r="Q308" s="2"/>
-    </row>
-    <row r="309" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R308" s="2"/>
+    </row>
+    <row r="309" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A309" s="2" t="s">
         <v>9</v>
       </c>
@@ -19395,13 +20333,16 @@
       <c r="L309" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="M309" s="2"/>
+      <c r="M309" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N309" s="2"/>
       <c r="O309" s="2"/>
       <c r="P309" s="2"/>
       <c r="Q309" s="2"/>
-    </row>
-    <row r="310" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R309" s="2"/>
+    </row>
+    <row r="310" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A310" s="2" t="s">
         <v>9</v>
       </c>
@@ -19436,13 +20377,16 @@
       <c r="L310" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="M310" s="2"/>
+      <c r="M310" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N310" s="2"/>
       <c r="O310" s="2"/>
       <c r="P310" s="2"/>
       <c r="Q310" s="2"/>
-    </row>
-    <row r="311" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R310" s="2"/>
+    </row>
+    <row r="311" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A311" s="2" t="s">
         <v>9</v>
       </c>
@@ -19477,13 +20421,16 @@
       <c r="L311" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="M311" s="2"/>
+      <c r="M311" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N311" s="2"/>
       <c r="O311" s="2"/>
       <c r="P311" s="2"/>
       <c r="Q311" s="2"/>
-    </row>
-    <row r="312" spans="1:17" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R311" s="2"/>
+    </row>
+    <row r="312" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A312" s="2" t="s">
         <v>9</v>
       </c>
@@ -19518,13 +20465,16 @@
       <c r="L312" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="M312" s="2"/>
+      <c r="M312" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N312" s="2"/>
       <c r="O312" s="2"/>
       <c r="P312" s="2"/>
       <c r="Q312" s="2"/>
-    </row>
-    <row r="313" spans="1:17" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R312" s="2"/>
+    </row>
+    <row r="313" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A313" s="2" t="s">
         <v>9</v>
       </c>
@@ -19559,13 +20509,16 @@
       <c r="L313" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="M313" s="2"/>
+      <c r="M313" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N313" s="2"/>
       <c r="O313" s="2"/>
       <c r="P313" s="2"/>
       <c r="Q313" s="2"/>
-    </row>
-    <row r="314" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R313" s="2"/>
+    </row>
+    <row r="314" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A314" s="2" t="s">
         <v>9</v>
       </c>
@@ -19602,13 +20555,16 @@
       <c r="L314" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="M314" s="2"/>
+      <c r="M314" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N314" s="2"/>
       <c r="O314" s="2"/>
       <c r="P314" s="2"/>
       <c r="Q314" s="2"/>
-    </row>
-    <row r="315" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R314" s="2"/>
+    </row>
+    <row r="315" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A315" s="2" t="s">
         <v>9</v>
       </c>
@@ -19645,13 +20601,16 @@
       <c r="L315" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="M315" s="2"/>
+      <c r="M315" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N315" s="2"/>
       <c r="O315" s="2"/>
       <c r="P315" s="2"/>
       <c r="Q315" s="2"/>
-    </row>
-    <row r="316" spans="1:17" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R315" s="2"/>
+    </row>
+    <row r="316" spans="1:18" ht="87" x14ac:dyDescent="0.35">
       <c r="A316" s="2" t="s">
         <v>9</v>
       </c>
@@ -19686,13 +20645,16 @@
       <c r="L316" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="M316" s="2"/>
+      <c r="M316" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N316" s="2"/>
       <c r="O316" s="2"/>
       <c r="P316" s="2"/>
       <c r="Q316" s="2"/>
-    </row>
-    <row r="317" spans="1:17" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R316" s="2"/>
+    </row>
+    <row r="317" spans="1:18" ht="87" x14ac:dyDescent="0.35">
       <c r="A317" s="2" t="s">
         <v>9</v>
       </c>
@@ -19727,13 +20689,16 @@
       <c r="L317" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="M317" s="2"/>
+      <c r="M317" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N317" s="2"/>
       <c r="O317" s="2"/>
       <c r="P317" s="2"/>
       <c r="Q317" s="2"/>
-    </row>
-    <row r="318" spans="1:17" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R317" s="2"/>
+    </row>
+    <row r="318" spans="1:18" ht="87" x14ac:dyDescent="0.35">
       <c r="A318" s="2" t="s">
         <v>9</v>
       </c>
@@ -19768,13 +20733,16 @@
       <c r="L318" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="M318" s="2"/>
+      <c r="M318" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N318" s="2"/>
       <c r="O318" s="2"/>
       <c r="P318" s="2"/>
       <c r="Q318" s="2"/>
-    </row>
-    <row r="319" spans="1:17" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R318" s="2"/>
+    </row>
+    <row r="319" spans="1:18" ht="87" x14ac:dyDescent="0.35">
       <c r="A319" s="2" t="s">
         <v>9</v>
       </c>
@@ -19809,13 +20777,16 @@
       <c r="L319" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="M319" s="2"/>
+      <c r="M319" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N319" s="2"/>
       <c r="O319" s="2"/>
       <c r="P319" s="2"/>
       <c r="Q319" s="2"/>
-    </row>
-    <row r="320" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R319" s="2"/>
+    </row>
+    <row r="320" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A320" s="2" t="s">
         <v>9</v>
       </c>
@@ -19850,13 +20821,16 @@
       <c r="L320" s="11" t="s">
         <v>366</v>
       </c>
-      <c r="M320" s="2"/>
+      <c r="M320" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N320" s="2"/>
       <c r="O320" s="2"/>
       <c r="P320" s="2"/>
       <c r="Q320" s="2"/>
-    </row>
-    <row r="321" spans="1:17" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R320" s="2"/>
+    </row>
+    <row r="321" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A321" s="2" t="s">
         <v>9</v>
       </c>
@@ -19891,13 +20865,16 @@
       <c r="L321" s="11" t="s">
         <v>366</v>
       </c>
-      <c r="M321" s="2"/>
+      <c r="M321" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N321" s="2"/>
       <c r="O321" s="2"/>
       <c r="P321" s="2"/>
       <c r="Q321" s="2"/>
-    </row>
-    <row r="322" spans="1:17" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R321" s="2"/>
+    </row>
+    <row r="322" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A322" s="2" t="s">
         <v>9</v>
       </c>
@@ -19932,13 +20909,16 @@
       <c r="L322" s="11" t="s">
         <v>366</v>
       </c>
-      <c r="M322" s="2"/>
+      <c r="M322" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N322" s="2"/>
       <c r="O322" s="2"/>
       <c r="P322" s="2"/>
       <c r="Q322" s="2"/>
-    </row>
-    <row r="323" spans="1:17" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R322" s="2"/>
+    </row>
+    <row r="323" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A323" s="2" t="s">
         <v>9</v>
       </c>
@@ -19973,13 +20953,16 @@
       <c r="L323" s="11" t="s">
         <v>366</v>
       </c>
-      <c r="M323" s="2"/>
+      <c r="M323" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N323" s="2"/>
       <c r="O323" s="2"/>
       <c r="P323" s="2"/>
       <c r="Q323" s="2"/>
-    </row>
-    <row r="324" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R323" s="2"/>
+    </row>
+    <row r="324" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A324" s="2" t="s">
         <v>9</v>
       </c>
@@ -20014,13 +20997,16 @@
       <c r="L324" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="M324" s="2"/>
+      <c r="M324" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N324" s="2"/>
       <c r="O324" s="2"/>
       <c r="P324" s="2"/>
       <c r="Q324" s="2"/>
-    </row>
-    <row r="325" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R324" s="2"/>
+    </row>
+    <row r="325" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A325" s="2" t="s">
         <v>9</v>
       </c>
@@ -20055,13 +21041,16 @@
       <c r="L325" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="M325" s="2"/>
+      <c r="M325" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N325" s="2"/>
       <c r="O325" s="2"/>
       <c r="P325" s="2"/>
       <c r="Q325" s="2"/>
-    </row>
-    <row r="326" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R325" s="2"/>
+    </row>
+    <row r="326" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A326" s="2" t="s">
         <v>9</v>
       </c>
@@ -20096,13 +21085,16 @@
       <c r="L326" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="M326" s="2"/>
+      <c r="M326" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N326" s="2"/>
       <c r="O326" s="2"/>
       <c r="P326" s="2"/>
       <c r="Q326" s="2"/>
-    </row>
-    <row r="327" spans="1:17" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R326" s="2"/>
+    </row>
+    <row r="327" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A327" s="2" t="s">
         <v>9</v>
       </c>
@@ -20137,13 +21129,16 @@
       <c r="L327" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="M327" s="2"/>
+      <c r="M327" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N327" s="2"/>
       <c r="O327" s="2"/>
       <c r="P327" s="2"/>
       <c r="Q327" s="2"/>
-    </row>
-    <row r="328" spans="1:17" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R327" s="2"/>
+    </row>
+    <row r="328" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A328" s="2" t="s">
         <v>9</v>
       </c>
@@ -20178,13 +21173,16 @@
       <c r="L328" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="M328" s="2"/>
+      <c r="M328" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N328" s="2"/>
       <c r="O328" s="2"/>
       <c r="P328" s="2"/>
       <c r="Q328" s="2"/>
-    </row>
-    <row r="329" spans="1:17" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R328" s="2"/>
+    </row>
+    <row r="329" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A329" s="2" t="s">
         <v>9</v>
       </c>
@@ -20219,13 +21217,16 @@
       <c r="L329" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="M329" s="2"/>
+      <c r="M329" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N329" s="2"/>
       <c r="O329" s="2"/>
       <c r="P329" s="2"/>
       <c r="Q329" s="2"/>
-    </row>
-    <row r="330" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R329" s="2"/>
+    </row>
+    <row r="330" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A330" s="2" t="s">
         <v>9</v>
       </c>
@@ -20260,13 +21261,16 @@
       <c r="L330" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M330" s="2"/>
+      <c r="M330" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N330" s="2"/>
       <c r="O330" s="2"/>
       <c r="P330" s="2"/>
       <c r="Q330" s="2"/>
-    </row>
-    <row r="331" spans="1:17" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R330" s="2"/>
+    </row>
+    <row r="331" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A331" s="2" t="s">
         <v>9</v>
       </c>
@@ -20301,13 +21305,16 @@
       <c r="L331" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M331" s="2"/>
+      <c r="M331" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N331" s="2"/>
       <c r="O331" s="2"/>
       <c r="P331" s="2"/>
       <c r="Q331" s="2"/>
-    </row>
-    <row r="332" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R331" s="2"/>
+    </row>
+    <row r="332" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A332" s="2" t="s">
         <v>9</v>
       </c>
@@ -20342,13 +21349,16 @@
       <c r="L332" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="M332" s="2"/>
+      <c r="M332" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N332" s="2"/>
       <c r="O332" s="2"/>
       <c r="P332" s="2"/>
       <c r="Q332" s="2"/>
-    </row>
-    <row r="333" spans="1:17" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R332" s="2"/>
+    </row>
+    <row r="333" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A333" s="2" t="s">
         <v>9</v>
       </c>
@@ -20383,13 +21393,16 @@
       <c r="L333" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="M333" s="2"/>
+      <c r="M333" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N333" s="2"/>
       <c r="O333" s="2"/>
       <c r="P333" s="2"/>
       <c r="Q333" s="2"/>
-    </row>
-    <row r="334" spans="1:17" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R333" s="2"/>
+    </row>
+    <row r="334" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A334" s="2" t="s">
         <v>9</v>
       </c>
@@ -20424,13 +21437,16 @@
       <c r="L334" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="M334" s="2"/>
+      <c r="M334" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N334" s="2"/>
       <c r="O334" s="2"/>
       <c r="P334" s="2"/>
       <c r="Q334" s="2"/>
-    </row>
-    <row r="335" spans="1:17" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R334" s="2"/>
+    </row>
+    <row r="335" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A335" s="2" t="s">
         <v>9</v>
       </c>
@@ -20465,13 +21481,16 @@
       <c r="L335" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="M335" s="2"/>
+      <c r="M335" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N335" s="2"/>
       <c r="O335" s="2"/>
       <c r="P335" s="2"/>
       <c r="Q335" s="2"/>
-    </row>
-    <row r="336" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R335" s="2"/>
+    </row>
+    <row r="336" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A336" s="2" t="s">
         <v>9</v>
       </c>
@@ -20506,13 +21525,16 @@
       <c r="L336" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M336" s="2"/>
+      <c r="M336" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N336" s="2"/>
       <c r="O336" s="2"/>
       <c r="P336" s="2"/>
       <c r="Q336" s="2"/>
-    </row>
-    <row r="337" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R336" s="2"/>
+    </row>
+    <row r="337" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A337" s="2" t="s">
         <v>9</v>
       </c>
@@ -20547,13 +21569,16 @@
       <c r="L337" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M337" s="2"/>
+      <c r="M337" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N337" s="2"/>
       <c r="O337" s="2"/>
       <c r="P337" s="2"/>
       <c r="Q337" s="2"/>
-    </row>
-    <row r="338" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R337" s="2"/>
+    </row>
+    <row r="338" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A338" s="2" t="s">
         <v>9</v>
       </c>
@@ -20588,13 +21613,16 @@
       <c r="L338" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M338" s="2"/>
+      <c r="M338" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N338" s="2"/>
       <c r="O338" s="2"/>
       <c r="P338" s="2"/>
       <c r="Q338" s="2"/>
-    </row>
-    <row r="339" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R338" s="2"/>
+    </row>
+    <row r="339" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A339" s="2" t="s">
         <v>9</v>
       </c>
@@ -20629,13 +21657,16 @@
       <c r="L339" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M339" s="2"/>
+      <c r="M339" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N339" s="2"/>
       <c r="O339" s="2"/>
       <c r="P339" s="2"/>
       <c r="Q339" s="2"/>
-    </row>
-    <row r="340" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R339" s="2"/>
+    </row>
+    <row r="340" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A340" s="2" t="s">
         <v>9</v>
       </c>
@@ -20670,13 +21701,16 @@
       <c r="L340" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M340" s="2"/>
+      <c r="M340" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N340" s="2"/>
       <c r="O340" s="2"/>
       <c r="P340" s="2"/>
       <c r="Q340" s="2"/>
-    </row>
-    <row r="341" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R340" s="2"/>
+    </row>
+    <row r="341" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A341" s="2" t="s">
         <v>9</v>
       </c>
@@ -20711,13 +21745,16 @@
       <c r="L341" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M341" s="2"/>
+      <c r="M341" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N341" s="2"/>
       <c r="O341" s="2"/>
       <c r="P341" s="2"/>
       <c r="Q341" s="2"/>
-    </row>
-    <row r="342" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R341" s="2"/>
+    </row>
+    <row r="342" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A342" s="2" t="s">
         <v>9</v>
       </c>
@@ -20752,13 +21789,16 @@
       <c r="L342" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="M342" s="2"/>
+      <c r="M342" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N342" s="2"/>
       <c r="O342" s="2"/>
       <c r="P342" s="2"/>
       <c r="Q342" s="2"/>
-    </row>
-    <row r="343" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R342" s="2"/>
+    </row>
+    <row r="343" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A343" s="2" t="s">
         <v>9</v>
       </c>
@@ -20793,13 +21833,16 @@
       <c r="L343" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="M343" s="2"/>
+      <c r="M343" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N343" s="2"/>
       <c r="O343" s="2"/>
       <c r="P343" s="2"/>
       <c r="Q343" s="2"/>
-    </row>
-    <row r="344" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R343" s="2"/>
+    </row>
+    <row r="344" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A344" s="2" t="s">
         <v>9</v>
       </c>
@@ -20834,13 +21877,16 @@
       <c r="L344" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="M344" s="2"/>
+      <c r="M344" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N344" s="2"/>
       <c r="O344" s="2"/>
       <c r="P344" s="2"/>
       <c r="Q344" s="2"/>
-    </row>
-    <row r="345" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R344" s="2"/>
+    </row>
+    <row r="345" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A345" s="2" t="s">
         <v>9</v>
       </c>
@@ -20875,13 +21921,16 @@
       <c r="L345" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="M345" s="2"/>
+      <c r="M345" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N345" s="2"/>
       <c r="O345" s="2"/>
       <c r="P345" s="2"/>
       <c r="Q345" s="2"/>
-    </row>
-    <row r="346" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R345" s="2"/>
+    </row>
+    <row r="346" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A346" s="2" t="s">
         <v>9</v>
       </c>
@@ -20916,13 +21965,16 @@
       <c r="L346" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M346" s="2"/>
+      <c r="M346" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N346" s="2"/>
       <c r="O346" s="2"/>
       <c r="P346" s="2"/>
       <c r="Q346" s="2"/>
-    </row>
-    <row r="347" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R346" s="2"/>
+    </row>
+    <row r="347" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A347" s="2" t="s">
         <v>9</v>
       </c>
@@ -20957,13 +22009,16 @@
       <c r="L347" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M347" s="2"/>
+      <c r="M347" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N347" s="2"/>
       <c r="O347" s="2"/>
       <c r="P347" s="2"/>
       <c r="Q347" s="2"/>
-    </row>
-    <row r="348" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R347" s="2"/>
+    </row>
+    <row r="348" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A348" s="2" t="s">
         <v>9</v>
       </c>
@@ -20998,13 +22053,16 @@
       <c r="L348" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M348" s="2"/>
+      <c r="M348" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N348" s="2"/>
       <c r="O348" s="2"/>
       <c r="P348" s="2"/>
       <c r="Q348" s="2"/>
-    </row>
-    <row r="349" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R348" s="2"/>
+    </row>
+    <row r="349" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A349" s="2" t="s">
         <v>9</v>
       </c>
@@ -21039,13 +22097,16 @@
       <c r="L349" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="M349" s="2"/>
+      <c r="M349" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N349" s="2"/>
       <c r="O349" s="2"/>
       <c r="P349" s="2"/>
       <c r="Q349" s="2"/>
-    </row>
-    <row r="350" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R349" s="2"/>
+    </row>
+    <row r="350" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A350" s="2" t="s">
         <v>9</v>
       </c>
@@ -21080,13 +22141,16 @@
       <c r="L350" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="M350" s="2"/>
+      <c r="M350" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N350" s="2"/>
       <c r="O350" s="2"/>
       <c r="P350" s="2"/>
       <c r="Q350" s="2"/>
-    </row>
-    <row r="351" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R350" s="2"/>
+    </row>
+    <row r="351" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A351" s="2" t="s">
         <v>9</v>
       </c>
@@ -21121,13 +22185,16 @@
       <c r="L351" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M351" s="2"/>
+      <c r="M351" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N351" s="2"/>
       <c r="O351" s="2"/>
       <c r="P351" s="2"/>
       <c r="Q351" s="2"/>
-    </row>
-    <row r="352" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R351" s="2"/>
+    </row>
+    <row r="352" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A352" s="2" t="s">
         <v>9</v>
       </c>
@@ -21162,13 +22229,16 @@
       <c r="L352" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="M352" s="2"/>
+      <c r="M352" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N352" s="2"/>
       <c r="O352" s="2"/>
       <c r="P352" s="2"/>
       <c r="Q352" s="2"/>
-    </row>
-    <row r="353" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R352" s="2"/>
+    </row>
+    <row r="353" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A353" s="2" t="s">
         <v>9</v>
       </c>
@@ -21203,13 +22273,16 @@
       <c r="L353" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M353" s="2"/>
+      <c r="M353" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N353" s="2"/>
       <c r="O353" s="2"/>
       <c r="P353" s="2"/>
       <c r="Q353" s="2"/>
-    </row>
-    <row r="354" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R353" s="2"/>
+    </row>
+    <row r="354" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A354" s="2" t="s">
         <v>9</v>
       </c>
@@ -21244,13 +22317,16 @@
       <c r="L354" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="M354" s="2"/>
+      <c r="M354" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N354" s="2"/>
       <c r="O354" s="2"/>
       <c r="P354" s="2"/>
       <c r="Q354" s="2"/>
-    </row>
-    <row r="355" spans="1:17" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="R354" s="2"/>
+    </row>
+    <row r="355" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A355" s="2" t="s">
         <v>9</v>
       </c>
@@ -21285,13 +22361,16 @@
       <c r="L355" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M355" s="2"/>
+      <c r="M355" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N355" s="2"/>
       <c r="O355" s="2"/>
       <c r="P355" s="2"/>
       <c r="Q355" s="2"/>
-    </row>
-    <row r="356" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R355" s="2"/>
+    </row>
+    <row r="356" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A356" s="2" t="s">
         <v>9</v>
       </c>
@@ -21326,13 +22405,16 @@
       <c r="L356" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M356" s="2"/>
+      <c r="M356" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N356" s="2"/>
       <c r="O356" s="2"/>
       <c r="P356" s="2"/>
       <c r="Q356" s="2"/>
-    </row>
-    <row r="357" spans="1:17" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="R356" s="2"/>
+    </row>
+    <row r="357" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A357" s="2" t="s">
         <v>9</v>
       </c>
@@ -21367,13 +22449,16 @@
       <c r="L357" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="M357" s="2"/>
+      <c r="M357" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N357" s="2"/>
       <c r="O357" s="2"/>
       <c r="P357" s="2"/>
       <c r="Q357" s="2"/>
-    </row>
-    <row r="358" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R357" s="2"/>
+    </row>
+    <row r="358" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A358" s="2" t="s">
         <v>9</v>
       </c>
@@ -21408,13 +22493,16 @@
       <c r="L358" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M358" s="2"/>
+      <c r="M358" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N358" s="2"/>
       <c r="O358" s="2"/>
       <c r="P358" s="2"/>
       <c r="Q358" s="2"/>
-    </row>
-    <row r="359" spans="1:17" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="R358" s="2"/>
+    </row>
+    <row r="359" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A359" s="2" t="s">
         <v>9</v>
       </c>
@@ -21449,13 +22537,16 @@
       <c r="L359" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="M359" s="2"/>
+      <c r="M359" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N359" s="2"/>
       <c r="O359" s="2"/>
       <c r="P359" s="2"/>
       <c r="Q359" s="2"/>
-    </row>
-    <row r="360" spans="1:17" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R359" s="2"/>
+    </row>
+    <row r="360" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A360" s="2" t="s">
         <v>9</v>
       </c>
@@ -21490,13 +22581,16 @@
       <c r="L360" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M360" s="2"/>
+      <c r="M360" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N360" s="2"/>
       <c r="O360" s="2"/>
       <c r="P360" s="2"/>
       <c r="Q360" s="2"/>
-    </row>
-    <row r="361" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R360" s="2"/>
+    </row>
+    <row r="361" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A361" s="2" t="s">
         <v>9</v>
       </c>
@@ -21531,13 +22625,16 @@
       <c r="L361" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M361" s="2"/>
+      <c r="M361" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N361" s="2"/>
       <c r="O361" s="2"/>
       <c r="P361" s="2"/>
       <c r="Q361" s="2"/>
-    </row>
-    <row r="362" spans="1:17" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="R361" s="2"/>
+    </row>
+    <row r="362" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A362" s="2" t="s">
         <v>9</v>
       </c>
@@ -21572,13 +22669,16 @@
       <c r="L362" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M362" s="2"/>
+      <c r="M362" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N362" s="2"/>
       <c r="O362" s="2"/>
       <c r="P362" s="2"/>
       <c r="Q362" s="2"/>
-    </row>
-    <row r="363" spans="1:17" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="R362" s="2"/>
+    </row>
+    <row r="363" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A363" s="2" t="s">
         <v>9</v>
       </c>
@@ -21613,13 +22713,16 @@
       <c r="L363" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="M363" s="2"/>
+      <c r="M363" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N363" s="2"/>
       <c r="O363" s="2"/>
       <c r="P363" s="2"/>
       <c r="Q363" s="2"/>
-    </row>
-    <row r="364" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R363" s="2"/>
+    </row>
+    <row r="364" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A364" s="2" t="s">
         <v>9</v>
       </c>
@@ -21654,13 +22757,16 @@
       <c r="L364" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="M364" s="2"/>
+      <c r="M364" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N364" s="2"/>
       <c r="O364" s="2"/>
       <c r="P364" s="2"/>
       <c r="Q364" s="2"/>
-    </row>
-    <row r="365" spans="1:17" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="R364" s="2"/>
+    </row>
+    <row r="365" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A365" s="2" t="s">
         <v>9</v>
       </c>
@@ -21695,13 +22801,16 @@
       <c r="L365" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M365" s="2"/>
+      <c r="M365" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N365" s="2"/>
       <c r="O365" s="2"/>
       <c r="P365" s="2"/>
       <c r="Q365" s="2"/>
-    </row>
-    <row r="366" spans="1:17" s="3" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="R365" s="2"/>
+    </row>
+    <row r="366" spans="1:18" s="3" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A366" s="2" t="s">
         <v>9</v>
       </c>
@@ -21736,13 +22845,16 @@
       <c r="L366" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="M366" s="2"/>
+      <c r="M366" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N366" s="2"/>
       <c r="O366" s="2"/>
       <c r="P366" s="2"/>
       <c r="Q366" s="2"/>
-    </row>
-    <row r="367" spans="1:17" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="R366" s="2"/>
+    </row>
+    <row r="367" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A367" s="2" t="s">
         <v>9</v>
       </c>
@@ -21777,13 +22889,16 @@
       <c r="L367" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M367" s="2"/>
+      <c r="M367" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N367" s="2"/>
       <c r="O367" s="2"/>
       <c r="P367" s="2"/>
       <c r="Q367" s="2"/>
-    </row>
-    <row r="368" spans="1:17" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="R367" s="2"/>
+    </row>
+    <row r="368" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A368" s="2" t="s">
         <v>9</v>
       </c>
@@ -21818,13 +22933,16 @@
       <c r="L368" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="M368" s="2"/>
+      <c r="M368" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N368" s="2"/>
       <c r="O368" s="2"/>
       <c r="P368" s="2"/>
       <c r="Q368" s="2"/>
-    </row>
-    <row r="369" spans="1:17" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="R368" s="2"/>
+    </row>
+    <row r="369" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A369" s="2" t="s">
         <v>9</v>
       </c>
@@ -21859,13 +22977,16 @@
       <c r="L369" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="M369" s="2"/>
+      <c r="M369" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N369" s="2"/>
       <c r="O369" s="2"/>
       <c r="P369" s="2"/>
       <c r="Q369" s="2"/>
-    </row>
-    <row r="370" spans="1:17" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="R369" s="2"/>
+    </row>
+    <row r="370" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A370" s="2" t="s">
         <v>9</v>
       </c>
@@ -21900,13 +23021,16 @@
       <c r="L370" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="M370" s="2"/>
+      <c r="M370" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N370" s="2"/>
       <c r="O370" s="2"/>
       <c r="P370" s="2"/>
       <c r="Q370" s="2"/>
-    </row>
-    <row r="371" spans="1:17" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="R370" s="2"/>
+    </row>
+    <row r="371" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A371" s="2" t="s">
         <v>9</v>
       </c>
@@ -21941,13 +23065,16 @@
       <c r="L371" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="M371" s="2"/>
+      <c r="M371" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N371" s="2"/>
       <c r="O371" s="2"/>
       <c r="P371" s="2"/>
       <c r="Q371" s="2"/>
-    </row>
-    <row r="372" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R371" s="2"/>
+    </row>
+    <row r="372" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A372" s="2" t="s">
         <v>9</v>
       </c>
@@ -21982,13 +23109,16 @@
       <c r="L372" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="M372" s="2"/>
+      <c r="M372" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N372" s="2"/>
       <c r="O372" s="2"/>
       <c r="P372" s="2"/>
       <c r="Q372" s="2"/>
-    </row>
-    <row r="373" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R372" s="2"/>
+    </row>
+    <row r="373" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A373" s="2" t="s">
         <v>9</v>
       </c>
@@ -22023,13 +23153,16 @@
       <c r="L373" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M373" s="2"/>
+      <c r="M373" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N373" s="2"/>
       <c r="O373" s="2"/>
       <c r="P373" s="2"/>
       <c r="Q373" s="2"/>
-    </row>
-    <row r="374" spans="1:17" s="3" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R373" s="2"/>
+    </row>
+    <row r="374" spans="1:18" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A374" s="2" t="s">
         <v>9</v>
       </c>
@@ -22066,13 +23199,16 @@
       <c r="L374" s="2" t="s">
         <v>1317</v>
       </c>
-      <c r="M374" s="2"/>
+      <c r="M374" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N374" s="2"/>
       <c r="O374" s="2"/>
       <c r="P374" s="2"/>
       <c r="Q374" s="2"/>
-    </row>
-    <row r="375" spans="1:17" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="R374" s="2"/>
+    </row>
+    <row r="375" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A375" s="2" t="s">
         <v>9</v>
       </c>
@@ -22109,13 +23245,16 @@
       <c r="L375" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="M375" s="2"/>
+      <c r="M375" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N375" s="2"/>
       <c r="O375" s="2"/>
       <c r="P375" s="2"/>
       <c r="Q375" s="2"/>
-    </row>
-    <row r="376" spans="1:17" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="R375" s="2"/>
+    </row>
+    <row r="376" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A376" s="2" t="s">
         <v>9</v>
       </c>
@@ -22152,13 +23291,16 @@
       <c r="L376" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="M376" s="2"/>
+      <c r="M376" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N376" s="2"/>
       <c r="O376" s="2"/>
       <c r="P376" s="2"/>
       <c r="Q376" s="2"/>
-    </row>
-    <row r="377" spans="1:17" s="3" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R376" s="2"/>
+    </row>
+    <row r="377" spans="1:18" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A377" s="2" t="s">
         <v>9</v>
       </c>
@@ -22195,13 +23337,16 @@
       <c r="L377" s="2" t="s">
         <v>1317</v>
       </c>
-      <c r="M377" s="2"/>
+      <c r="M377" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N377" s="2"/>
       <c r="O377" s="2"/>
       <c r="P377" s="2"/>
       <c r="Q377" s="2"/>
-    </row>
-    <row r="378" spans="1:17" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="R377" s="2"/>
+    </row>
+    <row r="378" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A378" s="2" t="s">
         <v>9</v>
       </c>
@@ -22238,13 +23383,16 @@
       <c r="L378" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="M378" s="2"/>
+      <c r="M378" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N378" s="2"/>
       <c r="O378" s="2"/>
       <c r="P378" s="2"/>
       <c r="Q378" s="2"/>
-    </row>
-    <row r="379" spans="1:17" s="3" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R378" s="2"/>
+    </row>
+    <row r="379" spans="1:18" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A379" s="2" t="s">
         <v>9</v>
       </c>
@@ -22281,13 +23429,16 @@
       <c r="L379" s="2" t="s">
         <v>1317</v>
       </c>
-      <c r="M379" s="2"/>
+      <c r="M379" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N379" s="2"/>
       <c r="O379" s="2"/>
       <c r="P379" s="2"/>
       <c r="Q379" s="2"/>
-    </row>
-    <row r="380" spans="1:17" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="R379" s="2"/>
+    </row>
+    <row r="380" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A380" s="2" t="s">
         <v>9</v>
       </c>
@@ -22324,13 +23475,16 @@
       <c r="L380" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="M380" s="2"/>
+      <c r="M380" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N380" s="2"/>
       <c r="O380" s="2"/>
       <c r="P380" s="2"/>
       <c r="Q380" s="2"/>
-    </row>
-    <row r="381" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R380" s="2"/>
+    </row>
+    <row r="381" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A381" s="2" t="s">
         <v>9</v>
       </c>
@@ -22367,13 +23521,16 @@
       <c r="L381" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="M381" s="2"/>
+      <c r="M381" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N381" s="2"/>
       <c r="O381" s="2"/>
       <c r="P381" s="2"/>
       <c r="Q381" s="2"/>
-    </row>
-    <row r="382" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R381" s="2"/>
+    </row>
+    <row r="382" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A382" s="2" t="s">
         <v>9</v>
       </c>
@@ -22410,13 +23567,16 @@
       <c r="L382" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="M382" s="2"/>
+      <c r="M382" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N382" s="2"/>
       <c r="O382" s="2"/>
       <c r="P382" s="2"/>
       <c r="Q382" s="2"/>
-    </row>
-    <row r="383" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R382" s="2"/>
+    </row>
+    <row r="383" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A383" s="2" t="s">
         <v>9</v>
       </c>
@@ -22453,13 +23613,16 @@
       <c r="L383" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="M383" s="2"/>
+      <c r="M383" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N383" s="2"/>
       <c r="O383" s="2"/>
       <c r="P383" s="2"/>
       <c r="Q383" s="2"/>
-    </row>
-    <row r="384" spans="1:17" s="3" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R383" s="2"/>
+    </row>
+    <row r="384" spans="1:18" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A384" s="2" t="s">
         <v>9</v>
       </c>
@@ -22494,13 +23657,16 @@
       <c r="L384" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="M384" s="2"/>
+      <c r="M384" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N384" s="2"/>
       <c r="O384" s="2"/>
       <c r="P384" s="2"/>
       <c r="Q384" s="2"/>
-    </row>
-    <row r="385" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R384" s="2"/>
+    </row>
+    <row r="385" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A385" s="2" t="s">
         <v>9</v>
       </c>
@@ -22537,13 +23703,16 @@
       <c r="L385" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="M385" s="2"/>
+      <c r="M385" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N385" s="2"/>
       <c r="O385" s="2"/>
       <c r="P385" s="2"/>
       <c r="Q385" s="2"/>
-    </row>
-    <row r="386" spans="1:17" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R385" s="2"/>
+    </row>
+    <row r="386" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A386" s="2" t="s">
         <v>9</v>
       </c>
@@ -22580,13 +23749,16 @@
       <c r="L386" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="M386" s="2"/>
+      <c r="M386" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N386" s="2"/>
       <c r="O386" s="2"/>
       <c r="P386" s="2"/>
       <c r="Q386" s="2"/>
-    </row>
-    <row r="387" spans="1:17" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="R386" s="2"/>
+    </row>
+    <row r="387" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A387" s="2" t="s">
         <v>9</v>
       </c>
@@ -22623,13 +23795,16 @@
       <c r="L387" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="M387" s="2"/>
+      <c r="M387" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N387" s="2"/>
       <c r="O387" s="2"/>
       <c r="P387" s="2"/>
       <c r="Q387" s="2"/>
-    </row>
-    <row r="388" spans="1:17" s="3" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R387" s="2"/>
+    </row>
+    <row r="388" spans="1:18" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A388" s="2" t="s">
         <v>9</v>
       </c>
@@ -22664,13 +23839,16 @@
       <c r="L388" s="2" t="s">
         <v>1317</v>
       </c>
-      <c r="M388" s="2"/>
+      <c r="M388" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N388" s="2"/>
       <c r="O388" s="2"/>
       <c r="P388" s="2"/>
       <c r="Q388" s="2"/>
-    </row>
-    <row r="389" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R388" s="2"/>
+    </row>
+    <row r="389" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A389" s="2" t="s">
         <v>9</v>
       </c>
@@ -22707,13 +23885,16 @@
       <c r="L389" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="M389" s="2"/>
+      <c r="M389" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N389" s="2"/>
       <c r="O389" s="2"/>
       <c r="P389" s="2"/>
       <c r="Q389" s="2"/>
-    </row>
-    <row r="390" spans="1:17" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="R389" s="2"/>
+    </row>
+    <row r="390" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A390" s="2" t="s">
         <v>9</v>
       </c>
@@ -22750,13 +23931,16 @@
       <c r="L390" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="M390" s="2"/>
+      <c r="M390" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N390" s="2"/>
       <c r="O390" s="2"/>
       <c r="P390" s="2"/>
       <c r="Q390" s="2"/>
-    </row>
-    <row r="391" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R390" s="2"/>
+    </row>
+    <row r="391" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A391" s="2" t="s">
         <v>9</v>
       </c>
@@ -22793,13 +23977,16 @@
       <c r="L391" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="M391" s="2"/>
+      <c r="M391" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N391" s="2"/>
       <c r="O391" s="2"/>
       <c r="P391" s="2"/>
       <c r="Q391" s="2"/>
-    </row>
-    <row r="392" spans="1:17" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="R391" s="2"/>
+    </row>
+    <row r="392" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A392" s="2" t="s">
         <v>9</v>
       </c>
@@ -22836,13 +24023,16 @@
       <c r="L392" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="M392" s="2"/>
+      <c r="M392" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N392" s="2"/>
       <c r="O392" s="2"/>
       <c r="P392" s="2"/>
       <c r="Q392" s="2"/>
-    </row>
-    <row r="393" spans="1:17" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="R392" s="2"/>
+    </row>
+    <row r="393" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A393" s="2" t="s">
         <v>9</v>
       </c>
@@ -22879,13 +24069,16 @@
       <c r="L393" s="2" t="s">
         <v>1671</v>
       </c>
-      <c r="M393" s="2"/>
+      <c r="M393" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N393" s="2"/>
       <c r="O393" s="2"/>
       <c r="P393" s="2"/>
       <c r="Q393" s="2"/>
-    </row>
-    <row r="394" spans="1:17" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="R393" s="2"/>
+    </row>
+    <row r="394" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A394" s="2" t="s">
         <v>9</v>
       </c>
@@ -22922,13 +24115,16 @@
       <c r="L394" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="M394" s="2"/>
+      <c r="M394" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N394" s="2"/>
       <c r="O394" s="2"/>
       <c r="P394" s="2"/>
       <c r="Q394" s="2"/>
-    </row>
-    <row r="395" spans="1:17" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="R394" s="2"/>
+    </row>
+    <row r="395" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A395" s="2" t="s">
         <v>9</v>
       </c>
@@ -22965,13 +24161,16 @@
       <c r="L395" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="M395" s="2"/>
+      <c r="M395" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N395" s="2"/>
       <c r="O395" s="2"/>
       <c r="P395" s="2"/>
       <c r="Q395" s="2"/>
-    </row>
-    <row r="396" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R395" s="2"/>
+    </row>
+    <row r="396" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A396" s="2" t="s">
         <v>9</v>
       </c>
@@ -23008,13 +24207,16 @@
       <c r="L396" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="M396" s="2"/>
+      <c r="M396" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N396" s="2"/>
       <c r="O396" s="2"/>
       <c r="P396" s="2"/>
       <c r="Q396" s="2"/>
-    </row>
-    <row r="397" spans="1:17" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R396" s="2"/>
+    </row>
+    <row r="397" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A397" s="2" t="s">
         <v>9</v>
       </c>
@@ -23051,13 +24253,16 @@
       <c r="L397" s="2" t="s">
         <v>1671</v>
       </c>
-      <c r="M397" s="2"/>
+      <c r="M397" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N397" s="2"/>
       <c r="O397" s="2"/>
       <c r="P397" s="2"/>
       <c r="Q397" s="2"/>
-    </row>
-    <row r="398" spans="1:17" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="R397" s="2"/>
+    </row>
+    <row r="398" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A398" s="2" t="s">
         <v>9</v>
       </c>
@@ -23094,13 +24299,16 @@
       <c r="L398" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="M398" s="2"/>
+      <c r="M398" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N398" s="2"/>
       <c r="O398" s="2"/>
       <c r="P398" s="2"/>
       <c r="Q398" s="2"/>
-    </row>
-    <row r="399" spans="1:17" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="R398" s="2"/>
+    </row>
+    <row r="399" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A399" s="2" t="s">
         <v>9</v>
       </c>
@@ -23137,13 +24345,16 @@
       <c r="L399" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="M399" s="2"/>
+      <c r="M399" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N399" s="2"/>
       <c r="O399" s="2"/>
       <c r="P399" s="2"/>
       <c r="Q399" s="2"/>
-    </row>
-    <row r="400" spans="1:17" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="R399" s="2"/>
+    </row>
+    <row r="400" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A400" s="2" t="s">
         <v>9</v>
       </c>
@@ -23180,13 +24391,16 @@
       <c r="L400" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="M400" s="2"/>
+      <c r="M400" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N400" s="2"/>
       <c r="O400" s="2"/>
       <c r="P400" s="2"/>
       <c r="Q400" s="2"/>
-    </row>
-    <row r="401" spans="1:17" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="R400" s="2"/>
+    </row>
+    <row r="401" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A401" s="2" t="s">
         <v>9</v>
       </c>
@@ -23223,13 +24437,16 @@
       <c r="L401" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="M401" s="2"/>
+      <c r="M401" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N401" s="2"/>
       <c r="O401" s="2"/>
       <c r="P401" s="2"/>
       <c r="Q401" s="2"/>
-    </row>
-    <row r="402" spans="1:17" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="R401" s="2"/>
+    </row>
+    <row r="402" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A402" s="2" t="s">
         <v>9</v>
       </c>
@@ -23266,13 +24483,16 @@
       <c r="L402" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="M402" s="2"/>
+      <c r="M402" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N402" s="2"/>
       <c r="O402" s="2"/>
       <c r="P402" s="2"/>
       <c r="Q402" s="2"/>
-    </row>
-    <row r="403" spans="1:17" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="R402" s="2"/>
+    </row>
+    <row r="403" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A403" s="2" t="s">
         <v>9</v>
       </c>
@@ -23309,13 +24529,16 @@
       <c r="L403" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="M403" s="2"/>
+      <c r="M403" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N403" s="2"/>
       <c r="O403" s="2"/>
       <c r="P403" s="2"/>
       <c r="Q403" s="2"/>
-    </row>
-    <row r="404" spans="1:17" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R403" s="2"/>
+    </row>
+    <row r="404" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A404" s="2" t="s">
         <v>9</v>
       </c>
@@ -23352,13 +24575,16 @@
       <c r="L404" s="2" t="s">
         <v>1669</v>
       </c>
-      <c r="M404" s="2"/>
+      <c r="M404" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N404" s="2"/>
       <c r="O404" s="2"/>
       <c r="P404" s="2"/>
       <c r="Q404" s="2"/>
-    </row>
-    <row r="405" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R404" s="2"/>
+    </row>
+    <row r="405" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A405" s="2" t="s">
         <v>9</v>
       </c>
@@ -23395,13 +24621,16 @@
       <c r="L405" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="M405" s="2"/>
+      <c r="M405" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N405" s="2"/>
       <c r="O405" s="2"/>
       <c r="P405" s="2"/>
       <c r="Q405" s="2"/>
-    </row>
-    <row r="406" spans="1:17" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="R405" s="2"/>
+    </row>
+    <row r="406" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A406" s="2" t="s">
         <v>9</v>
       </c>
@@ -23438,13 +24667,16 @@
       <c r="L406" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="M406" s="2"/>
+      <c r="M406" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N406" s="2"/>
       <c r="O406" s="2"/>
       <c r="P406" s="2"/>
       <c r="Q406" s="2"/>
-    </row>
-    <row r="407" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R406" s="2"/>
+    </row>
+    <row r="407" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A407" s="2" t="s">
         <v>9</v>
       </c>
@@ -23481,13 +24713,16 @@
       <c r="L407" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="M407" s="2"/>
+      <c r="M407" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N407" s="2"/>
       <c r="O407" s="2"/>
       <c r="P407" s="2"/>
       <c r="Q407" s="2"/>
-    </row>
-    <row r="408" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R407" s="2"/>
+    </row>
+    <row r="408" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A408" s="2" t="s">
         <v>9</v>
       </c>
@@ -23524,13 +24759,16 @@
       <c r="L408" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="M408" s="2"/>
+      <c r="M408" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N408" s="2"/>
       <c r="O408" s="2"/>
       <c r="P408" s="2"/>
       <c r="Q408" s="2"/>
-    </row>
-    <row r="409" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R408" s="2"/>
+    </row>
+    <row r="409" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A409" s="2" t="s">
         <v>9</v>
       </c>
@@ -23567,13 +24805,16 @@
       <c r="L409" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="M409" s="2"/>
+      <c r="M409" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N409" s="2"/>
       <c r="O409" s="2"/>
       <c r="P409" s="2"/>
       <c r="Q409" s="2"/>
-    </row>
-    <row r="410" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R409" s="2"/>
+    </row>
+    <row r="410" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A410" s="2" t="s">
         <v>9</v>
       </c>
@@ -23610,13 +24851,16 @@
       <c r="L410" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="M410" s="2"/>
+      <c r="M410" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N410" s="2"/>
       <c r="O410" s="2"/>
       <c r="P410" s="2"/>
       <c r="Q410" s="2"/>
-    </row>
-    <row r="411" spans="1:17" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R410" s="2"/>
+    </row>
+    <row r="411" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A411" s="2" t="s">
         <v>9</v>
       </c>
@@ -23653,13 +24897,16 @@
       <c r="L411" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="M411" s="2"/>
+      <c r="M411" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N411" s="2"/>
       <c r="O411" s="2"/>
       <c r="P411" s="2"/>
       <c r="Q411" s="2"/>
-    </row>
-    <row r="412" spans="1:17" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="R411" s="2"/>
+    </row>
+    <row r="412" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A412" s="2" t="s">
         <v>9</v>
       </c>
@@ -23694,13 +24941,16 @@
       <c r="L412" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="M412" s="2"/>
+      <c r="M412" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N412" s="2"/>
       <c r="O412" s="2"/>
       <c r="P412" s="2"/>
       <c r="Q412" s="2"/>
-    </row>
-    <row r="413" spans="1:17" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="R412" s="2"/>
+    </row>
+    <row r="413" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A413" s="2" t="s">
         <v>9</v>
       </c>
@@ -23735,13 +24985,16 @@
       <c r="L413" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="M413" s="2"/>
+      <c r="M413" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N413" s="2"/>
       <c r="O413" s="2"/>
       <c r="P413" s="2"/>
       <c r="Q413" s="2"/>
-    </row>
-    <row r="414" spans="1:17" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="R413" s="2"/>
+    </row>
+    <row r="414" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A414" s="2" t="s">
         <v>9</v>
       </c>
@@ -23776,13 +25029,16 @@
       <c r="L414" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="M414" s="2"/>
+      <c r="M414" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N414" s="2"/>
       <c r="O414" s="2"/>
       <c r="P414" s="2"/>
       <c r="Q414" s="2"/>
-    </row>
-    <row r="415" spans="1:17" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R414" s="2"/>
+    </row>
+    <row r="415" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A415" s="2" t="s">
         <v>9</v>
       </c>
@@ -23817,13 +25073,16 @@
       <c r="L415" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="M415" s="2"/>
+      <c r="M415" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N415" s="2"/>
       <c r="O415" s="2"/>
       <c r="P415" s="2"/>
       <c r="Q415" s="2"/>
-    </row>
-    <row r="416" spans="1:17" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R415" s="2"/>
+    </row>
+    <row r="416" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A416" s="2" t="s">
         <v>9</v>
       </c>
@@ -23858,20 +25117,17 @@
       <c r="L416" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M416" s="2"/>
+      <c r="M416" s="2" t="s">
+        <v>1782</v>
+      </c>
       <c r="N416" s="2"/>
       <c r="O416" s="2"/>
       <c r="P416" s="2"/>
       <c r="Q416" s="2"/>
+      <c r="R416" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q416" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="INCONNUE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:R416" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L229">
     <sortCondition ref="C2:C424"/>
   </sortState>

--- a/Data/FairCarboN_Datas_Contacts.xlsx
+++ b/Data/FairCarboN_Datas_Contacts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122DAB6C-F776-4063-B01B-0089419CD2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19295A30-A204-4B94-AC95-864977D60788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Data/FairCarboN_Datas_Contacts.xlsx
+++ b/Data/FairCarboN_Datas_Contacts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19295A30-A204-4B94-AC95-864977D60788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02120EBC-792D-4174-9868-72A6DD7F0358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Liste" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Liste!$A$1:$R$416</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Liste!$A$1:$R$417</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5284" uniqueCount="1783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5323" uniqueCount="1799">
   <si>
     <t>Titre : Liste des unités du PEPR FairCarboN</t>
   </si>
@@ -5400,6 +5400,54 @@
   </si>
   <si>
     <t>NON</t>
+  </si>
+  <si>
+    <t>PEPR</t>
+  </si>
+  <si>
+    <t>Jérôme Dutroncy</t>
+  </si>
+  <si>
+    <t>jerome.dutroncy@univ-grenoble-alpes.fr</t>
+  </si>
+  <si>
+    <t>DUTRONCY</t>
+  </si>
+  <si>
+    <t>Perrine Franquet</t>
+  </si>
+  <si>
+    <t>perrine.franquet@inrae.fr</t>
+  </si>
+  <si>
+    <t>FRANQUET</t>
+  </si>
+  <si>
+    <t>Perrine</t>
+  </si>
+  <si>
+    <t>Centre-Siège INRAE</t>
+  </si>
+  <si>
+    <t>INRAE</t>
+  </si>
+  <si>
+    <t>Antony</t>
+  </si>
+  <si>
+    <t>48.753613</t>
+  </si>
+  <si>
+    <t>2.2958034</t>
+  </si>
+  <si>
+    <t>HEITZ</t>
+  </si>
+  <si>
+    <t>Claire Heitz</t>
+  </si>
+  <si>
+    <t>claire.heitz@inrae.fr</t>
   </si>
 </sst>
 </file>
@@ -6214,7 +6262,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R416"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:R419"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.54296875" style="8" bestFit="1" customWidth="1"/>
@@ -6292,7 +6341,7 @@
         <v>1765</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="188.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -6338,7 +6387,7 @@
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -6430,7 +6479,7 @@
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
     </row>
-    <row r="5" spans="1:18" s="3" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" s="3" customFormat="1" ht="188.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -6476,7 +6525,7 @@
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
     </row>
-    <row r="6" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -6522,7 +6571,7 @@
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
     </row>
-    <row r="7" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
@@ -6568,7 +6617,7 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
     </row>
-    <row r="8" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -6614,7 +6663,7 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
     </row>
-    <row r="9" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
@@ -6660,7 +6709,7 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
     </row>
-    <row r="10" spans="1:18" s="3" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" s="3" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -6706,7 +6755,7 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
     </row>
-    <row r="11" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -6752,7 +6801,7 @@
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
     </row>
-    <row r="12" spans="1:18" s="3" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" s="3" customFormat="1" ht="188.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -6798,7 +6847,7 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
     </row>
-    <row r="13" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
@@ -6844,7 +6893,7 @@
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
     </row>
-    <row r="14" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
@@ -6890,7 +6939,7 @@
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
     </row>
-    <row r="15" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
@@ -6936,7 +6985,7 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
     </row>
-    <row r="16" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
@@ -6982,7 +7031,7 @@
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
     </row>
-    <row r="17" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>9</v>
       </c>
@@ -7028,7 +7077,7 @@
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
     </row>
-    <row r="18" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>9</v>
       </c>
@@ -7074,7 +7123,7 @@
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
     </row>
-    <row r="19" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
@@ -7120,7 +7169,7 @@
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
     </row>
-    <row r="20" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
@@ -7166,7 +7215,7 @@
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
     </row>
-    <row r="21" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
@@ -7212,7 +7261,7 @@
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
     </row>
-    <row r="22" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
@@ -7258,7 +7307,7 @@
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
     </row>
-    <row r="23" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
@@ -7304,7 +7353,7 @@
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
     </row>
-    <row r="24" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>9</v>
       </c>
@@ -7350,7 +7399,7 @@
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
     </row>
-    <row r="25" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>9</v>
       </c>
@@ -7396,7 +7445,7 @@
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
     </row>
-    <row r="26" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>9</v>
       </c>
@@ -7442,7 +7491,7 @@
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
     </row>
-    <row r="27" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>9</v>
       </c>
@@ -7488,7 +7537,7 @@
       <c r="Q27" s="2"/>
       <c r="R27" s="2"/>
     </row>
-    <row r="28" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>9</v>
       </c>
@@ -7534,7 +7583,7 @@
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
     </row>
-    <row r="29" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>9</v>
       </c>
@@ -7580,7 +7629,7 @@
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
     </row>
-    <row r="30" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>9</v>
       </c>
@@ -7626,7 +7675,7 @@
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
     </row>
-    <row r="31" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>9</v>
       </c>
@@ -7672,7 +7721,7 @@
       <c r="Q31" s="2"/>
       <c r="R31" s="2"/>
     </row>
-    <row r="32" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>9</v>
       </c>
@@ -7718,7 +7767,7 @@
       <c r="Q32" s="2"/>
       <c r="R32" s="2"/>
     </row>
-    <row r="33" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>9</v>
       </c>
@@ -7764,7 +7813,7 @@
       <c r="Q33" s="2"/>
       <c r="R33" s="2"/>
     </row>
-    <row r="34" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>9</v>
       </c>
@@ -7810,7 +7859,7 @@
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
     </row>
-    <row r="35" spans="1:18" s="3" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" s="3" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>9</v>
       </c>
@@ -7856,7 +7905,7 @@
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
     </row>
-    <row r="36" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>9</v>
       </c>
@@ -7902,7 +7951,7 @@
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
     </row>
-    <row r="37" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>9</v>
       </c>
@@ -7948,7 +7997,7 @@
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
     </row>
-    <row r="38" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>9</v>
       </c>
@@ -7994,7 +8043,7 @@
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
     </row>
-    <row r="39" spans="1:18" s="3" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" s="3" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>9</v>
       </c>
@@ -8040,7 +8089,7 @@
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
     </row>
-    <row r="40" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>9</v>
       </c>
@@ -8086,7 +8135,7 @@
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
     </row>
-    <row r="41" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>9</v>
       </c>
@@ -8132,7 +8181,7 @@
       <c r="Q41" s="2"/>
       <c r="R41" s="2"/>
     </row>
-    <row r="42" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>9</v>
       </c>
@@ -8178,7 +8227,7 @@
       <c r="Q42" s="2"/>
       <c r="R42" s="2"/>
     </row>
-    <row r="43" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>9</v>
       </c>
@@ -8224,7 +8273,7 @@
       <c r="Q43" s="2"/>
       <c r="R43" s="2"/>
     </row>
-    <row r="44" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>9</v>
       </c>
@@ -8270,7 +8319,7 @@
       <c r="Q44" s="2"/>
       <c r="R44" s="2"/>
     </row>
-    <row r="45" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>9</v>
       </c>
@@ -8316,7 +8365,7 @@
       <c r="Q45" s="2"/>
       <c r="R45" s="2"/>
     </row>
-    <row r="46" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>9</v>
       </c>
@@ -8362,7 +8411,7 @@
       <c r="Q46" s="2"/>
       <c r="R46" s="2"/>
     </row>
-    <row r="47" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>9</v>
       </c>
@@ -8408,7 +8457,7 @@
       <c r="Q47" s="2"/>
       <c r="R47" s="2"/>
     </row>
-    <row r="48" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>9</v>
       </c>
@@ -8454,7 +8503,7 @@
       <c r="Q48" s="2"/>
       <c r="R48" s="2"/>
     </row>
-    <row r="49" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>9</v>
       </c>
@@ -8500,7 +8549,7 @@
       <c r="Q49" s="2"/>
       <c r="R49" s="2"/>
     </row>
-    <row r="50" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>9</v>
       </c>
@@ -8546,7 +8595,7 @@
       <c r="Q50" s="2"/>
       <c r="R50" s="2"/>
     </row>
-    <row r="51" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>9</v>
       </c>
@@ -8592,7 +8641,7 @@
       <c r="Q51" s="2"/>
       <c r="R51" s="2"/>
     </row>
-    <row r="52" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>9</v>
       </c>
@@ -8638,7 +8687,7 @@
       <c r="Q52" s="2"/>
       <c r="R52" s="2"/>
     </row>
-    <row r="53" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>9</v>
       </c>
@@ -8684,7 +8733,7 @@
       <c r="Q53" s="2"/>
       <c r="R53" s="2"/>
     </row>
-    <row r="54" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>9</v>
       </c>
@@ -8730,7 +8779,7 @@
       <c r="Q54" s="2"/>
       <c r="R54" s="2"/>
     </row>
-    <row r="55" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>9</v>
       </c>
@@ -8776,7 +8825,7 @@
       <c r="Q55" s="2"/>
       <c r="R55" s="2"/>
     </row>
-    <row r="56" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>9</v>
       </c>
@@ -8822,7 +8871,7 @@
       <c r="Q56" s="2"/>
       <c r="R56" s="2"/>
     </row>
-    <row r="57" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>9</v>
       </c>
@@ -8868,7 +8917,7 @@
       <c r="Q57" s="2"/>
       <c r="R57" s="2"/>
     </row>
-    <row r="58" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>9</v>
       </c>
@@ -8914,7 +8963,7 @@
       <c r="Q58" s="2"/>
       <c r="R58" s="2"/>
     </row>
-    <row r="59" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>9</v>
       </c>
@@ -8960,7 +9009,7 @@
       <c r="Q59" s="2"/>
       <c r="R59" s="2"/>
     </row>
-    <row r="60" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>9</v>
       </c>
@@ -9006,7 +9055,7 @@
       <c r="Q60" s="2"/>
       <c r="R60" s="2"/>
     </row>
-    <row r="61" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>9</v>
       </c>
@@ -9052,7 +9101,7 @@
       <c r="Q61" s="2"/>
       <c r="R61" s="2"/>
     </row>
-    <row r="62" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>9</v>
       </c>
@@ -9098,7 +9147,7 @@
       <c r="Q62" s="2"/>
       <c r="R62" s="2"/>
     </row>
-    <row r="63" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>9</v>
       </c>
@@ -9144,7 +9193,7 @@
       <c r="Q63" s="2"/>
       <c r="R63" s="2"/>
     </row>
-    <row r="64" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>9</v>
       </c>
@@ -9190,7 +9239,7 @@
       <c r="Q64" s="2"/>
       <c r="R64" s="2"/>
     </row>
-    <row r="65" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>9</v>
       </c>
@@ -9236,7 +9285,7 @@
       <c r="Q65" s="2"/>
       <c r="R65" s="2"/>
     </row>
-    <row r="66" spans="1:18" s="3" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:18" s="3" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>9</v>
       </c>
@@ -9282,7 +9331,7 @@
       <c r="Q66" s="2"/>
       <c r="R66" s="2"/>
     </row>
-    <row r="67" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>9</v>
       </c>
@@ -9328,7 +9377,7 @@
       <c r="Q67" s="2"/>
       <c r="R67" s="2"/>
     </row>
-    <row r="68" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>9</v>
       </c>
@@ -9374,7 +9423,7 @@
       <c r="Q68" s="2"/>
       <c r="R68" s="2"/>
     </row>
-    <row r="69" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>9</v>
       </c>
@@ -9420,7 +9469,7 @@
       <c r="Q69" s="2"/>
       <c r="R69" s="2"/>
     </row>
-    <row r="70" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>9</v>
       </c>
@@ -9466,7 +9515,7 @@
       <c r="Q70" s="2"/>
       <c r="R70" s="2"/>
     </row>
-    <row r="71" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>9</v>
       </c>
@@ -9512,7 +9561,7 @@
       <c r="Q71" s="2"/>
       <c r="R71" s="2"/>
     </row>
-    <row r="72" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>9</v>
       </c>
@@ -9558,7 +9607,7 @@
       <c r="Q72" s="2"/>
       <c r="R72" s="2"/>
     </row>
-    <row r="73" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>9</v>
       </c>
@@ -9604,7 +9653,7 @@
       <c r="Q73" s="2"/>
       <c r="R73" s="2"/>
     </row>
-    <row r="74" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>9</v>
       </c>
@@ -9650,7 +9699,7 @@
       <c r="Q74" s="2"/>
       <c r="R74" s="2"/>
     </row>
-    <row r="75" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>9</v>
       </c>
@@ -9696,7 +9745,7 @@
       <c r="Q75" s="2"/>
       <c r="R75" s="2"/>
     </row>
-    <row r="76" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>9</v>
       </c>
@@ -9742,7 +9791,7 @@
       <c r="Q76" s="2"/>
       <c r="R76" s="2"/>
     </row>
-    <row r="77" spans="1:18" s="3" customFormat="1" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:18" s="3" customFormat="1" ht="27.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>9</v>
       </c>
@@ -9788,7 +9837,7 @@
       <c r="Q77" s="2"/>
       <c r="R77" s="2"/>
     </row>
-    <row r="78" spans="1:18" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:18" s="3" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>9</v>
       </c>
@@ -9834,7 +9883,7 @@
       <c r="Q78" s="2"/>
       <c r="R78" s="2"/>
     </row>
-    <row r="79" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>9</v>
       </c>
@@ -9880,7 +9929,7 @@
       <c r="Q79" s="2"/>
       <c r="R79" s="2"/>
     </row>
-    <row r="80" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>9</v>
       </c>
@@ -9926,7 +9975,7 @@
       <c r="Q80" s="2"/>
       <c r="R80" s="2"/>
     </row>
-    <row r="81" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>9</v>
       </c>
@@ -9972,7 +10021,7 @@
       <c r="Q81" s="2"/>
       <c r="R81" s="2"/>
     </row>
-    <row r="82" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>9</v>
       </c>
@@ -10018,7 +10067,7 @@
       <c r="Q82" s="2"/>
       <c r="R82" s="2"/>
     </row>
-    <row r="83" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>9</v>
       </c>
@@ -10064,7 +10113,7 @@
       <c r="Q83" s="2"/>
       <c r="R83" s="2"/>
     </row>
-    <row r="84" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:18" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>9</v>
       </c>
@@ -10110,7 +10159,7 @@
       <c r="Q84" s="2"/>
       <c r="R84" s="2"/>
     </row>
-    <row r="85" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>9</v>
       </c>
@@ -10156,7 +10205,7 @@
       <c r="Q85" s="2"/>
       <c r="R85" s="2"/>
     </row>
-    <row r="86" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>9</v>
       </c>
@@ -10202,7 +10251,7 @@
       <c r="Q86" s="2"/>
       <c r="R86" s="2"/>
     </row>
-    <row r="87" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>9</v>
       </c>
@@ -10248,7 +10297,7 @@
       <c r="Q87" s="2"/>
       <c r="R87" s="2"/>
     </row>
-    <row r="88" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>9</v>
       </c>
@@ -10294,7 +10343,7 @@
       <c r="Q88" s="2"/>
       <c r="R88" s="2"/>
     </row>
-    <row r="89" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>9</v>
       </c>
@@ -10338,7 +10387,7 @@
       <c r="Q89" s="2"/>
       <c r="R89" s="2"/>
     </row>
-    <row r="90" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>9</v>
       </c>
@@ -10384,7 +10433,7 @@
       <c r="Q90" s="2"/>
       <c r="R90" s="2"/>
     </row>
-    <row r="91" spans="1:18" s="3" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:18" s="3" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>9</v>
       </c>
@@ -10430,7 +10479,7 @@
       <c r="Q91" s="2"/>
       <c r="R91" s="2"/>
     </row>
-    <row r="92" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>9</v>
       </c>
@@ -10476,7 +10525,7 @@
       <c r="Q92" s="2"/>
       <c r="R92" s="2"/>
     </row>
-    <row r="93" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>9</v>
       </c>
@@ -10522,7 +10571,7 @@
       <c r="Q93" s="2"/>
       <c r="R93" s="2"/>
     </row>
-    <row r="94" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>9</v>
       </c>
@@ -10568,7 +10617,7 @@
       <c r="Q94" s="2"/>
       <c r="R94" s="2"/>
     </row>
-    <row r="95" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>9</v>
       </c>
@@ -10614,7 +10663,7 @@
       <c r="Q95" s="2"/>
       <c r="R95" s="2"/>
     </row>
-    <row r="96" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>9</v>
       </c>
@@ -10660,7 +10709,7 @@
       <c r="Q96" s="2"/>
       <c r="R96" s="2"/>
     </row>
-    <row r="97" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>9</v>
       </c>
@@ -10706,7 +10755,7 @@
       <c r="Q97" s="2"/>
       <c r="R97" s="2"/>
     </row>
-    <row r="98" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>9</v>
       </c>
@@ -10752,7 +10801,7 @@
       <c r="Q98" s="2"/>
       <c r="R98" s="2"/>
     </row>
-    <row r="99" spans="1:18" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:18" s="3" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>9</v>
       </c>
@@ -10798,7 +10847,7 @@
       <c r="Q99" s="2"/>
       <c r="R99" s="2"/>
     </row>
-    <row r="100" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>9</v>
       </c>
@@ -10844,7 +10893,7 @@
       <c r="Q100" s="2"/>
       <c r="R100" s="2"/>
     </row>
-    <row r="101" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>9</v>
       </c>
@@ -10888,7 +10937,7 @@
       <c r="Q101" s="2"/>
       <c r="R101" s="2"/>
     </row>
-    <row r="102" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>9</v>
       </c>
@@ -10934,7 +10983,7 @@
       <c r="Q102" s="2"/>
       <c r="R102" s="2"/>
     </row>
-    <row r="103" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>9</v>
       </c>
@@ -10980,7 +11029,7 @@
       <c r="Q103" s="2"/>
       <c r="R103" s="2"/>
     </row>
-    <row r="104" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>9</v>
       </c>
@@ -11024,7 +11073,7 @@
       <c r="Q104" s="2"/>
       <c r="R104" s="2"/>
     </row>
-    <row r="105" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>9</v>
       </c>
@@ -11070,7 +11119,7 @@
       <c r="Q105" s="2"/>
       <c r="R105" s="2"/>
     </row>
-    <row r="106" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>9</v>
       </c>
@@ -11116,7 +11165,7 @@
       <c r="Q106" s="2"/>
       <c r="R106" s="2"/>
     </row>
-    <row r="107" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:18" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>9</v>
       </c>
@@ -11162,7 +11211,7 @@
       <c r="Q107" s="2"/>
       <c r="R107" s="2"/>
     </row>
-    <row r="108" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>9</v>
       </c>
@@ -11208,7 +11257,7 @@
       <c r="Q108" s="2"/>
       <c r="R108" s="2"/>
     </row>
-    <row r="109" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>9</v>
       </c>
@@ -11252,7 +11301,7 @@
       <c r="Q109" s="2"/>
       <c r="R109" s="2"/>
     </row>
-    <row r="110" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>9</v>
       </c>
@@ -11298,7 +11347,7 @@
       <c r="Q110" s="2"/>
       <c r="R110" s="2"/>
     </row>
-    <row r="111" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>9</v>
       </c>
@@ -11344,7 +11393,7 @@
       <c r="Q111" s="2"/>
       <c r="R111" s="2"/>
     </row>
-    <row r="112" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>9</v>
       </c>
@@ -11390,7 +11439,7 @@
       <c r="Q112" s="2"/>
       <c r="R112" s="2"/>
     </row>
-    <row r="113" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>9</v>
       </c>
@@ -11436,7 +11485,7 @@
       <c r="Q113" s="2"/>
       <c r="R113" s="2"/>
     </row>
-    <row r="114" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>9</v>
       </c>
@@ -11482,7 +11531,7 @@
       <c r="Q114" s="2"/>
       <c r="R114" s="2"/>
     </row>
-    <row r="115" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>9</v>
       </c>
@@ -11528,7 +11577,7 @@
       <c r="Q115" s="2"/>
       <c r="R115" s="2"/>
     </row>
-    <row r="116" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>9</v>
       </c>
@@ -11574,7 +11623,7 @@
       <c r="Q116" s="2"/>
       <c r="R116" s="2"/>
     </row>
-    <row r="117" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>9</v>
       </c>
@@ -11620,7 +11669,7 @@
       <c r="Q117" s="2"/>
       <c r="R117" s="2"/>
     </row>
-    <row r="118" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>9</v>
       </c>
@@ -11666,7 +11715,7 @@
       <c r="Q118" s="2"/>
       <c r="R118" s="2"/>
     </row>
-    <row r="119" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>9</v>
       </c>
@@ -11712,7 +11761,7 @@
       <c r="Q119" s="2"/>
       <c r="R119" s="2"/>
     </row>
-    <row r="120" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>9</v>
       </c>
@@ -11758,7 +11807,7 @@
       <c r="Q120" s="2"/>
       <c r="R120" s="2"/>
     </row>
-    <row r="121" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>9</v>
       </c>
@@ -11804,7 +11853,7 @@
       <c r="Q121" s="2"/>
       <c r="R121" s="2"/>
     </row>
-    <row r="122" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>9</v>
       </c>
@@ -11850,7 +11899,7 @@
       <c r="Q122" s="2"/>
       <c r="R122" s="2"/>
     </row>
-    <row r="123" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>9</v>
       </c>
@@ -11896,7 +11945,7 @@
       <c r="Q123" s="2"/>
       <c r="R123" s="2"/>
     </row>
-    <row r="124" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>9</v>
       </c>
@@ -11942,7 +11991,7 @@
       <c r="Q124" s="2"/>
       <c r="R124" s="2"/>
     </row>
-    <row r="125" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>9</v>
       </c>
@@ -11988,7 +12037,7 @@
       <c r="Q125" s="2"/>
       <c r="R125" s="2"/>
     </row>
-    <row r="126" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>9</v>
       </c>
@@ -12034,7 +12083,7 @@
       <c r="Q126" s="2"/>
       <c r="R126" s="2"/>
     </row>
-    <row r="127" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>9</v>
       </c>
@@ -12080,7 +12129,7 @@
       <c r="Q127" s="2"/>
       <c r="R127" s="2"/>
     </row>
-    <row r="128" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>9</v>
       </c>
@@ -12126,7 +12175,7 @@
       <c r="Q128" s="2"/>
       <c r="R128" s="2"/>
     </row>
-    <row r="129" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>9</v>
       </c>
@@ -12172,7 +12221,7 @@
       <c r="Q129" s="2"/>
       <c r="R129" s="2"/>
     </row>
-    <row r="130" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>9</v>
       </c>
@@ -12218,7 +12267,7 @@
       <c r="Q130" s="2"/>
       <c r="R130" s="2"/>
     </row>
-    <row r="131" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>9</v>
       </c>
@@ -12264,7 +12313,7 @@
       <c r="Q131" s="2"/>
       <c r="R131" s="2"/>
     </row>
-    <row r="132" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>9</v>
       </c>
@@ -12310,7 +12359,7 @@
       <c r="Q132" s="2"/>
       <c r="R132" s="2"/>
     </row>
-    <row r="133" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:18" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>9</v>
       </c>
@@ -12356,7 +12405,7 @@
       <c r="Q133" s="2"/>
       <c r="R133" s="2"/>
     </row>
-    <row r="134" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>9</v>
       </c>
@@ -12402,7 +12451,7 @@
       <c r="Q134" s="2"/>
       <c r="R134" s="2"/>
     </row>
-    <row r="135" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>9</v>
       </c>
@@ -12448,7 +12497,7 @@
       <c r="Q135" s="2"/>
       <c r="R135" s="2"/>
     </row>
-    <row r="136" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>9</v>
       </c>
@@ -12494,7 +12543,7 @@
       <c r="Q136" s="2"/>
       <c r="R136" s="2"/>
     </row>
-    <row r="137" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>9</v>
       </c>
@@ -12540,7 +12589,7 @@
       <c r="Q137" s="2"/>
       <c r="R137" s="2"/>
     </row>
-    <row r="138" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>9</v>
       </c>
@@ -12586,7 +12635,7 @@
       <c r="Q138" s="2"/>
       <c r="R138" s="2"/>
     </row>
-    <row r="139" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>9</v>
       </c>
@@ -12632,7 +12681,7 @@
       <c r="Q139" s="2"/>
       <c r="R139" s="2"/>
     </row>
-    <row r="140" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>9</v>
       </c>
@@ -12678,7 +12727,7 @@
       <c r="Q140" s="2"/>
       <c r="R140" s="2"/>
     </row>
-    <row r="141" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>9</v>
       </c>
@@ -12724,7 +12773,7 @@
       <c r="Q141" s="2"/>
       <c r="R141" s="2"/>
     </row>
-    <row r="142" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>9</v>
       </c>
@@ -12770,7 +12819,7 @@
       <c r="Q142" s="2"/>
       <c r="R142" s="2"/>
     </row>
-    <row r="143" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>9</v>
       </c>
@@ -12816,7 +12865,7 @@
       <c r="Q143" s="2"/>
       <c r="R143" s="2"/>
     </row>
-    <row r="144" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>9</v>
       </c>
@@ -12862,7 +12911,7 @@
       <c r="Q144" s="2"/>
       <c r="R144" s="2"/>
     </row>
-    <row r="145" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>9</v>
       </c>
@@ -12908,7 +12957,7 @@
       <c r="Q145" s="2"/>
       <c r="R145" s="2"/>
     </row>
-    <row r="146" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>9</v>
       </c>
@@ -12954,7 +13003,7 @@
       <c r="Q146" s="2"/>
       <c r="R146" s="2"/>
     </row>
-    <row r="147" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:18" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>9</v>
       </c>
@@ -13000,7 +13049,7 @@
       <c r="Q147" s="2"/>
       <c r="R147" s="2"/>
     </row>
-    <row r="148" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>9</v>
       </c>
@@ -13046,7 +13095,7 @@
       <c r="Q148" s="2"/>
       <c r="R148" s="2"/>
     </row>
-    <row r="149" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>9</v>
       </c>
@@ -13092,7 +13141,7 @@
       <c r="Q149" s="2"/>
       <c r="R149" s="2"/>
     </row>
-    <row r="150" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>9</v>
       </c>
@@ -13138,7 +13187,7 @@
       <c r="Q150" s="2"/>
       <c r="R150" s="2"/>
     </row>
-    <row r="151" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>9</v>
       </c>
@@ -13184,7 +13233,7 @@
       <c r="Q151" s="2"/>
       <c r="R151" s="2"/>
     </row>
-    <row r="152" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>9</v>
       </c>
@@ -13230,7 +13279,7 @@
       <c r="Q152" s="2"/>
       <c r="R152" s="2"/>
     </row>
-    <row r="153" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>9</v>
       </c>
@@ -13276,7 +13325,7 @@
       <c r="Q153" s="2"/>
       <c r="R153" s="2"/>
     </row>
-    <row r="154" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>9</v>
       </c>
@@ -13322,7 +13371,7 @@
       <c r="Q154" s="2"/>
       <c r="R154" s="2"/>
     </row>
-    <row r="155" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>9</v>
       </c>
@@ -13368,7 +13417,7 @@
       <c r="Q155" s="2"/>
       <c r="R155" s="2"/>
     </row>
-    <row r="156" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>9</v>
       </c>
@@ -13414,7 +13463,7 @@
       <c r="Q156" s="2"/>
       <c r="R156" s="2"/>
     </row>
-    <row r="157" spans="1:18" s="3" customFormat="1" ht="65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:18" s="3" customFormat="1" ht="65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>9</v>
       </c>
@@ -13470,7 +13519,7 @@
         <v>1768</v>
       </c>
     </row>
-    <row r="158" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>9</v>
       </c>
@@ -13518,7 +13567,7 @@
       <c r="Q158" s="2"/>
       <c r="R158" s="2"/>
     </row>
-    <row r="159" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>9</v>
       </c>
@@ -13566,7 +13615,7 @@
       <c r="Q159" s="2"/>
       <c r="R159" s="2"/>
     </row>
-    <row r="160" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>9</v>
       </c>
@@ -13614,7 +13663,7 @@
       <c r="Q160" s="2"/>
       <c r="R160" s="2"/>
     </row>
-    <row r="161" spans="1:18" s="3" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:18" s="3" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>9</v>
       </c>
@@ -13662,7 +13711,7 @@
       <c r="Q161" s="2"/>
       <c r="R161" s="2"/>
     </row>
-    <row r="162" spans="1:18" s="3" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:18" s="3" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>9</v>
       </c>
@@ -13710,7 +13759,7 @@
       <c r="Q162" s="2"/>
       <c r="R162" s="2"/>
     </row>
-    <row r="163" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>9</v>
       </c>
@@ -13758,7 +13807,7 @@
       <c r="Q163" s="2"/>
       <c r="R163" s="2"/>
     </row>
-    <row r="164" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>9</v>
       </c>
@@ -13806,7 +13855,7 @@
       <c r="Q164" s="2"/>
       <c r="R164" s="2"/>
     </row>
-    <row r="165" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>9</v>
       </c>
@@ -13854,7 +13903,7 @@
       <c r="Q165" s="2"/>
       <c r="R165" s="2"/>
     </row>
-    <row r="166" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>9</v>
       </c>
@@ -13902,7 +13951,7 @@
       <c r="Q166" s="2"/>
       <c r="R166" s="2"/>
     </row>
-    <row r="167" spans="1:18" s="3" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:18" s="3" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>9</v>
       </c>
@@ -13950,7 +13999,7 @@
       <c r="Q167" s="2"/>
       <c r="R167" s="2"/>
     </row>
-    <row r="168" spans="1:18" s="3" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:18" s="3" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>9</v>
       </c>
@@ -13998,7 +14047,7 @@
       <c r="Q168" s="2"/>
       <c r="R168" s="2"/>
     </row>
-    <row r="169" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>9</v>
       </c>
@@ -14046,7 +14095,7 @@
       <c r="Q169" s="2"/>
       <c r="R169" s="2"/>
     </row>
-    <row r="170" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>9</v>
       </c>
@@ -14094,7 +14143,7 @@
       <c r="Q170" s="2"/>
       <c r="R170" s="2"/>
     </row>
-    <row r="171" spans="1:18" s="3" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:18" s="3" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>9</v>
       </c>
@@ -14142,7 +14191,7 @@
       <c r="Q171" s="2"/>
       <c r="R171" s="2"/>
     </row>
-    <row r="172" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>9</v>
       </c>
@@ -14190,7 +14239,7 @@
       <c r="Q172" s="2"/>
       <c r="R172" s="2"/>
     </row>
-    <row r="173" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>9</v>
       </c>
@@ -14236,7 +14285,7 @@
       <c r="Q173" s="2"/>
       <c r="R173" s="2"/>
     </row>
-    <row r="174" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>9</v>
       </c>
@@ -14282,7 +14331,7 @@
       <c r="Q174" s="2"/>
       <c r="R174" s="2"/>
     </row>
-    <row r="175" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>9</v>
       </c>
@@ -14328,7 +14377,7 @@
       <c r="Q175" s="2"/>
       <c r="R175" s="2"/>
     </row>
-    <row r="176" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>9</v>
       </c>
@@ -14374,7 +14423,7 @@
       <c r="Q176" s="2"/>
       <c r="R176" s="2"/>
     </row>
-    <row r="177" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>9</v>
       </c>
@@ -14420,7 +14469,7 @@
       <c r="Q177" s="2"/>
       <c r="R177" s="2"/>
     </row>
-    <row r="178" spans="1:18" s="3" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:18" s="3" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>9</v>
       </c>
@@ -14466,7 +14515,7 @@
       <c r="Q178" s="2"/>
       <c r="R178" s="2"/>
     </row>
-    <row r="179" spans="1:18" s="3" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:18" s="3" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>9</v>
       </c>
@@ -14512,7 +14561,7 @@
       <c r="Q179" s="2"/>
       <c r="R179" s="2"/>
     </row>
-    <row r="180" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>9</v>
       </c>
@@ -14558,7 +14607,7 @@
       <c r="Q180" s="2"/>
       <c r="R180" s="2"/>
     </row>
-    <row r="181" spans="1:18" s="3" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:18" s="3" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>9</v>
       </c>
@@ -14604,7 +14653,7 @@
       <c r="Q181" s="2"/>
       <c r="R181" s="2"/>
     </row>
-    <row r="182" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>9</v>
       </c>
@@ -14650,7 +14699,7 @@
       <c r="Q182" s="2"/>
       <c r="R182" s="2"/>
     </row>
-    <row r="183" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>9</v>
       </c>
@@ -14696,7 +14745,7 @@
       <c r="Q183" s="2"/>
       <c r="R183" s="2"/>
     </row>
-    <row r="184" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>9</v>
       </c>
@@ -14742,7 +14791,7 @@
       <c r="Q184" s="2"/>
       <c r="R184" s="2"/>
     </row>
-    <row r="185" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>9</v>
       </c>
@@ -14788,7 +14837,7 @@
       <c r="Q185" s="2"/>
       <c r="R185" s="2"/>
     </row>
-    <row r="186" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>9</v>
       </c>
@@ -14834,7 +14883,7 @@
       <c r="Q186" s="2"/>
       <c r="R186" s="2"/>
     </row>
-    <row r="187" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>9</v>
       </c>
@@ -14880,7 +14929,7 @@
       <c r="Q187" s="2"/>
       <c r="R187" s="2"/>
     </row>
-    <row r="188" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>9</v>
       </c>
@@ -14926,7 +14975,7 @@
       <c r="Q188" s="2"/>
       <c r="R188" s="2"/>
     </row>
-    <row r="189" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>9</v>
       </c>
@@ -14972,7 +15021,7 @@
       <c r="Q189" s="2"/>
       <c r="R189" s="2"/>
     </row>
-    <row r="190" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>9</v>
       </c>
@@ -15018,7 +15067,7 @@
       <c r="Q190" s="2"/>
       <c r="R190" s="2"/>
     </row>
-    <row r="191" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>9</v>
       </c>
@@ -15064,7 +15113,7 @@
       <c r="Q191" s="2"/>
       <c r="R191" s="2"/>
     </row>
-    <row r="192" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>9</v>
       </c>
@@ -15110,7 +15159,7 @@
       <c r="Q192" s="2"/>
       <c r="R192" s="2"/>
     </row>
-    <row r="193" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>9</v>
       </c>
@@ -15156,7 +15205,7 @@
       <c r="Q193" s="2"/>
       <c r="R193" s="2"/>
     </row>
-    <row r="194" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>9</v>
       </c>
@@ -15202,7 +15251,7 @@
       <c r="Q194" s="2"/>
       <c r="R194" s="2"/>
     </row>
-    <row r="195" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>9</v>
       </c>
@@ -15248,7 +15297,7 @@
       <c r="Q195" s="2"/>
       <c r="R195" s="2"/>
     </row>
-    <row r="196" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>9</v>
       </c>
@@ -15294,7 +15343,7 @@
       <c r="Q196" s="2"/>
       <c r="R196" s="2"/>
     </row>
-    <row r="197" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>9</v>
       </c>
@@ -15340,7 +15389,7 @@
       <c r="Q197" s="2"/>
       <c r="R197" s="2"/>
     </row>
-    <row r="198" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>9</v>
       </c>
@@ -15386,7 +15435,7 @@
       <c r="Q198" s="2"/>
       <c r="R198" s="2"/>
     </row>
-    <row r="199" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>9</v>
       </c>
@@ -15432,7 +15481,7 @@
       <c r="Q199" s="2"/>
       <c r="R199" s="2"/>
     </row>
-    <row r="200" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>9</v>
       </c>
@@ -15478,7 +15527,7 @@
       <c r="Q200" s="2"/>
       <c r="R200" s="2"/>
     </row>
-    <row r="201" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>9</v>
       </c>
@@ -15524,7 +15573,7 @@
       <c r="Q201" s="2"/>
       <c r="R201" s="2"/>
     </row>
-    <row r="202" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>9</v>
       </c>
@@ -15570,7 +15619,7 @@
       <c r="Q202" s="2"/>
       <c r="R202" s="2"/>
     </row>
-    <row r="203" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>9</v>
       </c>
@@ -15616,7 +15665,7 @@
       <c r="Q203" s="2"/>
       <c r="R203" s="2"/>
     </row>
-    <row r="204" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>9</v>
       </c>
@@ -15662,7 +15711,7 @@
       <c r="Q204" s="2"/>
       <c r="R204" s="2"/>
     </row>
-    <row r="205" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>9</v>
       </c>
@@ -15708,7 +15757,7 @@
       <c r="Q205" s="2"/>
       <c r="R205" s="2"/>
     </row>
-    <row r="206" spans="1:18" ht="87" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>9</v>
       </c>
@@ -15754,7 +15803,7 @@
       <c r="Q206" s="2"/>
       <c r="R206" s="2"/>
     </row>
-    <row r="207" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>9</v>
       </c>
@@ -15800,7 +15849,7 @@
       <c r="Q207" s="2"/>
       <c r="R207" s="2"/>
     </row>
-    <row r="208" spans="1:18" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:18" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>9</v>
       </c>
@@ -15846,7 +15895,7 @@
       <c r="Q208" s="2"/>
       <c r="R208" s="2"/>
     </row>
-    <row r="209" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>9</v>
       </c>
@@ -15892,7 +15941,7 @@
       <c r="Q209" s="2"/>
       <c r="R209" s="2"/>
     </row>
-    <row r="210" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>9</v>
       </c>
@@ -15938,7 +15987,7 @@
       <c r="Q210" s="2"/>
       <c r="R210" s="2"/>
     </row>
-    <row r="211" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>9</v>
       </c>
@@ -15982,7 +16031,7 @@
       <c r="Q211" s="2"/>
       <c r="R211" s="2"/>
     </row>
-    <row r="212" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>9</v>
       </c>
@@ -16026,7 +16075,7 @@
       <c r="Q212" s="2"/>
       <c r="R212" s="2"/>
     </row>
-    <row r="213" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:18" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>9</v>
       </c>
@@ -16070,7 +16119,7 @@
       <c r="Q213" s="2"/>
       <c r="R213" s="2"/>
     </row>
-    <row r="214" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>9</v>
       </c>
@@ -16114,7 +16163,7 @@
       <c r="Q214" s="2"/>
       <c r="R214" s="2"/>
     </row>
-    <row r="215" spans="1:18" s="3" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:18" s="3" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>9</v>
       </c>
@@ -16158,7 +16207,7 @@
       <c r="Q215" s="2"/>
       <c r="R215" s="2"/>
     </row>
-    <row r="216" spans="1:18" s="3" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:18" s="3" customFormat="1" ht="188.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>9</v>
       </c>
@@ -16202,7 +16251,7 @@
       <c r="Q216" s="2"/>
       <c r="R216" s="2"/>
     </row>
-    <row r="217" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:18" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>9</v>
       </c>
@@ -16246,7 +16295,7 @@
       <c r="Q217" s="2"/>
       <c r="R217" s="2"/>
     </row>
-    <row r="218" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>9</v>
       </c>
@@ -16292,7 +16341,7 @@
       <c r="Q218" s="2"/>
       <c r="R218" s="2"/>
     </row>
-    <row r="219" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>9</v>
       </c>
@@ -16338,7 +16387,7 @@
       <c r="Q219" s="2"/>
       <c r="R219" s="2"/>
     </row>
-    <row r="220" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>9</v>
       </c>
@@ -16384,7 +16433,7 @@
       <c r="Q220" s="2"/>
       <c r="R220" s="2"/>
     </row>
-    <row r="221" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:18" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>9</v>
       </c>
@@ -16430,7 +16479,7 @@
       <c r="Q221" s="2"/>
       <c r="R221" s="2"/>
     </row>
-    <row r="222" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>9</v>
       </c>
@@ -16474,7 +16523,7 @@
       <c r="Q222" s="2"/>
       <c r="R222" s="2"/>
     </row>
-    <row r="223" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>9</v>
       </c>
@@ -16520,7 +16569,7 @@
       <c r="Q223" s="2"/>
       <c r="R223" s="2"/>
     </row>
-    <row r="224" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>9</v>
       </c>
@@ -16566,7 +16615,7 @@
       <c r="Q224" s="2"/>
       <c r="R224" s="2"/>
     </row>
-    <row r="225" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>9</v>
       </c>
@@ -16612,7 +16661,7 @@
       <c r="Q225" s="2"/>
       <c r="R225" s="2"/>
     </row>
-    <row r="226" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
         <v>9</v>
       </c>
@@ -16656,7 +16705,7 @@
       <c r="Q226" s="2"/>
       <c r="R226" s="2"/>
     </row>
-    <row r="227" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>9</v>
       </c>
@@ -16700,7 +16749,7 @@
       <c r="Q227" s="2"/>
       <c r="R227" s="2"/>
     </row>
-    <row r="228" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
         <v>9</v>
       </c>
@@ -16744,7 +16793,7 @@
       <c r="Q228" s="2"/>
       <c r="R228" s="2"/>
     </row>
-    <row r="229" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
         <v>9</v>
       </c>
@@ -16790,7 +16839,7 @@
       <c r="Q229" s="2"/>
       <c r="R229" s="2"/>
     </row>
-    <row r="230" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
         <v>9</v>
       </c>
@@ -16834,7 +16883,7 @@
       <c r="Q230" s="2"/>
       <c r="R230" s="2"/>
     </row>
-    <row r="231" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:18" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
         <v>9</v>
       </c>
@@ -16878,7 +16927,7 @@
       <c r="Q231" s="2"/>
       <c r="R231" s="2"/>
     </row>
-    <row r="232" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>9</v>
       </c>
@@ -16922,7 +16971,7 @@
       <c r="Q232" s="2"/>
       <c r="R232" s="2"/>
     </row>
-    <row r="233" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>9</v>
       </c>
@@ -16966,7 +17015,7 @@
       <c r="Q233" s="2"/>
       <c r="R233" s="2"/>
     </row>
-    <row r="234" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>9</v>
       </c>
@@ -17010,7 +17059,7 @@
       <c r="Q234" s="2"/>
       <c r="R234" s="2"/>
     </row>
-    <row r="235" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
         <v>9</v>
       </c>
@@ -17054,7 +17103,7 @@
       <c r="Q235" s="2"/>
       <c r="R235" s="2"/>
     </row>
-    <row r="236" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" s="2" t="s">
         <v>9</v>
       </c>
@@ -17098,7 +17147,7 @@
       <c r="Q236" s="2"/>
       <c r="R236" s="2"/>
     </row>
-    <row r="237" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>9</v>
       </c>
@@ -17142,7 +17191,7 @@
       <c r="Q237" s="2"/>
       <c r="R237" s="2"/>
     </row>
-    <row r="238" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" s="2" t="s">
         <v>9</v>
       </c>
@@ -17186,7 +17235,7 @@
       <c r="Q238" s="2"/>
       <c r="R238" s="2"/>
     </row>
-    <row r="239" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>9</v>
       </c>
@@ -17230,7 +17279,7 @@
       <c r="Q239" s="2"/>
       <c r="R239" s="2"/>
     </row>
-    <row r="240" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>9</v>
       </c>
@@ -17274,7 +17323,7 @@
       <c r="Q240" s="2"/>
       <c r="R240" s="2"/>
     </row>
-    <row r="241" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>9</v>
       </c>
@@ -17318,7 +17367,7 @@
       <c r="Q241" s="2"/>
       <c r="R241" s="2"/>
     </row>
-    <row r="242" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" s="2" t="s">
         <v>9</v>
       </c>
@@ -17362,7 +17411,7 @@
       <c r="Q242" s="2"/>
       <c r="R242" s="2"/>
     </row>
-    <row r="243" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" s="2" t="s">
         <v>9</v>
       </c>
@@ -17406,7 +17455,7 @@
       <c r="Q243" s="2"/>
       <c r="R243" s="2"/>
     </row>
-    <row r="244" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
         <v>9</v>
       </c>
@@ -17582,7 +17631,7 @@
       <c r="Q247" s="2"/>
       <c r="R247" s="2"/>
     </row>
-    <row r="248" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" s="2" t="s">
         <v>9</v>
       </c>
@@ -17626,7 +17675,7 @@
       <c r="Q248" s="2"/>
       <c r="R248" s="2"/>
     </row>
-    <row r="249" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" s="2" t="s">
         <v>9</v>
       </c>
@@ -17670,7 +17719,7 @@
       <c r="Q249" s="2"/>
       <c r="R249" s="2"/>
     </row>
-    <row r="250" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:18" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" s="2" t="s">
         <v>9</v>
       </c>
@@ -17714,7 +17763,7 @@
       <c r="Q250" s="2"/>
       <c r="R250" s="2"/>
     </row>
-    <row r="251" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:18" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" s="2" t="s">
         <v>9</v>
       </c>
@@ -17758,7 +17807,7 @@
       <c r="Q251" s="2"/>
       <c r="R251" s="2"/>
     </row>
-    <row r="252" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:18" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
         <v>9</v>
       </c>
@@ -17802,7 +17851,7 @@
       <c r="Q252" s="2"/>
       <c r="R252" s="2"/>
     </row>
-    <row r="253" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" s="2" t="s">
         <v>9</v>
       </c>
@@ -17848,7 +17897,7 @@
       <c r="Q253" s="2"/>
       <c r="R253" s="2"/>
     </row>
-    <row r="254" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:18" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
         <v>9</v>
       </c>
@@ -17892,7 +17941,7 @@
       <c r="Q254" s="2"/>
       <c r="R254" s="2"/>
     </row>
-    <row r="255" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" s="2" t="s">
         <v>9</v>
       </c>
@@ -17938,7 +17987,7 @@
       <c r="Q255" s="2"/>
       <c r="R255" s="2"/>
     </row>
-    <row r="256" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" s="2" t="s">
         <v>9</v>
       </c>
@@ -17982,7 +18031,7 @@
       <c r="Q256" s="2"/>
       <c r="R256" s="2"/>
     </row>
-    <row r="257" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" s="2" t="s">
         <v>9</v>
       </c>
@@ -18026,7 +18075,7 @@
       <c r="Q257" s="2"/>
       <c r="R257" s="2"/>
     </row>
-    <row r="258" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:18" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" s="2" t="s">
         <v>9</v>
       </c>
@@ -18070,7 +18119,7 @@
       <c r="Q258" s="2"/>
       <c r="R258" s="2"/>
     </row>
-    <row r="259" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
         <v>9</v>
       </c>
@@ -18114,7 +18163,7 @@
       <c r="Q259" s="2"/>
       <c r="R259" s="2"/>
     </row>
-    <row r="260" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>9</v>
       </c>
@@ -18158,7 +18207,7 @@
       <c r="Q260" s="2"/>
       <c r="R260" s="2"/>
     </row>
-    <row r="261" spans="1:18" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:18" s="3" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" s="2" t="s">
         <v>9</v>
       </c>
@@ -18202,7 +18251,7 @@
       <c r="Q261" s="2"/>
       <c r="R261" s="2"/>
     </row>
-    <row r="262" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" s="2" t="s">
         <v>9</v>
       </c>
@@ -18246,7 +18295,7 @@
       <c r="Q262" s="2"/>
       <c r="R262" s="2"/>
     </row>
-    <row r="263" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:18" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" s="2" t="s">
         <v>9</v>
       </c>
@@ -18290,7 +18339,7 @@
       <c r="Q263" s="2"/>
       <c r="R263" s="2"/>
     </row>
-    <row r="264" spans="1:18" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:18" s="3" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" s="2" t="s">
         <v>9</v>
       </c>
@@ -18334,7 +18383,7 @@
       <c r="Q264" s="2"/>
       <c r="R264" s="2"/>
     </row>
-    <row r="265" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" s="2" t="s">
         <v>9</v>
       </c>
@@ -18378,7 +18427,7 @@
       <c r="Q265" s="2"/>
       <c r="R265" s="2"/>
     </row>
-    <row r="266" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:18" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" s="2" t="s">
         <v>9</v>
       </c>
@@ -18422,7 +18471,7 @@
       <c r="Q266" s="2"/>
       <c r="R266" s="2"/>
     </row>
-    <row r="267" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>9</v>
       </c>
@@ -18466,7 +18515,7 @@
       <c r="Q267" s="2"/>
       <c r="R267" s="2"/>
     </row>
-    <row r="268" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>9</v>
       </c>
@@ -18510,7 +18559,7 @@
       <c r="Q268" s="2"/>
       <c r="R268" s="2"/>
     </row>
-    <row r="269" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:18" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
         <v>9</v>
       </c>
@@ -18554,7 +18603,7 @@
       <c r="Q269" s="2"/>
       <c r="R269" s="2"/>
     </row>
-    <row r="270" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" s="2" t="s">
         <v>9</v>
       </c>
@@ -18598,7 +18647,7 @@
       <c r="Q270" s="2"/>
       <c r="R270" s="2"/>
     </row>
-    <row r="271" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" s="2" t="s">
         <v>9</v>
       </c>
@@ -18642,7 +18691,7 @@
       <c r="Q271" s="2"/>
       <c r="R271" s="2"/>
     </row>
-    <row r="272" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
         <v>9</v>
       </c>
@@ -18688,7 +18737,7 @@
       <c r="Q272" s="2"/>
       <c r="R272" s="2"/>
     </row>
-    <row r="273" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
         <v>9</v>
       </c>
@@ -18734,7 +18783,7 @@
       <c r="Q273" s="2"/>
       <c r="R273" s="2"/>
     </row>
-    <row r="274" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>9</v>
       </c>
@@ -18780,7 +18829,7 @@
       <c r="Q274" s="2"/>
       <c r="R274" s="2"/>
     </row>
-    <row r="275" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>9</v>
       </c>
@@ -18826,7 +18875,7 @@
       <c r="Q275" s="2"/>
       <c r="R275" s="2"/>
     </row>
-    <row r="276" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>9</v>
       </c>
@@ -18872,7 +18921,7 @@
       <c r="Q276" s="2"/>
       <c r="R276" s="2"/>
     </row>
-    <row r="277" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
         <v>9</v>
       </c>
@@ -18918,7 +18967,7 @@
       <c r="Q277" s="2"/>
       <c r="R277" s="2"/>
     </row>
-    <row r="278" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>9</v>
       </c>
@@ -18964,7 +19013,7 @@
       <c r="Q278" s="2"/>
       <c r="R278" s="2"/>
     </row>
-    <row r="279" spans="1:18" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:18" s="3" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>9</v>
       </c>
@@ -19010,7 +19059,7 @@
       <c r="Q279" s="2"/>
       <c r="R279" s="2"/>
     </row>
-    <row r="280" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>9</v>
       </c>
@@ -19056,7 +19105,7 @@
       <c r="Q280" s="2"/>
       <c r="R280" s="2"/>
     </row>
-    <row r="281" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>9</v>
       </c>
@@ -19102,7 +19151,7 @@
       <c r="Q281" s="2"/>
       <c r="R281" s="2"/>
     </row>
-    <row r="282" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:18" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>9</v>
       </c>
@@ -19148,7 +19197,7 @@
       <c r="Q282" s="2"/>
       <c r="R282" s="2"/>
     </row>
-    <row r="283" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>9</v>
       </c>
@@ -19194,7 +19243,7 @@
       <c r="Q283" s="2"/>
       <c r="R283" s="2"/>
     </row>
-    <row r="284" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:18" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" s="2" t="s">
         <v>9</v>
       </c>
@@ -19240,7 +19289,7 @@
       <c r="Q284" s="2"/>
       <c r="R284" s="2"/>
     </row>
-    <row r="285" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
         <v>9</v>
       </c>
@@ -19284,7 +19333,7 @@
       <c r="Q285" s="2"/>
       <c r="R285" s="2"/>
     </row>
-    <row r="286" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" s="2" t="s">
         <v>9</v>
       </c>
@@ -19328,7 +19377,7 @@
       <c r="Q286" s="2"/>
       <c r="R286" s="2"/>
     </row>
-    <row r="287" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" s="2" t="s">
         <v>9</v>
       </c>
@@ -19372,7 +19421,7 @@
       <c r="Q287" s="2"/>
       <c r="R287" s="2"/>
     </row>
-    <row r="288" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" s="2" t="s">
         <v>9</v>
       </c>
@@ -19416,7 +19465,7 @@
       <c r="Q288" s="2"/>
       <c r="R288" s="2"/>
     </row>
-    <row r="289" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
         <v>9</v>
       </c>
@@ -19460,7 +19509,7 @@
       <c r="Q289" s="2"/>
       <c r="R289" s="2"/>
     </row>
-    <row r="290" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:18" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" s="2" t="s">
         <v>9</v>
       </c>
@@ -19504,7 +19553,7 @@
       <c r="Q290" s="2"/>
       <c r="R290" s="2"/>
     </row>
-    <row r="291" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:18" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" s="2" t="s">
         <v>9</v>
       </c>
@@ -19548,7 +19597,7 @@
       <c r="Q291" s="2"/>
       <c r="R291" s="2"/>
     </row>
-    <row r="292" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:18" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
         <v>9</v>
       </c>
@@ -19592,7 +19641,7 @@
       <c r="Q292" s="2"/>
       <c r="R292" s="2"/>
     </row>
-    <row r="293" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" s="2" t="s">
         <v>9</v>
       </c>
@@ -19636,7 +19685,7 @@
       <c r="Q293" s="2"/>
       <c r="R293" s="2"/>
     </row>
-    <row r="294" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" s="2" t="s">
         <v>9</v>
       </c>
@@ -19680,7 +19729,7 @@
       <c r="Q294" s="2"/>
       <c r="R294" s="2"/>
     </row>
-    <row r="295" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" s="2" t="s">
         <v>9</v>
       </c>
@@ -19724,7 +19773,7 @@
       <c r="Q295" s="2"/>
       <c r="R295" s="2"/>
     </row>
-    <row r="296" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" s="2" t="s">
         <v>9</v>
       </c>
@@ -19768,7 +19817,7 @@
       <c r="Q296" s="2"/>
       <c r="R296" s="2"/>
     </row>
-    <row r="297" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>9</v>
       </c>
@@ -19812,7 +19861,7 @@
       <c r="Q297" s="2"/>
       <c r="R297" s="2"/>
     </row>
-    <row r="298" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
         <v>9</v>
       </c>
@@ -19856,7 +19905,7 @@
       <c r="Q298" s="2"/>
       <c r="R298" s="2"/>
     </row>
-    <row r="299" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
         <v>9</v>
       </c>
@@ -19900,7 +19949,7 @@
       <c r="Q299" s="2"/>
       <c r="R299" s="2"/>
     </row>
-    <row r="300" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" s="2" t="s">
         <v>9</v>
       </c>
@@ -19944,7 +19993,7 @@
       <c r="Q300" s="2"/>
       <c r="R300" s="2"/>
     </row>
-    <row r="301" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" s="2" t="s">
         <v>9</v>
       </c>
@@ -19988,7 +20037,7 @@
       <c r="Q301" s="2"/>
       <c r="R301" s="2"/>
     </row>
-    <row r="302" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" s="2" t="s">
         <v>9</v>
       </c>
@@ -20032,7 +20081,7 @@
       <c r="Q302" s="2"/>
       <c r="R302" s="2"/>
     </row>
-    <row r="303" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:18" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" s="2" t="s">
         <v>9</v>
       </c>
@@ -20078,7 +20127,7 @@
       <c r="Q303" s="2"/>
       <c r="R303" s="2"/>
     </row>
-    <row r="304" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" s="2" t="s">
         <v>9</v>
       </c>
@@ -20122,7 +20171,7 @@
       <c r="Q304" s="2"/>
       <c r="R304" s="2"/>
     </row>
-    <row r="305" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:18" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" s="2" t="s">
         <v>9</v>
       </c>
@@ -20166,7 +20215,7 @@
       <c r="Q305" s="2"/>
       <c r="R305" s="2"/>
     </row>
-    <row r="306" spans="1:18" s="3" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:18" s="3" customFormat="1" ht="76.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="2" t="s">
         <v>9</v>
       </c>
@@ -20210,7 +20259,7 @@
       <c r="Q306" s="2"/>
       <c r="R306" s="2"/>
     </row>
-    <row r="307" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:18" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" s="2" t="s">
         <v>9</v>
       </c>
@@ -20254,7 +20303,7 @@
       <c r="Q307" s="2"/>
       <c r="R307" s="2"/>
     </row>
-    <row r="308" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:18" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" s="2" t="s">
         <v>9</v>
       </c>
@@ -20298,7 +20347,7 @@
       <c r="Q308" s="2"/>
       <c r="R308" s="2"/>
     </row>
-    <row r="309" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" s="2" t="s">
         <v>9</v>
       </c>
@@ -20342,7 +20391,7 @@
       <c r="Q309" s="2"/>
       <c r="R309" s="2"/>
     </row>
-    <row r="310" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" s="2" t="s">
         <v>9</v>
       </c>
@@ -20386,7 +20435,7 @@
       <c r="Q310" s="2"/>
       <c r="R310" s="2"/>
     </row>
-    <row r="311" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" s="2" t="s">
         <v>9</v>
       </c>
@@ -20430,7 +20479,7 @@
       <c r="Q311" s="2"/>
       <c r="R311" s="2"/>
     </row>
-    <row r="312" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:18" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" s="2" t="s">
         <v>9</v>
       </c>
@@ -20474,7 +20523,7 @@
       <c r="Q312" s="2"/>
       <c r="R312" s="2"/>
     </row>
-    <row r="313" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:18" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" s="2" t="s">
         <v>9</v>
       </c>
@@ -20518,7 +20567,7 @@
       <c r="Q313" s="2"/>
       <c r="R313" s="2"/>
     </row>
-    <row r="314" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" s="2" t="s">
         <v>9</v>
       </c>
@@ -20564,7 +20613,7 @@
       <c r="Q314" s="2"/>
       <c r="R314" s="2"/>
     </row>
-    <row r="315" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" s="2" t="s">
         <v>9</v>
       </c>
@@ -20610,7 +20659,7 @@
       <c r="Q315" s="2"/>
       <c r="R315" s="2"/>
     </row>
-    <row r="316" spans="1:18" ht="87" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" s="2" t="s">
         <v>9</v>
       </c>
@@ -20654,7 +20703,7 @@
       <c r="Q316" s="2"/>
       <c r="R316" s="2"/>
     </row>
-    <row r="317" spans="1:18" ht="87" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" s="2" t="s">
         <v>9</v>
       </c>
@@ -20698,7 +20747,7 @@
       <c r="Q317" s="2"/>
       <c r="R317" s="2"/>
     </row>
-    <row r="318" spans="1:18" ht="87" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" s="2" t="s">
         <v>9</v>
       </c>
@@ -20742,7 +20791,7 @@
       <c r="Q318" s="2"/>
       <c r="R318" s="2"/>
     </row>
-    <row r="319" spans="1:18" ht="87" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" s="2" t="s">
         <v>9</v>
       </c>
@@ -20786,7 +20835,7 @@
       <c r="Q319" s="2"/>
       <c r="R319" s="2"/>
     </row>
-    <row r="320" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" s="2" t="s">
         <v>9</v>
       </c>
@@ -20830,7 +20879,7 @@
       <c r="Q320" s="2"/>
       <c r="R320" s="2"/>
     </row>
-    <row r="321" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:18" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" s="2" t="s">
         <v>9</v>
       </c>
@@ -20874,7 +20923,7 @@
       <c r="Q321" s="2"/>
       <c r="R321" s="2"/>
     </row>
-    <row r="322" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:18" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" s="2" t="s">
         <v>9</v>
       </c>
@@ -20918,7 +20967,7 @@
       <c r="Q322" s="2"/>
       <c r="R322" s="2"/>
     </row>
-    <row r="323" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:18" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" s="2" t="s">
         <v>9</v>
       </c>
@@ -20962,7 +21011,7 @@
       <c r="Q323" s="2"/>
       <c r="R323" s="2"/>
     </row>
-    <row r="324" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" s="2" t="s">
         <v>9</v>
       </c>
@@ -21006,7 +21055,7 @@
       <c r="Q324" s="2"/>
       <c r="R324" s="2"/>
     </row>
-    <row r="325" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" s="2" t="s">
         <v>9</v>
       </c>
@@ -21050,7 +21099,7 @@
       <c r="Q325" s="2"/>
       <c r="R325" s="2"/>
     </row>
-    <row r="326" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" s="2" t="s">
         <v>9</v>
       </c>
@@ -21094,7 +21143,7 @@
       <c r="Q326" s="2"/>
       <c r="R326" s="2"/>
     </row>
-    <row r="327" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:18" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" s="2" t="s">
         <v>9</v>
       </c>
@@ -21138,7 +21187,7 @@
       <c r="Q327" s="2"/>
       <c r="R327" s="2"/>
     </row>
-    <row r="328" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:18" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" s="2" t="s">
         <v>9</v>
       </c>
@@ -21182,7 +21231,7 @@
       <c r="Q328" s="2"/>
       <c r="R328" s="2"/>
     </row>
-    <row r="329" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:18" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" s="2" t="s">
         <v>9</v>
       </c>
@@ -21226,7 +21275,7 @@
       <c r="Q329" s="2"/>
       <c r="R329" s="2"/>
     </row>
-    <row r="330" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" s="2" t="s">
         <v>9</v>
       </c>
@@ -21270,7 +21319,7 @@
       <c r="Q330" s="2"/>
       <c r="R330" s="2"/>
     </row>
-    <row r="331" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:18" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" s="2" t="s">
         <v>9</v>
       </c>
@@ -21314,7 +21363,7 @@
       <c r="Q331" s="2"/>
       <c r="R331" s="2"/>
     </row>
-    <row r="332" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" s="2" t="s">
         <v>9</v>
       </c>
@@ -21358,7 +21407,7 @@
       <c r="Q332" s="2"/>
       <c r="R332" s="2"/>
     </row>
-    <row r="333" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:18" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" s="2" t="s">
         <v>9</v>
       </c>
@@ -21402,7 +21451,7 @@
       <c r="Q333" s="2"/>
       <c r="R333" s="2"/>
     </row>
-    <row r="334" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:18" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" s="2" t="s">
         <v>9</v>
       </c>
@@ -21446,7 +21495,7 @@
       <c r="Q334" s="2"/>
       <c r="R334" s="2"/>
     </row>
-    <row r="335" spans="1:18" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:18" s="3" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" s="2" t="s">
         <v>9</v>
       </c>
@@ -21490,7 +21539,7 @@
       <c r="Q335" s="2"/>
       <c r="R335" s="2"/>
     </row>
-    <row r="336" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" s="2" t="s">
         <v>9</v>
       </c>
@@ -21534,7 +21583,7 @@
       <c r="Q336" s="2"/>
       <c r="R336" s="2"/>
     </row>
-    <row r="337" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" s="2" t="s">
         <v>9</v>
       </c>
@@ -21578,7 +21627,7 @@
       <c r="Q337" s="2"/>
       <c r="R337" s="2"/>
     </row>
-    <row r="338" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" s="2" t="s">
         <v>9</v>
       </c>
@@ -21622,7 +21671,7 @@
       <c r="Q338" s="2"/>
       <c r="R338" s="2"/>
     </row>
-    <row r="339" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" s="2" t="s">
         <v>9</v>
       </c>
@@ -21666,7 +21715,7 @@
       <c r="Q339" s="2"/>
       <c r="R339" s="2"/>
     </row>
-    <row r="340" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" s="2" t="s">
         <v>9</v>
       </c>
@@ -21710,7 +21759,7 @@
       <c r="Q340" s="2"/>
       <c r="R340" s="2"/>
     </row>
-    <row r="341" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" s="2" t="s">
         <v>9</v>
       </c>
@@ -21754,7 +21803,7 @@
       <c r="Q341" s="2"/>
       <c r="R341" s="2"/>
     </row>
-    <row r="342" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" s="2" t="s">
         <v>9</v>
       </c>
@@ -21798,7 +21847,7 @@
       <c r="Q342" s="2"/>
       <c r="R342" s="2"/>
     </row>
-    <row r="343" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" s="2" t="s">
         <v>9</v>
       </c>
@@ -21842,7 +21891,7 @@
       <c r="Q343" s="2"/>
       <c r="R343" s="2"/>
     </row>
-    <row r="344" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" s="2" t="s">
         <v>9</v>
       </c>
@@ -21886,7 +21935,7 @@
       <c r="Q344" s="2"/>
       <c r="R344" s="2"/>
     </row>
-    <row r="345" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" s="2" t="s">
         <v>9</v>
       </c>
@@ -21930,7 +21979,7 @@
       <c r="Q345" s="2"/>
       <c r="R345" s="2"/>
     </row>
-    <row r="346" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" s="2" t="s">
         <v>9</v>
       </c>
@@ -21974,7 +22023,7 @@
       <c r="Q346" s="2"/>
       <c r="R346" s="2"/>
     </row>
-    <row r="347" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" s="2" t="s">
         <v>9</v>
       </c>
@@ -22018,7 +22067,7 @@
       <c r="Q347" s="2"/>
       <c r="R347" s="2"/>
     </row>
-    <row r="348" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" s="2" t="s">
         <v>9</v>
       </c>
@@ -22062,7 +22111,7 @@
       <c r="Q348" s="2"/>
       <c r="R348" s="2"/>
     </row>
-    <row r="349" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" s="2" t="s">
         <v>9</v>
       </c>
@@ -22106,7 +22155,7 @@
       <c r="Q349" s="2"/>
       <c r="R349" s="2"/>
     </row>
-    <row r="350" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" s="2" t="s">
         <v>9</v>
       </c>
@@ -22150,7 +22199,7 @@
       <c r="Q350" s="2"/>
       <c r="R350" s="2"/>
     </row>
-    <row r="351" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" s="2" t="s">
         <v>9</v>
       </c>
@@ -22194,7 +22243,7 @@
       <c r="Q351" s="2"/>
       <c r="R351" s="2"/>
     </row>
-    <row r="352" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" s="2" t="s">
         <v>9</v>
       </c>
@@ -22238,7 +22287,7 @@
       <c r="Q352" s="2"/>
       <c r="R352" s="2"/>
     </row>
-    <row r="353" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" s="2" t="s">
         <v>9</v>
       </c>
@@ -22282,7 +22331,7 @@
       <c r="Q353" s="2"/>
       <c r="R353" s="2"/>
     </row>
-    <row r="354" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" s="2" t="s">
         <v>9</v>
       </c>
@@ -22326,7 +22375,7 @@
       <c r="Q354" s="2"/>
       <c r="R354" s="2"/>
     </row>
-    <row r="355" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" s="2" t="s">
         <v>9</v>
       </c>
@@ -22370,7 +22419,7 @@
       <c r="Q355" s="2"/>
       <c r="R355" s="2"/>
     </row>
-    <row r="356" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" s="2" t="s">
         <v>9</v>
       </c>
@@ -22414,7 +22463,7 @@
       <c r="Q356" s="2"/>
       <c r="R356" s="2"/>
     </row>
-    <row r="357" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" s="2" t="s">
         <v>9</v>
       </c>
@@ -22458,7 +22507,7 @@
       <c r="Q357" s="2"/>
       <c r="R357" s="2"/>
     </row>
-    <row r="358" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" s="2" t="s">
         <v>9</v>
       </c>
@@ -22502,7 +22551,7 @@
       <c r="Q358" s="2"/>
       <c r="R358" s="2"/>
     </row>
-    <row r="359" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" s="2" t="s">
         <v>9</v>
       </c>
@@ -22546,7 +22595,7 @@
       <c r="Q359" s="2"/>
       <c r="R359" s="2"/>
     </row>
-    <row r="360" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" s="2" t="s">
         <v>9</v>
       </c>
@@ -22590,7 +22639,7 @@
       <c r="Q360" s="2"/>
       <c r="R360" s="2"/>
     </row>
-    <row r="361" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" s="2" t="s">
         <v>9</v>
       </c>
@@ -22634,7 +22683,7 @@
       <c r="Q361" s="2"/>
       <c r="R361" s="2"/>
     </row>
-    <row r="362" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" s="2" t="s">
         <v>9</v>
       </c>
@@ -22678,7 +22727,7 @@
       <c r="Q362" s="2"/>
       <c r="R362" s="2"/>
     </row>
-    <row r="363" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" s="2" t="s">
         <v>9</v>
       </c>
@@ -22722,7 +22771,7 @@
       <c r="Q363" s="2"/>
       <c r="R363" s="2"/>
     </row>
-    <row r="364" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" s="2" t="s">
         <v>9</v>
       </c>
@@ -22766,7 +22815,7 @@
       <c r="Q364" s="2"/>
       <c r="R364" s="2"/>
     </row>
-    <row r="365" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" s="2" t="s">
         <v>9</v>
       </c>
@@ -22810,7 +22859,7 @@
       <c r="Q365" s="2"/>
       <c r="R365" s="2"/>
     </row>
-    <row r="366" spans="1:18" s="3" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:18" s="3" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" s="2" t="s">
         <v>9</v>
       </c>
@@ -22854,7 +22903,7 @@
       <c r="Q366" s="2"/>
       <c r="R366" s="2"/>
     </row>
-    <row r="367" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" s="2" t="s">
         <v>9</v>
       </c>
@@ -22898,7 +22947,7 @@
       <c r="Q367" s="2"/>
       <c r="R367" s="2"/>
     </row>
-    <row r="368" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:18" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" s="2" t="s">
         <v>9</v>
       </c>
@@ -22942,7 +22991,7 @@
       <c r="Q368" s="2"/>
       <c r="R368" s="2"/>
     </row>
-    <row r="369" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" s="2" t="s">
         <v>9</v>
       </c>
@@ -22986,7 +23035,7 @@
       <c r="Q369" s="2"/>
       <c r="R369" s="2"/>
     </row>
-    <row r="370" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" s="2" t="s">
         <v>9</v>
       </c>
@@ -23030,7 +23079,7 @@
       <c r="Q370" s="2"/>
       <c r="R370" s="2"/>
     </row>
-    <row r="371" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371" s="2" t="s">
         <v>9</v>
       </c>
@@ -23074,7 +23123,7 @@
       <c r="Q371" s="2"/>
       <c r="R371" s="2"/>
     </row>
-    <row r="372" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" s="2" t="s">
         <v>9</v>
       </c>
@@ -23118,7 +23167,7 @@
       <c r="Q372" s="2"/>
       <c r="R372" s="2"/>
     </row>
-    <row r="373" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" s="2" t="s">
         <v>9</v>
       </c>
@@ -23162,7 +23211,7 @@
       <c r="Q373" s="2"/>
       <c r="R373" s="2"/>
     </row>
-    <row r="374" spans="1:18" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:18" s="3" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" s="2" t="s">
         <v>9</v>
       </c>
@@ -23208,7 +23257,7 @@
       <c r="Q374" s="2"/>
       <c r="R374" s="2"/>
     </row>
-    <row r="375" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375" s="2" t="s">
         <v>9</v>
       </c>
@@ -23254,7 +23303,7 @@
       <c r="Q375" s="2"/>
       <c r="R375" s="2"/>
     </row>
-    <row r="376" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:18" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" s="2" t="s">
         <v>9</v>
       </c>
@@ -23300,7 +23349,7 @@
       <c r="Q376" s="2"/>
       <c r="R376" s="2"/>
     </row>
-    <row r="377" spans="1:18" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:18" s="3" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" s="2" t="s">
         <v>9</v>
       </c>
@@ -23346,7 +23395,7 @@
       <c r="Q377" s="2"/>
       <c r="R377" s="2"/>
     </row>
-    <row r="378" spans="1:18" s="3" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:18" s="3" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" s="2" t="s">
         <v>9</v>
       </c>
@@ -23392,7 +23441,7 @@
       <c r="Q378" s="2"/>
       <c r="R378" s="2"/>
     </row>
-    <row r="379" spans="1:18" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:18" s="3" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" s="2" t="s">
         <v>9</v>
       </c>
@@ -23438,7 +23487,7 @@
       <c r="Q379" s="2"/>
       <c r="R379" s="2"/>
     </row>
-    <row r="380" spans="1:18" s="3" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:18" s="3" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" s="2" t="s">
         <v>9</v>
       </c>
@@ -23576,7 +23625,7 @@
       <c r="Q382" s="2"/>
       <c r="R382" s="2"/>
     </row>
-    <row r="383" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" s="2" t="s">
         <v>9</v>
       </c>
@@ -23622,7 +23671,7 @@
       <c r="Q383" s="2"/>
       <c r="R383" s="2"/>
     </row>
-    <row r="384" spans="1:18" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:18" s="3" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" s="2" t="s">
         <v>9</v>
       </c>
@@ -23666,7 +23715,7 @@
       <c r="Q384" s="2"/>
       <c r="R384" s="2"/>
     </row>
-    <row r="385" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A385" s="2" t="s">
         <v>9</v>
       </c>
@@ -23712,7 +23761,7 @@
       <c r="Q385" s="2"/>
       <c r="R385" s="2"/>
     </row>
-    <row r="386" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" s="2" t="s">
         <v>9</v>
       </c>
@@ -23758,7 +23807,7 @@
       <c r="Q386" s="2"/>
       <c r="R386" s="2"/>
     </row>
-    <row r="387" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387" s="2" t="s">
         <v>9</v>
       </c>
@@ -23804,7 +23853,7 @@
       <c r="Q387" s="2"/>
       <c r="R387" s="2"/>
     </row>
-    <row r="388" spans="1:18" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:18" s="3" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A388" s="2" t="s">
         <v>9</v>
       </c>
@@ -23848,7 +23897,7 @@
       <c r="Q388" s="2"/>
       <c r="R388" s="2"/>
     </row>
-    <row r="389" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A389" s="2" t="s">
         <v>9</v>
       </c>
@@ -23894,7 +23943,7 @@
       <c r="Q389" s="2"/>
       <c r="R389" s="2"/>
     </row>
-    <row r="390" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A390" s="2" t="s">
         <v>9</v>
       </c>
@@ -23940,7 +23989,7 @@
       <c r="Q390" s="2"/>
       <c r="R390" s="2"/>
     </row>
-    <row r="391" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A391" s="2" t="s">
         <v>9</v>
       </c>
@@ -23986,7 +24035,7 @@
       <c r="Q391" s="2"/>
       <c r="R391" s="2"/>
     </row>
-    <row r="392" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A392" s="2" t="s">
         <v>9</v>
       </c>
@@ -24032,7 +24081,7 @@
       <c r="Q392" s="2"/>
       <c r="R392" s="2"/>
     </row>
-    <row r="393" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:18" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393" s="2" t="s">
         <v>9</v>
       </c>
@@ -24078,7 +24127,7 @@
       <c r="Q393" s="2"/>
       <c r="R393" s="2"/>
     </row>
-    <row r="394" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394" s="2" t="s">
         <v>9</v>
       </c>
@@ -24124,7 +24173,7 @@
       <c r="Q394" s="2"/>
       <c r="R394" s="2"/>
     </row>
-    <row r="395" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" s="2" t="s">
         <v>9</v>
       </c>
@@ -24216,7 +24265,7 @@
       <c r="Q396" s="2"/>
       <c r="R396" s="2"/>
     </row>
-    <row r="397" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:18" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A397" s="2" t="s">
         <v>9</v>
       </c>
@@ -24262,7 +24311,7 @@
       <c r="Q397" s="2"/>
       <c r="R397" s="2"/>
     </row>
-    <row r="398" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A398" s="2" t="s">
         <v>9</v>
       </c>
@@ -24308,7 +24357,7 @@
       <c r="Q398" s="2"/>
       <c r="R398" s="2"/>
     </row>
-    <row r="399" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" s="2" t="s">
         <v>9</v>
       </c>
@@ -24354,7 +24403,7 @@
       <c r="Q399" s="2"/>
       <c r="R399" s="2"/>
     </row>
-    <row r="400" spans="1:18" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:18" s="3" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" s="2" t="s">
         <v>9</v>
       </c>
@@ -24400,7 +24449,7 @@
       <c r="Q400" s="2"/>
       <c r="R400" s="2"/>
     </row>
-    <row r="401" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" s="2" t="s">
         <v>9</v>
       </c>
@@ -24446,7 +24495,7 @@
       <c r="Q401" s="2"/>
       <c r="R401" s="2"/>
     </row>
-    <row r="402" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" s="2" t="s">
         <v>9</v>
       </c>
@@ -24538,7 +24587,7 @@
       <c r="Q403" s="2"/>
       <c r="R403" s="2"/>
     </row>
-    <row r="404" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A404" s="2" t="s">
         <v>9</v>
       </c>
@@ -24584,7 +24633,7 @@
       <c r="Q404" s="2"/>
       <c r="R404" s="2"/>
     </row>
-    <row r="405" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A405" s="2" t="s">
         <v>9</v>
       </c>
@@ -24630,7 +24679,7 @@
       <c r="Q405" s="2"/>
       <c r="R405" s="2"/>
     </row>
-    <row r="406" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406" s="2" t="s">
         <v>9</v>
       </c>
@@ -24676,7 +24725,7 @@
       <c r="Q406" s="2"/>
       <c r="R406" s="2"/>
     </row>
-    <row r="407" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A407" s="2" t="s">
         <v>9</v>
       </c>
@@ -24722,7 +24771,7 @@
       <c r="Q407" s="2"/>
       <c r="R407" s="2"/>
     </row>
-    <row r="408" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A408" s="2" t="s">
         <v>9</v>
       </c>
@@ -24768,7 +24817,7 @@
       <c r="Q408" s="2"/>
       <c r="R408" s="2"/>
     </row>
-    <row r="409" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A409" s="2" t="s">
         <v>9</v>
       </c>
@@ -24814,7 +24863,7 @@
       <c r="Q409" s="2"/>
       <c r="R409" s="2"/>
     </row>
-    <row r="410" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" s="2" t="s">
         <v>9</v>
       </c>
@@ -24860,7 +24909,7 @@
       <c r="Q410" s="2"/>
       <c r="R410" s="2"/>
     </row>
-    <row r="411" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411" s="2" t="s">
         <v>9</v>
       </c>
@@ -24906,7 +24955,7 @@
       <c r="Q411" s="2"/>
       <c r="R411" s="2"/>
     </row>
-    <row r="412" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" s="2" t="s">
         <v>9</v>
       </c>
@@ -24950,7 +24999,7 @@
       <c r="Q412" s="2"/>
       <c r="R412" s="2"/>
     </row>
-    <row r="413" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" s="2" t="s">
         <v>9</v>
       </c>
@@ -24994,7 +25043,7 @@
       <c r="Q413" s="2"/>
       <c r="R413" s="2"/>
     </row>
-    <row r="414" spans="1:18" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:18" s="3" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414" s="2" t="s">
         <v>9</v>
       </c>
@@ -25038,7 +25087,7 @@
       <c r="Q414" s="2"/>
       <c r="R414" s="2"/>
     </row>
-    <row r="415" spans="1:18" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:18" s="3" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415" s="2" t="s">
         <v>9</v>
       </c>
@@ -25082,7 +25131,7 @@
       <c r="Q415" s="2"/>
       <c r="R415" s="2"/>
     </row>
-    <row r="416" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:18" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416" s="2" t="s">
         <v>9</v>
       </c>
@@ -25126,8 +25175,152 @@
       <c r="Q416" s="2"/>
       <c r="R416" s="2"/>
     </row>
+    <row r="417" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+      <c r="A417" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B417" s="22" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C417" s="22" t="s">
+        <v>1784</v>
+      </c>
+      <c r="D417" s="14" t="s">
+        <v>1785</v>
+      </c>
+      <c r="E417" s="22" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F417" s="22" t="s">
+        <v>623</v>
+      </c>
+      <c r="G417" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="H417" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I417" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="J417" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="K417" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="L417" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="M417" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="N417" s="2"/>
+      <c r="O417" s="2"/>
+      <c r="P417" s="2"/>
+      <c r="Q417" s="2"/>
+      <c r="R417" s="2"/>
+    </row>
+    <row r="418" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A418" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B418" s="22" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C418" s="22" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D418" s="14" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E418" s="22" t="s">
+        <v>1789</v>
+      </c>
+      <c r="F418" s="22" t="s">
+        <v>1790</v>
+      </c>
+      <c r="G418" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="H418" s="2" t="s">
+        <v>1791</v>
+      </c>
+      <c r="I418" s="22" t="s">
+        <v>1792</v>
+      </c>
+      <c r="J418" s="2" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K418" s="2" t="s">
+        <v>1794</v>
+      </c>
+      <c r="L418" s="2" t="s">
+        <v>1795</v>
+      </c>
+      <c r="M418" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="N418" s="2"/>
+      <c r="O418" s="2"/>
+      <c r="P418" s="2"/>
+      <c r="Q418" s="2"/>
+      <c r="R418" s="2"/>
+    </row>
+    <row r="419" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A419" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B419" s="22" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C419" s="22" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D419" s="14" t="s">
+        <v>1798</v>
+      </c>
+      <c r="E419" s="22" t="s">
+        <v>1796</v>
+      </c>
+      <c r="F419" s="22" t="s">
+        <v>491</v>
+      </c>
+      <c r="G419" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H419" s="2" t="s">
+        <v>1791</v>
+      </c>
+      <c r="I419" s="22" t="s">
+        <v>1792</v>
+      </c>
+      <c r="J419" s="2" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K419" s="2" t="s">
+        <v>1794</v>
+      </c>
+      <c r="L419" s="2" t="s">
+        <v>1795</v>
+      </c>
+      <c r="M419" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="N419" s="2"/>
+      <c r="O419" s="2"/>
+      <c r="P419" s="2"/>
+      <c r="Q419" s="2"/>
+      <c r="R419" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R416" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:R417" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="IGE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L229">
     <sortCondition ref="C2:C424"/>
   </sortState>
@@ -25400,8 +25593,11 @@
     <hyperlink ref="D253" r:id="rId265" xr:uid="{DA3A1AE2-F4FD-41A9-97F8-0072003EA92E}"/>
     <hyperlink ref="D219" r:id="rId266" xr:uid="{20C18E58-ED58-41E9-945A-471B9F09477D}"/>
     <hyperlink ref="D314" r:id="rId267" xr:uid="{88B14105-E72E-49AA-B14C-B5EE9252467B}"/>
+    <hyperlink ref="D417" r:id="rId268" xr:uid="{EA39C09B-4B20-4316-8DF4-675B77129A46}"/>
+    <hyperlink ref="D418" r:id="rId269" xr:uid="{1D6715C0-F782-4275-B1A5-935F69FE9808}"/>
+    <hyperlink ref="D419" r:id="rId270" xr:uid="{9310D1D4-AE37-4F8D-B778-E14D476B480F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId268"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId271"/>
 </worksheet>
 </file>
--- a/Data/FairCarboN_Datas_Contacts.xlsx
+++ b/Data/FairCarboN_Datas_Contacts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCCD8027-95E0-44E7-8AAE-52EB49F89DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D87CDB89-D825-4788-8395-EB9D8789BBAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6316,6 +6316,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:V719"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -6409,7 +6410,7 @@
         <v>1761</v>
       </c>
     </row>
-    <row r="2" spans="1:22" s="2" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" s="2" customFormat="1" ht="188.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -6463,7 +6464,7 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
     </row>
-    <row r="3" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -6517,7 +6518,7 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
     </row>
-    <row r="4" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -6571,7 +6572,7 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
     </row>
-    <row r="5" spans="1:22" s="2" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" s="2" customFormat="1" ht="188.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -6625,7 +6626,7 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
     </row>
-    <row r="6" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -6681,7 +6682,7 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
     </row>
-    <row r="7" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -6737,7 +6738,7 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
     </row>
-    <row r="8" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -6791,7 +6792,7 @@
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
     </row>
-    <row r="9" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -6845,7 +6846,7 @@
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
     </row>
-    <row r="10" spans="1:22" s="2" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" s="2" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -6899,7 +6900,7 @@
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
     </row>
-    <row r="11" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
@@ -6953,7 +6954,7 @@
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
     </row>
-    <row r="12" spans="1:22" s="2" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" s="2" customFormat="1" ht="188.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
@@ -7007,7 +7008,7 @@
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
     </row>
-    <row r="13" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
@@ -7061,7 +7062,7 @@
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
     </row>
-    <row r="14" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>6</v>
       </c>
@@ -7115,7 +7116,7 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
     </row>
-    <row r="15" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>6</v>
       </c>
@@ -7171,7 +7172,7 @@
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
     </row>
-    <row r="16" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>6</v>
       </c>
@@ -7225,7 +7226,7 @@
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
     </row>
-    <row r="17" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>6</v>
       </c>
@@ -7281,7 +7282,7 @@
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
     </row>
-    <row r="18" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>6</v>
       </c>
@@ -7335,7 +7336,7 @@
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
     </row>
-    <row r="19" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>6</v>
       </c>
@@ -7389,7 +7390,7 @@
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
     </row>
-    <row r="20" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>6</v>
       </c>
@@ -7443,7 +7444,7 @@
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
     </row>
-    <row r="21" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>6</v>
       </c>
@@ -7497,7 +7498,7 @@
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
     </row>
-    <row r="22" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>6</v>
       </c>
@@ -7551,7 +7552,7 @@
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
     </row>
-    <row r="23" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>6</v>
       </c>
@@ -7605,7 +7606,7 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
     </row>
-    <row r="24" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>6</v>
       </c>
@@ -7659,7 +7660,7 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
     </row>
-    <row r="25" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>6</v>
       </c>
@@ -7715,7 +7716,7 @@
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
     </row>
-    <row r="26" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>6</v>
       </c>
@@ -7769,7 +7770,7 @@
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
     </row>
-    <row r="27" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>6</v>
       </c>
@@ -7823,7 +7824,7 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
     </row>
-    <row r="28" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>6</v>
       </c>
@@ -7877,7 +7878,7 @@
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
     </row>
-    <row r="29" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>6</v>
       </c>
@@ -7931,7 +7932,7 @@
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
     </row>
-    <row r="30" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>6</v>
       </c>
@@ -7985,7 +7986,7 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
     </row>
-    <row r="31" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>6</v>
       </c>
@@ -8039,7 +8040,7 @@
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
     </row>
-    <row r="32" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>6</v>
       </c>
@@ -8095,7 +8096,7 @@
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
     </row>
-    <row r="33" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>6</v>
       </c>
@@ -8149,7 +8150,7 @@
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
     </row>
-    <row r="34" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>6</v>
       </c>
@@ -8203,7 +8204,7 @@
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
     </row>
-    <row r="35" spans="1:22" s="2" customFormat="1" ht="232" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:22" s="2" customFormat="1" ht="232" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>6</v>
       </c>
@@ -8259,7 +8260,7 @@
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
     </row>
-    <row r="36" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>6</v>
       </c>
@@ -8313,7 +8314,7 @@
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
     </row>
-    <row r="37" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>6</v>
       </c>
@@ -8367,7 +8368,7 @@
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
     </row>
-    <row r="38" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>6</v>
       </c>
@@ -8421,7 +8422,7 @@
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
     </row>
-    <row r="39" spans="1:22" s="2" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:22" s="2" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>6</v>
       </c>
@@ -8475,7 +8476,7 @@
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
     </row>
-    <row r="40" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>6</v>
       </c>
@@ -8529,7 +8530,7 @@
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
     </row>
-    <row r="41" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>6</v>
       </c>
@@ -8583,7 +8584,7 @@
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
     </row>
-    <row r="42" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>6</v>
       </c>
@@ -8637,7 +8638,7 @@
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
     </row>
-    <row r="43" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>6</v>
       </c>
@@ -8691,7 +8692,7 @@
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
     </row>
-    <row r="44" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>6</v>
       </c>
@@ -8745,7 +8746,7 @@
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
     </row>
-    <row r="45" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>6</v>
       </c>
@@ -8799,7 +8800,7 @@
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
     </row>
-    <row r="46" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>6</v>
       </c>
@@ -8853,7 +8854,7 @@
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
     </row>
-    <row r="47" spans="1:22" s="2" customFormat="1" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:22" s="2" customFormat="1" ht="275.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>6</v>
       </c>
@@ -8911,7 +8912,7 @@
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
     </row>
-    <row r="48" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>6</v>
       </c>
@@ -8965,7 +8966,7 @@
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
     </row>
-    <row r="49" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>6</v>
       </c>
@@ -9021,7 +9022,7 @@
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
     </row>
-    <row r="50" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>6</v>
       </c>
@@ -9075,7 +9076,7 @@
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
     </row>
-    <row r="51" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>6</v>
       </c>
@@ -9129,7 +9130,7 @@
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
     </row>
-    <row r="52" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>6</v>
       </c>
@@ -9183,7 +9184,7 @@
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
     </row>
-    <row r="53" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>6</v>
       </c>
@@ -9237,7 +9238,7 @@
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
     </row>
-    <row r="54" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>6</v>
       </c>
@@ -9291,7 +9292,7 @@
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
     </row>
-    <row r="55" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>6</v>
       </c>
@@ -9345,7 +9346,7 @@
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
     </row>
-    <row r="56" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>6</v>
       </c>
@@ -9399,7 +9400,7 @@
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
     </row>
-    <row r="57" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>6</v>
       </c>
@@ -9453,7 +9454,7 @@
       <c r="U57" s="1"/>
       <c r="V57" s="1"/>
     </row>
-    <row r="58" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>6</v>
       </c>
@@ -9507,7 +9508,7 @@
       <c r="U58" s="1"/>
       <c r="V58" s="1"/>
     </row>
-    <row r="59" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>6</v>
       </c>
@@ -9563,7 +9564,7 @@
       <c r="U59" s="1"/>
       <c r="V59" s="1"/>
     </row>
-    <row r="60" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>6</v>
       </c>
@@ -9619,7 +9620,7 @@
       <c r="U60" s="1"/>
       <c r="V60" s="1"/>
     </row>
-    <row r="61" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>6</v>
       </c>
@@ -9675,7 +9676,7 @@
       <c r="U61" s="1"/>
       <c r="V61" s="1"/>
     </row>
-    <row r="62" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>6</v>
       </c>
@@ -9731,7 +9732,7 @@
       <c r="U62" s="1"/>
       <c r="V62" s="1"/>
     </row>
-    <row r="63" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>6</v>
       </c>
@@ -9785,7 +9786,7 @@
       <c r="U63" s="1"/>
       <c r="V63" s="1"/>
     </row>
-    <row r="64" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>6</v>
       </c>
@@ -9841,7 +9842,7 @@
       <c r="U64" s="1"/>
       <c r="V64" s="1"/>
     </row>
-    <row r="65" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>6</v>
       </c>
@@ -9939,7 +9940,7 @@
         <v>1</v>
       </c>
       <c r="O66" s="52">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P66" s="1" t="s">
         <v>1800</v>
@@ -9953,7 +9954,7 @@
       <c r="U66" s="1"/>
       <c r="V66" s="1"/>
     </row>
-    <row r="67" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:22" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>6</v>
       </c>
@@ -10007,7 +10008,7 @@
       <c r="U67" s="1"/>
       <c r="V67" s="1"/>
     </row>
-    <row r="68" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>6</v>
       </c>
@@ -10063,7 +10064,7 @@
       <c r="U68" s="1"/>
       <c r="V68" s="1"/>
     </row>
-    <row r="69" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>6</v>
       </c>
@@ -10117,7 +10118,7 @@
       <c r="U69" s="1"/>
       <c r="V69" s="1"/>
     </row>
-    <row r="70" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>6</v>
       </c>
@@ -10171,7 +10172,7 @@
       <c r="U70" s="1"/>
       <c r="V70" s="1"/>
     </row>
-    <row r="71" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>6</v>
       </c>
@@ -10225,7 +10226,7 @@
       <c r="U71" s="1"/>
       <c r="V71" s="1"/>
     </row>
-    <row r="72" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>6</v>
       </c>
@@ -10279,7 +10280,7 @@
       <c r="U72" s="1"/>
       <c r="V72" s="1"/>
     </row>
-    <row r="73" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>6</v>
       </c>
@@ -10333,7 +10334,7 @@
       <c r="U73" s="1"/>
       <c r="V73" s="1"/>
     </row>
-    <row r="74" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>6</v>
       </c>
@@ -10387,7 +10388,7 @@
       <c r="U74" s="1"/>
       <c r="V74" s="1"/>
     </row>
-    <row r="75" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>6</v>
       </c>
@@ -10441,7 +10442,7 @@
       <c r="U75" s="1"/>
       <c r="V75" s="1"/>
     </row>
-    <row r="76" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>6</v>
       </c>
@@ -10495,7 +10496,7 @@
       <c r="U76" s="1"/>
       <c r="V76" s="1"/>
     </row>
-    <row r="77" spans="1:22" s="2" customFormat="1" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:22" s="2" customFormat="1" ht="27.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>6</v>
       </c>
@@ -10551,7 +10552,7 @@
       <c r="U77" s="1"/>
       <c r="V77" s="1"/>
     </row>
-    <row r="78" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>6</v>
       </c>
@@ -10605,7 +10606,7 @@
       <c r="U78" s="1"/>
       <c r="V78" s="1"/>
     </row>
-    <row r="79" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>6</v>
       </c>
@@ -10659,7 +10660,7 @@
       <c r="U79" s="1"/>
       <c r="V79" s="1"/>
     </row>
-    <row r="80" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>6</v>
       </c>
@@ -10713,7 +10714,7 @@
       <c r="U80" s="1"/>
       <c r="V80" s="1"/>
     </row>
-    <row r="81" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>6</v>
       </c>
@@ -10769,7 +10770,7 @@
       <c r="U81" s="1"/>
       <c r="V81" s="1"/>
     </row>
-    <row r="82" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>6</v>
       </c>
@@ -10823,7 +10824,7 @@
       <c r="U82" s="1"/>
       <c r="V82" s="1"/>
     </row>
-    <row r="83" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>6</v>
       </c>
@@ -10879,7 +10880,7 @@
       <c r="U83" s="1"/>
       <c r="V83" s="1"/>
     </row>
-    <row r="84" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>6</v>
       </c>
@@ -10933,7 +10934,7 @@
       <c r="U84" s="1"/>
       <c r="V84" s="1"/>
     </row>
-    <row r="85" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>6</v>
       </c>
@@ -10989,7 +10990,7 @@
       <c r="U85" s="1"/>
       <c r="V85" s="1"/>
     </row>
-    <row r="86" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>6</v>
       </c>
@@ -11045,7 +11046,7 @@
       <c r="U86" s="1"/>
       <c r="V86" s="1"/>
     </row>
-    <row r="87" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>6</v>
       </c>
@@ -11099,7 +11100,7 @@
       <c r="U87" s="1"/>
       <c r="V87" s="1"/>
     </row>
-    <row r="88" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>6</v>
       </c>
@@ -11153,7 +11154,7 @@
       <c r="U88" s="1"/>
       <c r="V88" s="1"/>
     </row>
-    <row r="89" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>6</v>
       </c>
@@ -11205,7 +11206,7 @@
       <c r="U89" s="1"/>
       <c r="V89" s="1"/>
     </row>
-    <row r="90" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>6</v>
       </c>
@@ -11261,7 +11262,7 @@
       <c r="U90" s="1"/>
       <c r="V90" s="1"/>
     </row>
-    <row r="91" spans="1:22" s="2" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:22" s="2" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>6</v>
       </c>
@@ -11315,7 +11316,7 @@
       <c r="U91" s="1"/>
       <c r="V91" s="1"/>
     </row>
-    <row r="92" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>6</v>
       </c>
@@ -11369,7 +11370,7 @@
       <c r="U92" s="1"/>
       <c r="V92" s="1"/>
     </row>
-    <row r="93" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>6</v>
       </c>
@@ -11423,7 +11424,7 @@
       <c r="U93" s="1"/>
       <c r="V93" s="1"/>
     </row>
-    <row r="94" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>6</v>
       </c>
@@ -11477,7 +11478,7 @@
       <c r="U94" s="1"/>
       <c r="V94" s="1"/>
     </row>
-    <row r="95" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>6</v>
       </c>
@@ -11531,7 +11532,7 @@
       <c r="U95" s="1"/>
       <c r="V95" s="1"/>
     </row>
-    <row r="96" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>6</v>
       </c>
@@ -11585,7 +11586,7 @@
       <c r="U96" s="1"/>
       <c r="V96" s="1"/>
     </row>
-    <row r="97" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>6</v>
       </c>
@@ -11639,7 +11640,7 @@
       <c r="U97" s="1"/>
       <c r="V97" s="1"/>
     </row>
-    <row r="98" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>6</v>
       </c>
@@ -11693,7 +11694,7 @@
       <c r="U98" s="1"/>
       <c r="V98" s="1"/>
     </row>
-    <row r="99" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>6</v>
       </c>
@@ -11747,7 +11748,7 @@
       <c r="U99" s="1"/>
       <c r="V99" s="1"/>
     </row>
-    <row r="100" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>6</v>
       </c>
@@ -11801,7 +11802,7 @@
       <c r="U100" s="1"/>
       <c r="V100" s="1"/>
     </row>
-    <row r="101" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>6</v>
       </c>
@@ -11853,7 +11854,7 @@
       <c r="U101" s="1"/>
       <c r="V101" s="1"/>
     </row>
-    <row r="102" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>6</v>
       </c>
@@ -11909,7 +11910,7 @@
       <c r="U102" s="1"/>
       <c r="V102" s="1"/>
     </row>
-    <row r="103" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>6</v>
       </c>
@@ -11963,7 +11964,7 @@
       <c r="U103" s="1"/>
       <c r="V103" s="1"/>
     </row>
-    <row r="104" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>6</v>
       </c>
@@ -12015,7 +12016,7 @@
       <c r="U104" s="1"/>
       <c r="V104" s="1"/>
     </row>
-    <row r="105" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>6</v>
       </c>
@@ -12071,7 +12072,7 @@
       <c r="U105" s="1"/>
       <c r="V105" s="1"/>
     </row>
-    <row r="106" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>6</v>
       </c>
@@ -12125,7 +12126,7 @@
       <c r="U106" s="1"/>
       <c r="V106" s="1"/>
     </row>
-    <row r="107" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>6</v>
       </c>
@@ -12179,7 +12180,7 @@
       <c r="U107" s="1"/>
       <c r="V107" s="1"/>
     </row>
-    <row r="108" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>6</v>
       </c>
@@ -12233,7 +12234,7 @@
       <c r="U108" s="1"/>
       <c r="V108" s="1"/>
     </row>
-    <row r="109" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>6</v>
       </c>
@@ -12285,7 +12286,7 @@
       <c r="U109" s="1"/>
       <c r="V109" s="1"/>
     </row>
-    <row r="110" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>6</v>
       </c>
@@ -12339,7 +12340,7 @@
       <c r="U110" s="1"/>
       <c r="V110" s="1"/>
     </row>
-    <row r="111" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>6</v>
       </c>
@@ -12395,7 +12396,7 @@
       <c r="U111" s="1"/>
       <c r="V111" s="1"/>
     </row>
-    <row r="112" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>6</v>
       </c>
@@ -12449,7 +12450,7 @@
       <c r="U112" s="1"/>
       <c r="V112" s="1"/>
     </row>
-    <row r="113" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>6</v>
       </c>
@@ -12503,7 +12504,7 @@
       <c r="U113" s="1"/>
       <c r="V113" s="1"/>
     </row>
-    <row r="114" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>6</v>
       </c>
@@ -12557,7 +12558,7 @@
       <c r="U114" s="1"/>
       <c r="V114" s="1"/>
     </row>
-    <row r="115" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>6</v>
       </c>
@@ -12611,7 +12612,7 @@
       <c r="U115" s="1"/>
       <c r="V115" s="1"/>
     </row>
-    <row r="116" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>6</v>
       </c>
@@ -12665,7 +12666,7 @@
       <c r="U116" s="1"/>
       <c r="V116" s="1"/>
     </row>
-    <row r="117" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>6</v>
       </c>
@@ -12719,7 +12720,7 @@
       <c r="U117" s="1"/>
       <c r="V117" s="1"/>
     </row>
-    <row r="118" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>6</v>
       </c>
@@ -12773,7 +12774,7 @@
       <c r="U118" s="1"/>
       <c r="V118" s="1"/>
     </row>
-    <row r="119" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>6</v>
       </c>
@@ -12827,7 +12828,7 @@
       <c r="U119" s="1"/>
       <c r="V119" s="1"/>
     </row>
-    <row r="120" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>6</v>
       </c>
@@ -12881,7 +12882,7 @@
       <c r="U120" s="1"/>
       <c r="V120" s="1"/>
     </row>
-    <row r="121" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>6</v>
       </c>
@@ -12937,7 +12938,7 @@
       <c r="U121" s="1"/>
       <c r="V121" s="1"/>
     </row>
-    <row r="122" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>6</v>
       </c>
@@ -12991,7 +12992,7 @@
       <c r="U122" s="1"/>
       <c r="V122" s="1"/>
     </row>
-    <row r="123" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>6</v>
       </c>
@@ -13045,7 +13046,7 @@
       <c r="U123" s="1"/>
       <c r="V123" s="1"/>
     </row>
-    <row r="124" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>6</v>
       </c>
@@ -13099,7 +13100,7 @@
       <c r="U124" s="1"/>
       <c r="V124" s="1"/>
     </row>
-    <row r="125" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>6</v>
       </c>
@@ -13153,7 +13154,7 @@
       <c r="U125" s="1"/>
       <c r="V125" s="1"/>
     </row>
-    <row r="126" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>6</v>
       </c>
@@ -13207,7 +13208,7 @@
       <c r="U126" s="1"/>
       <c r="V126" s="1"/>
     </row>
-    <row r="127" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>6</v>
       </c>
@@ -13261,7 +13262,7 @@
       <c r="U127" s="1"/>
       <c r="V127" s="1"/>
     </row>
-    <row r="128" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>6</v>
       </c>
@@ -13315,7 +13316,7 @@
       <c r="U128" s="1"/>
       <c r="V128" s="1"/>
     </row>
-    <row r="129" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>6</v>
       </c>
@@ -13369,7 +13370,7 @@
       <c r="U129" s="1"/>
       <c r="V129" s="1"/>
     </row>
-    <row r="130" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>6</v>
       </c>
@@ -13423,7 +13424,7 @@
       <c r="U130" s="1"/>
       <c r="V130" s="1"/>
     </row>
-    <row r="131" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>6</v>
       </c>
@@ -13477,7 +13478,7 @@
       <c r="U131" s="1"/>
       <c r="V131" s="1"/>
     </row>
-    <row r="132" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>6</v>
       </c>
@@ -13531,7 +13532,7 @@
       <c r="U132" s="1"/>
       <c r="V132" s="1"/>
     </row>
-    <row r="133" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>6</v>
       </c>
@@ -13585,7 +13586,7 @@
       <c r="U133" s="1"/>
       <c r="V133" s="1"/>
     </row>
-    <row r="134" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>6</v>
       </c>
@@ -13639,7 +13640,7 @@
       <c r="U134" s="1"/>
       <c r="V134" s="1"/>
     </row>
-    <row r="135" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>6</v>
       </c>
@@ -13693,7 +13694,7 @@
       <c r="U135" s="1"/>
       <c r="V135" s="1"/>
     </row>
-    <row r="136" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>6</v>
       </c>
@@ -13747,7 +13748,7 @@
       <c r="U136" s="1"/>
       <c r="V136" s="1"/>
     </row>
-    <row r="137" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>6</v>
       </c>
@@ -13801,7 +13802,7 @@
       <c r="U137" s="1"/>
       <c r="V137" s="1"/>
     </row>
-    <row r="138" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>6</v>
       </c>
@@ -13855,7 +13856,7 @@
       <c r="U138" s="1"/>
       <c r="V138" s="1"/>
     </row>
-    <row r="139" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>6</v>
       </c>
@@ -13909,7 +13910,7 @@
       <c r="U139" s="1"/>
       <c r="V139" s="1"/>
     </row>
-    <row r="140" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>6</v>
       </c>
@@ -13965,7 +13966,7 @@
       <c r="U140" s="1"/>
       <c r="V140" s="1"/>
     </row>
-    <row r="141" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>6</v>
       </c>
@@ -14019,7 +14020,7 @@
       <c r="U141" s="1"/>
       <c r="V141" s="1"/>
     </row>
-    <row r="142" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>6</v>
       </c>
@@ -14073,7 +14074,7 @@
       <c r="U142" s="1"/>
       <c r="V142" s="1"/>
     </row>
-    <row r="143" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>6</v>
       </c>
@@ -14127,7 +14128,7 @@
       <c r="U143" s="1"/>
       <c r="V143" s="1"/>
     </row>
-    <row r="144" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>6</v>
       </c>
@@ -14183,7 +14184,7 @@
       <c r="U144" s="1"/>
       <c r="V144" s="1"/>
     </row>
-    <row r="145" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>6</v>
       </c>
@@ -14237,7 +14238,7 @@
       <c r="U145" s="1"/>
       <c r="V145" s="1"/>
     </row>
-    <row r="146" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>6</v>
       </c>
@@ -14291,7 +14292,7 @@
       <c r="U146" s="1"/>
       <c r="V146" s="1"/>
     </row>
-    <row r="147" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>6</v>
       </c>
@@ -14347,7 +14348,7 @@
       <c r="U147" s="1"/>
       <c r="V147" s="1"/>
     </row>
-    <row r="148" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>6</v>
       </c>
@@ -14401,7 +14402,7 @@
       <c r="U148" s="1"/>
       <c r="V148" s="1"/>
     </row>
-    <row r="149" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>6</v>
       </c>
@@ -14455,7 +14456,7 @@
       <c r="U149" s="1"/>
       <c r="V149" s="1"/>
     </row>
-    <row r="150" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>6</v>
       </c>
@@ -14509,7 +14510,7 @@
       <c r="U150" s="1"/>
       <c r="V150" s="1"/>
     </row>
-    <row r="151" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>6</v>
       </c>
@@ -14563,7 +14564,7 @@
       <c r="U151" s="1"/>
       <c r="V151" s="1"/>
     </row>
-    <row r="152" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>6</v>
       </c>
@@ -14617,7 +14618,7 @@
       <c r="U152" s="1"/>
       <c r="V152" s="1"/>
     </row>
-    <row r="153" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>6</v>
       </c>
@@ -14671,7 +14672,7 @@
       <c r="U153" s="1"/>
       <c r="V153" s="1"/>
     </row>
-    <row r="154" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>6</v>
       </c>
@@ -14725,7 +14726,7 @@
       <c r="U154" s="1"/>
       <c r="V154" s="1"/>
     </row>
-    <row r="155" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>6</v>
       </c>
@@ -14779,7 +14780,7 @@
       <c r="U155" s="1"/>
       <c r="V155" s="1"/>
     </row>
-    <row r="156" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>6</v>
       </c>
@@ -14833,7 +14834,7 @@
       <c r="U156" s="1"/>
       <c r="V156" s="1"/>
     </row>
-    <row r="157" spans="1:22" s="2" customFormat="1" ht="65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:22" s="2" customFormat="1" ht="65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>6</v>
       </c>
@@ -14897,7 +14898,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="158" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>6</v>
       </c>
@@ -14953,7 +14954,7 @@
       <c r="U158" s="1"/>
       <c r="V158" s="1"/>
     </row>
-    <row r="159" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:22" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>6</v>
       </c>
@@ -15009,7 +15010,7 @@
       <c r="U159" s="1"/>
       <c r="V159" s="1"/>
     </row>
-    <row r="160" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:22" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>6</v>
       </c>
@@ -15065,7 +15066,7 @@
       <c r="U160" s="1"/>
       <c r="V160" s="1"/>
     </row>
-    <row r="161" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>6</v>
       </c>
@@ -15121,7 +15122,7 @@
       <c r="U161" s="1"/>
       <c r="V161" s="1"/>
     </row>
-    <row r="162" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
         <v>6</v>
       </c>
@@ -15179,7 +15180,7 @@
       <c r="U162" s="1"/>
       <c r="V162" s="1"/>
     </row>
-    <row r="163" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
         <v>6</v>
       </c>
@@ -15235,7 +15236,7 @@
       <c r="U163" s="1"/>
       <c r="V163" s="1"/>
     </row>
-    <row r="164" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
         <v>6</v>
       </c>
@@ -15291,7 +15292,7 @@
       <c r="U164" s="1"/>
       <c r="V164" s="1"/>
     </row>
-    <row r="165" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
         <v>6</v>
       </c>
@@ -15347,7 +15348,7 @@
       <c r="U165" s="1"/>
       <c r="V165" s="1"/>
     </row>
-    <row r="166" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
         <v>6</v>
       </c>
@@ -15403,7 +15404,7 @@
       <c r="U166" s="1"/>
       <c r="V166" s="1"/>
     </row>
-    <row r="167" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
         <v>6</v>
       </c>
@@ -15461,7 +15462,7 @@
       <c r="U167" s="1"/>
       <c r="V167" s="1"/>
     </row>
-    <row r="168" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
         <v>6</v>
       </c>
@@ -15521,7 +15522,7 @@
       <c r="U168" s="1"/>
       <c r="V168" s="1"/>
     </row>
-    <row r="169" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:22" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
         <v>6</v>
       </c>
@@ -15577,7 +15578,7 @@
       <c r="U169" s="1"/>
       <c r="V169" s="1"/>
     </row>
-    <row r="170" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
         <v>6</v>
       </c>
@@ -15633,7 +15634,7 @@
       <c r="U170" s="1"/>
       <c r="V170" s="1"/>
     </row>
-    <row r="171" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
         <v>6</v>
       </c>
@@ -15689,7 +15690,7 @@
       <c r="U171" s="1"/>
       <c r="V171" s="1"/>
     </row>
-    <row r="172" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
         <v>6</v>
       </c>
@@ -15745,7 +15746,7 @@
       <c r="U172" s="1"/>
       <c r="V172" s="1"/>
     </row>
-    <row r="173" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
         <v>6</v>
       </c>
@@ -15799,7 +15800,7 @@
       <c r="U173" s="1"/>
       <c r="V173" s="1"/>
     </row>
-    <row r="174" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
         <v>6</v>
       </c>
@@ -15853,7 +15854,7 @@
       <c r="U174" s="1"/>
       <c r="V174" s="1"/>
     </row>
-    <row r="175" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
         <v>6</v>
       </c>
@@ -15907,7 +15908,7 @@
       <c r="U175" s="1"/>
       <c r="V175" s="1"/>
     </row>
-    <row r="176" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
         <v>6</v>
       </c>
@@ -15961,7 +15962,7 @@
       <c r="U176" s="1"/>
       <c r="V176" s="1"/>
     </row>
-    <row r="177" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
         <v>6</v>
       </c>
@@ -16015,7 +16016,7 @@
       <c r="U177" s="1"/>
       <c r="V177" s="1"/>
     </row>
-    <row r="178" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
         <v>6</v>
       </c>
@@ -16069,7 +16070,7 @@
       <c r="U178" s="1"/>
       <c r="V178" s="1"/>
     </row>
-    <row r="179" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
         <v>6</v>
       </c>
@@ -16123,7 +16124,7 @@
       <c r="U179" s="1"/>
       <c r="V179" s="1"/>
     </row>
-    <row r="180" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
         <v>6</v>
       </c>
@@ -16177,7 +16178,7 @@
       <c r="U180" s="1"/>
       <c r="V180" s="1"/>
     </row>
-    <row r="181" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
         <v>6</v>
       </c>
@@ -16233,7 +16234,7 @@
       <c r="U181" s="1"/>
       <c r="V181" s="1"/>
     </row>
-    <row r="182" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
         <v>6</v>
       </c>
@@ -16287,7 +16288,7 @@
       <c r="U182" s="1"/>
       <c r="V182" s="1"/>
     </row>
-    <row r="183" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
         <v>6</v>
       </c>
@@ -16341,7 +16342,7 @@
       <c r="U183" s="1"/>
       <c r="V183" s="1"/>
     </row>
-    <row r="184" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
         <v>6</v>
       </c>
@@ -16395,7 +16396,7 @@
       <c r="U184" s="1"/>
       <c r="V184" s="1"/>
     </row>
-    <row r="185" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
         <v>6</v>
       </c>
@@ -16449,7 +16450,7 @@
       <c r="U185" s="1"/>
       <c r="V185" s="1"/>
     </row>
-    <row r="186" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
         <v>6</v>
       </c>
@@ -16505,7 +16506,7 @@
       <c r="U186" s="1"/>
       <c r="V186" s="1"/>
     </row>
-    <row r="187" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
         <v>6</v>
       </c>
@@ -16559,7 +16560,7 @@
       <c r="U187" s="1"/>
       <c r="V187" s="1"/>
     </row>
-    <row r="188" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
         <v>6</v>
       </c>
@@ -16613,7 +16614,7 @@
       <c r="U188" s="1"/>
       <c r="V188" s="1"/>
     </row>
-    <row r="189" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
         <v>6</v>
       </c>
@@ -16667,7 +16668,7 @@
       <c r="U189" s="1"/>
       <c r="V189" s="1"/>
     </row>
-    <row r="190" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
         <v>6</v>
       </c>
@@ -16721,7 +16722,7 @@
       <c r="U190" s="1"/>
       <c r="V190" s="1"/>
     </row>
-    <row r="191" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
         <v>6</v>
       </c>
@@ -16775,7 +16776,7 @@
       <c r="U191" s="1"/>
       <c r="V191" s="1"/>
     </row>
-    <row r="192" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
         <v>6</v>
       </c>
@@ -16829,7 +16830,7 @@
       <c r="U192" s="1"/>
       <c r="V192" s="1"/>
     </row>
-    <row r="193" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
         <v>6</v>
       </c>
@@ -16883,7 +16884,7 @@
       <c r="U193" s="1"/>
       <c r="V193" s="1"/>
     </row>
-    <row r="194" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
         <v>6</v>
       </c>
@@ -16937,7 +16938,7 @@
       <c r="U194" s="1"/>
       <c r="V194" s="1"/>
     </row>
-    <row r="195" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
         <v>6</v>
       </c>
@@ -16991,7 +16992,7 @@
       <c r="U195" s="1"/>
       <c r="V195" s="1"/>
     </row>
-    <row r="196" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
         <v>6</v>
       </c>
@@ -17045,7 +17046,7 @@
       <c r="U196" s="1"/>
       <c r="V196" s="1"/>
     </row>
-    <row r="197" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
         <v>6</v>
       </c>
@@ -17099,7 +17100,7 @@
       <c r="U197" s="1"/>
       <c r="V197" s="1"/>
     </row>
-    <row r="198" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
         <v>6</v>
       </c>
@@ -17153,7 +17154,7 @@
       <c r="U198" s="1"/>
       <c r="V198" s="1"/>
     </row>
-    <row r="199" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
         <v>6</v>
       </c>
@@ -17207,7 +17208,7 @@
       <c r="U199" s="1"/>
       <c r="V199" s="1"/>
     </row>
-    <row r="200" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
         <v>6</v>
       </c>
@@ -17261,7 +17262,7 @@
       <c r="U200" s="1"/>
       <c r="V200" s="1"/>
     </row>
-    <row r="201" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
         <v>6</v>
       </c>
@@ -17315,7 +17316,7 @@
       <c r="U201" s="1"/>
       <c r="V201" s="1"/>
     </row>
-    <row r="202" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
         <v>6</v>
       </c>
@@ -17369,7 +17370,7 @@
       <c r="U202" s="1"/>
       <c r="V202" s="1"/>
     </row>
-    <row r="203" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" s="1" t="s">
         <v>6</v>
       </c>
@@ -17423,7 +17424,7 @@
       <c r="U203" s="1"/>
       <c r="V203" s="1"/>
     </row>
-    <row r="204" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
         <v>6</v>
       </c>
@@ -17477,7 +17478,7 @@
       <c r="U204" s="1"/>
       <c r="V204" s="1"/>
     </row>
-    <row r="205" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
         <v>6</v>
       </c>
@@ -17531,7 +17532,7 @@
       <c r="U205" s="1"/>
       <c r="V205" s="1"/>
     </row>
-    <row r="206" spans="1:22" ht="87" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:22" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
         <v>6</v>
       </c>
@@ -17585,7 +17586,7 @@
       <c r="U206" s="1"/>
       <c r="V206" s="1"/>
     </row>
-    <row r="207" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
         <v>6</v>
       </c>
@@ -17639,7 +17640,7 @@
       <c r="U207" s="1"/>
       <c r="V207" s="1"/>
     </row>
-    <row r="208" spans="1:22" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:22" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
         <v>6</v>
       </c>
@@ -17693,7 +17694,7 @@
       <c r="U208" s="1"/>
       <c r="V208" s="1"/>
     </row>
-    <row r="209" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
         <v>6</v>
       </c>
@@ -17747,7 +17748,7 @@
       <c r="U209" s="1"/>
       <c r="V209" s="1"/>
     </row>
-    <row r="210" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
         <v>6</v>
       </c>
@@ -17801,7 +17802,7 @@
       <c r="U210" s="1"/>
       <c r="V210" s="1"/>
     </row>
-    <row r="211" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" s="1" t="s">
         <v>6</v>
       </c>
@@ -17853,7 +17854,7 @@
       <c r="U211" s="1"/>
       <c r="V211" s="1"/>
     </row>
-    <row r="212" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
         <v>6</v>
       </c>
@@ -17905,7 +17906,7 @@
       <c r="U212" s="1"/>
       <c r="V212" s="1"/>
     </row>
-    <row r="213" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
         <v>6</v>
       </c>
@@ -17959,7 +17960,7 @@
       <c r="U213" s="1"/>
       <c r="V213" s="1"/>
     </row>
-    <row r="214" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
         <v>6</v>
       </c>
@@ -18011,7 +18012,7 @@
       <c r="U214" s="1"/>
       <c r="V214" s="1"/>
     </row>
-    <row r="215" spans="1:22" s="2" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:22" s="2" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" s="1" t="s">
         <v>6</v>
       </c>
@@ -18063,7 +18064,7 @@
       <c r="U215" s="1"/>
       <c r="V215" s="1"/>
     </row>
-    <row r="216" spans="1:22" s="2" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:22" s="2" customFormat="1" ht="188.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" s="1" t="s">
         <v>6</v>
       </c>
@@ -18115,7 +18116,7 @@
       <c r="U216" s="1"/>
       <c r="V216" s="1"/>
     </row>
-    <row r="217" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
         <v>6</v>
       </c>
@@ -18167,7 +18168,7 @@
       <c r="U217" s="1"/>
       <c r="V217" s="1"/>
     </row>
-    <row r="218" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" s="1" t="s">
         <v>6</v>
       </c>
@@ -18221,7 +18222,7 @@
       <c r="U218" s="1"/>
       <c r="V218" s="1"/>
     </row>
-    <row r="219" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
         <v>6</v>
       </c>
@@ -18275,7 +18276,7 @@
       <c r="U219" s="1"/>
       <c r="V219" s="1"/>
     </row>
-    <row r="220" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
         <v>6</v>
       </c>
@@ -18331,7 +18332,7 @@
       <c r="U220" s="1"/>
       <c r="V220" s="1"/>
     </row>
-    <row r="221" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
         <v>6</v>
       </c>
@@ -18385,7 +18386,7 @@
       <c r="U221" s="1"/>
       <c r="V221" s="1"/>
     </row>
-    <row r="222" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" s="1" t="s">
         <v>6</v>
       </c>
@@ -18437,7 +18438,7 @@
       <c r="U222" s="1"/>
       <c r="V222" s="1"/>
     </row>
-    <row r="223" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" s="1" t="s">
         <v>6</v>
       </c>
@@ -18491,7 +18492,7 @@
       <c r="U223" s="1"/>
       <c r="V223" s="1"/>
     </row>
-    <row r="224" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" s="1" t="s">
         <v>6</v>
       </c>
@@ -18547,7 +18548,7 @@
       <c r="U224" s="1"/>
       <c r="V224" s="1"/>
     </row>
-    <row r="225" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
         <v>6</v>
       </c>
@@ -18603,7 +18604,7 @@
       <c r="U225" s="1"/>
       <c r="V225" s="1"/>
     </row>
-    <row r="226" spans="1:22" s="2" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:22" s="2" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
         <v>6</v>
       </c>
@@ -18657,7 +18658,7 @@
       <c r="U226" s="1"/>
       <c r="V226" s="1"/>
     </row>
-    <row r="227" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
         <v>6</v>
       </c>
@@ -18709,7 +18710,7 @@
       <c r="U227" s="1"/>
       <c r="V227" s="1"/>
     </row>
-    <row r="228" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
         <v>6</v>
       </c>
@@ -18761,7 +18762,7 @@
       <c r="U228" s="1"/>
       <c r="V228" s="1"/>
     </row>
-    <row r="229" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
         <v>6</v>
       </c>
@@ -18817,7 +18818,7 @@
       <c r="U229" s="1"/>
       <c r="V229" s="1"/>
     </row>
-    <row r="230" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" s="1" t="s">
         <v>6</v>
       </c>
@@ -18871,7 +18872,7 @@
       <c r="U230" s="1"/>
       <c r="V230" s="1"/>
     </row>
-    <row r="231" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" s="1" t="s">
         <v>6</v>
       </c>
@@ -18923,7 +18924,7 @@
       <c r="U231" s="1"/>
       <c r="V231" s="1"/>
     </row>
-    <row r="232" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
         <v>6</v>
       </c>
@@ -18975,7 +18976,7 @@
       <c r="U232" s="1"/>
       <c r="V232" s="1"/>
     </row>
-    <row r="233" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>6</v>
       </c>
@@ -19027,7 +19028,7 @@
       <c r="U233" s="1"/>
       <c r="V233" s="1"/>
     </row>
-    <row r="234" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
         <v>6</v>
       </c>
@@ -19079,7 +19080,7 @@
       <c r="U234" s="1"/>
       <c r="V234" s="1"/>
     </row>
-    <row r="235" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" s="1" t="s">
         <v>6</v>
       </c>
@@ -19131,7 +19132,7 @@
       <c r="U235" s="1"/>
       <c r="V235" s="1"/>
     </row>
-    <row r="236" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" s="1" t="s">
         <v>6</v>
       </c>
@@ -19183,7 +19184,7 @@
       <c r="U236" s="1"/>
       <c r="V236" s="1"/>
     </row>
-    <row r="237" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" s="1" t="s">
         <v>6</v>
       </c>
@@ -19235,7 +19236,7 @@
       <c r="U237" s="1"/>
       <c r="V237" s="1"/>
     </row>
-    <row r="238" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" s="1" t="s">
         <v>6</v>
       </c>
@@ -19289,7 +19290,7 @@
       <c r="U238" s="1"/>
       <c r="V238" s="1"/>
     </row>
-    <row r="239" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" s="1" t="s">
         <v>6</v>
       </c>
@@ -19341,7 +19342,7 @@
       <c r="U239" s="1"/>
       <c r="V239" s="1"/>
     </row>
-    <row r="240" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" s="1" t="s">
         <v>6</v>
       </c>
@@ -19393,7 +19394,7 @@
       <c r="U240" s="1"/>
       <c r="V240" s="1"/>
     </row>
-    <row r="241" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" s="1" t="s">
         <v>6</v>
       </c>
@@ -19445,7 +19446,7 @@
       <c r="U241" s="1"/>
       <c r="V241" s="1"/>
     </row>
-    <row r="242" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" s="1" t="s">
         <v>6</v>
       </c>
@@ -19497,7 +19498,7 @@
       <c r="U242" s="1"/>
       <c r="V242" s="1"/>
     </row>
-    <row r="243" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" s="1" t="s">
         <v>6</v>
       </c>
@@ -19549,7 +19550,7 @@
       <c r="U243" s="1"/>
       <c r="V243" s="1"/>
     </row>
-    <row r="244" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" s="1" t="s">
         <v>6</v>
       </c>
@@ -19601,7 +19602,7 @@
       <c r="U244" s="1"/>
       <c r="V244" s="1"/>
     </row>
-    <row r="245" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" s="1" t="s">
         <v>6</v>
       </c>
@@ -19655,7 +19656,7 @@
       <c r="U245" s="1"/>
       <c r="V245" s="1"/>
     </row>
-    <row r="246" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" s="1" t="s">
         <v>6</v>
       </c>
@@ -19709,7 +19710,7 @@
       <c r="U246" s="1"/>
       <c r="V246" s="1"/>
     </row>
-    <row r="247" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" s="1" t="s">
         <v>6</v>
       </c>
@@ -19761,7 +19762,7 @@
       <c r="U247" s="1"/>
       <c r="V247" s="1"/>
     </row>
-    <row r="248" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" s="1" t="s">
         <v>6</v>
       </c>
@@ -19813,7 +19814,7 @@
       <c r="U248" s="1"/>
       <c r="V248" s="1"/>
     </row>
-    <row r="249" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" s="1" t="s">
         <v>6</v>
       </c>
@@ -19865,7 +19866,7 @@
       <c r="U249" s="1"/>
       <c r="V249" s="1"/>
     </row>
-    <row r="250" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" s="1" t="s">
         <v>6</v>
       </c>
@@ -19917,7 +19918,7 @@
       <c r="U250" s="1"/>
       <c r="V250" s="1"/>
     </row>
-    <row r="251" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" s="1" t="s">
         <v>6</v>
       </c>
@@ -19969,7 +19970,7 @@
       <c r="U251" s="1"/>
       <c r="V251" s="1"/>
     </row>
-    <row r="252" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" s="1" t="s">
         <v>6</v>
       </c>
@@ -20021,7 +20022,7 @@
       <c r="U252" s="1"/>
       <c r="V252" s="1"/>
     </row>
-    <row r="253" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" s="1" t="s">
         <v>6</v>
       </c>
@@ -20077,7 +20078,7 @@
       <c r="U253" s="1"/>
       <c r="V253" s="1"/>
     </row>
-    <row r="254" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" s="1" t="s">
         <v>6</v>
       </c>
@@ -20131,7 +20132,7 @@
       <c r="U254" s="1"/>
       <c r="V254" s="1"/>
     </row>
-    <row r="255" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" s="1" t="s">
         <v>6</v>
       </c>
@@ -20185,7 +20186,7 @@
       <c r="U255" s="1"/>
       <c r="V255" s="1"/>
     </row>
-    <row r="256" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" s="1" t="s">
         <v>6</v>
       </c>
@@ -20237,7 +20238,7 @@
       <c r="U256" s="1"/>
       <c r="V256" s="1"/>
     </row>
-    <row r="257" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" s="1" t="s">
         <v>6</v>
       </c>
@@ -20289,7 +20290,7 @@
       <c r="U257" s="1"/>
       <c r="V257" s="1"/>
     </row>
-    <row r="258" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" s="1" t="s">
         <v>6</v>
       </c>
@@ -20341,7 +20342,7 @@
       <c r="U258" s="1"/>
       <c r="V258" s="1"/>
     </row>
-    <row r="259" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" s="1" t="s">
         <v>6</v>
       </c>
@@ -20393,7 +20394,7 @@
       <c r="U259" s="1"/>
       <c r="V259" s="1"/>
     </row>
-    <row r="260" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" s="1" t="s">
         <v>6</v>
       </c>
@@ -20445,7 +20446,7 @@
       <c r="U260" s="1"/>
       <c r="V260" s="1"/>
     </row>
-    <row r="261" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" s="1" t="s">
         <v>6</v>
       </c>
@@ -20499,7 +20500,7 @@
       <c r="U261" s="1"/>
       <c r="V261" s="1"/>
     </row>
-    <row r="262" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" s="1" t="s">
         <v>6</v>
       </c>
@@ -20551,7 +20552,7 @@
       <c r="U262" s="1"/>
       <c r="V262" s="1"/>
     </row>
-    <row r="263" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" s="1" t="s">
         <v>6</v>
       </c>
@@ -20603,7 +20604,7 @@
       <c r="U263" s="1"/>
       <c r="V263" s="1"/>
     </row>
-    <row r="264" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" s="1" t="s">
         <v>6</v>
       </c>
@@ -20655,7 +20656,7 @@
       <c r="U264" s="1"/>
       <c r="V264" s="1"/>
     </row>
-    <row r="265" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" s="1" t="s">
         <v>6</v>
       </c>
@@ -20707,7 +20708,7 @@
       <c r="U265" s="1"/>
       <c r="V265" s="1"/>
     </row>
-    <row r="266" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" s="1" t="s">
         <v>6</v>
       </c>
@@ -20759,7 +20760,7 @@
       <c r="U266" s="1"/>
       <c r="V266" s="1"/>
     </row>
-    <row r="267" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" s="1" t="s">
         <v>6</v>
       </c>
@@ -20811,7 +20812,7 @@
       <c r="U267" s="1"/>
       <c r="V267" s="1"/>
     </row>
-    <row r="268" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" s="1" t="s">
         <v>6</v>
       </c>
@@ -20865,7 +20866,7 @@
       <c r="U268" s="1"/>
       <c r="V268" s="1"/>
     </row>
-    <row r="269" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" s="1" t="s">
         <v>6</v>
       </c>
@@ -20917,7 +20918,7 @@
       <c r="U269" s="1"/>
       <c r="V269" s="1"/>
     </row>
-    <row r="270" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" s="1" t="s">
         <v>6</v>
       </c>
@@ -20969,7 +20970,7 @@
       <c r="U270" s="1"/>
       <c r="V270" s="1"/>
     </row>
-    <row r="271" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" s="1" t="s">
         <v>6</v>
       </c>
@@ -21021,7 +21022,7 @@
       <c r="U271" s="1"/>
       <c r="V271" s="1"/>
     </row>
-    <row r="272" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" s="1" t="s">
         <v>6</v>
       </c>
@@ -21075,7 +21076,7 @@
       <c r="U272" s="1"/>
       <c r="V272" s="1"/>
     </row>
-    <row r="273" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" s="1" t="s">
         <v>6</v>
       </c>
@@ -21129,7 +21130,7 @@
       <c r="U273" s="1"/>
       <c r="V273" s="1"/>
     </row>
-    <row r="274" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" s="1" t="s">
         <v>6</v>
       </c>
@@ -21183,7 +21184,7 @@
       <c r="U274" s="1"/>
       <c r="V274" s="1"/>
     </row>
-    <row r="275" spans="1:22" s="2" customFormat="1" ht="377" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:22" s="2" customFormat="1" ht="377" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" s="1" t="s">
         <v>6</v>
       </c>
@@ -21239,7 +21240,7 @@
       <c r="U275" s="1"/>
       <c r="V275" s="1"/>
     </row>
-    <row r="276" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" s="1" t="s">
         <v>6</v>
       </c>
@@ -21293,7 +21294,7 @@
       <c r="U276" s="1"/>
       <c r="V276" s="1"/>
     </row>
-    <row r="277" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" s="1" t="s">
         <v>6</v>
       </c>
@@ -21347,7 +21348,7 @@
       <c r="U277" s="1"/>
       <c r="V277" s="1"/>
     </row>
-    <row r="278" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" s="1" t="s">
         <v>6</v>
       </c>
@@ -21401,7 +21402,7 @@
       <c r="U278" s="1"/>
       <c r="V278" s="1"/>
     </row>
-    <row r="279" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" s="1" t="s">
         <v>6</v>
       </c>
@@ -21455,7 +21456,7 @@
       <c r="U279" s="1"/>
       <c r="V279" s="1"/>
     </row>
-    <row r="280" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" s="1" t="s">
         <v>6</v>
       </c>
@@ -21511,7 +21512,7 @@
       <c r="U280" s="1"/>
       <c r="V280" s="1"/>
     </row>
-    <row r="281" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" s="1" t="s">
         <v>6</v>
       </c>
@@ -21565,7 +21566,7 @@
       <c r="U281" s="1"/>
       <c r="V281" s="1"/>
     </row>
-    <row r="282" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" s="1" t="s">
         <v>6</v>
       </c>
@@ -21619,7 +21620,7 @@
       <c r="U282" s="1"/>
       <c r="V282" s="1"/>
     </row>
-    <row r="283" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" s="1" t="s">
         <v>6</v>
       </c>
@@ -21673,7 +21674,7 @@
       <c r="U283" s="1"/>
       <c r="V283" s="1"/>
     </row>
-    <row r="284" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" s="1" t="s">
         <v>6</v>
       </c>
@@ -21727,7 +21728,7 @@
       <c r="U284" s="1"/>
       <c r="V284" s="1"/>
     </row>
-    <row r="285" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" s="1" t="s">
         <v>6</v>
       </c>
@@ -21779,7 +21780,7 @@
       <c r="U285" s="1"/>
       <c r="V285" s="1"/>
     </row>
-    <row r="286" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" s="1" t="s">
         <v>6</v>
       </c>
@@ -21831,7 +21832,7 @@
       <c r="U286" s="1"/>
       <c r="V286" s="1"/>
     </row>
-    <row r="287" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" s="1" t="s">
         <v>6</v>
       </c>
@@ -21883,7 +21884,7 @@
       <c r="U287" s="1"/>
       <c r="V287" s="1"/>
     </row>
-    <row r="288" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" s="1" t="s">
         <v>6</v>
       </c>
@@ -21935,7 +21936,7 @@
       <c r="U288" s="1"/>
       <c r="V288" s="1"/>
     </row>
-    <row r="289" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" s="1" t="s">
         <v>6</v>
       </c>
@@ -21987,7 +21988,7 @@
       <c r="U289" s="1"/>
       <c r="V289" s="1"/>
     </row>
-    <row r="290" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" s="1" t="s">
         <v>6</v>
       </c>
@@ -22039,7 +22040,7 @@
       <c r="U290" s="1"/>
       <c r="V290" s="1"/>
     </row>
-    <row r="291" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" s="1" t="s">
         <v>6</v>
       </c>
@@ -22091,7 +22092,7 @@
       <c r="U291" s="1"/>
       <c r="V291" s="1"/>
     </row>
-    <row r="292" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" s="1" t="s">
         <v>6</v>
       </c>
@@ -22143,7 +22144,7 @@
       <c r="U292" s="1"/>
       <c r="V292" s="1"/>
     </row>
-    <row r="293" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" s="1" t="s">
         <v>6</v>
       </c>
@@ -22195,7 +22196,7 @@
       <c r="U293" s="1"/>
       <c r="V293" s="1"/>
     </row>
-    <row r="294" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" s="1" t="s">
         <v>6</v>
       </c>
@@ -22247,7 +22248,7 @@
       <c r="U294" s="1"/>
       <c r="V294" s="1"/>
     </row>
-    <row r="295" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" s="1" t="s">
         <v>6</v>
       </c>
@@ -22299,7 +22300,7 @@
       <c r="U295" s="1"/>
       <c r="V295" s="1"/>
     </row>
-    <row r="296" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" s="1" t="s">
         <v>6</v>
       </c>
@@ -22351,7 +22352,7 @@
       <c r="U296" s="1"/>
       <c r="V296" s="1"/>
     </row>
-    <row r="297" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" s="1" t="s">
         <v>6</v>
       </c>
@@ -22403,7 +22404,7 @@
       <c r="U297" s="1"/>
       <c r="V297" s="1"/>
     </row>
-    <row r="298" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" s="1" t="s">
         <v>6</v>
       </c>
@@ -22455,7 +22456,7 @@
       <c r="U298" s="1"/>
       <c r="V298" s="1"/>
     </row>
-    <row r="299" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" s="1" t="s">
         <v>6</v>
       </c>
@@ -22507,7 +22508,7 @@
       <c r="U299" s="1"/>
       <c r="V299" s="1"/>
     </row>
-    <row r="300" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" s="1" t="s">
         <v>6</v>
       </c>
@@ -22559,7 +22560,7 @@
       <c r="U300" s="1"/>
       <c r="V300" s="1"/>
     </row>
-    <row r="301" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" s="1" t="s">
         <v>6</v>
       </c>
@@ -22611,7 +22612,7 @@
       <c r="U301" s="1"/>
       <c r="V301" s="1"/>
     </row>
-    <row r="302" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" s="1" t="s">
         <v>6</v>
       </c>
@@ -22663,7 +22664,7 @@
       <c r="U302" s="1"/>
       <c r="V302" s="1"/>
     </row>
-    <row r="303" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" s="1" t="s">
         <v>6</v>
       </c>
@@ -22717,7 +22718,7 @@
       <c r="U303" s="1"/>
       <c r="V303" s="1"/>
     </row>
-    <row r="304" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" s="1" t="s">
         <v>6</v>
       </c>
@@ -22769,7 +22770,7 @@
       <c r="U304" s="1"/>
       <c r="V304" s="1"/>
     </row>
-    <row r="305" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" s="1" t="s">
         <v>6</v>
       </c>
@@ -22821,7 +22822,7 @@
       <c r="U305" s="1"/>
       <c r="V305" s="1"/>
     </row>
-    <row r="306" spans="1:22" s="2" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:22" s="2" customFormat="1" ht="76.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="1" t="s">
         <v>6</v>
       </c>
@@ -22873,7 +22874,7 @@
       <c r="U306" s="1"/>
       <c r="V306" s="1"/>
     </row>
-    <row r="307" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" s="1" t="s">
         <v>6</v>
       </c>
@@ -22925,7 +22926,7 @@
       <c r="U307" s="1"/>
       <c r="V307" s="1"/>
     </row>
-    <row r="308" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" s="1" t="s">
         <v>6</v>
       </c>
@@ -22977,7 +22978,7 @@
       <c r="U308" s="1"/>
       <c r="V308" s="1"/>
     </row>
-    <row r="309" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" s="1" t="s">
         <v>6</v>
       </c>
@@ -23029,7 +23030,7 @@
       <c r="U309" s="1"/>
       <c r="V309" s="1"/>
     </row>
-    <row r="310" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" s="1" t="s">
         <v>6</v>
       </c>
@@ -23081,7 +23082,7 @@
       <c r="U310" s="1"/>
       <c r="V310" s="1"/>
     </row>
-    <row r="311" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" s="1" t="s">
         <v>6</v>
       </c>
@@ -23133,7 +23134,7 @@
       <c r="U311" s="1"/>
       <c r="V311" s="1"/>
     </row>
-    <row r="312" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" s="1" t="s">
         <v>6</v>
       </c>
@@ -23185,7 +23186,7 @@
       <c r="U312" s="1"/>
       <c r="V312" s="1"/>
     </row>
-    <row r="313" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" s="1" t="s">
         <v>6</v>
       </c>
@@ -23237,7 +23238,7 @@
       <c r="U313" s="1"/>
       <c r="V313" s="1"/>
     </row>
-    <row r="314" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" s="1" t="s">
         <v>6</v>
       </c>
@@ -23293,7 +23294,7 @@
       <c r="U314" s="1"/>
       <c r="V314" s="1"/>
     </row>
-    <row r="315" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" s="1" t="s">
         <v>6</v>
       </c>
@@ -23351,7 +23352,7 @@
       <c r="U315" s="1"/>
       <c r="V315" s="1"/>
     </row>
-    <row r="316" spans="1:22" ht="87" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:22" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" s="1" t="s">
         <v>6</v>
       </c>
@@ -23407,7 +23408,7 @@
       <c r="U316" s="1"/>
       <c r="V316" s="1"/>
     </row>
-    <row r="317" spans="1:22" ht="87" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:22" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" s="1" t="s">
         <v>6</v>
       </c>
@@ -23461,7 +23462,7 @@
       <c r="U317" s="1"/>
       <c r="V317" s="1"/>
     </row>
-    <row r="318" spans="1:22" ht="87" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:22" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" s="1" t="s">
         <v>6</v>
       </c>
@@ -23511,7 +23512,7 @@
       <c r="U318" s="1"/>
       <c r="V318" s="1"/>
     </row>
-    <row r="319" spans="1:22" ht="87" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:22" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" s="1" t="s">
         <v>6</v>
       </c>
@@ -23567,7 +23568,7 @@
       <c r="U319" s="1"/>
       <c r="V319" s="1"/>
     </row>
-    <row r="320" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" s="1" t="s">
         <v>6</v>
       </c>
@@ -23619,7 +23620,7 @@
       <c r="U320" s="1"/>
       <c r="V320" s="1"/>
     </row>
-    <row r="321" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:22" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" s="1" t="s">
         <v>6</v>
       </c>
@@ -23673,7 +23674,7 @@
       <c r="U321" s="1"/>
       <c r="V321" s="1"/>
     </row>
-    <row r="322" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:22" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" s="1" t="s">
         <v>6</v>
       </c>
@@ -23725,7 +23726,7 @@
       <c r="U322" s="1"/>
       <c r="V322" s="1"/>
     </row>
-    <row r="323" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:22" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" s="1" t="s">
         <v>6</v>
       </c>
@@ -23781,7 +23782,7 @@
       <c r="U323" s="1"/>
       <c r="V323" s="1"/>
     </row>
-    <row r="324" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" s="1" t="s">
         <v>6</v>
       </c>
@@ -23833,7 +23834,7 @@
       <c r="U324" s="1"/>
       <c r="V324" s="1"/>
     </row>
-    <row r="325" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" s="1" t="s">
         <v>6</v>
       </c>
@@ -23885,7 +23886,7 @@
       <c r="U325" s="1"/>
       <c r="V325" s="1"/>
     </row>
-    <row r="326" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" s="1" t="s">
         <v>6</v>
       </c>
@@ -23937,7 +23938,7 @@
       <c r="U326" s="1"/>
       <c r="V326" s="1"/>
     </row>
-    <row r="327" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:22" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" s="1" t="s">
         <v>6</v>
       </c>
@@ -23989,7 +23990,7 @@
       <c r="U327" s="1"/>
       <c r="V327" s="1"/>
     </row>
-    <row r="328" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:22" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" s="1" t="s">
         <v>6</v>
       </c>
@@ -24041,7 +24042,7 @@
       <c r="U328" s="1"/>
       <c r="V328" s="1"/>
     </row>
-    <row r="329" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:22" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" s="1" t="s">
         <v>6</v>
       </c>
@@ -24093,7 +24094,7 @@
       <c r="U329" s="1"/>
       <c r="V329" s="1"/>
     </row>
-    <row r="330" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" s="1" t="s">
         <v>6</v>
       </c>
@@ -24145,7 +24146,7 @@
       <c r="U330" s="1"/>
       <c r="V330" s="1"/>
     </row>
-    <row r="331" spans="1:22" ht="58" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:22" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" s="1" t="s">
         <v>6</v>
       </c>
@@ -24197,7 +24198,7 @@
       <c r="U331" s="1"/>
       <c r="V331" s="1"/>
     </row>
-    <row r="332" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" s="1" t="s">
         <v>6</v>
       </c>
@@ -24251,7 +24252,7 @@
       <c r="U332" s="1"/>
       <c r="V332" s="1"/>
     </row>
-    <row r="333" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" s="1" t="s">
         <v>6</v>
       </c>
@@ -24305,7 +24306,7 @@
       <c r="U333" s="1"/>
       <c r="V333" s="1"/>
     </row>
-    <row r="334" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" s="1" t="s">
         <v>6</v>
       </c>
@@ -24359,7 +24360,7 @@
       <c r="U334" s="1"/>
       <c r="V334" s="1"/>
     </row>
-    <row r="335" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" s="1" t="s">
         <v>6</v>
       </c>
@@ -24411,7 +24412,7 @@
       <c r="U335" s="1"/>
       <c r="V335" s="1"/>
     </row>
-    <row r="336" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" s="1" t="s">
         <v>6</v>
       </c>
@@ -24463,7 +24464,7 @@
       <c r="U336" s="1"/>
       <c r="V336" s="1"/>
     </row>
-    <row r="337" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" s="1" t="s">
         <v>6</v>
       </c>
@@ -24515,7 +24516,7 @@
       <c r="U337" s="1"/>
       <c r="V337" s="1"/>
     </row>
-    <row r="338" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" s="1" t="s">
         <v>6</v>
       </c>
@@ -24569,7 +24570,7 @@
       <c r="U338" s="1"/>
       <c r="V338" s="1"/>
     </row>
-    <row r="339" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" s="1" t="s">
         <v>6</v>
       </c>
@@ -24621,7 +24622,7 @@
       <c r="U339" s="1"/>
       <c r="V339" s="1"/>
     </row>
-    <row r="340" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" s="1" t="s">
         <v>6</v>
       </c>
@@ -24673,7 +24674,7 @@
       <c r="U340" s="1"/>
       <c r="V340" s="1"/>
     </row>
-    <row r="341" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" s="1" t="s">
         <v>6</v>
       </c>
@@ -24725,7 +24726,7 @@
       <c r="U341" s="1"/>
       <c r="V341" s="1"/>
     </row>
-    <row r="342" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" s="1" t="s">
         <v>6</v>
       </c>
@@ -24779,7 +24780,7 @@
       <c r="U342" s="1"/>
       <c r="V342" s="1"/>
     </row>
-    <row r="343" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" s="1" t="s">
         <v>6</v>
       </c>
@@ -24833,7 +24834,7 @@
       <c r="U343" s="1"/>
       <c r="V343" s="1"/>
     </row>
-    <row r="344" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" s="1" t="s">
         <v>6</v>
       </c>
@@ -24885,7 +24886,7 @@
       <c r="U344" s="1"/>
       <c r="V344" s="1"/>
     </row>
-    <row r="345" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" s="1" t="s">
         <v>6</v>
       </c>
@@ -24937,7 +24938,7 @@
       <c r="U345" s="1"/>
       <c r="V345" s="1"/>
     </row>
-    <row r="346" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" s="1" t="s">
         <v>6</v>
       </c>
@@ -24989,7 +24990,7 @@
       <c r="U346" s="1"/>
       <c r="V346" s="1"/>
     </row>
-    <row r="347" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" s="1" t="s">
         <v>6</v>
       </c>
@@ -25043,7 +25044,7 @@
       <c r="U347" s="1"/>
       <c r="V347" s="1"/>
     </row>
-    <row r="348" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" s="1" t="s">
         <v>6</v>
       </c>
@@ -25095,7 +25096,7 @@
       <c r="U348" s="1"/>
       <c r="V348" s="1"/>
     </row>
-    <row r="349" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" s="1" t="s">
         <v>6</v>
       </c>
@@ -25149,7 +25150,7 @@
       <c r="U349" s="1"/>
       <c r="V349" s="1"/>
     </row>
-    <row r="350" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" s="1" t="s">
         <v>6</v>
       </c>
@@ -25201,7 +25202,7 @@
       <c r="U350" s="1"/>
       <c r="V350" s="1"/>
     </row>
-    <row r="351" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" s="1" t="s">
         <v>6</v>
       </c>
@@ -25253,7 +25254,7 @@
       <c r="U351" s="1"/>
       <c r="V351" s="1"/>
     </row>
-    <row r="352" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" s="1" t="s">
         <v>6</v>
       </c>
@@ -25307,7 +25308,7 @@
       <c r="U352" s="1"/>
       <c r="V352" s="1"/>
     </row>
-    <row r="353" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" s="1" t="s">
         <v>6</v>
       </c>
@@ -25357,7 +25358,7 @@
       <c r="U353" s="1"/>
       <c r="V353" s="1"/>
     </row>
-    <row r="354" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" s="1" t="s">
         <v>6</v>
       </c>
@@ -25407,7 +25408,7 @@
       <c r="U354" s="1"/>
       <c r="V354" s="1"/>
     </row>
-    <row r="355" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" s="1" t="s">
         <v>6</v>
       </c>
@@ -25459,7 +25460,7 @@
       <c r="U355" s="1"/>
       <c r="V355" s="1"/>
     </row>
-    <row r="356" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" s="1" t="s">
         <v>6</v>
       </c>
@@ -25511,7 +25512,7 @@
       <c r="U356" s="1"/>
       <c r="V356" s="1"/>
     </row>
-    <row r="357" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" s="1" t="s">
         <v>6</v>
       </c>
@@ -25563,7 +25564,7 @@
       <c r="U357" s="1"/>
       <c r="V357" s="1"/>
     </row>
-    <row r="358" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" s="1" t="s">
         <v>6</v>
       </c>
@@ -25615,7 +25616,7 @@
       <c r="U358" s="1"/>
       <c r="V358" s="1"/>
     </row>
-    <row r="359" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" s="1" t="s">
         <v>6</v>
       </c>
@@ -25669,7 +25670,7 @@
       <c r="U359" s="1"/>
       <c r="V359" s="1"/>
     </row>
-    <row r="360" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" s="1" t="s">
         <v>6</v>
       </c>
@@ -25721,7 +25722,7 @@
       <c r="U360" s="1"/>
       <c r="V360" s="1"/>
     </row>
-    <row r="361" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" s="1" t="s">
         <v>6</v>
       </c>
@@ -25773,7 +25774,7 @@
       <c r="U361" s="1"/>
       <c r="V361" s="1"/>
     </row>
-    <row r="362" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" s="1" t="s">
         <v>6</v>
       </c>
@@ -25825,7 +25826,7 @@
       <c r="U362" s="1"/>
       <c r="V362" s="1"/>
     </row>
-    <row r="363" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" s="1" t="s">
         <v>6</v>
       </c>
@@ -25879,7 +25880,7 @@
       <c r="U363" s="1"/>
       <c r="V363" s="1"/>
     </row>
-    <row r="364" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" s="1" t="s">
         <v>6</v>
       </c>
@@ -25931,7 +25932,7 @@
       <c r="U364" s="1"/>
       <c r="V364" s="1"/>
     </row>
-    <row r="365" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" s="1" t="s">
         <v>6</v>
       </c>
@@ -25983,7 +25984,7 @@
       <c r="U365" s="1"/>
       <c r="V365" s="1"/>
     </row>
-    <row r="366" spans="1:22" s="2" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:22" s="2" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" s="1" t="s">
         <v>6</v>
       </c>
@@ -26035,7 +26036,7 @@
       <c r="U366" s="1"/>
       <c r="V366" s="1"/>
     </row>
-    <row r="367" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" s="1" t="s">
         <v>6</v>
       </c>
@@ -26087,7 +26088,7 @@
       <c r="U367" s="1"/>
       <c r="V367" s="1"/>
     </row>
-    <row r="368" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" s="1" t="s">
         <v>6</v>
       </c>
@@ -26139,7 +26140,7 @@
       <c r="U368" s="1"/>
       <c r="V368" s="1"/>
     </row>
-    <row r="369" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" s="1" t="s">
         <v>6</v>
       </c>
@@ -26191,7 +26192,7 @@
       <c r="U369" s="1"/>
       <c r="V369" s="1"/>
     </row>
-    <row r="370" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" s="1" t="s">
         <v>6</v>
       </c>
@@ -26245,7 +26246,7 @@
       <c r="U370" s="1"/>
       <c r="V370" s="1"/>
     </row>
-    <row r="371" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371" s="1" t="s">
         <v>6</v>
       </c>
@@ -26297,7 +26298,7 @@
       <c r="U371" s="1"/>
       <c r="V371" s="1"/>
     </row>
-    <row r="372" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" s="1" t="s">
         <v>6</v>
       </c>
@@ -26349,7 +26350,7 @@
       <c r="U372" s="1"/>
       <c r="V372" s="1"/>
     </row>
-    <row r="373" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" s="1" t="s">
         <v>6</v>
       </c>
@@ -26401,7 +26402,7 @@
       <c r="U373" s="1"/>
       <c r="V373" s="1"/>
     </row>
-    <row r="374" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" s="1" t="s">
         <v>6</v>
       </c>
@@ -26455,7 +26456,7 @@
       <c r="U374" s="1"/>
       <c r="V374" s="1"/>
     </row>
-    <row r="375" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375" s="1" t="s">
         <v>6</v>
       </c>
@@ -26509,7 +26510,7 @@
       <c r="U375" s="1"/>
       <c r="V375" s="1"/>
     </row>
-    <row r="376" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" s="1" t="s">
         <v>6</v>
       </c>
@@ -26565,7 +26566,7 @@
       <c r="U376" s="1"/>
       <c r="V376" s="1"/>
     </row>
-    <row r="377" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" s="1" t="s">
         <v>6</v>
       </c>
@@ -26619,7 +26620,7 @@
       <c r="U377" s="1"/>
       <c r="V377" s="1"/>
     </row>
-    <row r="378" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" s="1" t="s">
         <v>6</v>
       </c>
@@ -26673,7 +26674,7 @@
       <c r="U378" s="1"/>
       <c r="V378" s="1"/>
     </row>
-    <row r="379" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" s="1" t="s">
         <v>6</v>
       </c>
@@ -26729,7 +26730,7 @@
       <c r="U379" s="1"/>
       <c r="V379" s="1"/>
     </row>
-    <row r="380" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" s="1" t="s">
         <v>6</v>
       </c>
@@ -26785,7 +26786,7 @@
       <c r="U380" s="1"/>
       <c r="V380" s="1"/>
     </row>
-    <row r="381" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" s="1" t="s">
         <v>6</v>
       </c>
@@ -26839,7 +26840,7 @@
       <c r="U381" s="1"/>
       <c r="V381" s="1"/>
     </row>
-    <row r="382" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" s="1" t="s">
         <v>6</v>
       </c>
@@ -26895,7 +26896,7 @@
       <c r="U382" s="1"/>
       <c r="V382" s="1"/>
     </row>
-    <row r="383" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" s="1" t="s">
         <v>6</v>
       </c>
@@ -26949,7 +26950,7 @@
       <c r="U383" s="1"/>
       <c r="V383" s="1"/>
     </row>
-    <row r="384" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" s="1" t="s">
         <v>6</v>
       </c>
@@ -27001,7 +27002,7 @@
       <c r="U384" s="1"/>
       <c r="V384" s="1"/>
     </row>
-    <row r="385" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A385" s="1" t="s">
         <v>6</v>
       </c>
@@ -27055,7 +27056,7 @@
       <c r="U385" s="1"/>
       <c r="V385" s="1"/>
     </row>
-    <row r="386" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" s="1" t="s">
         <v>6</v>
       </c>
@@ -27111,7 +27112,7 @@
       <c r="U386" s="1"/>
       <c r="V386" s="1"/>
     </row>
-    <row r="387" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387" s="1" t="s">
         <v>6</v>
       </c>
@@ -27165,7 +27166,7 @@
       <c r="U387" s="1"/>
       <c r="V387" s="1"/>
     </row>
-    <row r="388" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A388" s="1" t="s">
         <v>6</v>
       </c>
@@ -27219,7 +27220,7 @@
       <c r="U388" s="1"/>
       <c r="V388" s="1"/>
     </row>
-    <row r="389" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A389" s="1" t="s">
         <v>6</v>
       </c>
@@ -27273,7 +27274,7 @@
       <c r="U389" s="1"/>
       <c r="V389" s="1"/>
     </row>
-    <row r="390" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A390" s="1" t="s">
         <v>6</v>
       </c>
@@ -27327,7 +27328,7 @@
       <c r="U390" s="1"/>
       <c r="V390" s="1"/>
     </row>
-    <row r="391" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A391" s="1" t="s">
         <v>6</v>
       </c>
@@ -27383,7 +27384,7 @@
       <c r="U391" s="1"/>
       <c r="V391" s="1"/>
     </row>
-    <row r="392" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A392" s="1" t="s">
         <v>6</v>
       </c>
@@ -27437,7 +27438,7 @@
       <c r="U392" s="1"/>
       <c r="V392" s="1"/>
     </row>
-    <row r="393" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393" s="1" t="s">
         <v>6</v>
       </c>
@@ -27491,7 +27492,7 @@
       <c r="U393" s="1"/>
       <c r="V393" s="1"/>
     </row>
-    <row r="394" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394" s="1" t="s">
         <v>6</v>
       </c>
@@ -27545,7 +27546,7 @@
       <c r="U394" s="1"/>
       <c r="V394" s="1"/>
     </row>
-    <row r="395" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" s="1" t="s">
         <v>6</v>
       </c>
@@ -27599,7 +27600,7 @@
       <c r="U395" s="1"/>
       <c r="V395" s="1"/>
     </row>
-    <row r="396" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A396" s="1" t="s">
         <v>6</v>
       </c>
@@ -27655,7 +27656,7 @@
       <c r="U396" s="1"/>
       <c r="V396" s="1"/>
     </row>
-    <row r="397" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A397" s="1" t="s">
         <v>6</v>
       </c>
@@ -27711,7 +27712,7 @@
       <c r="U397" s="1"/>
       <c r="V397" s="1"/>
     </row>
-    <row r="398" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A398" s="1" t="s">
         <v>6</v>
       </c>
@@ -27765,7 +27766,7 @@
       <c r="U398" s="1"/>
       <c r="V398" s="1"/>
     </row>
-    <row r="399" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" s="1" t="s">
         <v>6</v>
       </c>
@@ -27819,7 +27820,7 @@
       <c r="U399" s="1"/>
       <c r="V399" s="1"/>
     </row>
-    <row r="400" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" s="1" t="s">
         <v>6</v>
       </c>
@@ -27875,7 +27876,7 @@
       <c r="U400" s="1"/>
       <c r="V400" s="1"/>
     </row>
-    <row r="401" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" s="1" t="s">
         <v>6</v>
       </c>
@@ -27929,7 +27930,7 @@
       <c r="U401" s="1"/>
       <c r="V401" s="1"/>
     </row>
-    <row r="402" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" s="1" t="s">
         <v>6</v>
       </c>
@@ -27983,7 +27984,7 @@
       <c r="U402" s="1"/>
       <c r="V402" s="1"/>
     </row>
-    <row r="403" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A403" s="1" t="s">
         <v>6</v>
       </c>
@@ -28037,7 +28038,7 @@
       <c r="U403" s="1"/>
       <c r="V403" s="1"/>
     </row>
-    <row r="404" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:22" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A404" s="1" t="s">
         <v>6</v>
       </c>
@@ -28091,7 +28092,7 @@
       <c r="U404" s="1"/>
       <c r="V404" s="1"/>
     </row>
-    <row r="405" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A405" s="1" t="s">
         <v>6</v>
       </c>
@@ -28145,7 +28146,7 @@
       <c r="U405" s="1"/>
       <c r="V405" s="1"/>
     </row>
-    <row r="406" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406" s="1" t="s">
         <v>6</v>
       </c>
@@ -28199,7 +28200,7 @@
       <c r="U406" s="1"/>
       <c r="V406" s="1"/>
     </row>
-    <row r="407" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A407" s="1" t="s">
         <v>6</v>
       </c>
@@ -28253,7 +28254,7 @@
       <c r="U407" s="1"/>
       <c r="V407" s="1"/>
     </row>
-    <row r="408" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A408" s="1" t="s">
         <v>6</v>
       </c>
@@ -28307,7 +28308,7 @@
       <c r="U408" s="1"/>
       <c r="V408" s="1"/>
     </row>
-    <row r="409" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A409" s="1" t="s">
         <v>6</v>
       </c>
@@ -28361,7 +28362,7 @@
       <c r="U409" s="1"/>
       <c r="V409" s="1"/>
     </row>
-    <row r="410" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" s="1" t="s">
         <v>6</v>
       </c>
@@ -28415,7 +28416,7 @@
       <c r="U410" s="1"/>
       <c r="V410" s="1"/>
     </row>
-    <row r="411" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411" s="1" t="s">
         <v>6</v>
       </c>
@@ -28469,7 +28470,7 @@
       <c r="U411" s="1"/>
       <c r="V411" s="1"/>
     </row>
-    <row r="412" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" s="1" t="s">
         <v>6</v>
       </c>
@@ -28523,7 +28524,7 @@
       <c r="U412" s="1"/>
       <c r="V412" s="1"/>
     </row>
-    <row r="413" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" s="1" t="s">
         <v>6</v>
       </c>
@@ -28575,7 +28576,7 @@
       <c r="U413" s="1"/>
       <c r="V413" s="1"/>
     </row>
-    <row r="414" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414" s="1" t="s">
         <v>6</v>
       </c>
@@ -28627,7 +28628,7 @@
       <c r="U414" s="1"/>
       <c r="V414" s="1"/>
     </row>
-    <row r="415" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415" s="1" t="s">
         <v>6</v>
       </c>
@@ -28679,7 +28680,7 @@
       <c r="U415" s="1"/>
       <c r="V415" s="1"/>
     </row>
-    <row r="416" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:22" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416" s="1" t="s">
         <v>6</v>
       </c>
@@ -28731,7 +28732,7 @@
       <c r="U416" s="1"/>
       <c r="V416" s="1"/>
     </row>
-    <row r="417" spans="1:22" ht="58" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:22" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417" s="1" t="s">
         <v>6</v>
       </c>
@@ -28785,7 +28786,7 @@
       <c r="U417" s="1"/>
       <c r="V417" s="1"/>
     </row>
-    <row r="418" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A418" s="1" t="s">
         <v>6</v>
       </c>
@@ -28839,7 +28840,7 @@
       <c r="U418" s="1"/>
       <c r="V418" s="1"/>
     </row>
-    <row r="419" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
       <c r="A419" s="1" t="s">
         <v>6</v>
       </c>
@@ -29039,7 +29040,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V419" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:V419" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Philippe Ciais"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L229">
     <sortCondition ref="C2:C424"/>
   </sortState>

--- a/Data/FairCarboN_Datas_Contacts.xlsx
+++ b/Data/FairCarboN_Datas_Contacts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D87CDB89-D825-4788-8395-EB9D8789BBAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCEAADA-B3E8-4D79-92A3-240B48ACC832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6316,22 +6316,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:V719"/>
+  <dimension ref="A1:V419"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.54296875" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.453125" style="35" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.453125" style="35" customWidth="1"/>
-    <col min="4" max="4" width="46.81640625" style="27" hidden="1" customWidth="1"/>
-    <col min="5" max="6" width="16.7265625" style="35" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="16.7265625" style="7" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="27.1796875" style="7" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="27.81640625" style="35" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="12" style="7" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="12.26953125" style="7" hidden="1" customWidth="1"/>
-    <col min="12" max="13" width="22.90625" style="7" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="22.90625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="46.81640625" style="27" customWidth="1"/>
+    <col min="5" max="6" width="16.7265625" style="35" customWidth="1"/>
+    <col min="7" max="7" width="16.7265625" style="7" customWidth="1"/>
+    <col min="8" max="8" width="27.1796875" style="7" customWidth="1"/>
+    <col min="9" max="9" width="27.81640625" style="35" customWidth="1"/>
+    <col min="10" max="10" width="12" style="7" customWidth="1"/>
+    <col min="11" max="11" width="12.26953125" style="7" customWidth="1"/>
+    <col min="12" max="14" width="22.90625" style="7" customWidth="1"/>
     <col min="15" max="15" width="22.90625" style="54" customWidth="1"/>
     <col min="16" max="17" width="48.7265625" style="7" customWidth="1"/>
     <col min="18" max="18" width="17.36328125" style="7" customWidth="1"/>
@@ -6410,7 +6408,7 @@
         <v>1761</v>
       </c>
     </row>
-    <row r="2" spans="1:22" s="2" customFormat="1" ht="188.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" s="2" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -6464,7 +6462,7 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
     </row>
-    <row r="3" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -6518,7 +6516,7 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
     </row>
-    <row r="4" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -6572,7 +6570,7 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
     </row>
-    <row r="5" spans="1:22" s="2" customFormat="1" ht="188.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" s="2" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -6626,7 +6624,7 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
     </row>
-    <row r="6" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -6682,7 +6680,7 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
     </row>
-    <row r="7" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -6738,7 +6736,7 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
     </row>
-    <row r="8" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -6792,7 +6790,7 @@
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
     </row>
-    <row r="9" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -6846,7 +6844,7 @@
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
     </row>
-    <row r="10" spans="1:22" s="2" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" s="2" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -6900,7 +6898,7 @@
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
     </row>
-    <row r="11" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
@@ -6954,7 +6952,7 @@
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
     </row>
-    <row r="12" spans="1:22" s="2" customFormat="1" ht="188.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" s="2" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
@@ -7008,7 +7006,7 @@
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
     </row>
-    <row r="13" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
@@ -7062,7 +7060,7 @@
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
     </row>
-    <row r="14" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>6</v>
       </c>
@@ -7116,7 +7114,7 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
     </row>
-    <row r="15" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>6</v>
       </c>
@@ -7172,7 +7170,7 @@
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
     </row>
-    <row r="16" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>6</v>
       </c>
@@ -7226,7 +7224,7 @@
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
     </row>
-    <row r="17" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>6</v>
       </c>
@@ -7282,7 +7280,7 @@
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
     </row>
-    <row r="18" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>6</v>
       </c>
@@ -7336,7 +7334,7 @@
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
     </row>
-    <row r="19" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>6</v>
       </c>
@@ -7390,7 +7388,7 @@
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
     </row>
-    <row r="20" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>6</v>
       </c>
@@ -7444,7 +7442,7 @@
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
     </row>
-    <row r="21" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>6</v>
       </c>
@@ -7498,7 +7496,7 @@
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
     </row>
-    <row r="22" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>6</v>
       </c>
@@ -7552,7 +7550,7 @@
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
     </row>
-    <row r="23" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>6</v>
       </c>
@@ -7606,7 +7604,7 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
     </row>
-    <row r="24" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>6</v>
       </c>
@@ -7660,7 +7658,7 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
     </row>
-    <row r="25" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>6</v>
       </c>
@@ -7716,7 +7714,7 @@
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
     </row>
-    <row r="26" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>6</v>
       </c>
@@ -7770,7 +7768,7 @@
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
     </row>
-    <row r="27" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>6</v>
       </c>
@@ -7824,7 +7822,7 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
     </row>
-    <row r="28" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>6</v>
       </c>
@@ -7878,7 +7876,7 @@
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
     </row>
-    <row r="29" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>6</v>
       </c>
@@ -7932,7 +7930,7 @@
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
     </row>
-    <row r="30" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>6</v>
       </c>
@@ -7986,7 +7984,7 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
     </row>
-    <row r="31" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>6</v>
       </c>
@@ -8040,7 +8038,7 @@
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
     </row>
-    <row r="32" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>6</v>
       </c>
@@ -8096,7 +8094,7 @@
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
     </row>
-    <row r="33" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>6</v>
       </c>
@@ -8150,7 +8148,7 @@
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
     </row>
-    <row r="34" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>6</v>
       </c>
@@ -8204,7 +8202,7 @@
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
     </row>
-    <row r="35" spans="1:22" s="2" customFormat="1" ht="232" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:22" s="2" customFormat="1" ht="232" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>6</v>
       </c>
@@ -8260,7 +8258,7 @@
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
     </row>
-    <row r="36" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>6</v>
       </c>
@@ -8314,7 +8312,7 @@
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
     </row>
-    <row r="37" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>6</v>
       </c>
@@ -8368,7 +8366,7 @@
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
     </row>
-    <row r="38" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>6</v>
       </c>
@@ -8422,7 +8420,7 @@
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
     </row>
-    <row r="39" spans="1:22" s="2" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:22" s="2" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>6</v>
       </c>
@@ -8476,7 +8474,7 @@
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
     </row>
-    <row r="40" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>6</v>
       </c>
@@ -8530,7 +8528,7 @@
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
     </row>
-    <row r="41" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>6</v>
       </c>
@@ -8584,7 +8582,7 @@
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
     </row>
-    <row r="42" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>6</v>
       </c>
@@ -8638,7 +8636,7 @@
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
     </row>
-    <row r="43" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>6</v>
       </c>
@@ -8692,7 +8690,7 @@
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
     </row>
-    <row r="44" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>6</v>
       </c>
@@ -8746,7 +8744,7 @@
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
     </row>
-    <row r="45" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>6</v>
       </c>
@@ -8800,7 +8798,7 @@
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
     </row>
-    <row r="46" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>6</v>
       </c>
@@ -8854,7 +8852,7 @@
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
     </row>
-    <row r="47" spans="1:22" s="2" customFormat="1" ht="275.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:22" s="2" customFormat="1" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>6</v>
       </c>
@@ -8912,7 +8910,7 @@
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
     </row>
-    <row r="48" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>6</v>
       </c>
@@ -8966,7 +8964,7 @@
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
     </row>
-    <row r="49" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>6</v>
       </c>
@@ -9022,7 +9020,7 @@
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
     </row>
-    <row r="50" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>6</v>
       </c>
@@ -9076,7 +9074,7 @@
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
     </row>
-    <row r="51" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>6</v>
       </c>
@@ -9130,7 +9128,7 @@
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
     </row>
-    <row r="52" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>6</v>
       </c>
@@ -9184,7 +9182,7 @@
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
     </row>
-    <row r="53" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>6</v>
       </c>
@@ -9238,7 +9236,7 @@
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
     </row>
-    <row r="54" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>6</v>
       </c>
@@ -9292,7 +9290,7 @@
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
     </row>
-    <row r="55" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>6</v>
       </c>
@@ -9346,7 +9344,7 @@
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
     </row>
-    <row r="56" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>6</v>
       </c>
@@ -9400,7 +9398,7 @@
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
     </row>
-    <row r="57" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>6</v>
       </c>
@@ -9454,7 +9452,7 @@
       <c r="U57" s="1"/>
       <c r="V57" s="1"/>
     </row>
-    <row r="58" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>6</v>
       </c>
@@ -9508,7 +9506,7 @@
       <c r="U58" s="1"/>
       <c r="V58" s="1"/>
     </row>
-    <row r="59" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>6</v>
       </c>
@@ -9564,7 +9562,7 @@
       <c r="U59" s="1"/>
       <c r="V59" s="1"/>
     </row>
-    <row r="60" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>6</v>
       </c>
@@ -9620,7 +9618,7 @@
       <c r="U60" s="1"/>
       <c r="V60" s="1"/>
     </row>
-    <row r="61" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>6</v>
       </c>
@@ -9676,7 +9674,7 @@
       <c r="U61" s="1"/>
       <c r="V61" s="1"/>
     </row>
-    <row r="62" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>6</v>
       </c>
@@ -9732,7 +9730,7 @@
       <c r="U62" s="1"/>
       <c r="V62" s="1"/>
     </row>
-    <row r="63" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>6</v>
       </c>
@@ -9786,7 +9784,7 @@
       <c r="U63" s="1"/>
       <c r="V63" s="1"/>
     </row>
-    <row r="64" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>6</v>
       </c>
@@ -9842,7 +9840,7 @@
       <c r="U64" s="1"/>
       <c r="V64" s="1"/>
     </row>
-    <row r="65" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>6</v>
       </c>
@@ -9954,7 +9952,7 @@
       <c r="U66" s="1"/>
       <c r="V66" s="1"/>
     </row>
-    <row r="67" spans="1:22" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>6</v>
       </c>
@@ -10008,7 +10006,7 @@
       <c r="U67" s="1"/>
       <c r="V67" s="1"/>
     </row>
-    <row r="68" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>6</v>
       </c>
@@ -10064,7 +10062,7 @@
       <c r="U68" s="1"/>
       <c r="V68" s="1"/>
     </row>
-    <row r="69" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>6</v>
       </c>
@@ -10118,7 +10116,7 @@
       <c r="U69" s="1"/>
       <c r="V69" s="1"/>
     </row>
-    <row r="70" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>6</v>
       </c>
@@ -10172,7 +10170,7 @@
       <c r="U70" s="1"/>
       <c r="V70" s="1"/>
     </row>
-    <row r="71" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>6</v>
       </c>
@@ -10226,7 +10224,7 @@
       <c r="U71" s="1"/>
       <c r="V71" s="1"/>
     </row>
-    <row r="72" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>6</v>
       </c>
@@ -10280,7 +10278,7 @@
       <c r="U72" s="1"/>
       <c r="V72" s="1"/>
     </row>
-    <row r="73" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>6</v>
       </c>
@@ -10334,7 +10332,7 @@
       <c r="U73" s="1"/>
       <c r="V73" s="1"/>
     </row>
-    <row r="74" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>6</v>
       </c>
@@ -10388,7 +10386,7 @@
       <c r="U74" s="1"/>
       <c r="V74" s="1"/>
     </row>
-    <row r="75" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>6</v>
       </c>
@@ -10442,7 +10440,7 @@
       <c r="U75" s="1"/>
       <c r="V75" s="1"/>
     </row>
-    <row r="76" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>6</v>
       </c>
@@ -10496,7 +10494,7 @@
       <c r="U76" s="1"/>
       <c r="V76" s="1"/>
     </row>
-    <row r="77" spans="1:22" s="2" customFormat="1" ht="27.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:22" s="2" customFormat="1" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>6</v>
       </c>
@@ -10552,7 +10550,7 @@
       <c r="U77" s="1"/>
       <c r="V77" s="1"/>
     </row>
-    <row r="78" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>6</v>
       </c>
@@ -10606,7 +10604,7 @@
       <c r="U78" s="1"/>
       <c r="V78" s="1"/>
     </row>
-    <row r="79" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>6</v>
       </c>
@@ -10660,7 +10658,7 @@
       <c r="U79" s="1"/>
       <c r="V79" s="1"/>
     </row>
-    <row r="80" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>6</v>
       </c>
@@ -10714,7 +10712,7 @@
       <c r="U80" s="1"/>
       <c r="V80" s="1"/>
     </row>
-    <row r="81" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>6</v>
       </c>
@@ -10770,7 +10768,7 @@
       <c r="U81" s="1"/>
       <c r="V81" s="1"/>
     </row>
-    <row r="82" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>6</v>
       </c>
@@ -10824,7 +10822,7 @@
       <c r="U82" s="1"/>
       <c r="V82" s="1"/>
     </row>
-    <row r="83" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>6</v>
       </c>
@@ -10880,7 +10878,7 @@
       <c r="U83" s="1"/>
       <c r="V83" s="1"/>
     </row>
-    <row r="84" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>6</v>
       </c>
@@ -10934,7 +10932,7 @@
       <c r="U84" s="1"/>
       <c r="V84" s="1"/>
     </row>
-    <row r="85" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>6</v>
       </c>
@@ -10990,7 +10988,7 @@
       <c r="U85" s="1"/>
       <c r="V85" s="1"/>
     </row>
-    <row r="86" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>6</v>
       </c>
@@ -11046,7 +11044,7 @@
       <c r="U86" s="1"/>
       <c r="V86" s="1"/>
     </row>
-    <row r="87" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>6</v>
       </c>
@@ -11100,7 +11098,7 @@
       <c r="U87" s="1"/>
       <c r="V87" s="1"/>
     </row>
-    <row r="88" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>6</v>
       </c>
@@ -11154,7 +11152,7 @@
       <c r="U88" s="1"/>
       <c r="V88" s="1"/>
     </row>
-    <row r="89" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>6</v>
       </c>
@@ -11206,7 +11204,7 @@
       <c r="U89" s="1"/>
       <c r="V89" s="1"/>
     </row>
-    <row r="90" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>6</v>
       </c>
@@ -11262,7 +11260,7 @@
       <c r="U90" s="1"/>
       <c r="V90" s="1"/>
     </row>
-    <row r="91" spans="1:22" s="2" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:22" s="2" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>6</v>
       </c>
@@ -11316,7 +11314,7 @@
       <c r="U91" s="1"/>
       <c r="V91" s="1"/>
     </row>
-    <row r="92" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>6</v>
       </c>
@@ -11370,7 +11368,7 @@
       <c r="U92" s="1"/>
       <c r="V92" s="1"/>
     </row>
-    <row r="93" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>6</v>
       </c>
@@ -11424,7 +11422,7 @@
       <c r="U93" s="1"/>
       <c r="V93" s="1"/>
     </row>
-    <row r="94" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>6</v>
       </c>
@@ -11478,7 +11476,7 @@
       <c r="U94" s="1"/>
       <c r="V94" s="1"/>
     </row>
-    <row r="95" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>6</v>
       </c>
@@ -11532,7 +11530,7 @@
       <c r="U95" s="1"/>
       <c r="V95" s="1"/>
     </row>
-    <row r="96" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>6</v>
       </c>
@@ -11586,7 +11584,7 @@
       <c r="U96" s="1"/>
       <c r="V96" s="1"/>
     </row>
-    <row r="97" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>6</v>
       </c>
@@ -11640,7 +11638,7 @@
       <c r="U97" s="1"/>
       <c r="V97" s="1"/>
     </row>
-    <row r="98" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>6</v>
       </c>
@@ -11694,7 +11692,7 @@
       <c r="U98" s="1"/>
       <c r="V98" s="1"/>
     </row>
-    <row r="99" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>6</v>
       </c>
@@ -11748,7 +11746,7 @@
       <c r="U99" s="1"/>
       <c r="V99" s="1"/>
     </row>
-    <row r="100" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>6</v>
       </c>
@@ -11802,7 +11800,7 @@
       <c r="U100" s="1"/>
       <c r="V100" s="1"/>
     </row>
-    <row r="101" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>6</v>
       </c>
@@ -11854,7 +11852,7 @@
       <c r="U101" s="1"/>
       <c r="V101" s="1"/>
     </row>
-    <row r="102" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>6</v>
       </c>
@@ -11910,7 +11908,7 @@
       <c r="U102" s="1"/>
       <c r="V102" s="1"/>
     </row>
-    <row r="103" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>6</v>
       </c>
@@ -11964,7 +11962,7 @@
       <c r="U103" s="1"/>
       <c r="V103" s="1"/>
     </row>
-    <row r="104" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>6</v>
       </c>
@@ -12016,7 +12014,7 @@
       <c r="U104" s="1"/>
       <c r="V104" s="1"/>
     </row>
-    <row r="105" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>6</v>
       </c>
@@ -12072,7 +12070,7 @@
       <c r="U105" s="1"/>
       <c r="V105" s="1"/>
     </row>
-    <row r="106" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>6</v>
       </c>
@@ -12126,7 +12124,7 @@
       <c r="U106" s="1"/>
       <c r="V106" s="1"/>
     </row>
-    <row r="107" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>6</v>
       </c>
@@ -12180,7 +12178,7 @@
       <c r="U107" s="1"/>
       <c r="V107" s="1"/>
     </row>
-    <row r="108" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>6</v>
       </c>
@@ -12234,7 +12232,7 @@
       <c r="U108" s="1"/>
       <c r="V108" s="1"/>
     </row>
-    <row r="109" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>6</v>
       </c>
@@ -12286,7 +12284,7 @@
       <c r="U109" s="1"/>
       <c r="V109" s="1"/>
     </row>
-    <row r="110" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>6</v>
       </c>
@@ -12340,7 +12338,7 @@
       <c r="U110" s="1"/>
       <c r="V110" s="1"/>
     </row>
-    <row r="111" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>6</v>
       </c>
@@ -12396,7 +12394,7 @@
       <c r="U111" s="1"/>
       <c r="V111" s="1"/>
     </row>
-    <row r="112" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>6</v>
       </c>
@@ -12450,7 +12448,7 @@
       <c r="U112" s="1"/>
       <c r="V112" s="1"/>
     </row>
-    <row r="113" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>6</v>
       </c>
@@ -12504,7 +12502,7 @@
       <c r="U113" s="1"/>
       <c r="V113" s="1"/>
     </row>
-    <row r="114" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>6</v>
       </c>
@@ -12558,7 +12556,7 @@
       <c r="U114" s="1"/>
       <c r="V114" s="1"/>
     </row>
-    <row r="115" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>6</v>
       </c>
@@ -12612,7 +12610,7 @@
       <c r="U115" s="1"/>
       <c r="V115" s="1"/>
     </row>
-    <row r="116" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>6</v>
       </c>
@@ -12666,7 +12664,7 @@
       <c r="U116" s="1"/>
       <c r="V116" s="1"/>
     </row>
-    <row r="117" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>6</v>
       </c>
@@ -12720,7 +12718,7 @@
       <c r="U117" s="1"/>
       <c r="V117" s="1"/>
     </row>
-    <row r="118" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>6</v>
       </c>
@@ -12774,7 +12772,7 @@
       <c r="U118" s="1"/>
       <c r="V118" s="1"/>
     </row>
-    <row r="119" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>6</v>
       </c>
@@ -12828,7 +12826,7 @@
       <c r="U119" s="1"/>
       <c r="V119" s="1"/>
     </row>
-    <row r="120" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>6</v>
       </c>
@@ -12882,7 +12880,7 @@
       <c r="U120" s="1"/>
       <c r="V120" s="1"/>
     </row>
-    <row r="121" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>6</v>
       </c>
@@ -12938,7 +12936,7 @@
       <c r="U121" s="1"/>
       <c r="V121" s="1"/>
     </row>
-    <row r="122" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>6</v>
       </c>
@@ -12992,7 +12990,7 @@
       <c r="U122" s="1"/>
       <c r="V122" s="1"/>
     </row>
-    <row r="123" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>6</v>
       </c>
@@ -13046,7 +13044,7 @@
       <c r="U123" s="1"/>
       <c r="V123" s="1"/>
     </row>
-    <row r="124" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>6</v>
       </c>
@@ -13100,7 +13098,7 @@
       <c r="U124" s="1"/>
       <c r="V124" s="1"/>
     </row>
-    <row r="125" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>6</v>
       </c>
@@ -13154,7 +13152,7 @@
       <c r="U125" s="1"/>
       <c r="V125" s="1"/>
     </row>
-    <row r="126" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>6</v>
       </c>
@@ -13208,7 +13206,7 @@
       <c r="U126" s="1"/>
       <c r="V126" s="1"/>
     </row>
-    <row r="127" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>6</v>
       </c>
@@ -13262,7 +13260,7 @@
       <c r="U127" s="1"/>
       <c r="V127" s="1"/>
     </row>
-    <row r="128" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>6</v>
       </c>
@@ -13316,7 +13314,7 @@
       <c r="U128" s="1"/>
       <c r="V128" s="1"/>
     </row>
-    <row r="129" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>6</v>
       </c>
@@ -13370,7 +13368,7 @@
       <c r="U129" s="1"/>
       <c r="V129" s="1"/>
     </row>
-    <row r="130" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>6</v>
       </c>
@@ -13424,7 +13422,7 @@
       <c r="U130" s="1"/>
       <c r="V130" s="1"/>
     </row>
-    <row r="131" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>6</v>
       </c>
@@ -13478,7 +13476,7 @@
       <c r="U131" s="1"/>
       <c r="V131" s="1"/>
     </row>
-    <row r="132" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>6</v>
       </c>
@@ -13532,7 +13530,7 @@
       <c r="U132" s="1"/>
       <c r="V132" s="1"/>
     </row>
-    <row r="133" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>6</v>
       </c>
@@ -13586,7 +13584,7 @@
       <c r="U133" s="1"/>
       <c r="V133" s="1"/>
     </row>
-    <row r="134" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>6</v>
       </c>
@@ -13640,7 +13638,7 @@
       <c r="U134" s="1"/>
       <c r="V134" s="1"/>
     </row>
-    <row r="135" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>6</v>
       </c>
@@ -13694,7 +13692,7 @@
       <c r="U135" s="1"/>
       <c r="V135" s="1"/>
     </row>
-    <row r="136" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>6</v>
       </c>
@@ -13748,7 +13746,7 @@
       <c r="U136" s="1"/>
       <c r="V136" s="1"/>
     </row>
-    <row r="137" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>6</v>
       </c>
@@ -13802,7 +13800,7 @@
       <c r="U137" s="1"/>
       <c r="V137" s="1"/>
     </row>
-    <row r="138" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>6</v>
       </c>
@@ -13856,7 +13854,7 @@
       <c r="U138" s="1"/>
       <c r="V138" s="1"/>
     </row>
-    <row r="139" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>6</v>
       </c>
@@ -13910,7 +13908,7 @@
       <c r="U139" s="1"/>
       <c r="V139" s="1"/>
     </row>
-    <row r="140" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>6</v>
       </c>
@@ -13966,7 +13964,7 @@
       <c r="U140" s="1"/>
       <c r="V140" s="1"/>
     </row>
-    <row r="141" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>6</v>
       </c>
@@ -14020,7 +14018,7 @@
       <c r="U141" s="1"/>
       <c r="V141" s="1"/>
     </row>
-    <row r="142" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>6</v>
       </c>
@@ -14074,7 +14072,7 @@
       <c r="U142" s="1"/>
       <c r="V142" s="1"/>
     </row>
-    <row r="143" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>6</v>
       </c>
@@ -14128,7 +14126,7 @@
       <c r="U143" s="1"/>
       <c r="V143" s="1"/>
     </row>
-    <row r="144" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>6</v>
       </c>
@@ -14184,7 +14182,7 @@
       <c r="U144" s="1"/>
       <c r="V144" s="1"/>
     </row>
-    <row r="145" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>6</v>
       </c>
@@ -14238,7 +14236,7 @@
       <c r="U145" s="1"/>
       <c r="V145" s="1"/>
     </row>
-    <row r="146" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>6</v>
       </c>
@@ -14292,7 +14290,7 @@
       <c r="U146" s="1"/>
       <c r="V146" s="1"/>
     </row>
-    <row r="147" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>6</v>
       </c>
@@ -14348,7 +14346,7 @@
       <c r="U147" s="1"/>
       <c r="V147" s="1"/>
     </row>
-    <row r="148" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>6</v>
       </c>
@@ -14402,7 +14400,7 @@
       <c r="U148" s="1"/>
       <c r="V148" s="1"/>
     </row>
-    <row r="149" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>6</v>
       </c>
@@ -14456,7 +14454,7 @@
       <c r="U149" s="1"/>
       <c r="V149" s="1"/>
     </row>
-    <row r="150" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>6</v>
       </c>
@@ -14510,7 +14508,7 @@
       <c r="U150" s="1"/>
       <c r="V150" s="1"/>
     </row>
-    <row r="151" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>6</v>
       </c>
@@ -14564,7 +14562,7 @@
       <c r="U151" s="1"/>
       <c r="V151" s="1"/>
     </row>
-    <row r="152" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>6</v>
       </c>
@@ -14618,7 +14616,7 @@
       <c r="U152" s="1"/>
       <c r="V152" s="1"/>
     </row>
-    <row r="153" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>6</v>
       </c>
@@ -14672,7 +14670,7 @@
       <c r="U153" s="1"/>
       <c r="V153" s="1"/>
     </row>
-    <row r="154" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>6</v>
       </c>
@@ -14726,7 +14724,7 @@
       <c r="U154" s="1"/>
       <c r="V154" s="1"/>
     </row>
-    <row r="155" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>6</v>
       </c>
@@ -14780,7 +14778,7 @@
       <c r="U155" s="1"/>
       <c r="V155" s="1"/>
     </row>
-    <row r="156" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>6</v>
       </c>
@@ -14834,7 +14832,7 @@
       <c r="U156" s="1"/>
       <c r="V156" s="1"/>
     </row>
-    <row r="157" spans="1:22" s="2" customFormat="1" ht="65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:22" s="2" customFormat="1" ht="65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>6</v>
       </c>
@@ -14898,7 +14896,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="158" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>6</v>
       </c>
@@ -14954,7 +14952,7 @@
       <c r="U158" s="1"/>
       <c r="V158" s="1"/>
     </row>
-    <row r="159" spans="1:22" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>6</v>
       </c>
@@ -15010,7 +15008,7 @@
       <c r="U159" s="1"/>
       <c r="V159" s="1"/>
     </row>
-    <row r="160" spans="1:22" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>6</v>
       </c>
@@ -15066,7 +15064,7 @@
       <c r="U160" s="1"/>
       <c r="V160" s="1"/>
     </row>
-    <row r="161" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>6</v>
       </c>
@@ -15122,7 +15120,7 @@
       <c r="U161" s="1"/>
       <c r="V161" s="1"/>
     </row>
-    <row r="162" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
         <v>6</v>
       </c>
@@ -15180,7 +15178,7 @@
       <c r="U162" s="1"/>
       <c r="V162" s="1"/>
     </row>
-    <row r="163" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
         <v>6</v>
       </c>
@@ -15236,7 +15234,7 @@
       <c r="U163" s="1"/>
       <c r="V163" s="1"/>
     </row>
-    <row r="164" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
         <v>6</v>
       </c>
@@ -15292,7 +15290,7 @@
       <c r="U164" s="1"/>
       <c r="V164" s="1"/>
     </row>
-    <row r="165" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
         <v>6</v>
       </c>
@@ -15348,7 +15346,7 @@
       <c r="U165" s="1"/>
       <c r="V165" s="1"/>
     </row>
-    <row r="166" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
         <v>6</v>
       </c>
@@ -15404,7 +15402,7 @@
       <c r="U166" s="1"/>
       <c r="V166" s="1"/>
     </row>
-    <row r="167" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
         <v>6</v>
       </c>
@@ -15462,7 +15460,7 @@
       <c r="U167" s="1"/>
       <c r="V167" s="1"/>
     </row>
-    <row r="168" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
         <v>6</v>
       </c>
@@ -15522,7 +15520,7 @@
       <c r="U168" s="1"/>
       <c r="V168" s="1"/>
     </row>
-    <row r="169" spans="1:22" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
         <v>6</v>
       </c>
@@ -15578,7 +15576,7 @@
       <c r="U169" s="1"/>
       <c r="V169" s="1"/>
     </row>
-    <row r="170" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
         <v>6</v>
       </c>
@@ -15634,7 +15632,7 @@
       <c r="U170" s="1"/>
       <c r="V170" s="1"/>
     </row>
-    <row r="171" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
         <v>6</v>
       </c>
@@ -15690,7 +15688,7 @@
       <c r="U171" s="1"/>
       <c r="V171" s="1"/>
     </row>
-    <row r="172" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
         <v>6</v>
       </c>
@@ -15746,7 +15744,7 @@
       <c r="U172" s="1"/>
       <c r="V172" s="1"/>
     </row>
-    <row r="173" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
         <v>6</v>
       </c>
@@ -15800,7 +15798,7 @@
       <c r="U173" s="1"/>
       <c r="V173" s="1"/>
     </row>
-    <row r="174" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
         <v>6</v>
       </c>
@@ -15854,7 +15852,7 @@
       <c r="U174" s="1"/>
       <c r="V174" s="1"/>
     </row>
-    <row r="175" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
         <v>6</v>
       </c>
@@ -15908,7 +15906,7 @@
       <c r="U175" s="1"/>
       <c r="V175" s="1"/>
     </row>
-    <row r="176" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
         <v>6</v>
       </c>
@@ -15962,7 +15960,7 @@
       <c r="U176" s="1"/>
       <c r="V176" s="1"/>
     </row>
-    <row r="177" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
         <v>6</v>
       </c>
@@ -16016,7 +16014,7 @@
       <c r="U177" s="1"/>
       <c r="V177" s="1"/>
     </row>
-    <row r="178" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
         <v>6</v>
       </c>
@@ -16070,7 +16068,7 @@
       <c r="U178" s="1"/>
       <c r="V178" s="1"/>
     </row>
-    <row r="179" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
         <v>6</v>
       </c>
@@ -16124,7 +16122,7 @@
       <c r="U179" s="1"/>
       <c r="V179" s="1"/>
     </row>
-    <row r="180" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
         <v>6</v>
       </c>
@@ -16178,7 +16176,7 @@
       <c r="U180" s="1"/>
       <c r="V180" s="1"/>
     </row>
-    <row r="181" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
         <v>6</v>
       </c>
@@ -16234,7 +16232,7 @@
       <c r="U181" s="1"/>
       <c r="V181" s="1"/>
     </row>
-    <row r="182" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
         <v>6</v>
       </c>
@@ -16288,7 +16286,7 @@
       <c r="U182" s="1"/>
       <c r="V182" s="1"/>
     </row>
-    <row r="183" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
         <v>6</v>
       </c>
@@ -16342,7 +16340,7 @@
       <c r="U183" s="1"/>
       <c r="V183" s="1"/>
     </row>
-    <row r="184" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
         <v>6</v>
       </c>
@@ -16396,7 +16394,7 @@
       <c r="U184" s="1"/>
       <c r="V184" s="1"/>
     </row>
-    <row r="185" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
         <v>6</v>
       </c>
@@ -16450,7 +16448,7 @@
       <c r="U185" s="1"/>
       <c r="V185" s="1"/>
     </row>
-    <row r="186" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
         <v>6</v>
       </c>
@@ -16506,7 +16504,7 @@
       <c r="U186" s="1"/>
       <c r="V186" s="1"/>
     </row>
-    <row r="187" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
         <v>6</v>
       </c>
@@ -16560,7 +16558,7 @@
       <c r="U187" s="1"/>
       <c r="V187" s="1"/>
     </row>
-    <row r="188" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
         <v>6</v>
       </c>
@@ -16614,7 +16612,7 @@
       <c r="U188" s="1"/>
       <c r="V188" s="1"/>
     </row>
-    <row r="189" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
         <v>6</v>
       </c>
@@ -16668,7 +16666,7 @@
       <c r="U189" s="1"/>
       <c r="V189" s="1"/>
     </row>
-    <row r="190" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
         <v>6</v>
       </c>
@@ -16722,7 +16720,7 @@
       <c r="U190" s="1"/>
       <c r="V190" s="1"/>
     </row>
-    <row r="191" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
         <v>6</v>
       </c>
@@ -16776,7 +16774,7 @@
       <c r="U191" s="1"/>
       <c r="V191" s="1"/>
     </row>
-    <row r="192" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
         <v>6</v>
       </c>
@@ -16830,7 +16828,7 @@
       <c r="U192" s="1"/>
       <c r="V192" s="1"/>
     </row>
-    <row r="193" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
         <v>6</v>
       </c>
@@ -16884,7 +16882,7 @@
       <c r="U193" s="1"/>
       <c r="V193" s="1"/>
     </row>
-    <row r="194" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
         <v>6</v>
       </c>
@@ -16938,7 +16936,7 @@
       <c r="U194" s="1"/>
       <c r="V194" s="1"/>
     </row>
-    <row r="195" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
         <v>6</v>
       </c>
@@ -16992,7 +16990,7 @@
       <c r="U195" s="1"/>
       <c r="V195" s="1"/>
     </row>
-    <row r="196" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
         <v>6</v>
       </c>
@@ -17046,7 +17044,7 @@
       <c r="U196" s="1"/>
       <c r="V196" s="1"/>
     </row>
-    <row r="197" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
         <v>6</v>
       </c>
@@ -17100,7 +17098,7 @@
       <c r="U197" s="1"/>
       <c r="V197" s="1"/>
     </row>
-    <row r="198" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
         <v>6</v>
       </c>
@@ -17154,7 +17152,7 @@
       <c r="U198" s="1"/>
       <c r="V198" s="1"/>
     </row>
-    <row r="199" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
         <v>6</v>
       </c>
@@ -17208,7 +17206,7 @@
       <c r="U199" s="1"/>
       <c r="V199" s="1"/>
     </row>
-    <row r="200" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
         <v>6</v>
       </c>
@@ -17262,7 +17260,7 @@
       <c r="U200" s="1"/>
       <c r="V200" s="1"/>
     </row>
-    <row r="201" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
         <v>6</v>
       </c>
@@ -17316,7 +17314,7 @@
       <c r="U201" s="1"/>
       <c r="V201" s="1"/>
     </row>
-    <row r="202" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
         <v>6</v>
       </c>
@@ -17370,7 +17368,7 @@
       <c r="U202" s="1"/>
       <c r="V202" s="1"/>
     </row>
-    <row r="203" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A203" s="1" t="s">
         <v>6</v>
       </c>
@@ -17424,7 +17422,7 @@
       <c r="U203" s="1"/>
       <c r="V203" s="1"/>
     </row>
-    <row r="204" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
         <v>6</v>
       </c>
@@ -17478,7 +17476,7 @@
       <c r="U204" s="1"/>
       <c r="V204" s="1"/>
     </row>
-    <row r="205" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
         <v>6</v>
       </c>
@@ -17532,7 +17530,7 @@
       <c r="U205" s="1"/>
       <c r="V205" s="1"/>
     </row>
-    <row r="206" spans="1:22" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:22" ht="87" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
         <v>6</v>
       </c>
@@ -17586,7 +17584,7 @@
       <c r="U206" s="1"/>
       <c r="V206" s="1"/>
     </row>
-    <row r="207" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
         <v>6</v>
       </c>
@@ -17640,7 +17638,7 @@
       <c r="U207" s="1"/>
       <c r="V207" s="1"/>
     </row>
-    <row r="208" spans="1:22" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:22" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
         <v>6</v>
       </c>
@@ -17694,7 +17692,7 @@
       <c r="U208" s="1"/>
       <c r="V208" s="1"/>
     </row>
-    <row r="209" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
         <v>6</v>
       </c>
@@ -17748,7 +17746,7 @@
       <c r="U209" s="1"/>
       <c r="V209" s="1"/>
     </row>
-    <row r="210" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
         <v>6</v>
       </c>
@@ -17802,7 +17800,7 @@
       <c r="U210" s="1"/>
       <c r="V210" s="1"/>
     </row>
-    <row r="211" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A211" s="1" t="s">
         <v>6</v>
       </c>
@@ -17854,7 +17852,7 @@
       <c r="U211" s="1"/>
       <c r="V211" s="1"/>
     </row>
-    <row r="212" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
         <v>6</v>
       </c>
@@ -17906,7 +17904,7 @@
       <c r="U212" s="1"/>
       <c r="V212" s="1"/>
     </row>
-    <row r="213" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
         <v>6</v>
       </c>
@@ -17960,7 +17958,7 @@
       <c r="U213" s="1"/>
       <c r="V213" s="1"/>
     </row>
-    <row r="214" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
         <v>6</v>
       </c>
@@ -18012,7 +18010,7 @@
       <c r="U214" s="1"/>
       <c r="V214" s="1"/>
     </row>
-    <row r="215" spans="1:22" s="2" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:22" s="2" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A215" s="1" t="s">
         <v>6</v>
       </c>
@@ -18064,7 +18062,7 @@
       <c r="U215" s="1"/>
       <c r="V215" s="1"/>
     </row>
-    <row r="216" spans="1:22" s="2" customFormat="1" ht="188.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:22" s="2" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A216" s="1" t="s">
         <v>6</v>
       </c>
@@ -18116,7 +18114,7 @@
       <c r="U216" s="1"/>
       <c r="V216" s="1"/>
     </row>
-    <row r="217" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
         <v>6</v>
       </c>
@@ -18168,7 +18166,7 @@
       <c r="U217" s="1"/>
       <c r="V217" s="1"/>
     </row>
-    <row r="218" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A218" s="1" t="s">
         <v>6</v>
       </c>
@@ -18222,7 +18220,7 @@
       <c r="U218" s="1"/>
       <c r="V218" s="1"/>
     </row>
-    <row r="219" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
         <v>6</v>
       </c>
@@ -18276,7 +18274,7 @@
       <c r="U219" s="1"/>
       <c r="V219" s="1"/>
     </row>
-    <row r="220" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
         <v>6</v>
       </c>
@@ -18332,7 +18330,7 @@
       <c r="U220" s="1"/>
       <c r="V220" s="1"/>
     </row>
-    <row r="221" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
         <v>6</v>
       </c>
@@ -18386,7 +18384,7 @@
       <c r="U221" s="1"/>
       <c r="V221" s="1"/>
     </row>
-    <row r="222" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A222" s="1" t="s">
         <v>6</v>
       </c>
@@ -18438,7 +18436,7 @@
       <c r="U222" s="1"/>
       <c r="V222" s="1"/>
     </row>
-    <row r="223" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A223" s="1" t="s">
         <v>6</v>
       </c>
@@ -18492,7 +18490,7 @@
       <c r="U223" s="1"/>
       <c r="V223" s="1"/>
     </row>
-    <row r="224" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A224" s="1" t="s">
         <v>6</v>
       </c>
@@ -18548,7 +18546,7 @@
       <c r="U224" s="1"/>
       <c r="V224" s="1"/>
     </row>
-    <row r="225" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
         <v>6</v>
       </c>
@@ -18604,7 +18602,7 @@
       <c r="U225" s="1"/>
       <c r="V225" s="1"/>
     </row>
-    <row r="226" spans="1:22" s="2" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:22" s="2" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
         <v>6</v>
       </c>
@@ -18658,7 +18656,7 @@
       <c r="U226" s="1"/>
       <c r="V226" s="1"/>
     </row>
-    <row r="227" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
         <v>6</v>
       </c>
@@ -18710,7 +18708,7 @@
       <c r="U227" s="1"/>
       <c r="V227" s="1"/>
     </row>
-    <row r="228" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
         <v>6</v>
       </c>
@@ -18762,7 +18760,7 @@
       <c r="U228" s="1"/>
       <c r="V228" s="1"/>
     </row>
-    <row r="229" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
         <v>6</v>
       </c>
@@ -18818,7 +18816,7 @@
       <c r="U229" s="1"/>
       <c r="V229" s="1"/>
     </row>
-    <row r="230" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A230" s="1" t="s">
         <v>6</v>
       </c>
@@ -18872,7 +18870,7 @@
       <c r="U230" s="1"/>
       <c r="V230" s="1"/>
     </row>
-    <row r="231" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A231" s="1" t="s">
         <v>6</v>
       </c>
@@ -18924,7 +18922,7 @@
       <c r="U231" s="1"/>
       <c r="V231" s="1"/>
     </row>
-    <row r="232" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
         <v>6</v>
       </c>
@@ -18976,7 +18974,7 @@
       <c r="U232" s="1"/>
       <c r="V232" s="1"/>
     </row>
-    <row r="233" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>6</v>
       </c>
@@ -19028,7 +19026,7 @@
       <c r="U233" s="1"/>
       <c r="V233" s="1"/>
     </row>
-    <row r="234" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
         <v>6</v>
       </c>
@@ -19080,7 +19078,7 @@
       <c r="U234" s="1"/>
       <c r="V234" s="1"/>
     </row>
-    <row r="235" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A235" s="1" t="s">
         <v>6</v>
       </c>
@@ -19132,7 +19130,7 @@
       <c r="U235" s="1"/>
       <c r="V235" s="1"/>
     </row>
-    <row r="236" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A236" s="1" t="s">
         <v>6</v>
       </c>
@@ -19184,7 +19182,7 @@
       <c r="U236" s="1"/>
       <c r="V236" s="1"/>
     </row>
-    <row r="237" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A237" s="1" t="s">
         <v>6</v>
       </c>
@@ -19236,7 +19234,7 @@
       <c r="U237" s="1"/>
       <c r="V237" s="1"/>
     </row>
-    <row r="238" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A238" s="1" t="s">
         <v>6</v>
       </c>
@@ -19290,7 +19288,7 @@
       <c r="U238" s="1"/>
       <c r="V238" s="1"/>
     </row>
-    <row r="239" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A239" s="1" t="s">
         <v>6</v>
       </c>
@@ -19342,7 +19340,7 @@
       <c r="U239" s="1"/>
       <c r="V239" s="1"/>
     </row>
-    <row r="240" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A240" s="1" t="s">
         <v>6</v>
       </c>
@@ -19394,7 +19392,7 @@
       <c r="U240" s="1"/>
       <c r="V240" s="1"/>
     </row>
-    <row r="241" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A241" s="1" t="s">
         <v>6</v>
       </c>
@@ -19446,7 +19444,7 @@
       <c r="U241" s="1"/>
       <c r="V241" s="1"/>
     </row>
-    <row r="242" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A242" s="1" t="s">
         <v>6</v>
       </c>
@@ -19498,7 +19496,7 @@
       <c r="U242" s="1"/>
       <c r="V242" s="1"/>
     </row>
-    <row r="243" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A243" s="1" t="s">
         <v>6</v>
       </c>
@@ -19550,7 +19548,7 @@
       <c r="U243" s="1"/>
       <c r="V243" s="1"/>
     </row>
-    <row r="244" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A244" s="1" t="s">
         <v>6</v>
       </c>
@@ -19602,7 +19600,7 @@
       <c r="U244" s="1"/>
       <c r="V244" s="1"/>
     </row>
-    <row r="245" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A245" s="1" t="s">
         <v>6</v>
       </c>
@@ -19656,7 +19654,7 @@
       <c r="U245" s="1"/>
       <c r="V245" s="1"/>
     </row>
-    <row r="246" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A246" s="1" t="s">
         <v>6</v>
       </c>
@@ -19710,7 +19708,7 @@
       <c r="U246" s="1"/>
       <c r="V246" s="1"/>
     </row>
-    <row r="247" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A247" s="1" t="s">
         <v>6</v>
       </c>
@@ -19762,7 +19760,7 @@
       <c r="U247" s="1"/>
       <c r="V247" s="1"/>
     </row>
-    <row r="248" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A248" s="1" t="s">
         <v>6</v>
       </c>
@@ -19814,7 +19812,7 @@
       <c r="U248" s="1"/>
       <c r="V248" s="1"/>
     </row>
-    <row r="249" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A249" s="1" t="s">
         <v>6</v>
       </c>
@@ -19866,7 +19864,7 @@
       <c r="U249" s="1"/>
       <c r="V249" s="1"/>
     </row>
-    <row r="250" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A250" s="1" t="s">
         <v>6</v>
       </c>
@@ -19918,7 +19916,7 @@
       <c r="U250" s="1"/>
       <c r="V250" s="1"/>
     </row>
-    <row r="251" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A251" s="1" t="s">
         <v>6</v>
       </c>
@@ -19970,7 +19968,7 @@
       <c r="U251" s="1"/>
       <c r="V251" s="1"/>
     </row>
-    <row r="252" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A252" s="1" t="s">
         <v>6</v>
       </c>
@@ -20022,7 +20020,7 @@
       <c r="U252" s="1"/>
       <c r="V252" s="1"/>
     </row>
-    <row r="253" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A253" s="1" t="s">
         <v>6</v>
       </c>
@@ -20078,7 +20076,7 @@
       <c r="U253" s="1"/>
       <c r="V253" s="1"/>
     </row>
-    <row r="254" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A254" s="1" t="s">
         <v>6</v>
       </c>
@@ -20132,7 +20130,7 @@
       <c r="U254" s="1"/>
       <c r="V254" s="1"/>
     </row>
-    <row r="255" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A255" s="1" t="s">
         <v>6</v>
       </c>
@@ -20186,7 +20184,7 @@
       <c r="U255" s="1"/>
       <c r="V255" s="1"/>
     </row>
-    <row r="256" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A256" s="1" t="s">
         <v>6</v>
       </c>
@@ -20238,7 +20236,7 @@
       <c r="U256" s="1"/>
       <c r="V256" s="1"/>
     </row>
-    <row r="257" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A257" s="1" t="s">
         <v>6</v>
       </c>
@@ -20290,7 +20288,7 @@
       <c r="U257" s="1"/>
       <c r="V257" s="1"/>
     </row>
-    <row r="258" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A258" s="1" t="s">
         <v>6</v>
       </c>
@@ -20342,7 +20340,7 @@
       <c r="U258" s="1"/>
       <c r="V258" s="1"/>
     </row>
-    <row r="259" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A259" s="1" t="s">
         <v>6</v>
       </c>
@@ -20394,7 +20392,7 @@
       <c r="U259" s="1"/>
       <c r="V259" s="1"/>
     </row>
-    <row r="260" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A260" s="1" t="s">
         <v>6</v>
       </c>
@@ -20446,7 +20444,7 @@
       <c r="U260" s="1"/>
       <c r="V260" s="1"/>
     </row>
-    <row r="261" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A261" s="1" t="s">
         <v>6</v>
       </c>
@@ -20500,7 +20498,7 @@
       <c r="U261" s="1"/>
       <c r="V261" s="1"/>
     </row>
-    <row r="262" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A262" s="1" t="s">
         <v>6</v>
       </c>
@@ -20552,7 +20550,7 @@
       <c r="U262" s="1"/>
       <c r="V262" s="1"/>
     </row>
-    <row r="263" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A263" s="1" t="s">
         <v>6</v>
       </c>
@@ -20604,7 +20602,7 @@
       <c r="U263" s="1"/>
       <c r="V263" s="1"/>
     </row>
-    <row r="264" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A264" s="1" t="s">
         <v>6</v>
       </c>
@@ -20656,7 +20654,7 @@
       <c r="U264" s="1"/>
       <c r="V264" s="1"/>
     </row>
-    <row r="265" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A265" s="1" t="s">
         <v>6</v>
       </c>
@@ -20708,7 +20706,7 @@
       <c r="U265" s="1"/>
       <c r="V265" s="1"/>
     </row>
-    <row r="266" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A266" s="1" t="s">
         <v>6</v>
       </c>
@@ -20760,7 +20758,7 @@
       <c r="U266" s="1"/>
       <c r="V266" s="1"/>
     </row>
-    <row r="267" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A267" s="1" t="s">
         <v>6</v>
       </c>
@@ -20812,7 +20810,7 @@
       <c r="U267" s="1"/>
       <c r="V267" s="1"/>
     </row>
-    <row r="268" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A268" s="1" t="s">
         <v>6</v>
       </c>
@@ -20866,7 +20864,7 @@
       <c r="U268" s="1"/>
       <c r="V268" s="1"/>
     </row>
-    <row r="269" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A269" s="1" t="s">
         <v>6</v>
       </c>
@@ -20918,7 +20916,7 @@
       <c r="U269" s="1"/>
       <c r="V269" s="1"/>
     </row>
-    <row r="270" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A270" s="1" t="s">
         <v>6</v>
       </c>
@@ -20970,7 +20968,7 @@
       <c r="U270" s="1"/>
       <c r="V270" s="1"/>
     </row>
-    <row r="271" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A271" s="1" t="s">
         <v>6</v>
       </c>
@@ -21022,7 +21020,7 @@
       <c r="U271" s="1"/>
       <c r="V271" s="1"/>
     </row>
-    <row r="272" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A272" s="1" t="s">
         <v>6</v>
       </c>
@@ -21076,7 +21074,7 @@
       <c r="U272" s="1"/>
       <c r="V272" s="1"/>
     </row>
-    <row r="273" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A273" s="1" t="s">
         <v>6</v>
       </c>
@@ -21130,7 +21128,7 @@
       <c r="U273" s="1"/>
       <c r="V273" s="1"/>
     </row>
-    <row r="274" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A274" s="1" t="s">
         <v>6</v>
       </c>
@@ -21184,7 +21182,7 @@
       <c r="U274" s="1"/>
       <c r="V274" s="1"/>
     </row>
-    <row r="275" spans="1:22" s="2" customFormat="1" ht="377" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:22" s="2" customFormat="1" ht="377" x14ac:dyDescent="0.35">
       <c r="A275" s="1" t="s">
         <v>6</v>
       </c>
@@ -21240,7 +21238,7 @@
       <c r="U275" s="1"/>
       <c r="V275" s="1"/>
     </row>
-    <row r="276" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A276" s="1" t="s">
         <v>6</v>
       </c>
@@ -21294,7 +21292,7 @@
       <c r="U276" s="1"/>
       <c r="V276" s="1"/>
     </row>
-    <row r="277" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A277" s="1" t="s">
         <v>6</v>
       </c>
@@ -21348,7 +21346,7 @@
       <c r="U277" s="1"/>
       <c r="V277" s="1"/>
     </row>
-    <row r="278" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A278" s="1" t="s">
         <v>6</v>
       </c>
@@ -21402,7 +21400,7 @@
       <c r="U278" s="1"/>
       <c r="V278" s="1"/>
     </row>
-    <row r="279" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A279" s="1" t="s">
         <v>6</v>
       </c>
@@ -21456,7 +21454,7 @@
       <c r="U279" s="1"/>
       <c r="V279" s="1"/>
     </row>
-    <row r="280" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A280" s="1" t="s">
         <v>6</v>
       </c>
@@ -21512,7 +21510,7 @@
       <c r="U280" s="1"/>
       <c r="V280" s="1"/>
     </row>
-    <row r="281" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A281" s="1" t="s">
         <v>6</v>
       </c>
@@ -21566,7 +21564,7 @@
       <c r="U281" s="1"/>
       <c r="V281" s="1"/>
     </row>
-    <row r="282" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A282" s="1" t="s">
         <v>6</v>
       </c>
@@ -21620,7 +21618,7 @@
       <c r="U282" s="1"/>
       <c r="V282" s="1"/>
     </row>
-    <row r="283" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A283" s="1" t="s">
         <v>6</v>
       </c>
@@ -21674,7 +21672,7 @@
       <c r="U283" s="1"/>
       <c r="V283" s="1"/>
     </row>
-    <row r="284" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A284" s="1" t="s">
         <v>6</v>
       </c>
@@ -21728,7 +21726,7 @@
       <c r="U284" s="1"/>
       <c r="V284" s="1"/>
     </row>
-    <row r="285" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A285" s="1" t="s">
         <v>6</v>
       </c>
@@ -21780,7 +21778,7 @@
       <c r="U285" s="1"/>
       <c r="V285" s="1"/>
     </row>
-    <row r="286" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A286" s="1" t="s">
         <v>6</v>
       </c>
@@ -21832,7 +21830,7 @@
       <c r="U286" s="1"/>
       <c r="V286" s="1"/>
     </row>
-    <row r="287" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A287" s="1" t="s">
         <v>6</v>
       </c>
@@ -21884,7 +21882,7 @@
       <c r="U287" s="1"/>
       <c r="V287" s="1"/>
     </row>
-    <row r="288" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A288" s="1" t="s">
         <v>6</v>
       </c>
@@ -21936,7 +21934,7 @@
       <c r="U288" s="1"/>
       <c r="V288" s="1"/>
     </row>
-    <row r="289" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A289" s="1" t="s">
         <v>6</v>
       </c>
@@ -21988,7 +21986,7 @@
       <c r="U289" s="1"/>
       <c r="V289" s="1"/>
     </row>
-    <row r="290" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A290" s="1" t="s">
         <v>6</v>
       </c>
@@ -22040,7 +22038,7 @@
       <c r="U290" s="1"/>
       <c r="V290" s="1"/>
     </row>
-    <row r="291" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A291" s="1" t="s">
         <v>6</v>
       </c>
@@ -22092,7 +22090,7 @@
       <c r="U291" s="1"/>
       <c r="V291" s="1"/>
     </row>
-    <row r="292" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A292" s="1" t="s">
         <v>6</v>
       </c>
@@ -22144,7 +22142,7 @@
       <c r="U292" s="1"/>
       <c r="V292" s="1"/>
     </row>
-    <row r="293" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A293" s="1" t="s">
         <v>6</v>
       </c>
@@ -22196,7 +22194,7 @@
       <c r="U293" s="1"/>
       <c r="V293" s="1"/>
     </row>
-    <row r="294" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A294" s="1" t="s">
         <v>6</v>
       </c>
@@ -22248,7 +22246,7 @@
       <c r="U294" s="1"/>
       <c r="V294" s="1"/>
     </row>
-    <row r="295" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A295" s="1" t="s">
         <v>6</v>
       </c>
@@ -22300,7 +22298,7 @@
       <c r="U295" s="1"/>
       <c r="V295" s="1"/>
     </row>
-    <row r="296" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A296" s="1" t="s">
         <v>6</v>
       </c>
@@ -22352,7 +22350,7 @@
       <c r="U296" s="1"/>
       <c r="V296" s="1"/>
     </row>
-    <row r="297" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A297" s="1" t="s">
         <v>6</v>
       </c>
@@ -22404,7 +22402,7 @@
       <c r="U297" s="1"/>
       <c r="V297" s="1"/>
     </row>
-    <row r="298" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A298" s="1" t="s">
         <v>6</v>
       </c>
@@ -22456,7 +22454,7 @@
       <c r="U298" s="1"/>
       <c r="V298" s="1"/>
     </row>
-    <row r="299" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A299" s="1" t="s">
         <v>6</v>
       </c>
@@ -22508,7 +22506,7 @@
       <c r="U299" s="1"/>
       <c r="V299" s="1"/>
     </row>
-    <row r="300" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A300" s="1" t="s">
         <v>6</v>
       </c>
@@ -22560,7 +22558,7 @@
       <c r="U300" s="1"/>
       <c r="V300" s="1"/>
     </row>
-    <row r="301" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A301" s="1" t="s">
         <v>6</v>
       </c>
@@ -22612,7 +22610,7 @@
       <c r="U301" s="1"/>
       <c r="V301" s="1"/>
     </row>
-    <row r="302" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A302" s="1" t="s">
         <v>6</v>
       </c>
@@ -22664,7 +22662,7 @@
       <c r="U302" s="1"/>
       <c r="V302" s="1"/>
     </row>
-    <row r="303" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A303" s="1" t="s">
         <v>6</v>
       </c>
@@ -22718,7 +22716,7 @@
       <c r="U303" s="1"/>
       <c r="V303" s="1"/>
     </row>
-    <row r="304" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A304" s="1" t="s">
         <v>6</v>
       </c>
@@ -22770,7 +22768,7 @@
       <c r="U304" s="1"/>
       <c r="V304" s="1"/>
     </row>
-    <row r="305" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A305" s="1" t="s">
         <v>6</v>
       </c>
@@ -22822,7 +22820,7 @@
       <c r="U305" s="1"/>
       <c r="V305" s="1"/>
     </row>
-    <row r="306" spans="1:22" s="2" customFormat="1" ht="76.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:22" s="2" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="1" t="s">
         <v>6</v>
       </c>
@@ -22874,7 +22872,7 @@
       <c r="U306" s="1"/>
       <c r="V306" s="1"/>
     </row>
-    <row r="307" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A307" s="1" t="s">
         <v>6</v>
       </c>
@@ -22926,7 +22924,7 @@
       <c r="U307" s="1"/>
       <c r="V307" s="1"/>
     </row>
-    <row r="308" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A308" s="1" t="s">
         <v>6</v>
       </c>
@@ -22978,7 +22976,7 @@
       <c r="U308" s="1"/>
       <c r="V308" s="1"/>
     </row>
-    <row r="309" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A309" s="1" t="s">
         <v>6</v>
       </c>
@@ -23030,7 +23028,7 @@
       <c r="U309" s="1"/>
       <c r="V309" s="1"/>
     </row>
-    <row r="310" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A310" s="1" t="s">
         <v>6</v>
       </c>
@@ -23082,7 +23080,7 @@
       <c r="U310" s="1"/>
       <c r="V310" s="1"/>
     </row>
-    <row r="311" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A311" s="1" t="s">
         <v>6</v>
       </c>
@@ -23134,7 +23132,7 @@
       <c r="U311" s="1"/>
       <c r="V311" s="1"/>
     </row>
-    <row r="312" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A312" s="1" t="s">
         <v>6</v>
       </c>
@@ -23186,7 +23184,7 @@
       <c r="U312" s="1"/>
       <c r="V312" s="1"/>
     </row>
-    <row r="313" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A313" s="1" t="s">
         <v>6</v>
       </c>
@@ -23238,7 +23236,7 @@
       <c r="U313" s="1"/>
       <c r="V313" s="1"/>
     </row>
-    <row r="314" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A314" s="1" t="s">
         <v>6</v>
       </c>
@@ -23294,7 +23292,7 @@
       <c r="U314" s="1"/>
       <c r="V314" s="1"/>
     </row>
-    <row r="315" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A315" s="1" t="s">
         <v>6</v>
       </c>
@@ -23352,7 +23350,7 @@
       <c r="U315" s="1"/>
       <c r="V315" s="1"/>
     </row>
-    <row r="316" spans="1:22" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:22" ht="87" x14ac:dyDescent="0.35">
       <c r="A316" s="1" t="s">
         <v>6</v>
       </c>
@@ -23408,7 +23406,7 @@
       <c r="U316" s="1"/>
       <c r="V316" s="1"/>
     </row>
-    <row r="317" spans="1:22" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:22" ht="87" x14ac:dyDescent="0.35">
       <c r="A317" s="1" t="s">
         <v>6</v>
       </c>
@@ -23462,7 +23460,7 @@
       <c r="U317" s="1"/>
       <c r="V317" s="1"/>
     </row>
-    <row r="318" spans="1:22" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:22" ht="87" x14ac:dyDescent="0.35">
       <c r="A318" s="1" t="s">
         <v>6</v>
       </c>
@@ -23512,7 +23510,7 @@
       <c r="U318" s="1"/>
       <c r="V318" s="1"/>
     </row>
-    <row r="319" spans="1:22" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:22" ht="87" x14ac:dyDescent="0.35">
       <c r="A319" s="1" t="s">
         <v>6</v>
       </c>
@@ -23568,7 +23566,7 @@
       <c r="U319" s="1"/>
       <c r="V319" s="1"/>
     </row>
-    <row r="320" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A320" s="1" t="s">
         <v>6</v>
       </c>
@@ -23620,7 +23618,7 @@
       <c r="U320" s="1"/>
       <c r="V320" s="1"/>
     </row>
-    <row r="321" spans="1:22" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A321" s="1" t="s">
         <v>6</v>
       </c>
@@ -23674,7 +23672,7 @@
       <c r="U321" s="1"/>
       <c r="V321" s="1"/>
     </row>
-    <row r="322" spans="1:22" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A322" s="1" t="s">
         <v>6</v>
       </c>
@@ -23726,7 +23724,7 @@
       <c r="U322" s="1"/>
       <c r="V322" s="1"/>
     </row>
-    <row r="323" spans="1:22" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A323" s="1" t="s">
         <v>6</v>
       </c>
@@ -23782,7 +23780,7 @@
       <c r="U323" s="1"/>
       <c r="V323" s="1"/>
     </row>
-    <row r="324" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A324" s="1" t="s">
         <v>6</v>
       </c>
@@ -23834,7 +23832,7 @@
       <c r="U324" s="1"/>
       <c r="V324" s="1"/>
     </row>
-    <row r="325" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A325" s="1" t="s">
         <v>6</v>
       </c>
@@ -23886,7 +23884,7 @@
       <c r="U325" s="1"/>
       <c r="V325" s="1"/>
     </row>
-    <row r="326" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A326" s="1" t="s">
         <v>6</v>
       </c>
@@ -23938,7 +23936,7 @@
       <c r="U326" s="1"/>
       <c r="V326" s="1"/>
     </row>
-    <row r="327" spans="1:22" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A327" s="1" t="s">
         <v>6</v>
       </c>
@@ -23990,7 +23988,7 @@
       <c r="U327" s="1"/>
       <c r="V327" s="1"/>
     </row>
-    <row r="328" spans="1:22" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A328" s="1" t="s">
         <v>6</v>
       </c>
@@ -24042,7 +24040,7 @@
       <c r="U328" s="1"/>
       <c r="V328" s="1"/>
     </row>
-    <row r="329" spans="1:22" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A329" s="1" t="s">
         <v>6</v>
       </c>
@@ -24094,7 +24092,7 @@
       <c r="U329" s="1"/>
       <c r="V329" s="1"/>
     </row>
-    <row r="330" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A330" s="1" t="s">
         <v>6</v>
       </c>
@@ -24146,7 +24144,7 @@
       <c r="U330" s="1"/>
       <c r="V330" s="1"/>
     </row>
-    <row r="331" spans="1:22" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:22" ht="58" x14ac:dyDescent="0.35">
       <c r="A331" s="1" t="s">
         <v>6</v>
       </c>
@@ -24198,7 +24196,7 @@
       <c r="U331" s="1"/>
       <c r="V331" s="1"/>
     </row>
-    <row r="332" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A332" s="1" t="s">
         <v>6</v>
       </c>
@@ -24252,7 +24250,7 @@
       <c r="U332" s="1"/>
       <c r="V332" s="1"/>
     </row>
-    <row r="333" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A333" s="1" t="s">
         <v>6</v>
       </c>
@@ -24306,7 +24304,7 @@
       <c r="U333" s="1"/>
       <c r="V333" s="1"/>
     </row>
-    <row r="334" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A334" s="1" t="s">
         <v>6</v>
       </c>
@@ -24360,7 +24358,7 @@
       <c r="U334" s="1"/>
       <c r="V334" s="1"/>
     </row>
-    <row r="335" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A335" s="1" t="s">
         <v>6</v>
       </c>
@@ -24412,7 +24410,7 @@
       <c r="U335" s="1"/>
       <c r="V335" s="1"/>
     </row>
-    <row r="336" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A336" s="1" t="s">
         <v>6</v>
       </c>
@@ -24464,7 +24462,7 @@
       <c r="U336" s="1"/>
       <c r="V336" s="1"/>
     </row>
-    <row r="337" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A337" s="1" t="s">
         <v>6</v>
       </c>
@@ -24516,7 +24514,7 @@
       <c r="U337" s="1"/>
       <c r="V337" s="1"/>
     </row>
-    <row r="338" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A338" s="1" t="s">
         <v>6</v>
       </c>
@@ -24570,7 +24568,7 @@
       <c r="U338" s="1"/>
       <c r="V338" s="1"/>
     </row>
-    <row r="339" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A339" s="1" t="s">
         <v>6</v>
       </c>
@@ -24622,7 +24620,7 @@
       <c r="U339" s="1"/>
       <c r="V339" s="1"/>
     </row>
-    <row r="340" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A340" s="1" t="s">
         <v>6</v>
       </c>
@@ -24674,7 +24672,7 @@
       <c r="U340" s="1"/>
       <c r="V340" s="1"/>
     </row>
-    <row r="341" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A341" s="1" t="s">
         <v>6</v>
       </c>
@@ -24726,7 +24724,7 @@
       <c r="U341" s="1"/>
       <c r="V341" s="1"/>
     </row>
-    <row r="342" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A342" s="1" t="s">
         <v>6</v>
       </c>
@@ -24780,7 +24778,7 @@
       <c r="U342" s="1"/>
       <c r="V342" s="1"/>
     </row>
-    <row r="343" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A343" s="1" t="s">
         <v>6</v>
       </c>
@@ -24834,7 +24832,7 @@
       <c r="U343" s="1"/>
       <c r="V343" s="1"/>
     </row>
-    <row r="344" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A344" s="1" t="s">
         <v>6</v>
       </c>
@@ -24886,7 +24884,7 @@
       <c r="U344" s="1"/>
       <c r="V344" s="1"/>
     </row>
-    <row r="345" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A345" s="1" t="s">
         <v>6</v>
       </c>
@@ -24938,7 +24936,7 @@
       <c r="U345" s="1"/>
       <c r="V345" s="1"/>
     </row>
-    <row r="346" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A346" s="1" t="s">
         <v>6</v>
       </c>
@@ -24990,7 +24988,7 @@
       <c r="U346" s="1"/>
       <c r="V346" s="1"/>
     </row>
-    <row r="347" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A347" s="1" t="s">
         <v>6</v>
       </c>
@@ -25044,7 +25042,7 @@
       <c r="U347" s="1"/>
       <c r="V347" s="1"/>
     </row>
-    <row r="348" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A348" s="1" t="s">
         <v>6</v>
       </c>
@@ -25096,7 +25094,7 @@
       <c r="U348" s="1"/>
       <c r="V348" s="1"/>
     </row>
-    <row r="349" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A349" s="1" t="s">
         <v>6</v>
       </c>
@@ -25150,7 +25148,7 @@
       <c r="U349" s="1"/>
       <c r="V349" s="1"/>
     </row>
-    <row r="350" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A350" s="1" t="s">
         <v>6</v>
       </c>
@@ -25202,7 +25200,7 @@
       <c r="U350" s="1"/>
       <c r="V350" s="1"/>
     </row>
-    <row r="351" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A351" s="1" t="s">
         <v>6</v>
       </c>
@@ -25254,7 +25252,7 @@
       <c r="U351" s="1"/>
       <c r="V351" s="1"/>
     </row>
-    <row r="352" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A352" s="1" t="s">
         <v>6</v>
       </c>
@@ -25308,7 +25306,7 @@
       <c r="U352" s="1"/>
       <c r="V352" s="1"/>
     </row>
-    <row r="353" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A353" s="1" t="s">
         <v>6</v>
       </c>
@@ -25358,7 +25356,7 @@
       <c r="U353" s="1"/>
       <c r="V353" s="1"/>
     </row>
-    <row r="354" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A354" s="1" t="s">
         <v>6</v>
       </c>
@@ -25408,7 +25406,7 @@
       <c r="U354" s="1"/>
       <c r="V354" s="1"/>
     </row>
-    <row r="355" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A355" s="1" t="s">
         <v>6</v>
       </c>
@@ -25460,7 +25458,7 @@
       <c r="U355" s="1"/>
       <c r="V355" s="1"/>
     </row>
-    <row r="356" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A356" s="1" t="s">
         <v>6</v>
       </c>
@@ -25512,7 +25510,7 @@
       <c r="U356" s="1"/>
       <c r="V356" s="1"/>
     </row>
-    <row r="357" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A357" s="1" t="s">
         <v>6</v>
       </c>
@@ -25564,7 +25562,7 @@
       <c r="U357" s="1"/>
       <c r="V357" s="1"/>
     </row>
-    <row r="358" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A358" s="1" t="s">
         <v>6</v>
       </c>
@@ -25616,7 +25614,7 @@
       <c r="U358" s="1"/>
       <c r="V358" s="1"/>
     </row>
-    <row r="359" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A359" s="1" t="s">
         <v>6</v>
       </c>
@@ -25670,7 +25668,7 @@
       <c r="U359" s="1"/>
       <c r="V359" s="1"/>
     </row>
-    <row r="360" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A360" s="1" t="s">
         <v>6</v>
       </c>
@@ -25722,7 +25720,7 @@
       <c r="U360" s="1"/>
       <c r="V360" s="1"/>
     </row>
-    <row r="361" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A361" s="1" t="s">
         <v>6</v>
       </c>
@@ -25774,7 +25772,7 @@
       <c r="U361" s="1"/>
       <c r="V361" s="1"/>
     </row>
-    <row r="362" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A362" s="1" t="s">
         <v>6</v>
       </c>
@@ -25826,7 +25824,7 @@
       <c r="U362" s="1"/>
       <c r="V362" s="1"/>
     </row>
-    <row r="363" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A363" s="1" t="s">
         <v>6</v>
       </c>
@@ -25880,7 +25878,7 @@
       <c r="U363" s="1"/>
       <c r="V363" s="1"/>
     </row>
-    <row r="364" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A364" s="1" t="s">
         <v>6</v>
       </c>
@@ -25932,7 +25930,7 @@
       <c r="U364" s="1"/>
       <c r="V364" s="1"/>
     </row>
-    <row r="365" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A365" s="1" t="s">
         <v>6</v>
       </c>
@@ -25984,7 +25982,7 @@
       <c r="U365" s="1"/>
       <c r="V365" s="1"/>
     </row>
-    <row r="366" spans="1:22" s="2" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:22" s="2" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A366" s="1" t="s">
         <v>6</v>
       </c>
@@ -26036,7 +26034,7 @@
       <c r="U366" s="1"/>
       <c r="V366" s="1"/>
     </row>
-    <row r="367" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A367" s="1" t="s">
         <v>6</v>
       </c>
@@ -26088,7 +26086,7 @@
       <c r="U367" s="1"/>
       <c r="V367" s="1"/>
     </row>
-    <row r="368" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A368" s="1" t="s">
         <v>6</v>
       </c>
@@ -26140,7 +26138,7 @@
       <c r="U368" s="1"/>
       <c r="V368" s="1"/>
     </row>
-    <row r="369" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A369" s="1" t="s">
         <v>6</v>
       </c>
@@ -26192,7 +26190,7 @@
       <c r="U369" s="1"/>
       <c r="V369" s="1"/>
     </row>
-    <row r="370" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A370" s="1" t="s">
         <v>6</v>
       </c>
@@ -26246,7 +26244,7 @@
       <c r="U370" s="1"/>
       <c r="V370" s="1"/>
     </row>
-    <row r="371" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A371" s="1" t="s">
         <v>6</v>
       </c>
@@ -26298,7 +26296,7 @@
       <c r="U371" s="1"/>
       <c r="V371" s="1"/>
     </row>
-    <row r="372" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A372" s="1" t="s">
         <v>6</v>
       </c>
@@ -26350,7 +26348,7 @@
       <c r="U372" s="1"/>
       <c r="V372" s="1"/>
     </row>
-    <row r="373" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A373" s="1" t="s">
         <v>6</v>
       </c>
@@ -26402,7 +26400,7 @@
       <c r="U373" s="1"/>
       <c r="V373" s="1"/>
     </row>
-    <row r="374" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A374" s="1" t="s">
         <v>6</v>
       </c>
@@ -26456,7 +26454,7 @@
       <c r="U374" s="1"/>
       <c r="V374" s="1"/>
     </row>
-    <row r="375" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A375" s="1" t="s">
         <v>6</v>
       </c>
@@ -26510,7 +26508,7 @@
       <c r="U375" s="1"/>
       <c r="V375" s="1"/>
     </row>
-    <row r="376" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A376" s="1" t="s">
         <v>6</v>
       </c>
@@ -26566,7 +26564,7 @@
       <c r="U376" s="1"/>
       <c r="V376" s="1"/>
     </row>
-    <row r="377" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A377" s="1" t="s">
         <v>6</v>
       </c>
@@ -26620,7 +26618,7 @@
       <c r="U377" s="1"/>
       <c r="V377" s="1"/>
     </row>
-    <row r="378" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A378" s="1" t="s">
         <v>6</v>
       </c>
@@ -26674,7 +26672,7 @@
       <c r="U378" s="1"/>
       <c r="V378" s="1"/>
     </row>
-    <row r="379" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A379" s="1" t="s">
         <v>6</v>
       </c>
@@ -26730,7 +26728,7 @@
       <c r="U379" s="1"/>
       <c r="V379" s="1"/>
     </row>
-    <row r="380" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A380" s="1" t="s">
         <v>6</v>
       </c>
@@ -26786,7 +26784,7 @@
       <c r="U380" s="1"/>
       <c r="V380" s="1"/>
     </row>
-    <row r="381" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A381" s="1" t="s">
         <v>6</v>
       </c>
@@ -26840,7 +26838,7 @@
       <c r="U381" s="1"/>
       <c r="V381" s="1"/>
     </row>
-    <row r="382" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A382" s="1" t="s">
         <v>6</v>
       </c>
@@ -26896,7 +26894,7 @@
       <c r="U382" s="1"/>
       <c r="V382" s="1"/>
     </row>
-    <row r="383" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A383" s="1" t="s">
         <v>6</v>
       </c>
@@ -26950,7 +26948,7 @@
       <c r="U383" s="1"/>
       <c r="V383" s="1"/>
     </row>
-    <row r="384" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A384" s="1" t="s">
         <v>6</v>
       </c>
@@ -27002,7 +27000,7 @@
       <c r="U384" s="1"/>
       <c r="V384" s="1"/>
     </row>
-    <row r="385" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A385" s="1" t="s">
         <v>6</v>
       </c>
@@ -27056,7 +27054,7 @@
       <c r="U385" s="1"/>
       <c r="V385" s="1"/>
     </row>
-    <row r="386" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A386" s="1" t="s">
         <v>6</v>
       </c>
@@ -27112,7 +27110,7 @@
       <c r="U386" s="1"/>
       <c r="V386" s="1"/>
     </row>
-    <row r="387" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A387" s="1" t="s">
         <v>6</v>
       </c>
@@ -27166,7 +27164,7 @@
       <c r="U387" s="1"/>
       <c r="V387" s="1"/>
     </row>
-    <row r="388" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A388" s="1" t="s">
         <v>6</v>
       </c>
@@ -27220,7 +27218,7 @@
       <c r="U388" s="1"/>
       <c r="V388" s="1"/>
     </row>
-    <row r="389" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A389" s="1" t="s">
         <v>6</v>
       </c>
@@ -27274,7 +27272,7 @@
       <c r="U389" s="1"/>
       <c r="V389" s="1"/>
     </row>
-    <row r="390" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A390" s="1" t="s">
         <v>6</v>
       </c>
@@ -27328,7 +27326,7 @@
       <c r="U390" s="1"/>
       <c r="V390" s="1"/>
     </row>
-    <row r="391" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A391" s="1" t="s">
         <v>6</v>
       </c>
@@ -27384,7 +27382,7 @@
       <c r="U391" s="1"/>
       <c r="V391" s="1"/>
     </row>
-    <row r="392" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A392" s="1" t="s">
         <v>6</v>
       </c>
@@ -27438,7 +27436,7 @@
       <c r="U392" s="1"/>
       <c r="V392" s="1"/>
     </row>
-    <row r="393" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A393" s="1" t="s">
         <v>6</v>
       </c>
@@ -27492,7 +27490,7 @@
       <c r="U393" s="1"/>
       <c r="V393" s="1"/>
     </row>
-    <row r="394" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A394" s="1" t="s">
         <v>6</v>
       </c>
@@ -27546,7 +27544,7 @@
       <c r="U394" s="1"/>
       <c r="V394" s="1"/>
     </row>
-    <row r="395" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A395" s="1" t="s">
         <v>6</v>
       </c>
@@ -27600,7 +27598,7 @@
       <c r="U395" s="1"/>
       <c r="V395" s="1"/>
     </row>
-    <row r="396" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A396" s="1" t="s">
         <v>6</v>
       </c>
@@ -27656,7 +27654,7 @@
       <c r="U396" s="1"/>
       <c r="V396" s="1"/>
     </row>
-    <row r="397" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A397" s="1" t="s">
         <v>6</v>
       </c>
@@ -27712,7 +27710,7 @@
       <c r="U397" s="1"/>
       <c r="V397" s="1"/>
     </row>
-    <row r="398" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A398" s="1" t="s">
         <v>6</v>
       </c>
@@ -27766,7 +27764,7 @@
       <c r="U398" s="1"/>
       <c r="V398" s="1"/>
     </row>
-    <row r="399" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A399" s="1" t="s">
         <v>6</v>
       </c>
@@ -27820,7 +27818,7 @@
       <c r="U399" s="1"/>
       <c r="V399" s="1"/>
     </row>
-    <row r="400" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A400" s="1" t="s">
         <v>6</v>
       </c>
@@ -27876,7 +27874,7 @@
       <c r="U400" s="1"/>
       <c r="V400" s="1"/>
     </row>
-    <row r="401" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A401" s="1" t="s">
         <v>6</v>
       </c>
@@ -27930,7 +27928,7 @@
       <c r="U401" s="1"/>
       <c r="V401" s="1"/>
     </row>
-    <row r="402" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A402" s="1" t="s">
         <v>6</v>
       </c>
@@ -27984,7 +27982,7 @@
       <c r="U402" s="1"/>
       <c r="V402" s="1"/>
     </row>
-    <row r="403" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A403" s="1" t="s">
         <v>6</v>
       </c>
@@ -28038,7 +28036,7 @@
       <c r="U403" s="1"/>
       <c r="V403" s="1"/>
     </row>
-    <row r="404" spans="1:22" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A404" s="1" t="s">
         <v>6</v>
       </c>
@@ -28092,7 +28090,7 @@
       <c r="U404" s="1"/>
       <c r="V404" s="1"/>
     </row>
-    <row r="405" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A405" s="1" t="s">
         <v>6</v>
       </c>
@@ -28146,7 +28144,7 @@
       <c r="U405" s="1"/>
       <c r="V405" s="1"/>
     </row>
-    <row r="406" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A406" s="1" t="s">
         <v>6</v>
       </c>
@@ -28200,7 +28198,7 @@
       <c r="U406" s="1"/>
       <c r="V406" s="1"/>
     </row>
-    <row r="407" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A407" s="1" t="s">
         <v>6</v>
       </c>
@@ -28254,7 +28252,7 @@
       <c r="U407" s="1"/>
       <c r="V407" s="1"/>
     </row>
-    <row r="408" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A408" s="1" t="s">
         <v>6</v>
       </c>
@@ -28308,7 +28306,7 @@
       <c r="U408" s="1"/>
       <c r="V408" s="1"/>
     </row>
-    <row r="409" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A409" s="1" t="s">
         <v>6</v>
       </c>
@@ -28362,7 +28360,7 @@
       <c r="U409" s="1"/>
       <c r="V409" s="1"/>
     </row>
-    <row r="410" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A410" s="1" t="s">
         <v>6</v>
       </c>
@@ -28416,7 +28414,7 @@
       <c r="U410" s="1"/>
       <c r="V410" s="1"/>
     </row>
-    <row r="411" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A411" s="1" t="s">
         <v>6</v>
       </c>
@@ -28470,7 +28468,7 @@
       <c r="U411" s="1"/>
       <c r="V411" s="1"/>
     </row>
-    <row r="412" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A412" s="1" t="s">
         <v>6</v>
       </c>
@@ -28524,7 +28522,7 @@
       <c r="U412" s="1"/>
       <c r="V412" s="1"/>
     </row>
-    <row r="413" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A413" s="1" t="s">
         <v>6</v>
       </c>
@@ -28576,7 +28574,7 @@
       <c r="U413" s="1"/>
       <c r="V413" s="1"/>
     </row>
-    <row r="414" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A414" s="1" t="s">
         <v>6</v>
       </c>
@@ -28628,7 +28626,7 @@
       <c r="U414" s="1"/>
       <c r="V414" s="1"/>
     </row>
-    <row r="415" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A415" s="1" t="s">
         <v>6</v>
       </c>
@@ -28680,7 +28678,7 @@
       <c r="U415" s="1"/>
       <c r="V415" s="1"/>
     </row>
-    <row r="416" spans="1:22" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A416" s="1" t="s">
         <v>6</v>
       </c>
@@ -28732,7 +28730,7 @@
       <c r="U416" s="1"/>
       <c r="V416" s="1"/>
     </row>
-    <row r="417" spans="1:22" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:22" ht="58" x14ac:dyDescent="0.35">
       <c r="A417" s="1" t="s">
         <v>6</v>
       </c>
@@ -28786,7 +28784,7 @@
       <c r="U417" s="1"/>
       <c r="V417" s="1"/>
     </row>
-    <row r="418" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A418" s="1" t="s">
         <v>6</v>
       </c>
@@ -28840,7 +28838,7 @@
       <c r="U418" s="1"/>
       <c r="V418" s="1"/>
     </row>
-    <row r="419" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A419" s="1" t="s">
         <v>6</v>
       </c>
@@ -28894,159 +28892,8 @@
       <c r="U419" s="1"/>
       <c r="V419" s="1"/>
     </row>
-    <row r="690" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O690" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="691" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O691" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="692" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O692" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="693" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O693" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="694" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O694" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="695" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O695" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="696" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O696" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="697" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O697" s="54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="698" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O698" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="699" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O699" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="700" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O700" s="54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="701" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O701" s="54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="703" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O703" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="704" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O704" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="705" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O705" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="706" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O706" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="707" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O707" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="708" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O708" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="709" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O709" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="710" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O710" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="711" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O711" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="712" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O712" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="713" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O713" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="714" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O714" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="715" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O715" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="716" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O716" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="717" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O717" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="718" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O718" s="54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="719" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O719" s="54">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:V419" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Philippe Ciais"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:V419" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L229">
     <sortCondition ref="C2:C424"/>
   </sortState>

--- a/Data/FairCarboN_Datas_Contacts.xlsx
+++ b/Data/FairCarboN_Datas_Contacts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCEAADA-B3E8-4D79-92A3-240B48ACC832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{708A70D1-E731-49F8-8410-634B75BE5859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liste" sheetId="2" r:id="rId1"/>

--- a/Data/FairCarboN_Datas_Contacts.xlsx
+++ b/Data/FairCarboN_Datas_Contacts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB251C0A-F855-45B3-BCF4-2A2CAD47CDEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E22647-15D3-4EDC-8CEA-2959004EF425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Liste" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Liste!$A$1:$T$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Liste!$A$1:$T$418</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5932" uniqueCount="1848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5933" uniqueCount="1849">
   <si>
     <t>Acronyme PEPR</t>
   </si>
@@ -5597,6 +5597,9 @@
   </si>
   <si>
     <t>2023-A long-term monthly surface water storage dataset for the Congo basin from 1992 to 2015/2023-Panta Rhei benchmark dataset: socio-hydrological data of paired events of floods and droughts/2022-Oil slicks in the Gulf of Guinea – 10 years of Envisat Advanced Synthetic Aperture Radar observations</t>
+  </si>
+  <si>
+    <t>lionel.alletto@inrae.fr</t>
   </si>
 </sst>
 </file>
@@ -25279,7 +25282,9 @@
       <c r="C348" s="21" t="s">
         <v>1540</v>
       </c>
-      <c r="D348" s="26"/>
+      <c r="D348" s="16" t="s">
+        <v>1848</v>
+      </c>
       <c r="E348" s="34" t="s">
         <v>1539</v>
       </c>
@@ -27847,7 +27852,7 @@
       <c r="C396" s="21" t="s">
         <v>1666</v>
       </c>
-      <c r="D396" s="19" t="s">
+      <c r="D396" s="16" t="s">
         <v>1634</v>
       </c>
       <c r="E396" s="37" t="s">
@@ -29076,7 +29081,7 @@
       <c r="T418" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T1" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:T418" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L228">
     <sortCondition ref="C2:C423"/>
   </sortState>
@@ -29329,7 +29334,7 @@
     <hyperlink ref="D393" r:id="rId245" display="mailto:edouard.metzger@univ-angers.fr" xr:uid="{59E61568-78B5-41C8-85D1-CC43DBA55D0D}"/>
     <hyperlink ref="D394" r:id="rId246" display="mailto:jean-sebastien.moquet@cnrs-orleans.fr" xr:uid="{0517E78E-5BA6-4C99-95AF-C7D28D0EC215}"/>
     <hyperlink ref="D395" r:id="rId247" display="mailto:Julien.Nemery@grenoble-inp.fr" xr:uid="{6FDF451D-F42A-43B7-8022-12E0F273F4D3}"/>
-    <hyperlink ref="D396" r:id="rId248" display="mailto:Pierre.Polsenaere@Ifremer.fr" xr:uid="{4178A1DF-1C5B-4C5A-B6DD-D1A40885B42D}"/>
+    <hyperlink ref="D396" r:id="rId248" xr:uid="{4178A1DF-1C5B-4C5A-B6DD-D1A40885B42D}"/>
     <hyperlink ref="D397" r:id="rId249" display="mailto:cristina.ribaudo@ensegid.fr" xr:uid="{E0F33667-16B4-4954-A6A2-B927FEFD3616}"/>
     <hyperlink ref="D398" r:id="rId250" display="mailto:philippe.rosa@univ-nantes.fr" xr:uid="{399C084D-0179-479B-97B1-866B4936755B}"/>
     <hyperlink ref="D399" r:id="rId251" display="mailto:nicolas.savoye@u-bordeaux.fr" xr:uid="{9B1C3AF1-9F70-472A-9B83-1576E6459B24}"/>
@@ -29356,8 +29361,9 @@
     <hyperlink ref="D363" r:id="rId272" xr:uid="{B64D5E0B-23AE-4FDD-AA57-B0FBC122B4F1}"/>
     <hyperlink ref="D104" r:id="rId273" xr:uid="{7089C2BE-4027-4FC6-A1F9-6A1AE4B8725E}"/>
     <hyperlink ref="D101" r:id="rId274" xr:uid="{71155148-E90E-47B9-8E3F-E19F3F36A0ED}"/>
+    <hyperlink ref="D348" r:id="rId275" xr:uid="{81D62058-B298-48D5-BEA8-2A123AB178FF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId275"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId276"/>
 </worksheet>
 </file>
--- a/Data/FairCarboN_Datas_Contacts.xlsx
+++ b/Data/FairCarboN_Datas_Contacts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E00446C-74D1-4C3A-B380-8DC361E31816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3AE8110-ACA6-4C34-A0BE-221BC680E754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7670,7 +7670,7 @@
     <col min="23" max="16384" width="8.7265625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="46" t="s">
         <v>0</v>
       </c>

--- a/Data/FairCarboN_Datas_Contacts.xlsx
+++ b/Data/FairCarboN_Datas_Contacts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3AE8110-ACA6-4C34-A0BE-221BC680E754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9827F31-0211-4726-AD69-B257A1DAC88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liste" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6753" uniqueCount="2285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6760" uniqueCount="2291">
   <si>
     <t>Acronyme PEPR</t>
   </si>
@@ -6908,6 +6908,24 @@
   </si>
   <si>
     <t>0009-0007-1574-700X</t>
+  </si>
+  <si>
+    <t>Emmanuel.Tillard@Cirad.Fr</t>
+  </si>
+  <si>
+    <t>regis.gallon@lecnam.net</t>
+  </si>
+  <si>
+    <t>hubert.loisel@univ-littoral.fr</t>
+  </si>
+  <si>
+    <t>jean-luc.Maeght@ird.fr</t>
+  </si>
+  <si>
+    <t>olivier.marloie@inrae.fr</t>
+  </si>
+  <si>
+    <t>isabelle.chuine@cefe.cnrs.fr</t>
   </si>
 </sst>
 </file>
@@ -7656,14 +7674,14 @@
     <col min="4" max="4" width="46.81640625" style="27" customWidth="1"/>
     <col min="5" max="6" width="16.7265625" style="35" customWidth="1"/>
     <col min="7" max="7" width="16.7265625" style="7" customWidth="1"/>
-    <col min="8" max="8" width="27.1796875" style="7" customWidth="1"/>
-    <col min="9" max="9" width="27.81640625" style="35" customWidth="1"/>
-    <col min="10" max="10" width="12" style="7" customWidth="1"/>
-    <col min="11" max="11" width="12.26953125" style="7" customWidth="1"/>
-    <col min="12" max="13" width="22.90625" style="7" customWidth="1"/>
-    <col min="14" max="14" width="22.90625" style="54" customWidth="1"/>
-    <col min="15" max="16" width="48.7265625" style="7" customWidth="1"/>
-    <col min="17" max="17" width="17.36328125" style="7" customWidth="1"/>
+    <col min="8" max="8" width="27.1796875" style="7" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="27.81640625" style="35" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="12" style="7" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="12.26953125" style="7" hidden="1" customWidth="1"/>
+    <col min="12" max="13" width="22.90625" style="7" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="22.90625" style="54" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="48.7265625" style="7" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="17.36328125" style="7" hidden="1" customWidth="1"/>
     <col min="18" max="20" width="22.90625" style="7" customWidth="1"/>
     <col min="21" max="21" width="13" style="7" customWidth="1"/>
     <col min="22" max="22" width="14.81640625" style="7" customWidth="1"/>
@@ -7988,7 +8006,7 @@
       <c r="C6" s="21" t="s">
         <v>463</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="57" t="s">
         <v>455</v>
       </c>
       <c r="E6" s="14" t="s">
@@ -8027,12 +8045,14 @@
       </c>
       <c r="Q6" s="1"/>
       <c r="R6" s="1" t="s">
-        <v>1759</v>
+        <v>1835</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="T6" s="1"/>
+      <c r="T6" s="1">
+        <v>24</v>
+      </c>
       <c r="U6" s="60" t="s">
         <v>1854</v>
       </c>
@@ -8269,12 +8289,14 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1" t="s">
-        <v>1759</v>
+        <v>1835</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="T10" s="1"/>
+      <c r="T10" s="1">
+        <v>18</v>
+      </c>
       <c r="U10" s="60" t="s">
         <v>1861</v>
       </c>
@@ -9539,12 +9561,14 @@
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
       <c r="R31" s="1" t="s">
-        <v>1759</v>
+        <v>1835</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="T31" s="1"/>
+      <c r="T31" s="1">
+        <v>13</v>
+      </c>
       <c r="U31" s="61" t="s">
         <v>1896</v>
       </c>
@@ -9924,7 +9948,7 @@
       <c r="C38" s="21" t="s">
         <v>466</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="57" t="s">
         <v>459</v>
       </c>
       <c r="E38" s="14" t="s">
@@ -9961,12 +9985,14 @@
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
       <c r="R38" s="1" t="s">
-        <v>1759</v>
+        <v>1835</v>
       </c>
       <c r="S38" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="T38" s="1"/>
+      <c r="T38" s="1">
+        <v>18</v>
+      </c>
       <c r="U38" s="60" t="s">
         <v>1861</v>
       </c>
@@ -10890,7 +10916,7 @@
       <c r="C54" s="21" t="s">
         <v>701</v>
       </c>
-      <c r="D54" s="19" t="s">
+      <c r="D54" s="16" t="s">
         <v>669</v>
       </c>
       <c r="E54" s="14" t="s">
@@ -10927,12 +10953,14 @@
       <c r="P54" s="1"/>
       <c r="Q54" s="1"/>
       <c r="R54" s="1" t="s">
-        <v>1759</v>
+        <v>1835</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="T54" s="1"/>
+      <c r="T54" s="1">
+        <v>28</v>
+      </c>
       <c r="U54" s="60" t="s">
         <v>1925</v>
       </c>
@@ -11963,12 +11991,14 @@
       <c r="P71" s="1"/>
       <c r="Q71" s="1"/>
       <c r="R71" s="1" t="s">
-        <v>1759</v>
+        <v>1835</v>
       </c>
       <c r="S71" s="1" t="s">
-        <v>1759</v>
-      </c>
-      <c r="T71" s="1"/>
+        <v>1835</v>
+      </c>
+      <c r="T71" s="1">
+        <v>0</v>
+      </c>
       <c r="U71" s="61" t="s">
         <v>1950</v>
       </c>
@@ -14365,12 +14395,14 @@
         <v>1835</v>
       </c>
       <c r="R110" s="1" t="s">
-        <v>1759</v>
+        <v>1835</v>
       </c>
       <c r="S110" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="T110" s="1"/>
+      <c r="T110" s="1">
+        <v>13</v>
+      </c>
       <c r="U110" s="60" t="s">
         <v>1896</v>
       </c>
@@ -20706,7 +20738,9 @@
       <c r="C213" s="21" t="s">
         <v>1208</v>
       </c>
-      <c r="D213" s="1"/>
+      <c r="D213" s="13" t="s">
+        <v>2285</v>
+      </c>
       <c r="E213" s="1" t="s">
         <v>1201</v>
       </c>
@@ -20741,12 +20775,14 @@
       <c r="P213" s="1"/>
       <c r="Q213" s="1"/>
       <c r="R213" s="1" t="s">
-        <v>1759</v>
+        <v>1835</v>
       </c>
       <c r="S213" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="T213" s="1"/>
+      <c r="T213" s="1">
+        <v>3</v>
+      </c>
       <c r="U213" s="61" t="s">
         <v>2102</v>
       </c>
@@ -22834,7 +22870,9 @@
       <c r="C249" s="21" t="s">
         <v>1281</v>
       </c>
-      <c r="D249" s="1"/>
+      <c r="D249" s="13" t="s">
+        <v>2288</v>
+      </c>
       <c r="E249" s="1" t="s">
         <v>1258</v>
       </c>
@@ -22869,12 +22907,14 @@
       <c r="P249" s="1"/>
       <c r="Q249" s="1"/>
       <c r="R249" s="1" t="s">
-        <v>1759</v>
+        <v>1835</v>
       </c>
       <c r="S249" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="T249" s="1"/>
+      <c r="T249" s="1">
+        <v>9</v>
+      </c>
       <c r="U249" s="61" t="s">
         <v>2132</v>
       </c>
@@ -23012,7 +23052,9 @@
       <c r="C252" s="21" t="s">
         <v>1284</v>
       </c>
-      <c r="D252" s="1"/>
+      <c r="D252" s="13" t="s">
+        <v>2287</v>
+      </c>
       <c r="E252" s="1" t="s">
         <v>1262</v>
       </c>
@@ -23049,12 +23091,14 @@
       </c>
       <c r="Q252" s="1"/>
       <c r="R252" s="1" t="s">
-        <v>1759</v>
+        <v>1835</v>
       </c>
       <c r="S252" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="T252" s="1"/>
+      <c r="T252" s="1">
+        <v>12</v>
+      </c>
       <c r="U252" s="60" t="s">
         <v>2135</v>
       </c>
@@ -23890,7 +23934,9 @@
       <c r="C267" s="21" t="s">
         <v>1319</v>
       </c>
-      <c r="D267" s="1"/>
+      <c r="D267" s="13" t="s">
+        <v>2286</v>
+      </c>
       <c r="E267" s="1" t="s">
         <v>1312</v>
       </c>
@@ -23925,12 +23971,14 @@
       <c r="P267" s="1"/>
       <c r="Q267" s="1"/>
       <c r="R267" s="1" t="s">
-        <v>1759</v>
+        <v>1835</v>
       </c>
       <c r="S267" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="T267" s="1"/>
+      <c r="T267" s="1">
+        <v>4</v>
+      </c>
       <c r="U267" s="61" t="s">
         <v>2150</v>
       </c>
@@ -24477,12 +24525,14 @@
         <v>1835</v>
       </c>
       <c r="R276" s="1" t="s">
-        <v>1759</v>
+        <v>1835</v>
       </c>
       <c r="S276" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="T276" s="1"/>
+      <c r="T276" s="1">
+        <v>18</v>
+      </c>
       <c r="U276" s="60" t="s">
         <v>2158</v>
       </c>
@@ -26597,12 +26647,14 @@
       <c r="P312" s="1"/>
       <c r="Q312" s="1"/>
       <c r="R312" s="1" t="s">
-        <v>1759</v>
+        <v>1835</v>
       </c>
       <c r="S312" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="T312" s="1"/>
+      <c r="T312" s="1">
+        <v>13</v>
+      </c>
       <c r="U312" s="60" t="s">
         <v>1896</v>
       </c>
@@ -26806,7 +26858,9 @@
       <c r="C316" s="21" t="s">
         <v>1499</v>
       </c>
-      <c r="D316" s="26"/>
+      <c r="D316" s="13" t="s">
+        <v>2290</v>
+      </c>
       <c r="E316" s="33" t="s">
         <v>1464</v>
       </c>
@@ -26839,12 +26893,14 @@
       <c r="P316" s="1"/>
       <c r="Q316" s="1"/>
       <c r="R316" s="1" t="s">
-        <v>1759</v>
+        <v>1835</v>
       </c>
       <c r="S316" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="T316" s="1"/>
+      <c r="T316" s="1">
+        <v>17</v>
+      </c>
       <c r="U316" s="60" t="s">
         <v>2200</v>
       </c>
@@ -27042,7 +27098,9 @@
       <c r="C320" s="21" t="s">
         <v>1502</v>
       </c>
-      <c r="D320" s="26"/>
+      <c r="D320" s="13" t="s">
+        <v>2289</v>
+      </c>
       <c r="E320" s="33" t="s">
         <v>1472</v>
       </c>
@@ -27077,12 +27135,14 @@
       <c r="P320" s="1"/>
       <c r="Q320" s="1"/>
       <c r="R320" s="1" t="s">
-        <v>1759</v>
+        <v>1835</v>
       </c>
       <c r="S320" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="T320" s="1"/>
+      <c r="T320" s="1">
+        <v>11</v>
+      </c>
       <c r="U320" s="60" t="s">
         <v>2203</v>
       </c>
@@ -29622,7 +29682,9 @@
       <c r="C364" s="21" t="s">
         <v>1208</v>
       </c>
-      <c r="D364" s="26"/>
+      <c r="D364" s="13" t="s">
+        <v>2285</v>
+      </c>
       <c r="E364" s="21" t="s">
         <v>1201</v>
       </c>
@@ -29657,12 +29719,14 @@
       <c r="P364" s="1"/>
       <c r="Q364" s="1"/>
       <c r="R364" s="1" t="s">
-        <v>1759</v>
+        <v>1835</v>
       </c>
       <c r="S364" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="T364" s="1"/>
+      <c r="T364" s="1">
+        <v>3</v>
+      </c>
       <c r="U364" s="60" t="s">
         <v>2102</v>
       </c>
@@ -30212,7 +30276,7 @@
       <c r="C374" s="21" t="s">
         <v>1646</v>
       </c>
-      <c r="D374" s="19" t="s">
+      <c r="D374" s="16" t="s">
         <v>1611</v>
       </c>
       <c r="E374" s="37" t="s">
@@ -30251,12 +30315,14 @@
       </c>
       <c r="Q374" s="1"/>
       <c r="R374" s="1" t="s">
-        <v>1759</v>
+        <v>1835</v>
       </c>
       <c r="S374" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="T374" s="1"/>
+      <c r="T374" s="1">
+        <v>23</v>
+      </c>
       <c r="U374" s="60" t="s">
         <v>2257</v>
       </c>
@@ -31523,12 +31589,14 @@
       </c>
       <c r="Q395" s="1"/>
       <c r="R395" s="1" t="s">
-        <v>1759</v>
+        <v>1835</v>
       </c>
       <c r="S395" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="T395" s="1"/>
+      <c r="T395" s="1">
+        <v>8</v>
+      </c>
       <c r="U395" s="61" t="s">
         <v>2271</v>
       </c>
@@ -31606,7 +31674,7 @@
       <c r="C397" s="21" t="s">
         <v>1665</v>
       </c>
-      <c r="D397" s="19" t="s">
+      <c r="D397" s="16" t="s">
         <v>1633</v>
       </c>
       <c r="E397" s="37" t="s">
@@ -31643,12 +31711,14 @@
       <c r="P397" s="1"/>
       <c r="Q397" s="1"/>
       <c r="R397" s="1" t="s">
-        <v>1759</v>
+        <v>1835</v>
       </c>
       <c r="S397" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="T397" s="1"/>
+      <c r="T397" s="1">
+        <v>22</v>
+      </c>
       <c r="U397" s="61" t="s">
         <v>2274</v>
       </c>
@@ -33082,7 +33152,7 @@
     <hyperlink ref="D301" r:id="rId223" xr:uid="{86FFA566-E624-4AF7-8514-6C27F4C161C4}"/>
     <hyperlink ref="D372" r:id="rId224" display="mailto:benjamin.amann@univ-lr.fr" xr:uid="{FB37F046-3E8C-44B1-965B-C97F9EA82CED}"/>
     <hyperlink ref="D373" r:id="rId225" display="mailto:camille.bouchez@univ-rennes.fr" xr:uid="{02000C05-C2C4-4CA5-932D-0F19E3E8ADC3}"/>
-    <hyperlink ref="D374" r:id="rId226" display="mailto:bouchez@ipgp.fr" xr:uid="{EF7B83E6-8263-4F4A-8990-A4FF219972C0}"/>
+    <hyperlink ref="D374" r:id="rId226" xr:uid="{EF7B83E6-8263-4F4A-8990-A4FF219972C0}"/>
     <hyperlink ref="D375" r:id="rId227" display="mailto:eric.chaumillon@univ-lr.fr" xr:uid="{CF0D0627-8DC9-421B-8AB0-E2AA3037676C}"/>
     <hyperlink ref="D376" r:id="rId228" display="mailto:eliot.chatton@univ-rennes.fr" xr:uid="{AB33B82F-4B5B-4C6B-B2F7-2848C85803C3}"/>
     <hyperlink ref="D377" r:id="rId229" display="mailto:cdupuy@univ-lr.fr" xr:uid="{85C470E8-693B-4CDB-AC26-2B2F2605F62E}"/>
@@ -33105,7 +33175,7 @@
     <hyperlink ref="D394" r:id="rId246" display="mailto:Julien.Nemery@grenoble-inp.fr" xr:uid="{6FDF451D-F42A-43B7-8022-12E0F273F4D3}"/>
     <hyperlink ref="D395" r:id="rId247" xr:uid="{4178A1DF-1C5B-4C5A-B6DD-D1A40885B42D}"/>
     <hyperlink ref="D396" r:id="rId248" display="mailto:cristina.ribaudo@ensegid.fr" xr:uid="{E0F33667-16B4-4954-A6A2-B927FEFD3616}"/>
-    <hyperlink ref="D397" r:id="rId249" display="mailto:philippe.rosa@univ-nantes.fr" xr:uid="{399C084D-0179-479B-97B1-866B4936755B}"/>
+    <hyperlink ref="D397" r:id="rId249" xr:uid="{399C084D-0179-479B-97B1-866B4936755B}"/>
     <hyperlink ref="D398" r:id="rId250" display="mailto:nicolas.savoye@u-bordeaux.fr" xr:uid="{9B1C3AF1-9F70-472A-9B83-1576E6459B24}"/>
     <hyperlink ref="D399" r:id="rId251" display="mailto:vincent.thieu@sorbonne-universite.fr" xr:uid="{C2815038-D142-45FB-A194-E2F0C361D416}"/>
     <hyperlink ref="D400" r:id="rId252" display="mailto:delphine.tisserand@univ-grenoble-alpes.fr" xr:uid="{D7356312-9493-4442-90FB-FFFD508D3B30}"/>
@@ -33131,8 +33201,15 @@
     <hyperlink ref="D103" r:id="rId272" xr:uid="{7089C2BE-4027-4FC6-A1F9-6A1AE4B8725E}"/>
     <hyperlink ref="D100" r:id="rId273" xr:uid="{71155148-E90E-47B9-8E3F-E19F3F36A0ED}"/>
     <hyperlink ref="D347" r:id="rId274" xr:uid="{81D62058-B298-48D5-BEA8-2A123AB178FF}"/>
+    <hyperlink ref="D213" r:id="rId275" xr:uid="{78DE2F58-987A-484A-AF89-217D5EAE23C0}"/>
+    <hyperlink ref="D364" r:id="rId276" xr:uid="{4F33A286-1F0E-47CA-9ABD-7D8466C63771}"/>
+    <hyperlink ref="D267" r:id="rId277" xr:uid="{14E47318-C4D0-4AA4-98F9-0DCED3D68A79}"/>
+    <hyperlink ref="D252" r:id="rId278" xr:uid="{D3FF3E83-AA68-4EF8-9F7B-0E2057D0E740}"/>
+    <hyperlink ref="D249" r:id="rId279" xr:uid="{35DDB8DC-C0DF-47BC-9494-B0AFFE3D9CCC}"/>
+    <hyperlink ref="D320" r:id="rId280" xr:uid="{1C3E9AEE-E546-434D-AB91-1B2D579937C2}"/>
+    <hyperlink ref="D316" r:id="rId281" xr:uid="{09E32029-305F-4D3B-9C04-A812A87D30A9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId275"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId282"/>
 </worksheet>
 </file>
--- a/Data/FairCarboN_Datas_Contacts.xlsx
+++ b/Data/FairCarboN_Datas_Contacts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE6A123-8EF9-498C-97C8-5B653B74AF7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C8DF57-CD37-4F7B-A56D-45D3118E2B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6846" uniqueCount="2359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6848" uniqueCount="2361">
   <si>
     <t>Acronyme PEPR</t>
   </si>
@@ -7162,6 +7162,12 @@
   </si>
   <si>
     <t>christophe.proisy@ird.fr</t>
+  </si>
+  <si>
+    <t>marie.arnaud.1@sorbonne-universite.fr</t>
+  </si>
+  <si>
+    <t>adrien.baysse-laine@umrpacte.fr</t>
   </si>
 </sst>
 </file>
@@ -7901,7 +7907,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:V417"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -7994,7 +7999,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="2" spans="1:22" s="2" customFormat="1" ht="188.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" s="2" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -8054,7 +8059,7 @@
       </c>
       <c r="V2" s="1"/>
     </row>
-    <row r="3" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -8114,7 +8119,7 @@
       </c>
       <c r="V3" s="1"/>
     </row>
-    <row r="4" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -8174,7 +8179,7 @@
       </c>
       <c r="V4" s="1"/>
     </row>
-    <row r="5" spans="1:22" s="2" customFormat="1" ht="188.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" s="2" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -8234,7 +8239,7 @@
       </c>
       <c r="V5" s="1"/>
     </row>
-    <row r="6" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -8296,7 +8301,7 @@
       </c>
       <c r="V6" s="1"/>
     </row>
-    <row r="7" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -8358,7 +8363,7 @@
       </c>
       <c r="V7" s="1"/>
     </row>
-    <row r="8" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -8418,7 +8423,7 @@
       </c>
       <c r="V8" s="1"/>
     </row>
-    <row r="9" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -8478,7 +8483,7 @@
       </c>
       <c r="V9" s="1"/>
     </row>
-    <row r="10" spans="1:22" s="2" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" s="2" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -8538,7 +8543,7 @@
       </c>
       <c r="V10" s="1"/>
     </row>
-    <row r="11" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
@@ -8598,7 +8603,7 @@
       </c>
       <c r="V11" s="1"/>
     </row>
-    <row r="12" spans="1:22" s="2" customFormat="1" ht="188.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" s="2" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
@@ -8658,7 +8663,7 @@
       </c>
       <c r="V12" s="1"/>
     </row>
-    <row r="13" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
@@ -8718,7 +8723,7 @@
       </c>
       <c r="V13" s="1"/>
     </row>
-    <row r="14" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>6</v>
       </c>
@@ -8780,7 +8785,7 @@
       </c>
       <c r="V14" s="1"/>
     </row>
-    <row r="15" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>6</v>
       </c>
@@ -8840,7 +8845,7 @@
       </c>
       <c r="V15" s="1"/>
     </row>
-    <row r="16" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>6</v>
       </c>
@@ -8902,7 +8907,7 @@
       </c>
       <c r="V16" s="1"/>
     </row>
-    <row r="17" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>6</v>
       </c>
@@ -8962,7 +8967,7 @@
       </c>
       <c r="V17" s="1"/>
     </row>
-    <row r="18" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>6</v>
       </c>
@@ -9022,7 +9027,7 @@
       </c>
       <c r="V18" s="1"/>
     </row>
-    <row r="19" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>6</v>
       </c>
@@ -9082,7 +9087,7 @@
       </c>
       <c r="V19" s="1"/>
     </row>
-    <row r="20" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>6</v>
       </c>
@@ -9142,7 +9147,7 @@
       </c>
       <c r="V20" s="1"/>
     </row>
-    <row r="21" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>6</v>
       </c>
@@ -9202,7 +9207,7 @@
       </c>
       <c r="V21" s="1"/>
     </row>
-    <row r="22" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>6</v>
       </c>
@@ -9262,7 +9267,7 @@
       </c>
       <c r="V22" s="1"/>
     </row>
-    <row r="23" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>6</v>
       </c>
@@ -9322,7 +9327,7 @@
       </c>
       <c r="V23" s="1"/>
     </row>
-    <row r="24" spans="1:22" s="2" customFormat="1" ht="275.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:22" s="2" customFormat="1" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>6</v>
       </c>
@@ -9388,7 +9393,7 @@
         <v>2331</v>
       </c>
     </row>
-    <row r="25" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>6</v>
       </c>
@@ -9450,7 +9455,7 @@
       </c>
       <c r="V25" s="1"/>
     </row>
-    <row r="26" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>6</v>
       </c>
@@ -9510,7 +9515,7 @@
       </c>
       <c r="V26" s="1"/>
     </row>
-    <row r="27" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>6</v>
       </c>
@@ -9570,7 +9575,7 @@
       </c>
       <c r="V27" s="1"/>
     </row>
-    <row r="28" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>6</v>
       </c>
@@ -9630,7 +9635,7 @@
       </c>
       <c r="V28" s="1"/>
     </row>
-    <row r="29" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>6</v>
       </c>
@@ -9690,7 +9695,7 @@
       </c>
       <c r="V29" s="1"/>
     </row>
-    <row r="30" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>6</v>
       </c>
@@ -9750,7 +9755,7 @@
       </c>
       <c r="V30" s="1"/>
     </row>
-    <row r="31" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>6</v>
       </c>
@@ -9812,7 +9817,7 @@
       </c>
       <c r="V31" s="1"/>
     </row>
-    <row r="32" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>6</v>
       </c>
@@ -9872,7 +9877,7 @@
       </c>
       <c r="V32" s="1"/>
     </row>
-    <row r="33" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>6</v>
       </c>
@@ -9932,7 +9937,7 @@
       </c>
       <c r="V33" s="1"/>
     </row>
-    <row r="34" spans="1:22" s="2" customFormat="1" ht="232" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:22" s="2" customFormat="1" ht="232" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>6</v>
       </c>
@@ -9994,7 +9999,7 @@
       </c>
       <c r="V34" s="1"/>
     </row>
-    <row r="35" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>6</v>
       </c>
@@ -10054,7 +10059,7 @@
       </c>
       <c r="V35" s="1"/>
     </row>
-    <row r="36" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>6</v>
       </c>
@@ -10114,7 +10119,7 @@
       </c>
       <c r="V36" s="1"/>
     </row>
-    <row r="37" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>6</v>
       </c>
@@ -10174,7 +10179,7 @@
       </c>
       <c r="V37" s="1"/>
     </row>
-    <row r="38" spans="1:22" s="2" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:22" s="2" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>6</v>
       </c>
@@ -10234,7 +10239,7 @@
       </c>
       <c r="V38" s="1"/>
     </row>
-    <row r="39" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>6</v>
       </c>
@@ -10294,7 +10299,7 @@
       </c>
       <c r="V39" s="1"/>
     </row>
-    <row r="40" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>6</v>
       </c>
@@ -10354,7 +10359,7 @@
       </c>
       <c r="V40" s="1"/>
     </row>
-    <row r="41" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>6</v>
       </c>
@@ -10414,7 +10419,7 @@
       </c>
       <c r="V41" s="1"/>
     </row>
-    <row r="42" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>6</v>
       </c>
@@ -10474,7 +10479,7 @@
       </c>
       <c r="V42" s="1"/>
     </row>
-    <row r="43" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>6</v>
       </c>
@@ -10534,7 +10539,7 @@
       </c>
       <c r="V43" s="1"/>
     </row>
-    <row r="44" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>6</v>
       </c>
@@ -10594,7 +10599,7 @@
       </c>
       <c r="V44" s="1"/>
     </row>
-    <row r="45" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>6</v>
       </c>
@@ -10654,7 +10659,7 @@
       </c>
       <c r="V45" s="1"/>
     </row>
-    <row r="46" spans="1:22" s="2" customFormat="1" ht="275.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:22" s="2" customFormat="1" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>6</v>
       </c>
@@ -10718,7 +10723,7 @@
       </c>
       <c r="V46" s="1"/>
     </row>
-    <row r="47" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>6</v>
       </c>
@@ -10778,7 +10783,7 @@
       </c>
       <c r="V47" s="1"/>
     </row>
-    <row r="48" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>6</v>
       </c>
@@ -10840,7 +10845,7 @@
       </c>
       <c r="V48" s="1"/>
     </row>
-    <row r="49" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>6</v>
       </c>
@@ -10900,7 +10905,7 @@
       </c>
       <c r="V49" s="1"/>
     </row>
-    <row r="50" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>6</v>
       </c>
@@ -10960,7 +10965,7 @@
       </c>
       <c r="V50" s="1"/>
     </row>
-    <row r="51" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>6</v>
       </c>
@@ -11020,7 +11025,7 @@
       </c>
       <c r="V51" s="1"/>
     </row>
-    <row r="52" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>6</v>
       </c>
@@ -11080,7 +11085,7 @@
       </c>
       <c r="V52" s="1"/>
     </row>
-    <row r="53" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>6</v>
       </c>
@@ -11140,7 +11145,7 @@
       </c>
       <c r="V53" s="1"/>
     </row>
-    <row r="54" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>6</v>
       </c>
@@ -11200,7 +11205,7 @@
       </c>
       <c r="V54" s="1"/>
     </row>
-    <row r="55" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>6</v>
       </c>
@@ -11260,7 +11265,7 @@
       </c>
       <c r="V55" s="1"/>
     </row>
-    <row r="56" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>6</v>
       </c>
@@ -11320,7 +11325,7 @@
       </c>
       <c r="V56" s="1"/>
     </row>
-    <row r="57" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>6</v>
       </c>
@@ -11380,7 +11385,7 @@
       </c>
       <c r="V57" s="1"/>
     </row>
-    <row r="58" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>6</v>
       </c>
@@ -11442,7 +11447,7 @@
       </c>
       <c r="V58" s="1"/>
     </row>
-    <row r="59" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>6</v>
       </c>
@@ -11504,7 +11509,7 @@
       </c>
       <c r="V59" s="1"/>
     </row>
-    <row r="60" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>6</v>
       </c>
@@ -11566,7 +11571,7 @@
       </c>
       <c r="V60" s="1"/>
     </row>
-    <row r="61" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>6</v>
       </c>
@@ -11628,7 +11633,7 @@
       </c>
       <c r="V61" s="1"/>
     </row>
-    <row r="62" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>6</v>
       </c>
@@ -11688,7 +11693,7 @@
       </c>
       <c r="V62" s="1"/>
     </row>
-    <row r="63" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>6</v>
       </c>
@@ -11750,7 +11755,7 @@
       </c>
       <c r="V63" s="1"/>
     </row>
-    <row r="64" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>6</v>
       </c>
@@ -11810,7 +11815,7 @@
       </c>
       <c r="V64" s="1"/>
     </row>
-    <row r="65" spans="1:22" s="2" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:22" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>6</v>
       </c>
@@ -11874,7 +11879,7 @@
       </c>
       <c r="V65" s="1"/>
     </row>
-    <row r="66" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>6</v>
       </c>
@@ -11934,7 +11939,7 @@
       </c>
       <c r="V66" s="1"/>
     </row>
-    <row r="67" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>6</v>
       </c>
@@ -11996,7 +12001,7 @@
       </c>
       <c r="V67" s="1"/>
     </row>
-    <row r="68" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>6</v>
       </c>
@@ -12056,7 +12061,7 @@
       </c>
       <c r="V68" s="1"/>
     </row>
-    <row r="69" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>6</v>
       </c>
@@ -12116,7 +12121,7 @@
       </c>
       <c r="V69" s="1"/>
     </row>
-    <row r="70" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>6</v>
       </c>
@@ -12176,7 +12181,7 @@
       </c>
       <c r="V70" s="1"/>
     </row>
-    <row r="71" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>6</v>
       </c>
@@ -12238,7 +12243,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="72" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>6</v>
       </c>
@@ -12298,7 +12303,7 @@
       </c>
       <c r="V72" s="1"/>
     </row>
-    <row r="73" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>6</v>
       </c>
@@ -12358,7 +12363,7 @@
       </c>
       <c r="V73" s="1"/>
     </row>
-    <row r="74" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>6</v>
       </c>
@@ -12418,7 +12423,7 @@
       </c>
       <c r="V74" s="1"/>
     </row>
-    <row r="75" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>6</v>
       </c>
@@ -12478,7 +12483,7 @@
       </c>
       <c r="V75" s="1"/>
     </row>
-    <row r="76" spans="1:22" s="2" customFormat="1" ht="27.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:22" s="2" customFormat="1" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>6</v>
       </c>
@@ -12540,7 +12545,7 @@
       </c>
       <c r="V76" s="1"/>
     </row>
-    <row r="77" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>6</v>
       </c>
@@ -12600,7 +12605,7 @@
       </c>
       <c r="V77" s="1"/>
     </row>
-    <row r="78" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>6</v>
       </c>
@@ -12660,7 +12665,7 @@
       </c>
       <c r="V78" s="1"/>
     </row>
-    <row r="79" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>6</v>
       </c>
@@ -12720,7 +12725,7 @@
       </c>
       <c r="V79" s="1"/>
     </row>
-    <row r="80" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>6</v>
       </c>
@@ -12782,7 +12787,7 @@
       </c>
       <c r="V80" s="1"/>
     </row>
-    <row r="81" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>6</v>
       </c>
@@ -12842,7 +12847,7 @@
       </c>
       <c r="V81" s="1"/>
     </row>
-    <row r="82" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>6</v>
       </c>
@@ -12904,7 +12909,7 @@
       </c>
       <c r="V82" s="1"/>
     </row>
-    <row r="83" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>6</v>
       </c>
@@ -12966,7 +12971,7 @@
       </c>
       <c r="V83" s="1"/>
     </row>
-    <row r="84" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>6</v>
       </c>
@@ -13028,7 +13033,7 @@
       </c>
       <c r="V84" s="1"/>
     </row>
-    <row r="85" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>6</v>
       </c>
@@ -13092,7 +13097,7 @@
       </c>
       <c r="V85" s="1"/>
     </row>
-    <row r="86" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>6</v>
       </c>
@@ -13154,7 +13159,7 @@
       </c>
       <c r="V86" s="1"/>
     </row>
-    <row r="87" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>6</v>
       </c>
@@ -13216,7 +13221,7 @@
       </c>
       <c r="V87" s="1"/>
     </row>
-    <row r="88" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>6</v>
       </c>
@@ -13276,7 +13281,7 @@
       </c>
       <c r="V88" s="1"/>
     </row>
-    <row r="89" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>6</v>
       </c>
@@ -13340,7 +13345,7 @@
       </c>
       <c r="V89" s="1"/>
     </row>
-    <row r="90" spans="1:22" s="2" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:22" s="2" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>6</v>
       </c>
@@ -13402,7 +13407,7 @@
       </c>
       <c r="V90" s="1"/>
     </row>
-    <row r="91" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>6</v>
       </c>
@@ -13464,7 +13469,7 @@
       </c>
       <c r="V91" s="1"/>
     </row>
-    <row r="92" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>6</v>
       </c>
@@ -13526,7 +13531,7 @@
       </c>
       <c r="V92" s="1"/>
     </row>
-    <row r="93" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>6</v>
       </c>
@@ -13586,7 +13591,7 @@
       </c>
       <c r="V93" s="1"/>
     </row>
-    <row r="94" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>6</v>
       </c>
@@ -13648,7 +13653,7 @@
       </c>
       <c r="V94" s="1"/>
     </row>
-    <row r="95" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>6</v>
       </c>
@@ -13710,7 +13715,7 @@
       </c>
       <c r="V95" s="1"/>
     </row>
-    <row r="96" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>6</v>
       </c>
@@ -13772,7 +13777,7 @@
       </c>
       <c r="V96" s="1"/>
     </row>
-    <row r="97" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>6</v>
       </c>
@@ -13834,7 +13839,7 @@
       </c>
       <c r="V97" s="1"/>
     </row>
-    <row r="98" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>6</v>
       </c>
@@ -13896,7 +13901,7 @@
       </c>
       <c r="V98" s="1"/>
     </row>
-    <row r="99" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>6</v>
       </c>
@@ -13958,7 +13963,7 @@
       </c>
       <c r="V99" s="1"/>
     </row>
-    <row r="100" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>6</v>
       </c>
@@ -14020,7 +14025,7 @@
       </c>
       <c r="V100" s="1"/>
     </row>
-    <row r="101" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>6</v>
       </c>
@@ -14084,7 +14089,7 @@
       </c>
       <c r="V101" s="1"/>
     </row>
-    <row r="102" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>6</v>
       </c>
@@ -14146,7 +14151,7 @@
       </c>
       <c r="V102" s="1"/>
     </row>
-    <row r="103" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>6</v>
       </c>
@@ -14208,7 +14213,7 @@
       </c>
       <c r="V103" s="1"/>
     </row>
-    <row r="104" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>6</v>
       </c>
@@ -14272,7 +14277,7 @@
       </c>
       <c r="V104" s="1"/>
     </row>
-    <row r="105" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>6</v>
       </c>
@@ -14334,7 +14339,7 @@
       </c>
       <c r="V105" s="1"/>
     </row>
-    <row r="106" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>6</v>
       </c>
@@ -14394,7 +14399,7 @@
       </c>
       <c r="V106" s="1"/>
     </row>
-    <row r="107" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>6</v>
       </c>
@@ -14456,7 +14461,7 @@
       </c>
       <c r="V107" s="1"/>
     </row>
-    <row r="108" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>6</v>
       </c>
@@ -14514,7 +14519,7 @@
       </c>
       <c r="V108" s="1"/>
     </row>
-    <row r="109" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>6</v>
       </c>
@@ -14576,7 +14581,7 @@
       </c>
       <c r="V109" s="1"/>
     </row>
-    <row r="110" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>6</v>
       </c>
@@ -14640,7 +14645,7 @@
       </c>
       <c r="V110" s="1"/>
     </row>
-    <row r="111" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>6</v>
       </c>
@@ -14702,7 +14707,7 @@
       </c>
       <c r="V111" s="1"/>
     </row>
-    <row r="112" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>6</v>
       </c>
@@ -14764,7 +14769,7 @@
       </c>
       <c r="V112" s="1"/>
     </row>
-    <row r="113" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>6</v>
       </c>
@@ -14826,7 +14831,7 @@
       </c>
       <c r="V113" s="1"/>
     </row>
-    <row r="114" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>6</v>
       </c>
@@ -14886,7 +14891,7 @@
       </c>
       <c r="V114" s="1"/>
     </row>
-    <row r="115" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>6</v>
       </c>
@@ -14948,7 +14953,7 @@
       </c>
       <c r="V115" s="1"/>
     </row>
-    <row r="116" spans="1:22" s="2" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:22" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>6</v>
       </c>
@@ -15012,7 +15017,7 @@
         <v>2321</v>
       </c>
     </row>
-    <row r="117" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>6</v>
       </c>
@@ -15074,7 +15079,7 @@
       </c>
       <c r="V117" s="1"/>
     </row>
-    <row r="118" spans="1:22" s="2" customFormat="1" ht="406" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:22" s="2" customFormat="1" ht="406" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>6</v>
       </c>
@@ -15138,7 +15143,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="119" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>6</v>
       </c>
@@ -15200,7 +15205,7 @@
       </c>
       <c r="V119" s="1"/>
     </row>
-    <row r="120" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>6</v>
       </c>
@@ -15264,7 +15269,7 @@
       </c>
       <c r="V120" s="1"/>
     </row>
-    <row r="121" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>6</v>
       </c>
@@ -15326,7 +15331,7 @@
       </c>
       <c r="V121" s="1"/>
     </row>
-    <row r="122" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>6</v>
       </c>
@@ -15388,7 +15393,7 @@
       </c>
       <c r="V122" s="1"/>
     </row>
-    <row r="123" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>6</v>
       </c>
@@ -15450,7 +15455,7 @@
       </c>
       <c r="V123" s="1"/>
     </row>
-    <row r="124" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>6</v>
       </c>
@@ -15512,7 +15517,7 @@
       </c>
       <c r="V124" s="1"/>
     </row>
-    <row r="125" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>6</v>
       </c>
@@ -15574,7 +15579,7 @@
       </c>
       <c r="V125" s="1"/>
     </row>
-    <row r="126" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>6</v>
       </c>
@@ -15636,7 +15641,7 @@
       </c>
       <c r="V126" s="1"/>
     </row>
-    <row r="127" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>6</v>
       </c>
@@ -15698,7 +15703,7 @@
       </c>
       <c r="V127" s="1"/>
     </row>
-    <row r="128" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>6</v>
       </c>
@@ -15760,7 +15765,7 @@
       </c>
       <c r="V128" s="1"/>
     </row>
-    <row r="129" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>6</v>
       </c>
@@ -15822,7 +15827,7 @@
       </c>
       <c r="V129" s="1"/>
     </row>
-    <row r="130" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>6</v>
       </c>
@@ -15884,7 +15889,7 @@
       </c>
       <c r="V130" s="1"/>
     </row>
-    <row r="131" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>6</v>
       </c>
@@ -15946,7 +15951,7 @@
       </c>
       <c r="V131" s="1"/>
     </row>
-    <row r="132" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>6</v>
       </c>
@@ -16008,7 +16013,7 @@
       </c>
       <c r="V132" s="1"/>
     </row>
-    <row r="133" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>6</v>
       </c>
@@ -16070,7 +16075,7 @@
       </c>
       <c r="V133" s="1"/>
     </row>
-    <row r="134" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>6</v>
       </c>
@@ -16132,7 +16137,7 @@
       </c>
       <c r="V134" s="1"/>
     </row>
-    <row r="135" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>6</v>
       </c>
@@ -16194,7 +16199,7 @@
       </c>
       <c r="V135" s="1"/>
     </row>
-    <row r="136" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>6</v>
       </c>
@@ -16256,7 +16261,7 @@
       </c>
       <c r="V136" s="1"/>
     </row>
-    <row r="137" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>6</v>
       </c>
@@ -16318,7 +16323,7 @@
       </c>
       <c r="V137" s="1"/>
     </row>
-    <row r="138" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>6</v>
       </c>
@@ -16380,7 +16385,7 @@
       </c>
       <c r="V138" s="1"/>
     </row>
-    <row r="139" spans="1:22" s="2" customFormat="1" ht="275.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:22" s="2" customFormat="1" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>6</v>
       </c>
@@ -16446,7 +16451,7 @@
         <v>2331</v>
       </c>
     </row>
-    <row r="140" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>6</v>
       </c>
@@ -16508,7 +16513,7 @@
       </c>
       <c r="V140" s="1"/>
     </row>
-    <row r="141" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>6</v>
       </c>
@@ -16570,7 +16575,7 @@
       </c>
       <c r="V141" s="1"/>
     </row>
-    <row r="142" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>6</v>
       </c>
@@ -16632,7 +16637,7 @@
       </c>
       <c r="V142" s="1"/>
     </row>
-    <row r="143" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>6</v>
       </c>
@@ -16696,7 +16701,7 @@
       </c>
       <c r="V143" s="1"/>
     </row>
-    <row r="144" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>6</v>
       </c>
@@ -16758,7 +16763,7 @@
       </c>
       <c r="V144" s="1"/>
     </row>
-    <row r="145" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>6</v>
       </c>
@@ -16820,7 +16825,7 @@
       </c>
       <c r="V145" s="1"/>
     </row>
-    <row r="146" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>6</v>
       </c>
@@ -16884,7 +16889,7 @@
       </c>
       <c r="V146" s="1"/>
     </row>
-    <row r="147" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>6</v>
       </c>
@@ -16946,7 +16951,7 @@
       </c>
       <c r="V147" s="1"/>
     </row>
-    <row r="148" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>6</v>
       </c>
@@ -17008,7 +17013,7 @@
       </c>
       <c r="V148" s="1"/>
     </row>
-    <row r="149" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>6</v>
       </c>
@@ -17070,7 +17075,7 @@
       </c>
       <c r="V149" s="1"/>
     </row>
-    <row r="150" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>6</v>
       </c>
@@ -17132,7 +17137,7 @@
       </c>
       <c r="V150" s="1"/>
     </row>
-    <row r="151" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>6</v>
       </c>
@@ -17194,7 +17199,7 @@
       </c>
       <c r="V151" s="1"/>
     </row>
-    <row r="152" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>6</v>
       </c>
@@ -17256,7 +17261,7 @@
       </c>
       <c r="V152" s="1"/>
     </row>
-    <row r="153" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>6</v>
       </c>
@@ -17318,7 +17323,7 @@
       </c>
       <c r="V153" s="1"/>
     </row>
-    <row r="154" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>6</v>
       </c>
@@ -17380,7 +17385,7 @@
       </c>
       <c r="V154" s="1"/>
     </row>
-    <row r="155" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>6</v>
       </c>
@@ -17442,7 +17447,7 @@
       </c>
       <c r="V155" s="1"/>
     </row>
-    <row r="156" spans="1:22" s="2" customFormat="1" ht="65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:22" s="2" customFormat="1" ht="65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>6</v>
       </c>
@@ -17504,7 +17509,7 @@
       </c>
       <c r="V156" s="1"/>
     </row>
-    <row r="157" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>6</v>
       </c>
@@ -17566,7 +17571,7 @@
       </c>
       <c r="V157" s="1"/>
     </row>
-    <row r="158" spans="1:22" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>6</v>
       </c>
@@ -17628,7 +17633,7 @@
       </c>
       <c r="V158" s="1"/>
     </row>
-    <row r="159" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>6</v>
       </c>
@@ -17690,7 +17695,7 @@
       </c>
       <c r="V159" s="1"/>
     </row>
-    <row r="160" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>6</v>
       </c>
@@ -17754,7 +17759,7 @@
       </c>
       <c r="V160" s="1"/>
     </row>
-    <row r="161" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>6</v>
       </c>
@@ -17816,7 +17821,7 @@
       </c>
       <c r="V161" s="1"/>
     </row>
-    <row r="162" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
         <v>6</v>
       </c>
@@ -17878,7 +17883,7 @@
       </c>
       <c r="V162" s="1"/>
     </row>
-    <row r="163" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
         <v>6</v>
       </c>
@@ -17940,7 +17945,7 @@
       </c>
       <c r="V163" s="1"/>
     </row>
-    <row r="164" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
         <v>6</v>
       </c>
@@ -18002,7 +18007,7 @@
       </c>
       <c r="V164" s="1"/>
     </row>
-    <row r="165" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
         <v>6</v>
       </c>
@@ -18066,7 +18071,7 @@
       </c>
       <c r="V165" s="1"/>
     </row>
-    <row r="166" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
         <v>6</v>
       </c>
@@ -18132,7 +18137,7 @@
       </c>
       <c r="V166" s="1"/>
     </row>
-    <row r="167" spans="1:22" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
         <v>6</v>
       </c>
@@ -18194,7 +18199,7 @@
       </c>
       <c r="V167" s="1"/>
     </row>
-    <row r="168" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
         <v>6</v>
       </c>
@@ -18256,7 +18261,7 @@
       </c>
       <c r="V168" s="1"/>
     </row>
-    <row r="169" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
         <v>6</v>
       </c>
@@ -18318,7 +18323,7 @@
       </c>
       <c r="V169" s="1"/>
     </row>
-    <row r="170" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
         <v>6</v>
       </c>
@@ -18380,7 +18385,7 @@
       </c>
       <c r="V170" s="1"/>
     </row>
-    <row r="171" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
         <v>6</v>
       </c>
@@ -18442,7 +18447,7 @@
       </c>
       <c r="V171" s="1"/>
     </row>
-    <row r="172" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
         <v>6</v>
       </c>
@@ -18504,7 +18509,7 @@
       </c>
       <c r="V172" s="1"/>
     </row>
-    <row r="173" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
         <v>6</v>
       </c>
@@ -18566,7 +18571,7 @@
       </c>
       <c r="V173" s="1"/>
     </row>
-    <row r="174" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
         <v>6</v>
       </c>
@@ -18628,7 +18633,7 @@
       </c>
       <c r="V174" s="1"/>
     </row>
-    <row r="175" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
         <v>6</v>
       </c>
@@ -18690,7 +18695,7 @@
       </c>
       <c r="V175" s="1"/>
     </row>
-    <row r="176" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
         <v>6</v>
       </c>
@@ -18752,7 +18757,7 @@
       </c>
       <c r="V176" s="1"/>
     </row>
-    <row r="177" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
         <v>6</v>
       </c>
@@ -18814,7 +18819,7 @@
       </c>
       <c r="V177" s="1"/>
     </row>
-    <row r="178" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
         <v>6</v>
       </c>
@@ -18876,7 +18881,7 @@
       </c>
       <c r="V178" s="1"/>
     </row>
-    <row r="179" spans="1:22" s="2" customFormat="1" ht="174" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:22" s="2" customFormat="1" ht="174" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
         <v>6</v>
       </c>
@@ -18940,7 +18945,7 @@
       </c>
       <c r="V179" s="1"/>
     </row>
-    <row r="180" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
         <v>6</v>
       </c>
@@ -19002,7 +19007,7 @@
       </c>
       <c r="V180" s="1"/>
     </row>
-    <row r="181" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
         <v>6</v>
       </c>
@@ -19064,7 +19069,7 @@
       </c>
       <c r="V181" s="1"/>
     </row>
-    <row r="182" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
         <v>6</v>
       </c>
@@ -19126,7 +19131,7 @@
       </c>
       <c r="V182" s="1"/>
     </row>
-    <row r="183" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
         <v>6</v>
       </c>
@@ -19188,7 +19193,7 @@
       </c>
       <c r="V183" s="1"/>
     </row>
-    <row r="184" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
         <v>6</v>
       </c>
@@ -19252,7 +19257,7 @@
       </c>
       <c r="V184" s="1"/>
     </row>
-    <row r="185" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
         <v>6</v>
       </c>
@@ -19314,7 +19319,7 @@
       </c>
       <c r="V185" s="1"/>
     </row>
-    <row r="186" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
         <v>6</v>
       </c>
@@ -19376,7 +19381,7 @@
       </c>
       <c r="V186" s="1"/>
     </row>
-    <row r="187" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
         <v>6</v>
       </c>
@@ -19438,7 +19443,7 @@
       </c>
       <c r="V187" s="1"/>
     </row>
-    <row r="188" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
         <v>6</v>
       </c>
@@ -19500,7 +19505,7 @@
       </c>
       <c r="V188" s="1"/>
     </row>
-    <row r="189" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
         <v>6</v>
       </c>
@@ -19562,7 +19567,7 @@
       </c>
       <c r="V189" s="1"/>
     </row>
-    <row r="190" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
         <v>6</v>
       </c>
@@ -19622,7 +19627,7 @@
       </c>
       <c r="V190" s="1"/>
     </row>
-    <row r="191" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
         <v>6</v>
       </c>
@@ -19684,7 +19689,7 @@
       </c>
       <c r="V191" s="1"/>
     </row>
-    <row r="192" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
         <v>6</v>
       </c>
@@ -19746,7 +19751,7 @@
       </c>
       <c r="V192" s="1"/>
     </row>
-    <row r="193" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
         <v>6</v>
       </c>
@@ -19808,7 +19813,7 @@
       </c>
       <c r="V193" s="1"/>
     </row>
-    <row r="194" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
         <v>6</v>
       </c>
@@ -19868,7 +19873,7 @@
       </c>
       <c r="V194" s="1"/>
     </row>
-    <row r="195" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
         <v>6</v>
       </c>
@@ -19928,7 +19933,7 @@
       </c>
       <c r="V195" s="1"/>
     </row>
-    <row r="196" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
         <v>6</v>
       </c>
@@ -19988,7 +19993,7 @@
       </c>
       <c r="V196" s="1"/>
     </row>
-    <row r="197" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
         <v>6</v>
       </c>
@@ -20050,7 +20055,7 @@
       </c>
       <c r="V197" s="1"/>
     </row>
-    <row r="198" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
         <v>6</v>
       </c>
@@ -20112,7 +20117,7 @@
       </c>
       <c r="V198" s="1"/>
     </row>
-    <row r="199" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
         <v>6</v>
       </c>
@@ -20174,7 +20179,7 @@
       </c>
       <c r="V199" s="1"/>
     </row>
-    <row r="200" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
         <v>6</v>
       </c>
@@ -20236,7 +20241,7 @@
       </c>
       <c r="V200" s="1"/>
     </row>
-    <row r="201" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
         <v>6</v>
       </c>
@@ -20298,7 +20303,7 @@
       </c>
       <c r="V201" s="1"/>
     </row>
-    <row r="202" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
         <v>6</v>
       </c>
@@ -20360,7 +20365,7 @@
       </c>
       <c r="V202" s="1"/>
     </row>
-    <row r="203" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A203" s="1" t="s">
         <v>6</v>
       </c>
@@ -20422,7 +20427,7 @@
       </c>
       <c r="V203" s="1"/>
     </row>
-    <row r="204" spans="1:22" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:22" ht="87" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
         <v>6</v>
       </c>
@@ -20484,7 +20489,7 @@
       </c>
       <c r="V204" s="1"/>
     </row>
-    <row r="205" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
         <v>6</v>
       </c>
@@ -20546,7 +20551,7 @@
       </c>
       <c r="V205" s="1"/>
     </row>
-    <row r="206" spans="1:22" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:22" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
         <v>6</v>
       </c>
@@ -20606,7 +20611,7 @@
       </c>
       <c r="V206" s="1"/>
     </row>
-    <row r="207" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
         <v>6</v>
       </c>
@@ -20668,7 +20673,7 @@
       </c>
       <c r="V207" s="1"/>
     </row>
-    <row r="208" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
         <v>6</v>
       </c>
@@ -20730,7 +20735,7 @@
       </c>
       <c r="V208" s="1"/>
     </row>
-    <row r="209" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
         <v>6</v>
       </c>
@@ -20790,7 +20795,7 @@
       </c>
       <c r="V209" s="1"/>
     </row>
-    <row r="210" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
         <v>6</v>
       </c>
@@ -20850,7 +20855,7 @@
       </c>
       <c r="V210" s="1"/>
     </row>
-    <row r="211" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A211" s="1" t="s">
         <v>6</v>
       </c>
@@ -20910,7 +20915,7 @@
       </c>
       <c r="V211" s="1"/>
     </row>
-    <row r="212" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
         <v>6</v>
       </c>
@@ -20970,7 +20975,7 @@
       </c>
       <c r="V212" s="1"/>
     </row>
-    <row r="213" spans="1:22" s="2" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:22" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
         <v>6</v>
       </c>
@@ -21032,7 +21037,7 @@
         <v>2294</v>
       </c>
     </row>
-    <row r="214" spans="1:22" s="2" customFormat="1" ht="188.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:22" s="2" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
         <v>6</v>
       </c>
@@ -21092,7 +21097,7 @@
       </c>
       <c r="V214" s="1"/>
     </row>
-    <row r="215" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A215" s="1" t="s">
         <v>6</v>
       </c>
@@ -21152,7 +21157,7 @@
       </c>
       <c r="V215" s="1"/>
     </row>
-    <row r="216" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A216" s="1" t="s">
         <v>6</v>
       </c>
@@ -21212,7 +21217,7 @@
       </c>
       <c r="V216" s="1"/>
     </row>
-    <row r="217" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
         <v>6</v>
       </c>
@@ -21272,7 +21277,7 @@
       </c>
       <c r="V217" s="1"/>
     </row>
-    <row r="218" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A218" s="1" t="s">
         <v>6</v>
       </c>
@@ -21334,7 +21339,7 @@
       </c>
       <c r="V218" s="1"/>
     </row>
-    <row r="219" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
         <v>6</v>
       </c>
@@ -21396,7 +21401,7 @@
       </c>
       <c r="V219" s="1"/>
     </row>
-    <row r="220" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
         <v>6</v>
       </c>
@@ -21458,7 +21463,7 @@
       </c>
       <c r="V220" s="1"/>
     </row>
-    <row r="221" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
         <v>6</v>
       </c>
@@ -21518,7 +21523,7 @@
       </c>
       <c r="V221" s="1"/>
     </row>
-    <row r="222" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A222" s="1" t="s">
         <v>6</v>
       </c>
@@ -21580,7 +21585,7 @@
       </c>
       <c r="V222" s="1"/>
     </row>
-    <row r="223" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A223" s="1" t="s">
         <v>6</v>
       </c>
@@ -21642,7 +21647,7 @@
       </c>
       <c r="V223" s="1"/>
     </row>
-    <row r="224" spans="1:22" s="2" customFormat="1" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:22" s="2" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A224" s="1" t="s">
         <v>6</v>
       </c>
@@ -21702,7 +21707,7 @@
       </c>
       <c r="V224" s="1"/>
     </row>
-    <row r="225" spans="1:22" s="2" customFormat="1" ht="406" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:22" s="2" customFormat="1" ht="406" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
         <v>6</v>
       </c>
@@ -21764,7 +21769,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="226" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
         <v>6</v>
       </c>
@@ -21824,7 +21829,7 @@
       </c>
       <c r="V226" s="1"/>
     </row>
-    <row r="227" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
         <v>6</v>
       </c>
@@ -21886,7 +21891,7 @@
       </c>
       <c r="V227" s="1"/>
     </row>
-    <row r="228" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
         <v>6</v>
       </c>
@@ -21946,7 +21951,7 @@
       </c>
       <c r="V228" s="1"/>
     </row>
-    <row r="229" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
         <v>6</v>
       </c>
@@ -22016,7 +22021,9 @@
       <c r="C230" s="21" t="s">
         <v>1262</v>
       </c>
-      <c r="D230" s="1"/>
+      <c r="D230" s="13" t="s">
+        <v>2359</v>
+      </c>
       <c r="E230" s="1" t="s">
         <v>618</v>
       </c>
@@ -22064,7 +22071,7 @@
       </c>
       <c r="V230" s="1"/>
     </row>
-    <row r="231" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A231" s="1" t="s">
         <v>6</v>
       </c>
@@ -22124,7 +22131,7 @@
       </c>
       <c r="V231" s="1"/>
     </row>
-    <row r="232" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
         <v>6</v>
       </c>
@@ -22184,7 +22191,7 @@
       </c>
       <c r="V232" s="1"/>
     </row>
-    <row r="233" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>6</v>
       </c>
@@ -22244,7 +22251,7 @@
       </c>
       <c r="V233" s="1"/>
     </row>
-    <row r="234" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
         <v>6</v>
       </c>
@@ -22302,7 +22309,7 @@
       </c>
       <c r="V234" s="1"/>
     </row>
-    <row r="235" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A235" s="1" t="s">
         <v>6</v>
       </c>
@@ -22360,7 +22367,7 @@
       </c>
       <c r="V235" s="1"/>
     </row>
-    <row r="236" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A236" s="1" t="s">
         <v>6</v>
       </c>
@@ -22420,7 +22427,7 @@
       </c>
       <c r="V236" s="1"/>
     </row>
-    <row r="237" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A237" s="1" t="s">
         <v>6</v>
       </c>
@@ -22480,7 +22487,7 @@
       </c>
       <c r="V237" s="1"/>
     </row>
-    <row r="238" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A238" s="1" t="s">
         <v>6</v>
       </c>
@@ -22538,7 +22545,7 @@
       </c>
       <c r="V238" s="1"/>
     </row>
-    <row r="239" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A239" s="1" t="s">
         <v>6</v>
       </c>
@@ -22598,7 +22605,7 @@
       </c>
       <c r="V239" s="1"/>
     </row>
-    <row r="240" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A240" s="1" t="s">
         <v>6</v>
       </c>
@@ -22656,7 +22663,7 @@
       </c>
       <c r="V240" s="1"/>
     </row>
-    <row r="241" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A241" s="1" t="s">
         <v>6</v>
       </c>
@@ -22714,7 +22721,7 @@
       </c>
       <c r="V241" s="1"/>
     </row>
-    <row r="242" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A242" s="1" t="s">
         <v>6</v>
       </c>
@@ -22774,7 +22781,7 @@
       </c>
       <c r="V242" s="1"/>
     </row>
-    <row r="243" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A243" s="1" t="s">
         <v>6</v>
       </c>
@@ -22834,7 +22841,7 @@
       </c>
       <c r="V243" s="1"/>
     </row>
-    <row r="244" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A244" s="1" t="s">
         <v>6</v>
       </c>
@@ -22896,7 +22903,7 @@
       </c>
       <c r="V244" s="1"/>
     </row>
-    <row r="245" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A245" s="1" t="s">
         <v>6</v>
       </c>
@@ -22954,7 +22961,7 @@
       </c>
       <c r="V245" s="1"/>
     </row>
-    <row r="246" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A246" s="1" t="s">
         <v>6</v>
       </c>
@@ -23012,7 +23019,7 @@
       </c>
       <c r="V246" s="1"/>
     </row>
-    <row r="247" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A247" s="1" t="s">
         <v>6</v>
       </c>
@@ -23072,7 +23079,7 @@
       </c>
       <c r="V247" s="1"/>
     </row>
-    <row r="248" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A248" s="1" t="s">
         <v>6</v>
       </c>
@@ -23132,7 +23139,7 @@
       </c>
       <c r="V248" s="1"/>
     </row>
-    <row r="249" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A249" s="1" t="s">
         <v>6</v>
       </c>
@@ -23192,7 +23199,7 @@
       </c>
       <c r="V249" s="1"/>
     </row>
-    <row r="250" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A250" s="1" t="s">
         <v>6</v>
       </c>
@@ -23250,7 +23257,7 @@
       </c>
       <c r="V250" s="1"/>
     </row>
-    <row r="251" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A251" s="1" t="s">
         <v>6</v>
       </c>
@@ -23312,7 +23319,7 @@
       </c>
       <c r="V251" s="1"/>
     </row>
-    <row r="252" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A252" s="1" t="s">
         <v>6</v>
       </c>
@@ -23374,7 +23381,7 @@
       </c>
       <c r="V252" s="1"/>
     </row>
-    <row r="253" spans="1:22" s="2" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:22" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A253" s="1" t="s">
         <v>6</v>
       </c>
@@ -23436,7 +23443,7 @@
         <v>2313</v>
       </c>
     </row>
-    <row r="254" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A254" s="1" t="s">
         <v>6</v>
       </c>
@@ -23496,7 +23503,7 @@
       </c>
       <c r="V254" s="1"/>
     </row>
-    <row r="255" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A255" s="1" t="s">
         <v>6</v>
       </c>
@@ -23556,7 +23563,7 @@
       </c>
       <c r="V255" s="1"/>
     </row>
-    <row r="256" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A256" s="1" t="s">
         <v>6</v>
       </c>
@@ -23614,7 +23621,7 @@
       </c>
       <c r="V256" s="1"/>
     </row>
-    <row r="257" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A257" s="1" t="s">
         <v>6</v>
       </c>
@@ -23672,7 +23679,7 @@
       </c>
       <c r="V257" s="1"/>
     </row>
-    <row r="258" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A258" s="1" t="s">
         <v>6</v>
       </c>
@@ -23730,7 +23737,7 @@
       </c>
       <c r="V258" s="1"/>
     </row>
-    <row r="259" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A259" s="1" t="s">
         <v>6</v>
       </c>
@@ -23792,7 +23799,7 @@
       </c>
       <c r="V259" s="1"/>
     </row>
-    <row r="260" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A260" s="1" t="s">
         <v>6</v>
       </c>
@@ -23850,7 +23857,7 @@
       </c>
       <c r="V260" s="1"/>
     </row>
-    <row r="261" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A261" s="1" t="s">
         <v>6</v>
       </c>
@@ -23908,7 +23915,7 @@
       </c>
       <c r="V261" s="1"/>
     </row>
-    <row r="262" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A262" s="1" t="s">
         <v>6</v>
       </c>
@@ -23968,7 +23975,7 @@
       </c>
       <c r="V262" s="1"/>
     </row>
-    <row r="263" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A263" s="1" t="s">
         <v>6</v>
       </c>
@@ -24028,7 +24035,7 @@
       </c>
       <c r="V263" s="1"/>
     </row>
-    <row r="264" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A264" s="1" t="s">
         <v>6</v>
       </c>
@@ -24088,7 +24095,7 @@
       </c>
       <c r="V264" s="1"/>
     </row>
-    <row r="265" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A265" s="1" t="s">
         <v>6</v>
       </c>
@@ -24148,7 +24155,7 @@
       </c>
       <c r="V265" s="1"/>
     </row>
-    <row r="266" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A266" s="1" t="s">
         <v>6</v>
       </c>
@@ -24208,7 +24215,7 @@
       </c>
       <c r="V266" s="1"/>
     </row>
-    <row r="267" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A267" s="1" t="s">
         <v>6</v>
       </c>
@@ -24268,7 +24275,7 @@
       </c>
       <c r="V267" s="1"/>
     </row>
-    <row r="268" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A268" s="1" t="s">
         <v>6</v>
       </c>
@@ -24328,7 +24335,7 @@
       </c>
       <c r="V268" s="1"/>
     </row>
-    <row r="269" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A269" s="1" t="s">
         <v>6</v>
       </c>
@@ -24388,7 +24395,7 @@
       </c>
       <c r="V269" s="1"/>
     </row>
-    <row r="270" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A270" s="1" t="s">
         <v>6</v>
       </c>
@@ -24450,7 +24457,7 @@
       </c>
       <c r="V270" s="1"/>
     </row>
-    <row r="271" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A271" s="1" t="s">
         <v>6</v>
       </c>
@@ -24512,7 +24519,7 @@
       </c>
       <c r="V271" s="1"/>
     </row>
-    <row r="272" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A272" s="1" t="s">
         <v>6</v>
       </c>
@@ -24574,7 +24581,7 @@
       </c>
       <c r="V272" s="1"/>
     </row>
-    <row r="273" spans="1:22" s="2" customFormat="1" ht="377" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:22" s="2" customFormat="1" ht="377" x14ac:dyDescent="0.35">
       <c r="A273" s="1" t="s">
         <v>6</v>
       </c>
@@ -24638,7 +24645,7 @@
       </c>
       <c r="V273" s="1"/>
     </row>
-    <row r="274" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A274" s="1" t="s">
         <v>6</v>
       </c>
@@ -24700,7 +24707,7 @@
       </c>
       <c r="V274" s="1"/>
     </row>
-    <row r="275" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A275" s="1" t="s">
         <v>6</v>
       </c>
@@ -24762,7 +24769,7 @@
       </c>
       <c r="V275" s="1"/>
     </row>
-    <row r="276" spans="1:22" s="2" customFormat="1" ht="275.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:22" s="2" customFormat="1" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A276" s="1" t="s">
         <v>6</v>
       </c>
@@ -24826,7 +24833,7 @@
         <v>2293</v>
       </c>
     </row>
-    <row r="277" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A277" s="1" t="s">
         <v>6</v>
       </c>
@@ -24888,7 +24895,7 @@
       </c>
       <c r="V277" s="1"/>
     </row>
-    <row r="278" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A278" s="1" t="s">
         <v>6</v>
       </c>
@@ -24952,7 +24959,7 @@
       </c>
       <c r="V278" s="1"/>
     </row>
-    <row r="279" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A279" s="1" t="s">
         <v>6</v>
       </c>
@@ -25014,7 +25021,7 @@
       </c>
       <c r="V279" s="1"/>
     </row>
-    <row r="280" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A280" s="1" t="s">
         <v>6</v>
       </c>
@@ -25076,7 +25083,7 @@
       </c>
       <c r="V280" s="1"/>
     </row>
-    <row r="281" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A281" s="1" t="s">
         <v>6</v>
       </c>
@@ -25138,7 +25145,7 @@
       </c>
       <c r="V281" s="1"/>
     </row>
-    <row r="282" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A282" s="1" t="s">
         <v>6</v>
       </c>
@@ -25198,7 +25205,7 @@
       </c>
       <c r="V282" s="1"/>
     </row>
-    <row r="283" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A283" s="1" t="s">
         <v>6</v>
       </c>
@@ -25258,7 +25265,7 @@
       </c>
       <c r="V283" s="1"/>
     </row>
-    <row r="284" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A284" s="1" t="s">
         <v>6</v>
       </c>
@@ -25318,7 +25325,7 @@
       </c>
       <c r="V284" s="1"/>
     </row>
-    <row r="285" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A285" s="1" t="s">
         <v>6</v>
       </c>
@@ -25378,7 +25385,7 @@
       </c>
       <c r="V285" s="1"/>
     </row>
-    <row r="286" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A286" s="1" t="s">
         <v>6</v>
       </c>
@@ -25436,7 +25443,7 @@
       </c>
       <c r="V286" s="1"/>
     </row>
-    <row r="287" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A287" s="1" t="s">
         <v>6</v>
       </c>
@@ -25496,7 +25503,7 @@
       </c>
       <c r="V287" s="1"/>
     </row>
-    <row r="288" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A288" s="1" t="s">
         <v>6</v>
       </c>
@@ -25556,7 +25563,7 @@
       </c>
       <c r="V288" s="1"/>
     </row>
-    <row r="289" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A289" s="1" t="s">
         <v>6</v>
       </c>
@@ -25616,7 +25623,7 @@
       </c>
       <c r="V289" s="1"/>
     </row>
-    <row r="290" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A290" s="1" t="s">
         <v>6</v>
       </c>
@@ -25674,7 +25681,7 @@
       </c>
       <c r="V290" s="1"/>
     </row>
-    <row r="291" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A291" s="1" t="s">
         <v>6</v>
       </c>
@@ -25734,7 +25741,7 @@
       </c>
       <c r="V291" s="1"/>
     </row>
-    <row r="292" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A292" s="1" t="s">
         <v>6</v>
       </c>
@@ -25794,7 +25801,7 @@
       </c>
       <c r="V292" s="1"/>
     </row>
-    <row r="293" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A293" s="1" t="s">
         <v>6</v>
       </c>
@@ -25852,7 +25859,7 @@
       </c>
       <c r="V293" s="1"/>
     </row>
-    <row r="294" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A294" s="1" t="s">
         <v>6</v>
       </c>
@@ -25910,7 +25917,7 @@
       </c>
       <c r="V294" s="1"/>
     </row>
-    <row r="295" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A295" s="1" t="s">
         <v>6</v>
       </c>
@@ -25968,7 +25975,7 @@
       </c>
       <c r="V295" s="1"/>
     </row>
-    <row r="296" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A296" s="1" t="s">
         <v>6</v>
       </c>
@@ -26026,7 +26033,7 @@
       </c>
       <c r="V296" s="1"/>
     </row>
-    <row r="297" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A297" s="1" t="s">
         <v>6</v>
       </c>
@@ -26086,7 +26093,7 @@
       </c>
       <c r="V297" s="1"/>
     </row>
-    <row r="298" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A298" s="1" t="s">
         <v>6</v>
       </c>
@@ -26096,7 +26103,9 @@
       <c r="C298" s="21" t="s">
         <v>1423</v>
       </c>
-      <c r="D298" s="26"/>
+      <c r="D298" s="13" t="s">
+        <v>2360</v>
+      </c>
       <c r="E298" s="31" t="s">
         <v>1396</v>
       </c>
@@ -26131,7 +26140,7 @@
       <c r="P298" s="1"/>
       <c r="Q298" s="1"/>
       <c r="R298" s="1" t="s">
-        <v>1756</v>
+        <v>1832</v>
       </c>
       <c r="S298" s="1" t="s">
         <v>1756</v>
@@ -26144,7 +26153,7 @@
       </c>
       <c r="V298" s="1"/>
     </row>
-    <row r="299" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A299" s="1" t="s">
         <v>6</v>
       </c>
@@ -26204,7 +26213,7 @@
       </c>
       <c r="V299" s="1"/>
     </row>
-    <row r="300" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A300" s="1" t="s">
         <v>6</v>
       </c>
@@ -26262,7 +26271,7 @@
       </c>
       <c r="V300" s="1"/>
     </row>
-    <row r="301" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A301" s="1" t="s">
         <v>6</v>
       </c>
@@ -26322,7 +26331,7 @@
       </c>
       <c r="V301" s="1"/>
     </row>
-    <row r="302" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A302" s="1" t="s">
         <v>6</v>
       </c>
@@ -26380,7 +26389,7 @@
       </c>
       <c r="V302" s="1"/>
     </row>
-    <row r="303" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A303" s="1" t="s">
         <v>6</v>
       </c>
@@ -26438,7 +26447,7 @@
       </c>
       <c r="V303" s="1"/>
     </row>
-    <row r="304" spans="1:22" s="2" customFormat="1" ht="76.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:22" s="2" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="1" t="s">
         <v>6</v>
       </c>
@@ -26498,7 +26507,7 @@
       </c>
       <c r="V304" s="1"/>
     </row>
-    <row r="305" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A305" s="1" t="s">
         <v>6</v>
       </c>
@@ -26556,7 +26565,7 @@
       </c>
       <c r="V305" s="1"/>
     </row>
-    <row r="306" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A306" s="1" t="s">
         <v>6</v>
       </c>
@@ -26614,7 +26623,7 @@
       </c>
       <c r="V306" s="1"/>
     </row>
-    <row r="307" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A307" s="1" t="s">
         <v>6</v>
       </c>
@@ -26672,7 +26681,7 @@
       </c>
       <c r="V307" s="1"/>
     </row>
-    <row r="308" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A308" s="1" t="s">
         <v>6</v>
       </c>
@@ -26730,7 +26739,7 @@
       </c>
       <c r="V308" s="1"/>
     </row>
-    <row r="309" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A309" s="1" t="s">
         <v>6</v>
       </c>
@@ -26788,7 +26797,7 @@
       </c>
       <c r="V309" s="1"/>
     </row>
-    <row r="310" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A310" s="1" t="s">
         <v>6</v>
       </c>
@@ -26846,7 +26855,7 @@
       </c>
       <c r="V310" s="1"/>
     </row>
-    <row r="311" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A311" s="1" t="s">
         <v>6</v>
       </c>
@@ -26904,7 +26913,7 @@
       </c>
       <c r="V311" s="1"/>
     </row>
-    <row r="312" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A312" s="1" t="s">
         <v>6</v>
       </c>
@@ -26966,7 +26975,7 @@
       </c>
       <c r="V312" s="1"/>
     </row>
-    <row r="313" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A313" s="1" t="s">
         <v>6</v>
       </c>
@@ -27030,7 +27039,7 @@
       </c>
       <c r="V313" s="1"/>
     </row>
-    <row r="314" spans="1:22" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:22" ht="87" x14ac:dyDescent="0.35">
       <c r="A314" s="1" t="s">
         <v>6</v>
       </c>
@@ -27094,7 +27103,7 @@
       </c>
       <c r="V314" s="1"/>
     </row>
-    <row r="315" spans="1:22" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:22" ht="87" x14ac:dyDescent="0.35">
       <c r="A315" s="1" t="s">
         <v>6</v>
       </c>
@@ -27154,7 +27163,7 @@
       </c>
       <c r="V315" s="1"/>
     </row>
-    <row r="316" spans="1:22" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:22" ht="87" x14ac:dyDescent="0.35">
       <c r="A316" s="1" t="s">
         <v>6</v>
       </c>
@@ -27212,7 +27221,7 @@
       </c>
       <c r="V316" s="1"/>
     </row>
-    <row r="317" spans="1:22" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:22" ht="87" x14ac:dyDescent="0.35">
       <c r="A317" s="1" t="s">
         <v>6</v>
       </c>
@@ -27274,7 +27283,7 @@
       </c>
       <c r="V317" s="1"/>
     </row>
-    <row r="318" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A318" s="1" t="s">
         <v>6</v>
       </c>
@@ -27334,7 +27343,7 @@
       </c>
       <c r="V318" s="1"/>
     </row>
-    <row r="319" spans="1:22" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A319" s="1" t="s">
         <v>6</v>
       </c>
@@ -27396,7 +27405,7 @@
       </c>
       <c r="V319" s="1"/>
     </row>
-    <row r="320" spans="1:22" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A320" s="1" t="s">
         <v>6</v>
       </c>
@@ -27456,7 +27465,7 @@
       </c>
       <c r="V320" s="1"/>
     </row>
-    <row r="321" spans="1:22" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A321" s="1" t="s">
         <v>6</v>
       </c>
@@ -27518,7 +27527,7 @@
       </c>
       <c r="V321" s="1"/>
     </row>
-    <row r="322" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A322" s="1" t="s">
         <v>6</v>
       </c>
@@ -27576,7 +27585,7 @@
       </c>
       <c r="V322" s="1"/>
     </row>
-    <row r="323" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A323" s="1" t="s">
         <v>6</v>
       </c>
@@ -27634,7 +27643,7 @@
       </c>
       <c r="V323" s="1"/>
     </row>
-    <row r="324" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A324" s="1" t="s">
         <v>6</v>
       </c>
@@ -27694,7 +27703,7 @@
       </c>
       <c r="V324" s="1"/>
     </row>
-    <row r="325" spans="1:22" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A325" s="1" t="s">
         <v>6</v>
       </c>
@@ -27752,7 +27761,7 @@
       </c>
       <c r="V325" s="1"/>
     </row>
-    <row r="326" spans="1:22" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A326" s="1" t="s">
         <v>6</v>
       </c>
@@ -27812,7 +27821,7 @@
       </c>
       <c r="V326" s="1"/>
     </row>
-    <row r="327" spans="1:22" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A327" s="1" t="s">
         <v>6</v>
       </c>
@@ -27872,7 +27881,7 @@
       </c>
       <c r="V327" s="1"/>
     </row>
-    <row r="328" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A328" s="1" t="s">
         <v>6</v>
       </c>
@@ -27932,7 +27941,7 @@
       </c>
       <c r="V328" s="1"/>
     </row>
-    <row r="329" spans="1:22" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:22" ht="58" x14ac:dyDescent="0.35">
       <c r="A329" s="1" t="s">
         <v>6</v>
       </c>
@@ -27992,7 +28001,7 @@
       </c>
       <c r="V329" s="1"/>
     </row>
-    <row r="330" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A330" s="1" t="s">
         <v>6</v>
       </c>
@@ -28054,7 +28063,7 @@
       </c>
       <c r="V330" s="1"/>
     </row>
-    <row r="331" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A331" s="1" t="s">
         <v>6</v>
       </c>
@@ -28114,7 +28123,7 @@
       </c>
       <c r="V331" s="1"/>
     </row>
-    <row r="332" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A332" s="1" t="s">
         <v>6</v>
       </c>
@@ -28174,7 +28183,7 @@
       </c>
       <c r="V332" s="1"/>
     </row>
-    <row r="333" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A333" s="1" t="s">
         <v>6</v>
       </c>
@@ -28234,7 +28243,7 @@
       </c>
       <c r="V333" s="1"/>
     </row>
-    <row r="334" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A334" s="1" t="s">
         <v>6</v>
       </c>
@@ -28294,7 +28303,7 @@
       </c>
       <c r="V334" s="1"/>
     </row>
-    <row r="335" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A335" s="1" t="s">
         <v>6</v>
       </c>
@@ -28354,7 +28363,7 @@
       </c>
       <c r="V335" s="1"/>
     </row>
-    <row r="336" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A336" s="1" t="s">
         <v>6</v>
       </c>
@@ -28414,7 +28423,7 @@
       </c>
       <c r="V336" s="1"/>
     </row>
-    <row r="337" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A337" s="1" t="s">
         <v>6</v>
       </c>
@@ -28472,7 +28481,7 @@
       </c>
       <c r="V337" s="1"/>
     </row>
-    <row r="338" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A338" s="1" t="s">
         <v>6</v>
       </c>
@@ -28532,7 +28541,7 @@
       </c>
       <c r="V338" s="1"/>
     </row>
-    <row r="339" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A339" s="1" t="s">
         <v>6</v>
       </c>
@@ -28592,7 +28601,7 @@
       </c>
       <c r="V339" s="1"/>
     </row>
-    <row r="340" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A340" s="1" t="s">
         <v>6</v>
       </c>
@@ -28652,7 +28661,7 @@
       </c>
       <c r="V340" s="1"/>
     </row>
-    <row r="341" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A341" s="1" t="s">
         <v>6</v>
       </c>
@@ -28714,7 +28723,7 @@
       </c>
       <c r="V341" s="1"/>
     </row>
-    <row r="342" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A342" s="1" t="s">
         <v>6</v>
       </c>
@@ -28774,7 +28783,7 @@
       </c>
       <c r="V342" s="1"/>
     </row>
-    <row r="343" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A343" s="1" t="s">
         <v>6</v>
       </c>
@@ -28832,7 +28841,7 @@
       </c>
       <c r="V343" s="1"/>
     </row>
-    <row r="344" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A344" s="1" t="s">
         <v>6</v>
       </c>
@@ -28890,7 +28899,7 @@
       </c>
       <c r="V344" s="1"/>
     </row>
-    <row r="345" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A345" s="1" t="s">
         <v>6</v>
       </c>
@@ -28950,7 +28959,7 @@
       </c>
       <c r="V345" s="1"/>
     </row>
-    <row r="346" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A346" s="1" t="s">
         <v>6</v>
       </c>
@@ -29010,7 +29019,7 @@
       </c>
       <c r="V346" s="1"/>
     </row>
-    <row r="347" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A347" s="1" t="s">
         <v>6</v>
       </c>
@@ -29072,7 +29081,7 @@
       </c>
       <c r="V347" s="1"/>
     </row>
-    <row r="348" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A348" s="1" t="s">
         <v>6</v>
       </c>
@@ -29132,7 +29141,7 @@
       </c>
       <c r="V348" s="1"/>
     </row>
-    <row r="349" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A349" s="1" t="s">
         <v>6</v>
       </c>
@@ -29192,7 +29201,7 @@
       </c>
       <c r="V349" s="1"/>
     </row>
-    <row r="350" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A350" s="1" t="s">
         <v>6</v>
       </c>
@@ -29252,7 +29261,7 @@
       </c>
       <c r="V350" s="1"/>
     </row>
-    <row r="351" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A351" s="1" t="s">
         <v>6</v>
       </c>
@@ -29308,7 +29317,7 @@
       </c>
       <c r="V351" s="1"/>
     </row>
-    <row r="352" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A352" s="1" t="s">
         <v>6</v>
       </c>
@@ -29368,7 +29377,7 @@
       </c>
       <c r="V352" s="1"/>
     </row>
-    <row r="353" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A353" s="1" t="s">
         <v>6</v>
       </c>
@@ -29428,7 +29437,7 @@
       </c>
       <c r="V353" s="1"/>
     </row>
-    <row r="354" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A354" s="1" t="s">
         <v>6</v>
       </c>
@@ -29488,7 +29497,7 @@
       </c>
       <c r="V354" s="1"/>
     </row>
-    <row r="355" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A355" s="1" t="s">
         <v>6</v>
       </c>
@@ -29548,7 +29557,7 @@
       </c>
       <c r="V355" s="1"/>
     </row>
-    <row r="356" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A356" s="1" t="s">
         <v>6</v>
       </c>
@@ -29608,7 +29617,7 @@
       </c>
       <c r="V356" s="1"/>
     </row>
-    <row r="357" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A357" s="1" t="s">
         <v>6</v>
       </c>
@@ -29668,7 +29677,7 @@
       </c>
       <c r="V357" s="1"/>
     </row>
-    <row r="358" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A358" s="1" t="s">
         <v>6</v>
       </c>
@@ -29726,7 +29735,7 @@
       </c>
       <c r="V358" s="1"/>
     </row>
-    <row r="359" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A359" s="1" t="s">
         <v>6</v>
       </c>
@@ -29784,7 +29793,7 @@
       </c>
       <c r="V359" s="1"/>
     </row>
-    <row r="360" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A360" s="1" t="s">
         <v>6</v>
       </c>
@@ -29844,7 +29853,7 @@
       </c>
       <c r="V360" s="1"/>
     </row>
-    <row r="361" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A361" s="1" t="s">
         <v>6</v>
       </c>
@@ -29906,7 +29915,7 @@
       </c>
       <c r="V361" s="1"/>
     </row>
-    <row r="362" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A362" s="1" t="s">
         <v>6</v>
       </c>
@@ -29968,7 +29977,7 @@
       </c>
       <c r="V362" s="1"/>
     </row>
-    <row r="363" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A363" s="1" t="s">
         <v>6</v>
       </c>
@@ -30028,7 +30037,7 @@
       </c>
       <c r="V363" s="1"/>
     </row>
-    <row r="364" spans="1:22" s="2" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:22" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A364" s="1" t="s">
         <v>6</v>
       </c>
@@ -30090,7 +30099,7 @@
         <v>2294</v>
       </c>
     </row>
-    <row r="365" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A365" s="1" t="s">
         <v>6</v>
       </c>
@@ -30150,7 +30159,7 @@
       </c>
       <c r="V365" s="1"/>
     </row>
-    <row r="366" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A366" s="1" t="s">
         <v>6</v>
       </c>
@@ -30208,7 +30217,7 @@
       </c>
       <c r="V366" s="1"/>
     </row>
-    <row r="367" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A367" s="1" t="s">
         <v>6</v>
       </c>
@@ -30270,7 +30279,7 @@
       </c>
       <c r="V367" s="1"/>
     </row>
-    <row r="368" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A368" s="1" t="s">
         <v>6</v>
       </c>
@@ -30332,7 +30341,7 @@
       </c>
       <c r="V368" s="1"/>
     </row>
-    <row r="369" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A369" s="1" t="s">
         <v>6</v>
       </c>
@@ -30392,7 +30401,7 @@
       </c>
       <c r="V369" s="1"/>
     </row>
-    <row r="370" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A370" s="1" t="s">
         <v>6</v>
       </c>
@@ -30452,7 +30461,7 @@
       </c>
       <c r="V370" s="1"/>
     </row>
-    <row r="371" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A371" s="1" t="s">
         <v>6</v>
       </c>
@@ -30510,7 +30519,7 @@
       </c>
       <c r="V371" s="1"/>
     </row>
-    <row r="372" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A372" s="1" t="s">
         <v>6</v>
       </c>
@@ -30570,7 +30579,7 @@
       </c>
       <c r="V372" s="1"/>
     </row>
-    <row r="373" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A373" s="1" t="s">
         <v>6</v>
       </c>
@@ -30630,7 +30639,7 @@
       </c>
       <c r="V373" s="1"/>
     </row>
-    <row r="374" spans="1:22" s="2" customFormat="1" ht="362.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:22" s="2" customFormat="1" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A374" s="1" t="s">
         <v>6</v>
       </c>
@@ -30694,7 +30703,7 @@
         <v>2292</v>
       </c>
     </row>
-    <row r="375" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A375" s="1" t="s">
         <v>6</v>
       </c>
@@ -30754,7 +30763,7 @@
       </c>
       <c r="V375" s="1"/>
     </row>
-    <row r="376" spans="1:22" s="2" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A376" s="1" t="s">
         <v>6</v>
       </c>
@@ -30814,7 +30823,7 @@
       </c>
       <c r="V376" s="1"/>
     </row>
-    <row r="377" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A377" s="1" t="s">
         <v>6</v>
       </c>
@@ -30876,7 +30885,7 @@
       </c>
       <c r="V377" s="1"/>
     </row>
-    <row r="378" spans="1:22" s="2" customFormat="1" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A378" s="1" t="s">
         <v>6</v>
       </c>
@@ -30938,7 +30947,7 @@
       </c>
       <c r="V378" s="1"/>
     </row>
-    <row r="379" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A379" s="1" t="s">
         <v>6</v>
       </c>
@@ -30998,7 +31007,7 @@
       </c>
       <c r="V379" s="1"/>
     </row>
-    <row r="380" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A380" s="1" t="s">
         <v>6</v>
       </c>
@@ -31060,7 +31069,7 @@
       </c>
       <c r="V380" s="1"/>
     </row>
-    <row r="381" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A381" s="1" t="s">
         <v>6</v>
       </c>
@@ -31120,7 +31129,7 @@
       </c>
       <c r="V381" s="1"/>
     </row>
-    <row r="382" spans="1:22" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A382" s="1" t="s">
         <v>6</v>
       </c>
@@ -31178,7 +31187,7 @@
       </c>
       <c r="V382" s="1"/>
     </row>
-    <row r="383" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A383" s="1" t="s">
         <v>6</v>
       </c>
@@ -31238,7 +31247,7 @@
       </c>
       <c r="V383" s="1"/>
     </row>
-    <row r="384" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A384" s="1" t="s">
         <v>6</v>
       </c>
@@ -31300,7 +31309,7 @@
       </c>
       <c r="V384" s="1"/>
     </row>
-    <row r="385" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A385" s="1" t="s">
         <v>6</v>
       </c>
@@ -31360,7 +31369,7 @@
       </c>
       <c r="V385" s="1"/>
     </row>
-    <row r="386" spans="1:22" s="2" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:22" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A386" s="1" t="s">
         <v>6</v>
       </c>
@@ -31422,7 +31431,7 @@
         <v>2332</v>
       </c>
     </row>
-    <row r="387" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A387" s="1" t="s">
         <v>6</v>
       </c>
@@ -31482,7 +31491,7 @@
       </c>
       <c r="V387" s="1"/>
     </row>
-    <row r="388" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A388" s="1" t="s">
         <v>6</v>
       </c>
@@ -31542,7 +31551,7 @@
       </c>
       <c r="V388" s="1"/>
     </row>
-    <row r="389" spans="1:22" s="2" customFormat="1" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A389" s="1" t="s">
         <v>6</v>
       </c>
@@ -31604,7 +31613,7 @@
       </c>
       <c r="V389" s="1"/>
     </row>
-    <row r="390" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A390" s="1" t="s">
         <v>6</v>
       </c>
@@ -31664,7 +31673,7 @@
       </c>
       <c r="V390" s="1"/>
     </row>
-    <row r="391" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A391" s="1" t="s">
         <v>6</v>
       </c>
@@ -31724,7 +31733,7 @@
       </c>
       <c r="V391" s="1"/>
     </row>
-    <row r="392" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A392" s="1" t="s">
         <v>6</v>
       </c>
@@ -31784,7 +31793,7 @@
       </c>
       <c r="V392" s="1"/>
     </row>
-    <row r="393" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A393" s="1" t="s">
         <v>6</v>
       </c>
@@ -31844,7 +31853,7 @@
       </c>
       <c r="V393" s="1"/>
     </row>
-    <row r="394" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A394" s="1" t="s">
         <v>6</v>
       </c>
@@ -31906,7 +31915,7 @@
       </c>
       <c r="V394" s="1"/>
     </row>
-    <row r="395" spans="1:22" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A395" s="1" t="s">
         <v>6</v>
       </c>
@@ -31968,7 +31977,7 @@
       </c>
       <c r="V395" s="1"/>
     </row>
-    <row r="396" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A396" s="1" t="s">
         <v>6</v>
       </c>
@@ -32028,7 +32037,7 @@
       </c>
       <c r="V396" s="1"/>
     </row>
-    <row r="397" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A397" s="1" t="s">
         <v>6</v>
       </c>
@@ -32088,7 +32097,7 @@
       </c>
       <c r="V397" s="1"/>
     </row>
-    <row r="398" spans="1:22" s="2" customFormat="1" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A398" s="1" t="s">
         <v>6</v>
       </c>
@@ -32150,7 +32159,7 @@
       </c>
       <c r="V398" s="1"/>
     </row>
-    <row r="399" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A399" s="1" t="s">
         <v>6</v>
       </c>
@@ -32210,7 +32219,7 @@
       </c>
       <c r="V399" s="1"/>
     </row>
-    <row r="400" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A400" s="1" t="s">
         <v>6</v>
       </c>
@@ -32270,7 +32279,7 @@
       </c>
       <c r="V400" s="1"/>
     </row>
-    <row r="401" spans="1:22" s="2" customFormat="1" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A401" s="1" t="s">
         <v>6</v>
       </c>
@@ -32330,7 +32339,7 @@
       </c>
       <c r="V401" s="1"/>
     </row>
-    <row r="402" spans="1:22" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A402" s="1" t="s">
         <v>6</v>
       </c>
@@ -32390,7 +32399,7 @@
       </c>
       <c r="V402" s="1"/>
     </row>
-    <row r="403" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A403" s="1" t="s">
         <v>6</v>
       </c>
@@ -32450,7 +32459,7 @@
       </c>
       <c r="V403" s="1"/>
     </row>
-    <row r="404" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A404" s="1" t="s">
         <v>6</v>
       </c>
@@ -32510,7 +32519,7 @@
       </c>
       <c r="V404" s="1"/>
     </row>
-    <row r="405" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A405" s="1" t="s">
         <v>6</v>
       </c>
@@ -32570,7 +32579,7 @@
       </c>
       <c r="V405" s="1"/>
     </row>
-    <row r="406" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A406" s="1" t="s">
         <v>6</v>
       </c>
@@ -32630,7 +32639,7 @@
       </c>
       <c r="V406" s="1"/>
     </row>
-    <row r="407" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A407" s="1" t="s">
         <v>6</v>
       </c>
@@ -32690,7 +32699,7 @@
       </c>
       <c r="V407" s="1"/>
     </row>
-    <row r="408" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A408" s="1" t="s">
         <v>6</v>
       </c>
@@ -32750,7 +32759,7 @@
       </c>
       <c r="V408" s="1"/>
     </row>
-    <row r="409" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A409" s="1" t="s">
         <v>6</v>
       </c>
@@ -32810,7 +32819,7 @@
       </c>
       <c r="V409" s="1"/>
     </row>
-    <row r="410" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A410" s="1" t="s">
         <v>6</v>
       </c>
@@ -32870,7 +32879,7 @@
       </c>
       <c r="V410" s="1"/>
     </row>
-    <row r="411" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A411" s="1" t="s">
         <v>6</v>
       </c>
@@ -32928,7 +32937,7 @@
       </c>
       <c r="V411" s="1"/>
     </row>
-    <row r="412" spans="1:22" s="2" customFormat="1" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A412" s="1" t="s">
         <v>6</v>
       </c>
@@ -32990,7 +32999,7 @@
         <v>2297</v>
       </c>
     </row>
-    <row r="413" spans="1:22" s="2" customFormat="1" ht="377" hidden="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:22" s="2" customFormat="1" ht="377" x14ac:dyDescent="0.35">
       <c r="A413" s="1" t="s">
         <v>6</v>
       </c>
@@ -33052,7 +33061,7 @@
         <v>2330</v>
       </c>
     </row>
-    <row r="414" spans="1:22" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A414" s="1" t="s">
         <v>6</v>
       </c>
@@ -33112,7 +33121,7 @@
       </c>
       <c r="V414" s="1"/>
     </row>
-    <row r="415" spans="1:22" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:22" ht="58" x14ac:dyDescent="0.35">
       <c r="A415" s="1" t="s">
         <v>6</v>
       </c>
@@ -33172,7 +33181,7 @@
       </c>
       <c r="V415" s="1"/>
     </row>
-    <row r="416" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A416" s="1" t="s">
         <v>6</v>
       </c>
@@ -33232,7 +33241,7 @@
       </c>
       <c r="V416" s="1"/>
     </row>
-    <row r="417" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A417" s="1" t="s">
         <v>6</v>
       </c>
@@ -33293,13 +33302,7 @@
       <c r="V417" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V417" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Marie Arnaud"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:V417" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L227">
     <sortCondition ref="C2:C422"/>
   </sortState>
@@ -33656,8 +33659,10 @@
     <hyperlink ref="D342" r:id="rId349" xr:uid="{F9AF74BC-C5BD-4C4C-80E9-B7676EA47DD4}"/>
     <hyperlink ref="D361" r:id="rId350" xr:uid="{A24A0A03-18C8-4164-9C9C-C6D7E8079A60}"/>
     <hyperlink ref="D248" r:id="rId351" xr:uid="{3E7272D2-FD11-4455-A18D-8F4152E7C571}"/>
+    <hyperlink ref="D230" r:id="rId352" xr:uid="{8CF31450-9FF6-41B8-B89D-83C1B91BBFED}"/>
+    <hyperlink ref="D298" r:id="rId353" xr:uid="{837E84CE-D2C6-454F-9ABE-6CE8B0C7790A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId352"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId354"/>
 </worksheet>
 </file>
--- a/Data/FairCarboN_Datas_Contacts.xlsx
+++ b/Data/FairCarboN_Datas_Contacts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9806927A-E200-4A93-A2F0-C49C8D885C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F580A21E-2834-4E9D-B449-92CFBE6DA9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6899" uniqueCount="2405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6900" uniqueCount="2406">
   <si>
     <t>Acronyme PEPR</t>
   </si>
@@ -7327,6 +7327,10 @@
   </si>
   <si>
     <t>patricia.garnier@inrae.fr</t>
+  </si>
+  <si>
+    <t>29092025 - Cà c'est un email personnalisé dis-donc ! Tu arrives à faire ça pour tout le monde ?
+Oui je confirme que je depose fidèlement sur HAL depuis un an ou 2 environ. D'accord je vais regarder et compléter bien sûr.</t>
   </si>
 </sst>
 </file>
@@ -8535,7 +8539,7 @@
       </c>
       <c r="V7" s="1"/>
     </row>
-    <row r="8" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" s="2" customFormat="1" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -8585,7 +8589,7 @@
         <v>1825</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>1749</v>
+        <v>1825</v>
       </c>
       <c r="T8" s="60" t="s">
         <v>1847</v>
@@ -8593,7 +8597,9 @@
       <c r="U8" s="60" t="s">
         <v>1842</v>
       </c>
-      <c r="V8" s="1"/>
+      <c r="V8" s="1" t="s">
+        <v>2405</v>
+      </c>
     </row>
     <row r="9" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">

--- a/Data/FairCarboN_Datas_Contacts.xlsx
+++ b/Data/FairCarboN_Datas_Contacts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0735CEC4-B71B-41F5-BCD3-207B490B4EBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D2FB76A-CCC7-470E-AE9B-363BED912271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6895" uniqueCount="2425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6900" uniqueCount="2430">
   <si>
     <t>Acronyme PEPR</t>
   </si>
@@ -7389,6 +7389,25 @@
   </si>
   <si>
     <t>eric.justes@cirad.fr</t>
+  </si>
+  <si>
+    <t>30092025 - Merci pour l’initiative.
+Pour l’instant, je n’ai pas de publications à rattacher à FairCarbon. Tout est lié à la glace ou à l’air.
+Seule la publication soumise, mais pas encore acceptée, de Nico Hachgenei pourrait de loin se rattacher au programme… et encore, c’est limite, car ça ne parle pas de carbone!
+Donc pas d’action de ma part à ce stade.</t>
+  </si>
+  <si>
+    <t>30092025 - J'ai pris bien note de ce point. Les références ne correspondent pas du tout aux thématiques FairCarboN et ont été publiées avant que je ne bénéficie des financements. 
+Je transmets la consigne aux autres participants au projet (en cc) et le redirai cet AM lors de notre réunion semestrielle.</t>
+  </si>
+  <si>
+    <t>30092025 - Je ne comprends pas bien ton e-mail. Tous les articles du tableau sont déjà dans HAL. De manière générale, comme est tenus de tout mettre dans HAL par le CNRS, tous mes articles y sont. Tu peux donc compter sur moi pour afficher les futures publications du projet dans HAL. D'autre part, aucune de mes travaux peut  s'intégrer dans le PEPR FairCarboN, ni de près ni de loin, puisque nous n'avons pas encore valorisé les mesures issus de ce projet en cours.</t>
+  </si>
+  <si>
+    <t>30092025 - Merci pour ton mail. Pour le moment rien n'a été publié mais dès que c'est le cas je déposerai sur HAL dans la collection FairC.</t>
+  </si>
+  <si>
+    <t>30092025 -  je vais vous revenir rapidement pour participer à cet effort de visibilité de nos travaux et de nos projets dans le cadre du PEPR</t>
   </si>
 </sst>
 </file>
@@ -14583,7 +14602,7 @@
       </c>
       <c r="V105" s="1"/>
     </row>
-    <row r="106" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>6</v>
       </c>
@@ -14635,7 +14654,7 @@
         <v>1814</v>
       </c>
       <c r="S106" s="1" t="s">
-        <v>1738</v>
+        <v>1814</v>
       </c>
       <c r="T106" s="59" t="s">
         <v>1974</v>
@@ -14643,7 +14662,9 @@
       <c r="U106" s="59" t="s">
         <v>1862</v>
       </c>
-      <c r="V106" s="1"/>
+      <c r="V106" s="1" t="s">
+        <v>2428</v>
+      </c>
     </row>
     <row r="107" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
@@ -24955,7 +24976,7 @@
         <v>2275</v>
       </c>
     </row>
-    <row r="274" spans="1:22" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A274" s="1" t="s">
         <v>6</v>
       </c>
@@ -25007,7 +25028,7 @@
         <v>1814</v>
       </c>
       <c r="S274" s="1" t="s">
-        <v>1738</v>
+        <v>1814</v>
       </c>
       <c r="T274" s="59" t="s">
         <v>2138</v>
@@ -25015,7 +25036,9 @@
       <c r="U274" s="59" t="s">
         <v>2082</v>
       </c>
-      <c r="V274" s="1"/>
+      <c r="V274" s="1" t="s">
+        <v>2429</v>
+      </c>
     </row>
     <row r="275" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A275" s="1" t="s">
@@ -26409,7 +26432,7 @@
       </c>
       <c r="V297" s="1"/>
     </row>
-    <row r="298" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:22" s="2" customFormat="1" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A298" s="1" t="s">
         <v>6</v>
       </c>
@@ -26459,7 +26482,7 @@
         <v>1814</v>
       </c>
       <c r="S298" s="1" t="s">
-        <v>1738</v>
+        <v>1814</v>
       </c>
       <c r="T298" s="59" t="s">
         <v>2163</v>
@@ -26467,7 +26490,9 @@
       <c r="U298" s="59" t="s">
         <v>1964</v>
       </c>
-      <c r="V298" s="1"/>
+      <c r="V298" s="1" t="s">
+        <v>2426</v>
+      </c>
     </row>
     <row r="299" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A299" s="1" t="s">
@@ -27861,7 +27886,7 @@
       </c>
       <c r="V321" s="1"/>
     </row>
-    <row r="322" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:22" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A322" s="1" t="s">
         <v>6</v>
       </c>
@@ -27911,7 +27936,7 @@
         <v>1814</v>
       </c>
       <c r="S322" s="1" t="s">
-        <v>1738</v>
+        <v>1814</v>
       </c>
       <c r="T322" s="59" t="s">
         <v>2185</v>
@@ -27919,7 +27944,9 @@
       <c r="U322" s="59" t="s">
         <v>2107</v>
       </c>
-      <c r="V322" s="1"/>
+      <c r="V322" s="1" t="s">
+        <v>2427</v>
+      </c>
     </row>
     <row r="323" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A323" s="1" t="s">
@@ -31209,7 +31236,7 @@
       </c>
       <c r="V376" s="1"/>
     </row>
-    <row r="377" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:22" s="2" customFormat="1" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A377" s="1" t="s">
         <v>6</v>
       </c>
@@ -31261,7 +31288,7 @@
         <v>1814</v>
       </c>
       <c r="S377" s="1" t="s">
-        <v>1738</v>
+        <v>1814</v>
       </c>
       <c r="T377" s="58" t="s">
         <v>2239</v>
@@ -31269,7 +31296,9 @@
       <c r="U377" s="58" t="s">
         <v>1939</v>
       </c>
-      <c r="V377" s="1"/>
+      <c r="V377" s="1" t="s">
+        <v>2425</v>
+      </c>
     </row>
     <row r="378" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A378" s="1" t="s">

--- a/Data/FairCarboN_Datas_Contacts.xlsx
+++ b/Data/FairCarboN_Datas_Contacts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D2FB76A-CCC7-470E-AE9B-363BED912271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F46FDB4-2CD7-4A65-BE37-AD0208D6FE63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liste" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6900" uniqueCount="2430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6916" uniqueCount="2442">
   <si>
     <t>Acronyme PEPR</t>
   </si>
@@ -7408,6 +7408,60 @@
   </si>
   <si>
     <t>30092025 -  je vais vous revenir rapidement pour participer à cet effort de visibilité de nos travaux et de nos projets dans le cadre du PEPR</t>
+  </si>
+  <si>
+    <t>30092025 - Je pars demain sur le terrain jusqu'à la fin de la semaine ... mais je référencerai mes publications 2024-2025 qui relèvent de la thématique FairCarboN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30092025 - Je comprends parfaitement la démarche et me permet de mettre en copie de ma réponse Claude qui travaille avec moi à l'ISTO dans le cadre de DEEP-C.
+Pour tout te dire c'est notre documentaliste qui s'occupe ici des dépôts HAL et c'est bien de savoir qu'on peut ajouter le tag faircarbon pour le projet.
+Pour ce qui est des valo 2024-2025 que tu as recensées, il manque un article récemment accepté et écrit avec ma doctorante (intitulé Effect of sediment composition and accumulation on pharmaceutical product spatial distributions at the suburban pond scale (Beulie pond, SNO Observil, France)) mais le truc c'est qu'aucune d'entre elles n'est liée de pret ou de loin avec le projet faircarbon et DEEP-C. La plupart ont pour oint commun la matière organique et sa caractérisation mais je t'avoue que je ne me sens pas à l'aise de taguer le PEPR alors qu'il n'y a aucun lien. Après, je n'ai peut être pas totalement compris la manipe et je compte en conséquence sur toi pour m'éclairer </t>
+  </si>
+  <si>
+    <t>30092025 - pour l'instant je n'ai aucun travail référencé CABESTAN, ça viendra certainement en 2026.</t>
+  </si>
+  <si>
+    <t>30092025 - merci pour ton message et les efforts pour retrouver ces articles
+Aucun des articles dans la liste que tu m'as envoyée n'a été financé par FairCarboN (et pour beaucoup d'entre eux, les années de parution ne sont pas les bonnes)
+Tu trouveras ici: https://tropecos.fr/tropecos-publications  les 5 publications produites jusqu'ici par le projet TROPECOS avec des financements FairCarboN. Tu noteras que dans ces articles, FairCarboN est référencé dans les remerciements.
+Il ne me sera pas possible de référencer des articles comme faisant partie du PEPR FairCarboN dans HAL, même en "voyant large", lorsque ces articles n'ont pas été financé par le PEPR. Cela serait contraire à la déontologie et me mettrait en porte à faux vis à vis des organismes qui ont réellement financés ces recherches. 
+Je reste à ta disposition si nécessaire pour mettre à jour les publications du projet TROPECOS (les vraies)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30092025 - Nous prendrons le temps de discuter de tous ces points et de les décortiquer dans le détail au Croisic j'espere ! </t>
+  </si>
+  <si>
+    <t>01102025 - Les documents mentionnés dans le fichier excel n’ont pas été obtenus dans le cadre de Fair C.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01102025 - C'est noté mais pour l'instant je n'ai pas de publication qui reporte un travail de recherche financé par le PEPR. </t>
+  </si>
+  <si>
+    <t>01102025 - Merci de ton message.
+Voici le fichier. il n'y a que 2 éléments à ajouter à Faircarbon. j'ai chargé dans HAL le fichier et mis la ref Faircarbon Alamod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01102025 - Merci pour ton mail
+J’ai donc rajouté un poster présenté aux dernières journées FairCarboN dans hal,
+N’hésite pas à me dire si tu ne le retrouves pas
+Pour l’instant il n’y a pas la pièce jointe, mais elle y sera, il me faut juste le temps de demander l’accord des partenaires
+Et une question liée, pour faire un dépôt dans hal, il y a une case licence, est ce que vous avez une attente précise à ce sujet ? CC-BY ça irait, ou il faut autre chose ?  </t>
+  </si>
+  <si>
+    <t>01102025 - Jérôme, j'ai bien reçu mes devoirs pour HAL :-). J'attends la formation de lundi pour réorienter avantageusement quelques productions !</t>
+  </si>
+  <si>
+    <t>01102025 -our 2024-2025, j’ai 4 publications scientifiques -cf liste plus bas (je n’ai pas vérifié les communications)
+Il semble que ta requête ne prenne pas en compte l’année de publication mais la date de dépôt.
+De plus, certaines publications récentes ne sont pas extraites, c’est bizarre
+Ce travers est-il corrigé ?
+Ton tableau csv est très moche quand je l’ouvre sous Excel (en PJ). Les accents ne passent pas. pourrais tu transmettre le fichier directement sous format xlsx ? 
+merci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02102025 - Dsl pour la réponse tardive. J'étais au colloque OZCAR Tereno à Paris. 
+On pourrait se voir devant un ordi et ouvrir HAL pour faire cela ensemble. 
+Cela dit je n'ai pas grand chose encore en valo sur FairCarbon. </t>
   </si>
 </sst>
 </file>
@@ -8174,7 +8228,7 @@
     <col min="23" max="16384" width="8.7265625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
@@ -8908,7 +8962,7 @@
       </c>
       <c r="V12" s="1"/>
     </row>
-    <row r="13" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" s="2" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
@@ -8958,7 +9012,7 @@
         <v>1814</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>1738</v>
+        <v>1814</v>
       </c>
       <c r="T13" s="59" t="s">
         <v>1844</v>
@@ -8966,7 +9020,9 @@
       <c r="U13" s="59" t="s">
         <v>1845</v>
       </c>
-      <c r="V13" s="1"/>
+      <c r="V13" s="1" t="s">
+        <v>2439</v>
+      </c>
     </row>
     <row r="14" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
@@ -11884,7 +11940,7 @@
       </c>
       <c r="V61" s="1"/>
     </row>
-    <row r="62" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>6</v>
       </c>
@@ -11934,7 +11990,7 @@
         <v>1814</v>
       </c>
       <c r="S62" s="1" t="s">
-        <v>1738</v>
+        <v>1814</v>
       </c>
       <c r="T62" s="58" t="s">
         <v>1915</v>
@@ -11942,7 +11998,9 @@
       <c r="U62" s="58" t="s">
         <v>1916</v>
       </c>
-      <c r="V62" s="1"/>
+      <c r="V62" s="1" t="s">
+        <v>2436</v>
+      </c>
     </row>
     <row r="63" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
@@ -12372,7 +12430,7 @@
       </c>
       <c r="V69" s="1"/>
     </row>
-    <row r="70" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:22" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>6</v>
       </c>
@@ -12422,7 +12480,7 @@
         <v>1814</v>
       </c>
       <c r="S70" s="1" t="s">
-        <v>1738</v>
+        <v>1814</v>
       </c>
       <c r="T70" s="58" t="s">
         <v>1926</v>
@@ -12430,7 +12488,9 @@
       <c r="U70" s="58" t="s">
         <v>1927</v>
       </c>
-      <c r="V70" s="1"/>
+      <c r="V70" s="1" t="s">
+        <v>2431</v>
+      </c>
     </row>
     <row r="71" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
@@ -13788,7 +13848,7 @@
       </c>
       <c r="V92" s="1"/>
     </row>
-    <row r="93" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:22" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>6</v>
       </c>
@@ -13840,7 +13900,7 @@
         <v>1814</v>
       </c>
       <c r="S93" s="1" t="s">
-        <v>1738</v>
+        <v>1814</v>
       </c>
       <c r="T93" s="58" t="s">
         <v>1855</v>
@@ -13848,7 +13908,9 @@
       <c r="U93" s="58" t="s">
         <v>1855</v>
       </c>
-      <c r="V93" s="1"/>
+      <c r="V93" s="1" t="s">
+        <v>2438</v>
+      </c>
     </row>
     <row r="94" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
@@ -15484,7 +15546,7 @@
         <v>2365</v>
       </c>
     </row>
-    <row r="120" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:22" s="2" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>6</v>
       </c>
@@ -15536,7 +15598,7 @@
         <v>1814</v>
       </c>
       <c r="S120" s="1" t="s">
-        <v>1738</v>
+        <v>1814</v>
       </c>
       <c r="T120" s="59" t="s">
         <v>1985</v>
@@ -15544,7 +15606,9 @@
       <c r="U120" s="59" t="s">
         <v>1986</v>
       </c>
-      <c r="V120" s="1"/>
+      <c r="V120" s="1" t="s">
+        <v>2430</v>
+      </c>
     </row>
     <row r="121" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
@@ -16042,7 +16106,7 @@
       </c>
       <c r="V128" s="1"/>
     </row>
-    <row r="129" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:22" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>6</v>
       </c>
@@ -16094,7 +16158,7 @@
         <v>1814</v>
       </c>
       <c r="S129" s="1" t="s">
-        <v>1738</v>
+        <v>1814</v>
       </c>
       <c r="T129" s="58" t="s">
         <v>1998</v>
@@ -16102,7 +16166,9 @@
       <c r="U129" s="58" t="s">
         <v>1845</v>
       </c>
-      <c r="V129" s="1"/>
+      <c r="V129" s="1" t="s">
+        <v>2440</v>
+      </c>
     </row>
     <row r="130" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
@@ -16594,7 +16660,7 @@
         <v>1814</v>
       </c>
       <c r="S137" s="1" t="s">
-        <v>1738</v>
+        <v>1814</v>
       </c>
       <c r="T137" s="58" t="s">
         <v>2004</v>
@@ -16602,7 +16668,9 @@
       <c r="U137" s="58" t="s">
         <v>1871</v>
       </c>
-      <c r="V137" s="1"/>
+      <c r="V137" s="1" t="s">
+        <v>2435</v>
+      </c>
     </row>
     <row r="138" spans="1:22" s="2" customFormat="1" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
@@ -18844,7 +18912,7 @@
         <v>1814</v>
       </c>
       <c r="S173" s="1" t="s">
-        <v>1738</v>
+        <v>1814</v>
       </c>
       <c r="T173" s="58" t="s">
         <v>2036</v>
@@ -18852,7 +18920,9 @@
       <c r="U173" s="58" t="s">
         <v>2037</v>
       </c>
-      <c r="V173" s="1"/>
+      <c r="V173" s="1" t="s">
+        <v>2434</v>
+      </c>
     </row>
     <row r="174" spans="1:22" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
@@ -19354,7 +19424,7 @@
       </c>
       <c r="V181" s="1"/>
     </row>
-    <row r="182" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:22" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
         <v>6</v>
       </c>
@@ -19406,7 +19476,7 @@
         <v>1814</v>
       </c>
       <c r="S182" s="1" t="s">
-        <v>1738</v>
+        <v>1814</v>
       </c>
       <c r="T182" s="59" t="s">
         <v>1998</v>
@@ -19414,7 +19484,9 @@
       <c r="U182" s="59" t="s">
         <v>1845</v>
       </c>
-      <c r="V182" s="1"/>
+      <c r="V182" s="1" t="s">
+        <v>2440</v>
+      </c>
     </row>
     <row r="183" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
@@ -22118,7 +22190,7 @@
       </c>
       <c r="V226" s="1"/>
     </row>
-    <row r="227" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:22" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
         <v>6</v>
       </c>
@@ -22170,7 +22242,7 @@
         <v>1814</v>
       </c>
       <c r="S227" s="1" t="s">
-        <v>1738</v>
+        <v>1814</v>
       </c>
       <c r="T227" s="58" t="s">
         <v>2087</v>
@@ -22178,7 +22250,9 @@
       <c r="U227" s="58" t="s">
         <v>2088</v>
       </c>
-      <c r="V227" s="1"/>
+      <c r="V227" s="1" t="s">
+        <v>2433</v>
+      </c>
     </row>
     <row r="228" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
@@ -22904,7 +22978,7 @@
       </c>
       <c r="V239" s="1"/>
     </row>
-    <row r="240" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:22" s="2" customFormat="1" ht="203" x14ac:dyDescent="0.35">
       <c r="A240" s="1" t="s">
         <v>6</v>
       </c>
@@ -22956,7 +23030,7 @@
         <v>1814</v>
       </c>
       <c r="S240" s="1" t="s">
-        <v>1738</v>
+        <v>1814</v>
       </c>
       <c r="T240" s="59" t="s">
         <v>2102</v>
@@ -22964,7 +23038,9 @@
       <c r="U240" s="59" t="s">
         <v>2046</v>
       </c>
-      <c r="V240" s="1"/>
+      <c r="V240" s="1" t="s">
+        <v>2441</v>
+      </c>
     </row>
     <row r="241" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A241" s="1" t="s">
@@ -24294,7 +24370,7 @@
       </c>
       <c r="V262" s="1"/>
     </row>
-    <row r="263" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A263" s="1" t="s">
         <v>6</v>
       </c>
@@ -24346,7 +24422,7 @@
         <v>1814</v>
       </c>
       <c r="S263" s="1" t="s">
-        <v>1738</v>
+        <v>1814</v>
       </c>
       <c r="T263" s="58" t="s">
         <v>2127</v>
@@ -24354,7 +24430,9 @@
       <c r="U263" s="58" t="s">
         <v>1945</v>
       </c>
-      <c r="V263" s="1"/>
+      <c r="V263" s="1" t="s">
+        <v>2432</v>
+      </c>
     </row>
     <row r="264" spans="1:22" s="2" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A264" s="1" t="s">
@@ -29580,7 +29658,7 @@
         <v>1814</v>
       </c>
       <c r="S349" s="1" t="s">
-        <v>1738</v>
+        <v>1814</v>
       </c>
       <c r="T349" s="58" t="s">
         <v>2004</v>
@@ -29588,7 +29666,9 @@
       <c r="U349" s="58" t="s">
         <v>1871</v>
       </c>
-      <c r="V349" s="1"/>
+      <c r="V349" s="1" t="s">
+        <v>2435</v>
+      </c>
     </row>
     <row r="350" spans="1:22" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A350" s="1" t="s">
@@ -30014,7 +30094,7 @@
       </c>
       <c r="V356" s="1"/>
     </row>
-    <row r="357" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:22" s="2" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A357" s="1" t="s">
         <v>6</v>
       </c>
@@ -30064,7 +30144,7 @@
         <v>1814</v>
       </c>
       <c r="S357" s="1" t="s">
-        <v>1738</v>
+        <v>1814</v>
       </c>
       <c r="T357" s="58" t="s">
         <v>2220</v>
@@ -30072,7 +30152,9 @@
       <c r="U357" s="58" t="s">
         <v>2221</v>
       </c>
-      <c r="V357" s="1"/>
+      <c r="V357" s="1" t="s">
+        <v>2437</v>
+      </c>
     </row>
     <row r="358" spans="1:22" s="2" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A358" s="1" t="s">
@@ -30442,7 +30524,7 @@
       </c>
       <c r="V363" s="1"/>
     </row>
-    <row r="364" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:22" s="2" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A364" s="1" t="s">
         <v>6</v>
       </c>
@@ -30494,7 +30576,7 @@
         <v>1814</v>
       </c>
       <c r="S364" s="1" t="s">
-        <v>1738</v>
+        <v>1814</v>
       </c>
       <c r="T364" s="59" t="s">
         <v>1985</v>
@@ -30502,7 +30584,9 @@
       <c r="U364" s="59" t="s">
         <v>1986</v>
       </c>
-      <c r="V364" s="1"/>
+      <c r="V364" s="1" t="s">
+        <v>2430</v>
+      </c>
     </row>
     <row r="365" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A365" s="1" t="s">
@@ -32084,7 +32168,7 @@
       </c>
       <c r="V390" s="1"/>
     </row>
-    <row r="391" spans="1:22" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:22" s="2" customFormat="1" ht="203" x14ac:dyDescent="0.35">
       <c r="A391" s="1" t="s">
         <v>6</v>
       </c>
@@ -32136,7 +32220,7 @@
         <v>1814</v>
       </c>
       <c r="S391" s="1" t="s">
-        <v>1738</v>
+        <v>1814</v>
       </c>
       <c r="T391" s="58" t="s">
         <v>2102</v>
@@ -32144,7 +32228,9 @@
       <c r="U391" s="58" t="s">
         <v>2046</v>
       </c>
-      <c r="V391" s="1"/>
+      <c r="V391" s="1" t="s">
+        <v>2441</v>
+      </c>
     </row>
     <row r="392" spans="1:22" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A392" s="1" t="s">

--- a/Data/FairCarboN_Datas_Contacts.xlsx
+++ b/Data/FairCarboN_Datas_Contacts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A017DD94-B9A1-497B-9E52-8A87963ACC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF00677-62CA-46F0-9E6E-8F0DDCEBEF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6992" uniqueCount="2493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6993" uniqueCount="2494">
   <si>
     <t>Acronyme PEPR</t>
   </si>
@@ -7637,6 +7637,9 @@
   </si>
   <si>
     <t>09102025 - Je suis désolé du retard de réponse. J’essaie de me pencher sur la question dès que possible.</t>
+  </si>
+  <si>
+    <t>10102025 - j'ai réalisé les modifications suggérées en ajoutant "FairCarboN" dans les mots clés de plusieurs de mes articles déposés sur HAL.</t>
   </si>
 </sst>
 </file>
@@ -22750,7 +22753,7 @@
       </c>
       <c r="V232" s="1"/>
     </row>
-    <row r="233" spans="1:22" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:22" s="2" customFormat="1" ht="145" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>6</v>
       </c>
@@ -22800,7 +22803,7 @@
         <v>1813</v>
       </c>
       <c r="S233" s="1" t="s">
-        <v>1737</v>
+        <v>1813</v>
       </c>
       <c r="T233" s="58" t="s">
         <v>2094</v>
@@ -22808,7 +22811,9 @@
       <c r="U233" s="58" t="s">
         <v>1830</v>
       </c>
-      <c r="V233" s="1"/>
+      <c r="V233" s="1" t="s">
+        <v>2493</v>
+      </c>
     </row>
     <row r="234" spans="1:22" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">

--- a/Data/FairCarboN_Datas_Contacts.xlsx
+++ b/Data/FairCarboN_Datas_Contacts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3A9E9F-A80B-43FE-A010-44FA11C4A174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C7F048-FD65-4409-81EC-420225D4D72B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liste" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10346" uniqueCount="3110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10347" uniqueCount="3110">
   <si>
     <t>Acronyme PEPR</t>
   </si>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="AA17" s="17"/>
     </row>
-    <row r="18" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A18" s="17" t="s">
         <v>6</v>
       </c>
@@ -11497,7 +11497,9 @@
       <c r="K18" s="3" t="s">
         <v>2636</v>
       </c>
-      <c r="L18" s="3"/>
+      <c r="L18" s="5" t="s">
+        <v>2639</v>
+      </c>
       <c r="M18" s="17" t="s">
         <v>2637</v>
       </c>

--- a/Data/FairCarboN_Datas_Contacts.xlsx
+++ b/Data/FairCarboN_Datas_Contacts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{917AE5E7-9C01-411A-8B20-A90F05FEE732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DAD0D5A-F939-41B6-BFCE-4C6B058C3B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10065,11 +10065,18 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0;[Red]0"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -10369,149 +10376,152 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="5" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="5" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -10519,55 +10529,58 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10576,10 +10589,7 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10999,7 +11009,7 @@
       </c>
       <c r="AA2" s="17"/>
     </row>
-    <row r="3" spans="1:27" ht="87" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:27" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
         <v>6</v>
       </c>
@@ -11895,7 +11905,7 @@
       </c>
       <c r="AA14" s="17"/>
     </row>
-    <row r="15" spans="1:27" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:27" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A15" s="17" t="s">
         <v>6</v>
       </c>
@@ -11968,7 +11978,7 @@
       </c>
       <c r="AA15" s="17"/>
     </row>
-    <row r="16" spans="1:27" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:27" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A16" s="17" t="s">
         <v>6</v>
       </c>
@@ -12191,7 +12201,7 @@
       </c>
       <c r="AA18" s="17"/>
     </row>
-    <row r="19" spans="1:27" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:27" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A19" s="17" t="s">
         <v>6</v>
       </c>
@@ -12722,7 +12732,7 @@
         <v>2336</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:27" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A26" s="17" t="s">
         <v>6</v>
       </c>
@@ -12795,7 +12805,7 @@
       </c>
       <c r="AA26" s="17"/>
     </row>
-    <row r="27" spans="1:27" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:27" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A27" s="17" t="s">
         <v>6</v>
       </c>
@@ -12868,7 +12878,7 @@
       </c>
       <c r="AA27" s="17"/>
     </row>
-    <row r="28" spans="1:27" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:27" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A28" s="17" t="s">
         <v>6</v>
       </c>
@@ -13316,7 +13326,7 @@
       </c>
       <c r="AA33" s="17"/>
     </row>
-    <row r="34" spans="1:27" ht="232" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:27" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A34" s="17" t="s">
         <v>6</v>
       </c>
@@ -13464,7 +13474,7 @@
       </c>
       <c r="AA35" s="17"/>
     </row>
-    <row r="36" spans="1:27" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:27" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A36" s="17" t="s">
         <v>6</v>
       </c>
@@ -14056,7 +14066,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A44" s="17" t="s">
         <v>6</v>
       </c>
@@ -14285,7 +14295,7 @@
       </c>
       <c r="AA46" s="17"/>
     </row>
-    <row r="47" spans="1:27" ht="87" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:27" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A47" s="17" t="s">
         <v>6</v>
       </c>
@@ -14508,7 +14518,7 @@
       </c>
       <c r="AA49" s="17"/>
     </row>
-    <row r="50" spans="1:27" ht="87" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:27" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A50" s="17" t="s">
         <v>6</v>
       </c>
@@ -14731,7 +14741,7 @@
       </c>
       <c r="AA52" s="17"/>
     </row>
-    <row r="53" spans="1:27" ht="372" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:27" ht="356.5" x14ac:dyDescent="0.35">
       <c r="A53" s="17" t="s">
         <v>6</v>
       </c>
@@ -14806,7 +14816,7 @@
       </c>
       <c r="AA53" s="17"/>
     </row>
-    <row r="54" spans="1:27" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A54" s="17" t="s">
         <v>6</v>
       </c>
@@ -14881,7 +14891,7 @@
       </c>
       <c r="AA54" s="17"/>
     </row>
-    <row r="55" spans="1:27" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A55" s="17" t="s">
         <v>6</v>
       </c>
@@ -14956,7 +14966,7 @@
       </c>
       <c r="AA55" s="17"/>
     </row>
-    <row r="56" spans="1:27" ht="87" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:27" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A56" s="17" t="s">
         <v>6</v>
       </c>
@@ -15029,7 +15039,7 @@
       </c>
       <c r="AA56" s="17"/>
     </row>
-    <row r="57" spans="1:27" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A57" s="17" t="s">
         <v>6</v>
       </c>
@@ -15402,7 +15412,7 @@
       </c>
       <c r="AA61" s="17"/>
     </row>
-    <row r="62" spans="1:27" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A62" s="17" t="s">
         <v>6</v>
       </c>
@@ -15769,7 +15779,7 @@
       </c>
       <c r="AA66" s="17"/>
     </row>
-    <row r="67" spans="1:27" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A67" s="17" t="s">
         <v>6</v>
       </c>
@@ -16073,7 +16083,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A71" s="17" t="s">
         <v>6</v>
       </c>
@@ -16150,7 +16160,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="87" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:27" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A72" s="17" t="s">
         <v>6</v>
       </c>
@@ -16223,7 +16233,7 @@
       </c>
       <c r="AA72" s="17"/>
     </row>
-    <row r="73" spans="1:27" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A73" s="17" t="s">
         <v>6</v>
       </c>
@@ -16298,7 +16308,7 @@
       </c>
       <c r="AA73" s="17"/>
     </row>
-    <row r="74" spans="1:27" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A74" s="17" t="s">
         <v>6</v>
       </c>
@@ -16373,7 +16383,7 @@
       </c>
       <c r="AA74" s="17"/>
     </row>
-    <row r="75" spans="1:27" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A75" s="17" t="s">
         <v>6</v>
       </c>
@@ -25810,7 +25820,7 @@
       </c>
       <c r="AA197" s="17"/>
     </row>
-    <row r="198" spans="1:27" ht="387.5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:27" ht="372" x14ac:dyDescent="0.35">
       <c r="A198" s="17" t="s">
         <v>6</v>
       </c>
@@ -25887,7 +25897,7 @@
       </c>
       <c r="AA198" s="17"/>
     </row>
-    <row r="199" spans="1:27" ht="387.5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:27" ht="372" x14ac:dyDescent="0.35">
       <c r="A199" s="17" t="s">
         <v>6</v>
       </c>
@@ -26570,7 +26580,7 @@
       </c>
       <c r="AA207" s="17"/>
     </row>
-    <row r="208" spans="1:27" ht="333.5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:27" ht="348" x14ac:dyDescent="0.35">
       <c r="A208" s="17" t="s">
         <v>6</v>
       </c>
@@ -26601,7 +26611,7 @@
       <c r="J208" s="5" t="s">
         <v>2748</v>
       </c>
-      <c r="K208" s="17" t="s">
+      <c r="K208" s="71" t="s">
         <v>2750</v>
       </c>
       <c r="L208" s="5" t="s">
@@ -29799,7 +29809,7 @@
       </c>
       <c r="AA250" s="17"/>
     </row>
-    <row r="251" spans="1:27" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:27" ht="62" x14ac:dyDescent="0.35">
       <c r="A251" s="17" t="s">
         <v>6</v>
       </c>
@@ -31619,7 +31629,7 @@
       </c>
       <c r="AA274" s="17"/>
     </row>
-    <row r="275" spans="1:27" ht="232" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:27" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A275" s="17" t="s">
         <v>6</v>
       </c>
@@ -31771,7 +31781,7 @@
         <v>2336</v>
       </c>
     </row>
-    <row r="277" spans="1:27" ht="232" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:27" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A277" s="17" t="s">
         <v>6</v>
       </c>
@@ -31996,7 +32006,7 @@
       </c>
       <c r="AA279" s="17"/>
     </row>
-    <row r="280" spans="1:27" ht="232" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:27" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A280" s="17" t="s">
         <v>6</v>
       </c>
@@ -32071,7 +32081,7 @@
       </c>
       <c r="AA280" s="17"/>
     </row>
-    <row r="281" spans="1:27" ht="232" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:27" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A281" s="17" t="s">
         <v>6</v>
       </c>
@@ -32146,7 +32156,7 @@
       </c>
       <c r="AA281" s="17"/>
     </row>
-    <row r="282" spans="1:27" ht="232" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:27" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A282" s="17" t="s">
         <v>6</v>
       </c>
@@ -32221,7 +32231,7 @@
       </c>
       <c r="AA282" s="17"/>
     </row>
-    <row r="283" spans="1:27" ht="232" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:27" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A283" s="17" t="s">
         <v>6</v>
       </c>
@@ -32296,7 +32306,7 @@
       </c>
       <c r="AA283" s="17"/>
     </row>
-    <row r="284" spans="1:27" ht="232" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:27" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A284" s="17" t="s">
         <v>6</v>
       </c>
@@ -32371,7 +32381,7 @@
       </c>
       <c r="AA284" s="17"/>
     </row>
-    <row r="285" spans="1:27" ht="232" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:27" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A285" s="17" t="s">
         <v>6</v>
       </c>
@@ -33342,7 +33352,7 @@
       </c>
       <c r="AA297" s="17"/>
     </row>
-    <row r="298" spans="1:27" ht="232" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:27" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A298" s="17" t="s">
         <v>6</v>
       </c>
@@ -33865,7 +33875,7 @@
         <v>2360</v>
       </c>
     </row>
-    <row r="305" spans="1:27" ht="319" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:27" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A305" s="17" t="s">
         <v>6</v>
       </c>
@@ -33942,7 +33952,7 @@
       </c>
       <c r="AA305" s="17"/>
     </row>
-    <row r="306" spans="1:27" ht="319" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:27" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A306" s="17" t="s">
         <v>6</v>
       </c>
@@ -34021,7 +34031,7 @@
       </c>
       <c r="AA306" s="17"/>
     </row>
-    <row r="307" spans="1:27" ht="319" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:27" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A307" s="17" t="s">
         <v>6</v>
       </c>
@@ -34100,7 +34110,7 @@
       </c>
       <c r="AA307" s="17"/>
     </row>
-    <row r="308" spans="1:27" ht="319" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:27" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A308" s="17" t="s">
         <v>6</v>
       </c>
@@ -34177,7 +34187,7 @@
       </c>
       <c r="AA308" s="17"/>
     </row>
-    <row r="309" spans="1:27" ht="319" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:27" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A309" s="17" t="s">
         <v>6</v>
       </c>
@@ -34250,7 +34260,7 @@
       </c>
       <c r="AA309" s="17"/>
     </row>
-    <row r="310" spans="1:27" ht="319" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:27" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A310" s="17" t="s">
         <v>6</v>
       </c>
@@ -34629,7 +34639,7 @@
       </c>
       <c r="AA314" s="17"/>
     </row>
-    <row r="315" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A315" s="17" t="s">
         <v>6</v>
       </c>
@@ -35154,7 +35164,7 @@
         <v>2341</v>
       </c>
     </row>
-    <row r="322" spans="1:27" ht="319" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:27" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A322" s="17" t="s">
         <v>6</v>
       </c>
@@ -35231,7 +35241,7 @@
       </c>
       <c r="AA322" s="17"/>
     </row>
-    <row r="323" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A323" s="17" t="s">
         <v>6</v>
       </c>
@@ -35308,7 +35318,7 @@
       </c>
       <c r="AA323" s="17"/>
     </row>
-    <row r="324" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A324" s="17" t="s">
         <v>6</v>
       </c>
@@ -35387,7 +35397,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="325" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A325" s="17" t="s">
         <v>6</v>
       </c>
@@ -35462,7 +35472,7 @@
       </c>
       <c r="AA325" s="17"/>
     </row>
-    <row r="326" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A326" s="17" t="s">
         <v>6</v>
       </c>
@@ -35614,7 +35624,7 @@
         <v>2405</v>
       </c>
     </row>
-    <row r="328" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A328" s="17" t="s">
         <v>6</v>
       </c>
@@ -35691,7 +35701,7 @@
       </c>
       <c r="AA328" s="17"/>
     </row>
-    <row r="329" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A329" s="17" t="s">
         <v>6</v>
       </c>
@@ -35766,7 +35776,7 @@
       </c>
       <c r="AA329" s="17"/>
     </row>
-    <row r="330" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A330" s="17" t="s">
         <v>6</v>
       </c>
@@ -35841,7 +35851,7 @@
       </c>
       <c r="AA330" s="17"/>
     </row>
-    <row r="331" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:27" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A331" s="17" t="s">
         <v>6</v>
       </c>
@@ -35920,7 +35930,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="332" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:27" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A332" s="17" t="s">
         <v>6</v>
       </c>
@@ -35995,7 +36005,7 @@
       </c>
       <c r="AA332" s="17"/>
     </row>
-    <row r="333" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:27" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A333" s="17" t="s">
         <v>6</v>
       </c>
@@ -36374,7 +36384,7 @@
       </c>
       <c r="AA337" s="17"/>
     </row>
-    <row r="338" spans="1:27" ht="319" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:27" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A338" s="17" t="s">
         <v>6</v>
       </c>
@@ -36451,7 +36461,7 @@
         <v>2328</v>
       </c>
     </row>
-    <row r="339" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A339" s="17" t="s">
         <v>6</v>
       </c>
@@ -36526,7 +36536,7 @@
       </c>
       <c r="AA339" s="17"/>
     </row>
-    <row r="340" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A340" s="17" t="s">
         <v>6</v>
       </c>
@@ -36753,7 +36763,7 @@
         <v>2325</v>
       </c>
     </row>
-    <row r="343" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A343" s="17" t="s">
         <v>6</v>
       </c>
@@ -36828,7 +36838,7 @@
       </c>
       <c r="AA343" s="17"/>
     </row>
-    <row r="344" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:27" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A344" s="17" t="s">
         <v>6</v>
       </c>
@@ -36903,7 +36913,7 @@
       </c>
       <c r="AA344" s="17"/>
     </row>
-    <row r="345" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A345" s="17" t="s">
         <v>6</v>
       </c>
@@ -37053,7 +37063,7 @@
       </c>
       <c r="AA346" s="17"/>
     </row>
-    <row r="347" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A347" s="17" t="s">
         <v>6</v>
       </c>
@@ -37201,7 +37211,7 @@
       </c>
       <c r="AA348" s="17"/>
     </row>
-    <row r="349" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:27" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A349" s="17" t="s">
         <v>6</v>
       </c>
@@ -37355,7 +37365,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="351" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A351" s="17" t="s">
         <v>6</v>
       </c>
@@ -37507,7 +37517,7 @@
       </c>
       <c r="AA352" s="17"/>
     </row>
-    <row r="353" spans="1:27" ht="333.5" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:27" ht="348" x14ac:dyDescent="0.35">
       <c r="A353" s="17" t="s">
         <v>6</v>
       </c>
@@ -37584,7 +37594,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="354" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A354" s="17" t="s">
         <v>6</v>
       </c>
@@ -37811,7 +37821,7 @@
         <v>2392</v>
       </c>
     </row>
-    <row r="357" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:27" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A357" s="17" t="s">
         <v>6</v>
       </c>
@@ -38561,7 +38571,7 @@
       </c>
       <c r="AA366" s="17"/>
     </row>
-    <row r="367" spans="1:27" ht="319" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:27" ht="333.5" x14ac:dyDescent="0.35">
       <c r="A367" s="17" t="s">
         <v>6</v>
       </c>
@@ -38792,7 +38802,7 @@
         <v>2387</v>
       </c>
     </row>
-    <row r="370" spans="1:27" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A370" s="17" t="s">
         <v>6</v>
       </c>
@@ -40799,7 +40809,7 @@
       </c>
       <c r="AA396" s="17"/>
     </row>
-    <row r="397" spans="1:27" ht="232" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:27" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A397" s="17" t="s">
         <v>6</v>
       </c>
@@ -41024,7 +41034,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="400" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:27" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A400" s="17" t="s">
         <v>6</v>
       </c>
@@ -41308,7 +41318,7 @@
       </c>
       <c r="AA403" s="17"/>
     </row>
-    <row r="404" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A404" s="17" t="s">
         <v>6</v>
       </c>
@@ -41381,7 +41391,7 @@
       <c r="Z404" s="17"/>
       <c r="AA404" s="17"/>
     </row>
-    <row r="405" spans="1:27" ht="319" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:27" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A405" s="17" t="s">
         <v>6</v>
       </c>
@@ -41813,7 +41823,7 @@
       <c r="Z410" s="17"/>
       <c r="AA410" s="17"/>
     </row>
-    <row r="411" spans="1:27" ht="319" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:27" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A411" s="17" t="s">
         <v>6</v>
       </c>
@@ -41886,7 +41896,7 @@
       <c r="Z411" s="17"/>
       <c r="AA411" s="17"/>
     </row>
-    <row r="412" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A412" s="17" t="s">
         <v>6</v>
       </c>
@@ -42168,7 +42178,7 @@
       <c r="Z415" s="17"/>
       <c r="AA415" s="17"/>
     </row>
-    <row r="416" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A416" s="17" t="s">
         <v>6</v>
       </c>
@@ -42379,7 +42389,7 @@
       <c r="Z418" s="17"/>
       <c r="AA418" s="17"/>
     </row>
-    <row r="419" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A419" s="17" t="s">
         <v>6</v>
       </c>
@@ -42452,7 +42462,7 @@
       <c r="Z419" s="17"/>
       <c r="AA419" s="17"/>
     </row>
-    <row r="420" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A420" s="17" t="s">
         <v>6</v>
       </c>
@@ -43081,7 +43091,7 @@
       <c r="Z428" s="17"/>
       <c r="AA428" s="17"/>
     </row>
-    <row r="429" spans="1:27" ht="87" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:27" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A429" s="17" t="s">
         <v>6</v>
       </c>
@@ -43148,7 +43158,7 @@
       <c r="Z429" s="17"/>
       <c r="AA429" s="17"/>
     </row>
-    <row r="430" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:27" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A430" s="17" t="s">
         <v>6</v>
       </c>
@@ -43576,7 +43586,7 @@
       <c r="Z435" s="17"/>
       <c r="AA435" s="17"/>
     </row>
-    <row r="436" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A436" s="17" t="s">
         <v>6</v>
       </c>
@@ -43643,7 +43653,7 @@
       <c r="Z436" s="17"/>
       <c r="AA436" s="17"/>
     </row>
-    <row r="437" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A437" s="17" t="s">
         <v>6</v>
       </c>
@@ -43921,7 +43931,7 @@
       <c r="Z440" s="22"/>
       <c r="AA440" s="17"/>
     </row>
-    <row r="441" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A441" s="17" t="s">
         <v>6</v>
       </c>
@@ -43992,7 +44002,7 @@
       <c r="Z441" s="17"/>
       <c r="AA441" s="17"/>
     </row>
-    <row r="442" spans="1:27" ht="319" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:27" ht="348" x14ac:dyDescent="0.35">
       <c r="A442" s="17" t="s">
         <v>6</v>
       </c>
@@ -44061,7 +44071,7 @@
       <c r="Z442" s="17"/>
       <c r="AA442" s="17"/>
     </row>
-    <row r="443" spans="1:27" ht="319" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:27" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A443" s="17" t="s">
         <v>6</v>
       </c>
@@ -45465,7 +45475,7 @@
       <c r="Z462" s="17"/>
       <c r="AA462" s="17"/>
     </row>
-    <row r="463" spans="1:27" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A463" s="39" t="s">
         <v>6</v>
       </c>
@@ -45536,7 +45546,7 @@
       <c r="Z463" s="17"/>
       <c r="AA463" s="17"/>
     </row>
-    <row r="464" spans="1:27" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A464" s="39" t="s">
         <v>6</v>
       </c>
@@ -46627,7 +46637,7 @@
       <c r="Z478" s="17"/>
       <c r="AA478" s="17"/>
     </row>
-    <row r="479" spans="1:27" ht="58" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:27" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A479" s="42" t="s">
         <v>6</v>
       </c>
@@ -48977,7 +48987,7 @@
       <c r="Z514" s="17"/>
       <c r="AA514" s="17"/>
     </row>
-    <row r="515" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A515" s="49" t="s">
         <v>6</v>
       </c>
@@ -49119,7 +49129,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="517" spans="1:27" ht="87" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:27" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A517" s="17" t="s">
         <v>6</v>
       </c>
@@ -49600,7 +49610,7 @@
       <c r="Z523" s="17"/>
       <c r="AA523" s="17"/>
     </row>
-    <row r="524" spans="1:27" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:27" ht="232" x14ac:dyDescent="0.35">
       <c r="A524" s="49" t="s">
         <v>6</v>
       </c>
@@ -50034,10 +50044,10 @@
       <c r="M530" s="5" t="s">
         <v>2609</v>
       </c>
-      <c r="N530" s="5" t="s">
+      <c r="N530" s="5"/>
+      <c r="O530" s="5" t="s">
         <v>3191</v>
       </c>
-      <c r="O530" s="17"/>
       <c r="P530" s="17" t="s">
         <v>3189</v>
       </c>
@@ -50132,7 +50142,7 @@
       <c r="Z531" s="17"/>
       <c r="AA531" s="17"/>
     </row>
-    <row r="532" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:27" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A532" s="49" t="s">
         <v>6</v>
       </c>
@@ -50199,7 +50209,7 @@
       <c r="Z532" s="17"/>
       <c r="AA532" s="17"/>
     </row>
-    <row r="533" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:27" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A533" s="49" t="s">
         <v>6</v>
       </c>
@@ -50264,7 +50274,7 @@
       <c r="Z533" s="17"/>
       <c r="AA533" s="17"/>
     </row>
-    <row r="534" spans="1:27" ht="319" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:27" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A534" s="49" t="s">
         <v>6</v>
       </c>
@@ -50329,7 +50339,7 @@
       <c r="Z534" s="17"/>
       <c r="AA534" s="17"/>
     </row>
-    <row r="535" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:27" ht="174" x14ac:dyDescent="0.35">
       <c r="A535" s="49" t="s">
         <v>6</v>
       </c>
@@ -50396,7 +50406,7 @@
       <c r="Z535" s="17"/>
       <c r="AA535" s="17"/>
     </row>
-    <row r="536" spans="1:27" ht="201.5" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:27" ht="217" x14ac:dyDescent="0.35">
       <c r="A536" s="49" t="s">
         <v>6</v>
       </c>
@@ -50533,7 +50543,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q222">
     <sortCondition ref="C2:C417"/>
   </sortState>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{A888D081-6FD4-4DBA-B75D-11B8EF20FB9F}"/>
     <hyperlink ref="D4" r:id="rId2" xr:uid="{84186489-15CD-48F0-BE91-0362E1A8C1AB}"/>

--- a/Data/FairCarboN_Datas_Contacts.xlsx
+++ b/Data/FairCarboN_Datas_Contacts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C62A74E-8877-42B3-BAD9-07076D3E8A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334DC798-5390-4043-BD7A-E1C4099C62B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33630" yWindow="2820" windowWidth="14400" windowHeight="8175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liste" sheetId="2" r:id="rId1"/>

--- a/Data/FairCarboN_Datas_Contacts.xlsx
+++ b/Data/FairCarboN_Datas_Contacts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2C5F02-4035-4D7D-B02E-0A36ABE72D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3E46F9-42F7-4B1B-A984-1FF6B4876F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Data/FairCarboN_Datas_Contacts.xlsx
+++ b/Data/FairCarboN_Datas_Contacts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3E46F9-42F7-4B1B-A984-1FF6B4876F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CCE2BDD-C0C7-4EBF-BC7E-5844709731F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Data/FairCarboN_Datas_Contacts.xlsx
+++ b/Data/FairCarboN_Datas_Contacts.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CCE2BDD-C0C7-4EBF-BC7E-5844709731F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E153DFDE-39ED-4720-99AF-5B527363BFC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liste" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Liste!$A$1:$AA$536</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Liste!$A$1:$AA$537</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11087" uniqueCount="3272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11104" uniqueCount="3275">
   <si>
     <t>Libellé structure</t>
   </si>
@@ -10053,6 +10053,15 @@
   </si>
   <si>
     <t>Gouvernance</t>
+  </si>
+  <si>
+    <t>Elie Le Guyader</t>
+  </si>
+  <si>
+    <t>LE GUYADER</t>
+  </si>
+  <si>
+    <t>Elie</t>
   </si>
 </sst>
 </file>
@@ -10839,7 +10848,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:AA536"/>
+  <dimension ref="A1:AA537"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.54296875" style="19" bestFit="1" customWidth="1"/>
@@ -14755,7 +14764,7 @@
       </c>
       <c r="AA52" s="17"/>
     </row>
-    <row r="53" spans="1:27" ht="341" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:27" ht="356.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="17" t="s">
         <v>5</v>
       </c>
@@ -15203,7 +15212,7 @@
       </c>
       <c r="AA58" s="17"/>
     </row>
-    <row r="59" spans="1:27" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:27" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="17" t="s">
         <v>5</v>
       </c>
@@ -16989,7 +16998,7 @@
       </c>
       <c r="AA82" s="17"/>
     </row>
-    <row r="83" spans="1:27" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:27" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="17" t="s">
         <v>5</v>
       </c>
@@ -20389,7 +20398,7 @@
         <v>2395</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="203" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:27" ht="217.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="17" t="s">
         <v>5</v>
       </c>
@@ -22403,7 +22412,7 @@
       </c>
       <c r="AA152" s="17"/>
     </row>
-    <row r="153" spans="1:27" ht="186" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:27" ht="201.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="17" t="s">
         <v>5</v>
       </c>
@@ -23238,7 +23247,7 @@
       </c>
       <c r="AA163" s="17"/>
     </row>
-    <row r="164" spans="1:27" ht="186" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:27" ht="201.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="17" t="s">
         <v>5</v>
       </c>
@@ -23390,7 +23399,7 @@
       </c>
       <c r="AA165" s="17"/>
     </row>
-    <row r="166" spans="1:27" ht="186" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:27" ht="201.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="17" t="s">
         <v>5</v>
       </c>
@@ -27640,7 +27649,7 @@
       </c>
       <c r="AA221" s="17"/>
     </row>
-    <row r="222" spans="1:27" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:27" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A222" s="17" t="s">
         <v>5</v>
       </c>
@@ -28090,7 +28099,7 @@
         <v>2331</v>
       </c>
     </row>
-    <row r="228" spans="1:27" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:27" ht="77.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" s="17" t="s">
         <v>5</v>
       </c>
@@ -29748,7 +29757,7 @@
       </c>
       <c r="AA249" s="17"/>
     </row>
-    <row r="250" spans="1:27" ht="186" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:27" ht="201.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" s="17" t="s">
         <v>5</v>
       </c>
@@ -29823,7 +29832,7 @@
       </c>
       <c r="AA250" s="17"/>
     </row>
-    <row r="251" spans="1:27" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:27" ht="62" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" s="17" t="s">
         <v>5</v>
       </c>
@@ -30567,7 +30576,7 @@
       </c>
       <c r="AA260" s="17"/>
     </row>
-    <row r="261" spans="1:27" ht="186" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:27" ht="201.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" s="17" t="s">
         <v>5</v>
       </c>
@@ -30644,7 +30653,7 @@
         <v>2333</v>
       </c>
     </row>
-    <row r="262" spans="1:27" ht="186" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:27" ht="201.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" s="17" t="s">
         <v>5</v>
       </c>
@@ -30719,7 +30728,7 @@
       </c>
       <c r="AA262" s="17"/>
     </row>
-    <row r="263" spans="1:27" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:27" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" s="17" t="s">
         <v>5</v>
       </c>
@@ -30948,7 +30957,7 @@
       </c>
       <c r="AA265" s="17"/>
     </row>
-    <row r="266" spans="1:27" ht="377" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:27" ht="391.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" s="17" t="s">
         <v>5</v>
       </c>
@@ -32997,7 +33006,7 @@
       </c>
       <c r="AA292" s="17"/>
     </row>
-    <row r="293" spans="1:27" ht="174" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:27" ht="188.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" s="17" t="s">
         <v>5</v>
       </c>
@@ -37079,7 +37088,7 @@
       </c>
       <c r="AA346" s="17"/>
     </row>
-    <row r="347" spans="1:27" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:27" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" s="17" t="s">
         <v>5</v>
       </c>
@@ -37985,7 +37994,7 @@
       </c>
       <c r="AA358" s="17"/>
     </row>
-    <row r="359" spans="1:27" ht="261" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:27" ht="275.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" s="17" t="s">
         <v>5</v>
       </c>
@@ -38135,7 +38144,7 @@
       </c>
       <c r="AA360" s="17"/>
     </row>
-    <row r="361" spans="1:27" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A361" s="17" t="s">
         <v>5</v>
       </c>
@@ -38210,7 +38219,7 @@
       </c>
       <c r="AA361" s="17"/>
     </row>
-    <row r="362" spans="1:27" ht="356.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:27" ht="356.5" x14ac:dyDescent="0.35">
       <c r="A362" s="17" t="s">
         <v>5</v>
       </c>
@@ -38289,7 +38298,7 @@
         <v>2235</v>
       </c>
     </row>
-    <row r="363" spans="1:27" ht="124" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:27" ht="124" x14ac:dyDescent="0.35">
       <c r="A363" s="17" t="s">
         <v>5</v>
       </c>
@@ -38362,7 +38371,7 @@
       </c>
       <c r="AA363" s="17"/>
     </row>
-    <row r="364" spans="1:27" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A364" s="17" t="s">
         <v>5</v>
       </c>
@@ -38437,7 +38446,7 @@
       </c>
       <c r="AA364" s="17"/>
     </row>
-    <row r="365" spans="1:27" ht="124" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:27" ht="124" x14ac:dyDescent="0.35">
       <c r="A365" s="17" t="s">
         <v>5</v>
       </c>
@@ -38512,7 +38521,7 @@
       </c>
       <c r="AA365" s="17"/>
     </row>
-    <row r="366" spans="1:27" ht="319" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:27" ht="319" x14ac:dyDescent="0.35">
       <c r="A366" s="17" t="s">
         <v>5</v>
       </c>
@@ -38589,7 +38598,7 @@
       </c>
       <c r="AA366" s="17"/>
     </row>
-    <row r="367" spans="1:27" ht="304.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:27" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A367" s="17" t="s">
         <v>5</v>
       </c>
@@ -38664,7 +38673,7 @@
       </c>
       <c r="AA367" s="17"/>
     </row>
-    <row r="368" spans="1:27" ht="304.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:27" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A368" s="17" t="s">
         <v>5</v>
       </c>
@@ -38743,7 +38752,7 @@
         <v>2380</v>
       </c>
     </row>
-    <row r="369" spans="1:27" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:27" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A369" s="17" t="s">
         <v>5</v>
       </c>
@@ -38816,7 +38825,7 @@
       </c>
       <c r="AA369" s="17"/>
     </row>
-    <row r="370" spans="1:27" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A370" s="17" t="s">
         <v>5</v>
       </c>
@@ -38891,7 +38900,7 @@
       </c>
       <c r="AA370" s="17"/>
     </row>
-    <row r="371" spans="1:27" ht="304.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:27" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A371" s="17" t="s">
         <v>5</v>
       </c>
@@ -38968,7 +38977,7 @@
       </c>
       <c r="AA371" s="17"/>
     </row>
-    <row r="372" spans="1:27" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:27" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A372" s="17" t="s">
         <v>5</v>
       </c>
@@ -39039,7 +39048,7 @@
       </c>
       <c r="AA372" s="17"/>
     </row>
-    <row r="373" spans="1:27" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A373" s="17" t="s">
         <v>5</v>
       </c>
@@ -39110,7 +39119,7 @@
         <v>2273</v>
       </c>
     </row>
-    <row r="374" spans="1:27" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A374" s="17" t="s">
         <v>5</v>
       </c>
@@ -39183,7 +39192,7 @@
       </c>
       <c r="AA374" s="17"/>
     </row>
-    <row r="375" spans="1:27" ht="304.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:27" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A375" s="17" t="s">
         <v>5</v>
       </c>
@@ -39258,7 +39267,7 @@
       </c>
       <c r="AA375" s="17"/>
     </row>
-    <row r="376" spans="1:27" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:27" ht="116" x14ac:dyDescent="0.35">
       <c r="A376" s="17" t="s">
         <v>5</v>
       </c>
@@ -39333,7 +39342,7 @@
       </c>
       <c r="AA376" s="17"/>
     </row>
-    <row r="377" spans="1:27" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A377" s="17" t="s">
         <v>5</v>
       </c>
@@ -39406,7 +39415,7 @@
       </c>
       <c r="AA377" s="17"/>
     </row>
-    <row r="378" spans="1:27" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A378" s="17" t="s">
         <v>5</v>
       </c>
@@ -39477,7 +39486,7 @@
       </c>
       <c r="AA378" s="17"/>
     </row>
-    <row r="379" spans="1:27" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:27" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A379" s="17" t="s">
         <v>5</v>
       </c>
@@ -39550,7 +39559,7 @@
       </c>
       <c r="AA379" s="17"/>
     </row>
-    <row r="380" spans="1:27" ht="304.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:27" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A380" s="17" t="s">
         <v>5</v>
       </c>
@@ -39625,7 +39634,7 @@
       </c>
       <c r="AA380" s="17"/>
     </row>
-    <row r="381" spans="1:27" ht="304.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:27" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A381" s="17" t="s">
         <v>5</v>
       </c>
@@ -39704,7 +39713,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="382" spans="1:27" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A382" s="17" t="s">
         <v>5</v>
       </c>
@@ -39777,7 +39786,7 @@
       </c>
       <c r="AA382" s="17"/>
     </row>
-    <row r="383" spans="1:27" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A383" s="17" t="s">
         <v>5</v>
       </c>
@@ -39850,7 +39859,7 @@
       </c>
       <c r="AA383" s="17"/>
     </row>
-    <row r="384" spans="1:27" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A384" s="17" t="s">
         <v>5</v>
       </c>
@@ -39925,7 +39934,7 @@
       </c>
       <c r="AA384" s="17"/>
     </row>
-    <row r="385" spans="1:27" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A385" s="17" t="s">
         <v>5</v>
       </c>
@@ -40000,7 +40009,7 @@
       </c>
       <c r="AA385" s="17"/>
     </row>
-    <row r="386" spans="1:27" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A386" s="17" t="s">
         <v>5</v>
       </c>
@@ -40075,7 +40084,7 @@
       </c>
       <c r="AA386" s="17"/>
     </row>
-    <row r="387" spans="1:27" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A387" s="17" t="s">
         <v>5</v>
       </c>
@@ -40152,7 +40161,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="388" spans="1:27" ht="304.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:27" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A388" s="17" t="s">
         <v>5</v>
       </c>
@@ -40227,7 +40236,7 @@
       </c>
       <c r="AA388" s="17"/>
     </row>
-    <row r="389" spans="1:27" ht="124" hidden="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:27" ht="124" x14ac:dyDescent="0.35">
       <c r="A389" s="17" t="s">
         <v>5</v>
       </c>
@@ -40300,7 +40309,7 @@
       </c>
       <c r="AA389" s="17"/>
     </row>
-    <row r="390" spans="1:27" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A390" s="17" t="s">
         <v>5</v>
       </c>
@@ -40375,7 +40384,7 @@
       </c>
       <c r="AA390" s="17"/>
     </row>
-    <row r="391" spans="1:27" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A391" s="17" t="s">
         <v>5</v>
       </c>
@@ -40450,7 +40459,7 @@
       </c>
       <c r="AA391" s="17"/>
     </row>
-    <row r="392" spans="1:27" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A392" s="17" t="s">
         <v>5</v>
       </c>
@@ -40525,7 +40534,7 @@
       </c>
       <c r="AA392" s="17"/>
     </row>
-    <row r="393" spans="1:27" ht="77.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:27" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A393" s="17" t="s">
         <v>5</v>
       </c>
@@ -40598,7 +40607,7 @@
       </c>
       <c r="AA393" s="17"/>
     </row>
-    <row r="394" spans="1:27" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A394" s="17" t="s">
         <v>5</v>
       </c>
@@ -40975,7 +40984,7 @@
         <v>2271</v>
       </c>
     </row>
-    <row r="399" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:27" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" s="17" t="s">
         <v>5</v>
       </c>
@@ -41046,7 +41055,7 @@
       <c r="Z399" s="18"/>
       <c r="AA399" s="17"/>
     </row>
-    <row r="400" spans="1:27" ht="304.5" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:27" ht="304.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" s="17" t="s">
         <v>5</v>
       </c>
@@ -41121,7 +41130,7 @@
       </c>
       <c r="AA400" s="17"/>
     </row>
-    <row r="401" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:27" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" s="17" t="s">
         <v>5</v>
       </c>
@@ -41190,7 +41199,7 @@
       </c>
       <c r="AA401" s="17"/>
     </row>
-    <row r="402" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:27" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" s="17" t="s">
         <v>5</v>
       </c>
@@ -42541,7 +42550,7 @@
       <c r="Z420" s="17"/>
       <c r="AA420" s="17"/>
     </row>
-    <row r="421" spans="1:27" ht="304.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:27" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A421" s="17" t="s">
         <v>5</v>
       </c>
@@ -43170,7 +43179,7 @@
       <c r="Z429" s="17"/>
       <c r="AA429" s="17"/>
     </row>
-    <row r="430" spans="1:27" ht="201.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:27" ht="217" hidden="1" x14ac:dyDescent="0.35">
       <c r="A430" s="17" t="s">
         <v>5</v>
       </c>
@@ -43383,7 +43392,7 @@
       <c r="Z432" s="17"/>
       <c r="AA432" s="17"/>
     </row>
-    <row r="433" spans="1:27" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A433" s="17" t="s">
         <v>5</v>
       </c>
@@ -43456,7 +43465,7 @@
       <c r="Z433" s="17"/>
       <c r="AA433" s="17"/>
     </row>
-    <row r="434" spans="1:27" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A434" s="17" t="s">
         <v>5</v>
       </c>
@@ -44306,7 +44315,7 @@
         <v>2385</v>
       </c>
     </row>
-    <row r="446" spans="1:27" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A446" s="17" t="s">
         <v>5</v>
       </c>
@@ -44383,7 +44392,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="447" spans="1:27" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A447" s="38" t="s">
         <v>5</v>
       </c>
@@ -44456,7 +44465,7 @@
       <c r="Z447" s="17"/>
       <c r="AA447" s="17"/>
     </row>
-    <row r="448" spans="1:27" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A448" s="38" t="s">
         <v>5</v>
       </c>
@@ -44523,7 +44532,7 @@
       <c r="Z448" s="17"/>
       <c r="AA448" s="17"/>
     </row>
-    <row r="449" spans="1:27" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A449" s="38" t="s">
         <v>5</v>
       </c>
@@ -44592,7 +44601,7 @@
       <c r="Z449" s="17"/>
       <c r="AA449" s="17"/>
     </row>
-    <row r="450" spans="1:27" ht="304.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:27" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A450" s="38" t="s">
         <v>5</v>
       </c>
@@ -44659,7 +44668,7 @@
       <c r="Z450" s="17"/>
       <c r="AA450" s="17"/>
     </row>
-    <row r="451" spans="1:27" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:27" ht="58" x14ac:dyDescent="0.35">
       <c r="A451" s="38" t="s">
         <v>5</v>
       </c>
@@ -44728,7 +44737,7 @@
       <c r="Z451" s="17"/>
       <c r="AA451" s="17"/>
     </row>
-    <row r="452" spans="1:27" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A452" s="38" t="s">
         <v>5</v>
       </c>
@@ -44801,7 +44810,7 @@
       <c r="Z452" s="17"/>
       <c r="AA452" s="17"/>
     </row>
-    <row r="453" spans="1:27" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A453" s="38" t="s">
         <v>5</v>
       </c>
@@ -44868,7 +44877,7 @@
       <c r="Z453" s="17"/>
       <c r="AA453" s="17"/>
     </row>
-    <row r="454" spans="1:27" ht="304.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:27" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A454" s="38" t="s">
         <v>5</v>
       </c>
@@ -44937,7 +44946,7 @@
       <c r="Z454" s="17"/>
       <c r="AA454" s="17"/>
     </row>
-    <row r="455" spans="1:27" ht="201.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:27" ht="201.5" x14ac:dyDescent="0.35">
       <c r="A455" s="38" t="s">
         <v>5</v>
       </c>
@@ -45006,7 +45015,7 @@
       <c r="Z455" s="17"/>
       <c r="AA455" s="17"/>
     </row>
-    <row r="456" spans="1:27" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A456" s="38" t="s">
         <v>5</v>
       </c>
@@ -45079,7 +45088,7 @@
       <c r="Z456" s="17"/>
       <c r="AA456" s="17"/>
     </row>
-    <row r="457" spans="1:27" ht="304.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:27" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A457" s="38" t="s">
         <v>5</v>
       </c>
@@ -45148,7 +45157,7 @@
       <c r="Z457" s="17"/>
       <c r="AA457" s="17"/>
     </row>
-    <row r="458" spans="1:27" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A458" s="38" t="s">
         <v>5</v>
       </c>
@@ -45215,7 +45224,7 @@
       <c r="Z458" s="17"/>
       <c r="AA458" s="17"/>
     </row>
-    <row r="459" spans="1:27" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A459" s="38" t="s">
         <v>5</v>
       </c>
@@ -45280,7 +45289,7 @@
       <c r="Z459" s="17"/>
       <c r="AA459" s="17"/>
     </row>
-    <row r="460" spans="1:27" ht="304.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:27" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A460" s="38" t="s">
         <v>5</v>
       </c>
@@ -45349,7 +45358,7 @@
       <c r="Z460" s="17"/>
       <c r="AA460" s="17"/>
     </row>
-    <row r="461" spans="1:27" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A461" s="38" t="s">
         <v>5</v>
       </c>
@@ -45416,7 +45425,7 @@
       <c r="Z461" s="17"/>
       <c r="AA461" s="17"/>
     </row>
-    <row r="462" spans="1:27" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:27" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A462" s="38" t="s">
         <v>5</v>
       </c>
@@ -45487,7 +45496,7 @@
       <c r="Z462" s="17"/>
       <c r="AA462" s="17"/>
     </row>
-    <row r="463" spans="1:27" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:27" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A463" s="38" t="s">
         <v>5</v>
       </c>
@@ -45558,7 +45567,7 @@
       <c r="Z463" s="17"/>
       <c r="AA463" s="17"/>
     </row>
-    <row r="464" spans="1:27" ht="304.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:27" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A464" s="38" t="s">
         <v>5</v>
       </c>
@@ -45625,7 +45634,7 @@
       <c r="Z464" s="17"/>
       <c r="AA464" s="17"/>
     </row>
-    <row r="465" spans="1:27" ht="124" hidden="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:27" ht="124" x14ac:dyDescent="0.35">
       <c r="A465" s="17" t="s">
         <v>5</v>
       </c>
@@ -45698,7 +45707,7 @@
       </c>
       <c r="AA465" s="17"/>
     </row>
-    <row r="466" spans="1:27" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A466" s="17" t="s">
         <v>5</v>
       </c>
@@ -45773,7 +45782,7 @@
       </c>
       <c r="AA466" s="17"/>
     </row>
-    <row r="467" spans="1:27" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A467" s="17" t="s">
         <v>5</v>
       </c>
@@ -45846,7 +45855,7 @@
       </c>
       <c r="AA467" s="17"/>
     </row>
-    <row r="468" spans="1:27" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:27" ht="116" x14ac:dyDescent="0.35">
       <c r="A468" s="17" t="s">
         <v>5</v>
       </c>
@@ -45921,7 +45930,7 @@
       </c>
       <c r="AA468" s="17"/>
     </row>
-    <row r="469" spans="1:27" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A469" s="17" t="s">
         <v>5</v>
       </c>
@@ -45996,7 +46005,7 @@
       </c>
       <c r="AA469" s="17"/>
     </row>
-    <row r="470" spans="1:27" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A470" s="17" t="s">
         <v>5</v>
       </c>
@@ -46071,7 +46080,7 @@
       </c>
       <c r="AA470" s="17"/>
     </row>
-    <row r="471" spans="1:27" ht="304.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:27" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A471" s="17" t="s">
         <v>5</v>
       </c>
@@ -46146,7 +46155,7 @@
       </c>
       <c r="AA471" s="17"/>
     </row>
-    <row r="472" spans="1:27" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:27" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A472" s="41" t="s">
         <v>5</v>
       </c>
@@ -46215,7 +46224,7 @@
       <c r="Z472" s="17"/>
       <c r="AA472" s="17"/>
     </row>
-    <row r="473" spans="1:27" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A473" s="17" t="s">
         <v>5</v>
       </c>
@@ -46290,7 +46299,7 @@
       </c>
       <c r="AA473" s="17"/>
     </row>
-    <row r="474" spans="1:27" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A474" s="17" t="s">
         <v>5</v>
       </c>
@@ -46363,7 +46372,7 @@
       </c>
       <c r="AA474" s="17"/>
     </row>
-    <row r="475" spans="1:27" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A475" s="17" t="s">
         <v>5</v>
       </c>
@@ -46438,7 +46447,7 @@
       </c>
       <c r="AA475" s="17"/>
     </row>
-    <row r="476" spans="1:27" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A476" s="17" t="s">
         <v>5</v>
       </c>
@@ -46511,7 +46520,7 @@
       </c>
       <c r="AA476" s="17"/>
     </row>
-    <row r="477" spans="1:27" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:27" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A477" s="38" t="s">
         <v>5</v>
       </c>
@@ -47140,7 +47149,7 @@
       <c r="Z485" s="17"/>
       <c r="AA485" s="17"/>
     </row>
-    <row r="486" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:27" hidden="1" x14ac:dyDescent="0.35">
       <c r="A486" s="46" t="s">
         <v>5</v>
       </c>
@@ -47201,7 +47210,7 @@
       <c r="Z486" s="17"/>
       <c r="AA486" s="17"/>
     </row>
-    <row r="487" spans="1:27" ht="87" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:27" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A487" s="17" t="s">
         <v>5</v>
       </c>
@@ -48995,7 +49004,7 @@
       <c r="Z514" s="17"/>
       <c r="AA514" s="17"/>
     </row>
-    <row r="515" spans="1:27" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:27" ht="87" x14ac:dyDescent="0.35">
       <c r="A515" s="17" t="s">
         <v>5</v>
       </c>
@@ -50481,11 +50490,78 @@
       <c r="Z536" s="17"/>
       <c r="AA536" s="17"/>
     </row>
+    <row r="537" spans="1:27" ht="159.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A537" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="B537" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C537" s="5" t="s">
+        <v>3272</v>
+      </c>
+      <c r="D537" s="17"/>
+      <c r="E537" s="5" t="s">
+        <v>3273</v>
+      </c>
+      <c r="F537" s="5" t="s">
+        <v>3274</v>
+      </c>
+      <c r="G537" s="14" t="s">
+        <v>885</v>
+      </c>
+      <c r="H537" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="I537" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J537" s="5" t="s">
+        <v>2672</v>
+      </c>
+      <c r="K537" s="5" t="s">
+        <v>2882</v>
+      </c>
+      <c r="L537" s="5" t="s">
+        <v>2673</v>
+      </c>
+      <c r="M537" s="43" t="s">
+        <v>3039</v>
+      </c>
+      <c r="N537" s="17" t="s">
+        <v>2594</v>
+      </c>
+      <c r="O537" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="P537" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q537" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="R537" s="17">
+        <v>0</v>
+      </c>
+      <c r="S537" s="21">
+        <v>0</v>
+      </c>
+      <c r="T537" s="17"/>
+      <c r="U537" s="17"/>
+      <c r="V537" s="17"/>
+      <c r="W537" s="17"/>
+      <c r="X537" s="17"/>
+      <c r="Y537" s="18"/>
+      <c r="Z537" s="18" t="s">
+        <v>1933</v>
+      </c>
+      <c r="AA537" s="17"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA536" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <autoFilter ref="A1:AA537" xr:uid="{00000000-0001-0000-0100-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="PEPR"/>
+        <filter val="CarboNium"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -50572,425 +50648,425 @@
     <hyperlink ref="D77" r:id="rId76" xr:uid="{81FEA6BC-9141-4E8E-A60B-B379ACC1F576}"/>
     <hyperlink ref="D78" r:id="rId77" xr:uid="{18924F5B-E6BC-4835-9DCB-474C3EB0F829}"/>
     <hyperlink ref="D79" r:id="rId78" xr:uid="{B0F61863-7B64-41C8-80BD-522F8088E39D}"/>
-    <hyperlink ref="D80" r:id="rId79" xr:uid="{FF4D3CF3-B972-4816-93B0-7450E1009BA9}"/>
-    <hyperlink ref="D81" r:id="rId80" xr:uid="{992A24CC-B9F6-4F6E-A318-5F8018D26303}"/>
-    <hyperlink ref="D82" r:id="rId81" xr:uid="{3308EEBF-3DF3-4730-8880-767B8E2E9EE1}"/>
-    <hyperlink ref="D83" r:id="rId82" xr:uid="{30A97CBD-52C7-418C-B432-13411A97C559}"/>
-    <hyperlink ref="D86" r:id="rId83" xr:uid="{FACFB6D7-D4BB-4B16-98C5-21813B38CD7E}"/>
-    <hyperlink ref="D87" r:id="rId84" xr:uid="{C1010E98-4D8C-4634-B04B-D8D905CD4ACC}"/>
-    <hyperlink ref="D88" r:id="rId85" xr:uid="{6ADC728F-9161-4C8D-84FD-0963CD3266A2}"/>
-    <hyperlink ref="D89" r:id="rId86" xr:uid="{E3EA6B00-463E-4BF8-A48E-4C8F944950B8}"/>
-    <hyperlink ref="D84" r:id="rId87" xr:uid="{FACCC2BC-8378-40D0-9765-1CCD499D7036}"/>
-    <hyperlink ref="D90" r:id="rId88" xr:uid="{341D07D4-F1F4-4067-8DE5-9C093FD0B5AF}"/>
-    <hyperlink ref="D91" r:id="rId89" xr:uid="{B55EFD6D-0920-4D7D-886E-5AF05ECD3BF4}"/>
-    <hyperlink ref="D92" r:id="rId90" xr:uid="{E6635313-99DD-4729-89A6-1248A3D4B669}"/>
-    <hyperlink ref="D95" r:id="rId91" xr:uid="{B3374B68-4D56-4626-8BC8-E705D61B342D}"/>
-    <hyperlink ref="D102" r:id="rId92" xr:uid="{9D681E77-DEDF-41B8-BC1B-D9BB7E0FEEBC}"/>
-    <hyperlink ref="D98" r:id="rId93" xr:uid="{E1BD69CC-AB2E-4F9F-8D30-671496982B5F}"/>
-    <hyperlink ref="D103" r:id="rId94" xr:uid="{91A83172-2BA4-41EB-8DBC-11720ECE2846}"/>
-    <hyperlink ref="D108" r:id="rId95" xr:uid="{8936664B-6231-4629-B487-647C6AF6AD16}"/>
-    <hyperlink ref="D109" r:id="rId96" xr:uid="{2009A43D-6FDD-4652-B575-0FE996527B5B}"/>
-    <hyperlink ref="D110" r:id="rId97" xr:uid="{5BF513EC-08D6-4D76-8E8A-4FA925B137DE}"/>
-    <hyperlink ref="D111" r:id="rId98" xr:uid="{CE03A04B-1DA5-400A-874A-44B88D96D71F}"/>
-    <hyperlink ref="D107" r:id="rId99" xr:uid="{41AC2FFF-26F7-47CE-9C78-B20FDFC986DE}"/>
-    <hyperlink ref="D106" r:id="rId100" xr:uid="{9BA9C628-D43E-4F5A-8545-724D3E41C1C0}"/>
-    <hyperlink ref="D112" r:id="rId101" xr:uid="{FF2D1477-2E14-4762-BE11-4C583FD8A039}"/>
-    <hyperlink ref="D113" r:id="rId102" xr:uid="{F66DC899-8564-4936-BD57-441547CE11A6}"/>
-    <hyperlink ref="D114" r:id="rId103" xr:uid="{DCC85F56-CC4F-44AE-85F8-2207E542E607}"/>
-    <hyperlink ref="D115" r:id="rId104" xr:uid="{C292924A-CF8C-4049-A122-0C4BC247D857}"/>
-    <hyperlink ref="D116" r:id="rId105" xr:uid="{6B44D329-A9E4-4703-8C0E-FA6431859A48}"/>
-    <hyperlink ref="D117" r:id="rId106" xr:uid="{DEACF395-6D5C-40DE-AF5D-059BC1F467F7}"/>
-    <hyperlink ref="D118" r:id="rId107" xr:uid="{45E81D35-884D-4280-8CFB-D8DEC5DE4D34}"/>
-    <hyperlink ref="D119" r:id="rId108" xr:uid="{953131FB-0411-4595-A022-A3D1025AE9B7}"/>
-    <hyperlink ref="D120" r:id="rId109" xr:uid="{4A96FA4B-1254-422D-B697-57CC6BA43402}"/>
-    <hyperlink ref="D121" r:id="rId110" xr:uid="{E6658E27-3F09-4E67-8ED9-0511B04FD557}"/>
-    <hyperlink ref="D122" r:id="rId111" xr:uid="{3830F548-4508-48A9-B871-3D85E397B0D9}"/>
-    <hyperlink ref="D123" r:id="rId112" xr:uid="{EAE04C90-51E8-4B2A-A8D4-6FE15517BEBF}"/>
-    <hyperlink ref="D124" r:id="rId113" xr:uid="{52965897-EDFA-4485-9283-52E8EEC02C82}"/>
-    <hyperlink ref="D125" r:id="rId114" xr:uid="{888C9C36-17CF-48BC-A5B3-F8A917850594}"/>
-    <hyperlink ref="D126" r:id="rId115" xr:uid="{DF7AFFAB-6C45-4807-9B3C-78B3DD012DB3}"/>
-    <hyperlink ref="D127" r:id="rId116" xr:uid="{73FD4728-C8CF-4BEF-8361-F553FA664E98}"/>
-    <hyperlink ref="D128" r:id="rId117" xr:uid="{87096162-8858-4541-826A-DD86B394C052}"/>
-    <hyperlink ref="D129" r:id="rId118" xr:uid="{0911B5E6-13DC-4022-8FAA-5E2541FFBE7E}"/>
-    <hyperlink ref="D130" r:id="rId119" xr:uid="{279020EB-C73D-43FE-9F08-07307C38B7AB}"/>
-    <hyperlink ref="D137" r:id="rId120" xr:uid="{F7C8D236-719F-4EF2-A3CD-C7E4D6E81148}"/>
-    <hyperlink ref="D139" r:id="rId121" xr:uid="{32387BDF-45EC-4E54-B5EB-01E44CE4B52C}"/>
-    <hyperlink ref="D131" r:id="rId122" xr:uid="{026B0701-309C-486A-8F45-8FF84000221B}"/>
-    <hyperlink ref="D132" r:id="rId123" xr:uid="{375AA471-169A-4F9B-8A5D-1341D42A358C}"/>
-    <hyperlink ref="D133" r:id="rId124" xr:uid="{EA34FD32-70E9-4E21-8314-A66726994DD3}"/>
-    <hyperlink ref="D134" r:id="rId125" xr:uid="{94AAF235-6394-4FAD-AB94-D91897A229CD}"/>
-    <hyperlink ref="D135" r:id="rId126" xr:uid="{1A5F3837-7E19-453E-875E-681330D50A52}"/>
-    <hyperlink ref="D136" r:id="rId127" xr:uid="{85E77E4C-84DF-431F-9B7C-37AA63225770}"/>
-    <hyperlink ref="D140" r:id="rId128" xr:uid="{992213FB-B611-4AB7-919C-A9D5033600C0}"/>
-    <hyperlink ref="D141" r:id="rId129" xr:uid="{90F44307-6DBE-4D55-B371-1ACAD08A7D93}"/>
-    <hyperlink ref="D142" r:id="rId130" xr:uid="{C7C5CD5A-8D91-45FD-8249-9D8E4FFA9E18}"/>
-    <hyperlink ref="D143" r:id="rId131" xr:uid="{113742BC-1672-48C9-B351-A71B39E3E2D3}"/>
-    <hyperlink ref="D144" r:id="rId132" xr:uid="{B0348005-72F9-47D8-99DC-5623308FB9B3}"/>
-    <hyperlink ref="D145" r:id="rId133" xr:uid="{3587728B-0FC6-4089-BA43-AAB1AA70C2C1}"/>
-    <hyperlink ref="D146" r:id="rId134" xr:uid="{A2084BEE-38F4-499F-8791-16F60BBAB6CB}"/>
-    <hyperlink ref="D147" r:id="rId135" xr:uid="{AFE3A00F-6634-4F27-8AAA-785588CB3CA9}"/>
-    <hyperlink ref="D148" r:id="rId136" xr:uid="{57822340-657A-407C-8C65-F2566903C26A}"/>
-    <hyperlink ref="D149" r:id="rId137" xr:uid="{D3D81206-3512-4259-95B8-A98FB6503A64}"/>
-    <hyperlink ref="D150" r:id="rId138" xr:uid="{2FD3C88E-397B-4A9C-A08D-BAC9F4752572}"/>
-    <hyperlink ref="D151" r:id="rId139" xr:uid="{B113BBFE-9A26-406F-9805-C86669C65D7D}"/>
-    <hyperlink ref="D138" r:id="rId140" xr:uid="{5FAD256B-CDEB-4828-97AF-67A54E3C8F12}"/>
-    <hyperlink ref="D152" r:id="rId141" xr:uid="{3EAD9A31-3BDF-4B4A-BDA2-D569B59E233B}"/>
-    <hyperlink ref="D153" r:id="rId142" xr:uid="{12C300E0-DCD6-4C5C-9B23-1CB886E317AA}"/>
-    <hyperlink ref="D154" r:id="rId143" xr:uid="{AC653FFA-E170-43DA-A402-DB5AE1B22392}"/>
-    <hyperlink ref="D155" r:id="rId144" xr:uid="{256CB68D-7211-4C8F-B5B6-F29E5D9A3B34}"/>
-    <hyperlink ref="D156" r:id="rId145" xr:uid="{81431275-2CC2-4355-AF6E-BD7C863810D4}"/>
-    <hyperlink ref="D157" r:id="rId146" xr:uid="{BE30EBE2-EF38-481B-B570-4C9AA5DE79CF}"/>
-    <hyperlink ref="D163" r:id="rId147" xr:uid="{74AD4D7A-A665-4D81-9EC1-91ED550AE18A}"/>
-    <hyperlink ref="D164" r:id="rId148" xr:uid="{348CC46B-FA3B-4C67-BA17-586D43B3550A}"/>
-    <hyperlink ref="D161" r:id="rId149" xr:uid="{786E59F5-84C9-49DC-B788-60C7755B4474}"/>
-    <hyperlink ref="D165" r:id="rId150" xr:uid="{840984F6-CBC9-4BC1-927E-978E91FF2872}"/>
-    <hyperlink ref="D162" r:id="rId151" xr:uid="{40895C0A-3A34-46DD-8597-605C620B3396}"/>
-    <hyperlink ref="D166" r:id="rId152" display="mailto:clara.gilloteau@inrae.fr" xr:uid="{D884AD4F-80FF-4AAC-92F1-377C884E887C}"/>
-    <hyperlink ref="D158" r:id="rId153" xr:uid="{BD960D86-DE69-41C7-88A8-3E0A0E4336DD}"/>
-    <hyperlink ref="D159" r:id="rId154" xr:uid="{07AA7898-51AF-4233-B0C8-C926CA5AC508}"/>
-    <hyperlink ref="D160" r:id="rId155" xr:uid="{D1A9CAEC-794E-49B5-919D-49B8F2EE1840}"/>
-    <hyperlink ref="D167" r:id="rId156" xr:uid="{742F2CBF-E925-4643-89B1-A3980A99A80F}"/>
-    <hyperlink ref="D168" r:id="rId157" display="https://listes.cerege.fr/wws/editsubscriber/rhizoseqc?email=adeline.armelin%40cea.fr&amp;previous_action=review" xr:uid="{E113C167-87CA-4D16-A22E-E66EF4A35322}"/>
-    <hyperlink ref="D169" r:id="rId158" xr:uid="{61BE3872-98EA-4558-9CA3-46084F90C3BA}"/>
-    <hyperlink ref="D170" r:id="rId159" xr:uid="{025E4DEF-01E7-4C60-9565-416E471169C6}"/>
-    <hyperlink ref="D171" r:id="rId160" xr:uid="{067B0C9B-6450-4B12-8618-69DC27A86938}"/>
-    <hyperlink ref="D172" r:id="rId161" xr:uid="{EDF1B310-06B3-45EB-80D5-BE2819B91CED}"/>
-    <hyperlink ref="D173" r:id="rId162" xr:uid="{A93B5510-5A64-494B-BD89-1A794306D437}"/>
-    <hyperlink ref="D174" r:id="rId163" xr:uid="{7C115875-394E-4852-961A-341E761221E3}"/>
-    <hyperlink ref="D175" r:id="rId164" xr:uid="{68E3C4CB-86E1-4713-BEF8-E5A1D4E1208D}"/>
-    <hyperlink ref="D176" r:id="rId165" xr:uid="{41FEFCE0-F531-453B-A219-E4E9207E4ABD}"/>
-    <hyperlink ref="D177" r:id="rId166" xr:uid="{C6DA40E3-5386-4F75-8DFD-3F8E4FACE9A3}"/>
-    <hyperlink ref="D178" r:id="rId167" xr:uid="{8DAC9949-C651-4441-9EDE-7C84E9D21D7D}"/>
-    <hyperlink ref="D179" r:id="rId168" xr:uid="{B366F38E-6B8B-4EE3-8198-347988E214E6}"/>
-    <hyperlink ref="D180" r:id="rId169" display="https://listes.cerege.fr/wws/editsubscriber/rhizoseqc?email=dominique.masse%40ird.fr&amp;previous_action=review" xr:uid="{F66AE854-B847-402D-A975-1F12925CB99E}"/>
-    <hyperlink ref="D181" r:id="rId170" xr:uid="{799CDCEA-30ED-49D6-A18A-D3AB1A78291B}"/>
-    <hyperlink ref="D182" r:id="rId171" xr:uid="{922EECB1-18FB-431F-A50D-35BB11B7CAE8}"/>
-    <hyperlink ref="D183" r:id="rId172" xr:uid="{E1891978-EC57-4125-8695-E65007780A6F}"/>
-    <hyperlink ref="D184" r:id="rId173" xr:uid="{5048DDFD-2DAD-4E71-A59C-D099591CAC2D}"/>
-    <hyperlink ref="D185" r:id="rId174" xr:uid="{100CC261-4E92-4071-8B77-AAA4730BE390}"/>
-    <hyperlink ref="D186" r:id="rId175" xr:uid="{E88B3550-2E2E-441D-AE2E-9C341A75B899}"/>
-    <hyperlink ref="D187" r:id="rId176" xr:uid="{A5831976-C50A-4327-871C-3230DB6B56A1}"/>
-    <hyperlink ref="D188" r:id="rId177" xr:uid="{CDF8E337-A608-44BA-A365-87674AD5A4AA}"/>
-    <hyperlink ref="D189" r:id="rId178" xr:uid="{77E15C07-14CF-46A2-A380-3165C7BF71E1}"/>
-    <hyperlink ref="D190" r:id="rId179" xr:uid="{5812CB20-02BB-4D26-A5B0-0882E37403E3}"/>
-    <hyperlink ref="D191" r:id="rId180" xr:uid="{208B13EA-96C7-4352-85BF-3F3953BEFB79}"/>
-    <hyperlink ref="D192" r:id="rId181" xr:uid="{60A3F982-A15F-46D3-A3B2-2A3D1998CD1E}"/>
-    <hyperlink ref="D193" r:id="rId182" xr:uid="{35450EC9-24E8-4AF2-9BC5-6401E69D86C9}"/>
-    <hyperlink ref="D194" r:id="rId183" xr:uid="{EFB1470A-C326-4477-9E36-FE7AD01DE15A}"/>
-    <hyperlink ref="D195" r:id="rId184" xr:uid="{5A92DC38-EE48-485E-9492-3099AA7108D7}"/>
-    <hyperlink ref="D196" r:id="rId185" xr:uid="{A6A30117-6FE9-4B29-B0CB-6985AE8B7D8B}"/>
-    <hyperlink ref="D199" r:id="rId186" xr:uid="{9F93CFD9-FD67-43EB-AAB7-4A13F0ACE8CA}"/>
-    <hyperlink ref="D198" r:id="rId187" xr:uid="{8836D2E1-A1E8-4829-B3A4-F68897928D65}"/>
-    <hyperlink ref="D197" r:id="rId188" xr:uid="{59922D8F-19C3-4792-9D4D-CF3B62CC2889}"/>
-    <hyperlink ref="D200" r:id="rId189" xr:uid="{0983DF29-6698-4EC3-9B26-DF38025F02D9}"/>
-    <hyperlink ref="D202" r:id="rId190" xr:uid="{CFAAA63C-2872-4514-B6BB-C7AB42B01963}"/>
-    <hyperlink ref="D203" r:id="rId191" xr:uid="{ED76EEDE-512A-4868-BF51-62121C15C6A7}"/>
-    <hyperlink ref="D201" r:id="rId192" xr:uid="{DB77F737-D8CB-4475-A20B-21EB1061CF6E}"/>
-    <hyperlink ref="D211" r:id="rId193" xr:uid="{E10E7743-4F8F-4102-B589-0558BB215585}"/>
-    <hyperlink ref="D214" r:id="rId194" xr:uid="{BD93C876-AD84-4057-85DE-C81F4CC6E3D3}"/>
-    <hyperlink ref="D216" r:id="rId195" xr:uid="{E4354BAF-8DD9-4567-9775-D68870CE51D8}"/>
-    <hyperlink ref="D213" r:id="rId196" xr:uid="{C4B20045-BCB6-4110-8A03-9EE1407BFEBD}"/>
-    <hyperlink ref="D217" r:id="rId197" xr:uid="{AA36CB38-3294-4990-A881-B4178B4094EC}"/>
-    <hyperlink ref="D222" r:id="rId198" xr:uid="{26519EBA-A3A9-4425-A2F2-F4A16023238F}"/>
-    <hyperlink ref="D246" r:id="rId199" xr:uid="{328A955D-8038-4C9E-89D0-3DBB7634E2AC}"/>
-    <hyperlink ref="D263" r:id="rId200" xr:uid="{5944CC2D-2912-486D-8B2D-B2F1B803EB4C}"/>
-    <hyperlink ref="D265" r:id="rId201" xr:uid="{FBB02D20-D46A-4265-A382-F42AE2487354}"/>
-    <hyperlink ref="D266" r:id="rId202" xr:uid="{153C9299-725E-4687-AB2F-6AF71AD6D4BA}"/>
-    <hyperlink ref="D273" r:id="rId203" xr:uid="{CF372B3D-95AB-4C0C-AE48-A443E44E2E12}"/>
-    <hyperlink ref="D101" r:id="rId204" xr:uid="{3FEDEAE7-0885-43A2-9EDE-12398C4B1072}"/>
-    <hyperlink ref="D100" r:id="rId205" xr:uid="{4532F07F-C601-4FB1-B580-91AFEED4AB47}"/>
-    <hyperlink ref="D264" r:id="rId206" xr:uid="{D71D8727-99E0-4400-BE64-77DA46FEE4F4}"/>
-    <hyperlink ref="D267" r:id="rId207" xr:uid="{BC0A9543-5B0C-4EC3-89C8-C636A09D30FD}"/>
-    <hyperlink ref="D268" r:id="rId208" xr:uid="{DCC1CA4E-3E71-40EA-95C6-7490C364D8F2}"/>
-    <hyperlink ref="D269" r:id="rId209" xr:uid="{CA5C82F9-AAF5-47CE-BCC2-0DFE57955224}"/>
-    <hyperlink ref="D270" r:id="rId210" xr:uid="{0832F85F-D22A-43B6-875F-7E5CA33EBDBC}"/>
-    <hyperlink ref="D271" r:id="rId211" xr:uid="{330B5F6F-DC3D-46EA-B980-59CC1974BFA2}"/>
-    <hyperlink ref="D272" r:id="rId212" xr:uid="{D6849A02-2B82-43A0-92B0-FDAD2FA552F5}"/>
-    <hyperlink ref="D274" r:id="rId213" xr:uid="{E4477073-177E-4760-AA4F-5B46DFDA14F7}"/>
-    <hyperlink ref="D93" r:id="rId214" xr:uid="{ADE323D7-489E-414A-A0E0-162B849F80A7}"/>
-    <hyperlink ref="D94" r:id="rId215" xr:uid="{2EC6D3CD-FD36-4CAF-AEE2-07761FCB7CCA}"/>
-    <hyperlink ref="D97" r:id="rId216" xr:uid="{F555CB71-12F9-4040-91DB-3FD6F31EF36D}"/>
-    <hyperlink ref="D105" r:id="rId217" xr:uid="{F9AC4976-C48E-4978-A58E-57FBD9B49ECA}"/>
-    <hyperlink ref="D293" r:id="rId218" xr:uid="{86FFA566-E624-4AF7-8514-6C27F4C161C4}"/>
-    <hyperlink ref="D360" r:id="rId219" xr:uid="{FB37F046-3E8C-44B1-965B-C97F9EA82CED}"/>
-    <hyperlink ref="D361" r:id="rId220" xr:uid="{02000C05-C2C4-4CA5-932D-0F19E3E8ADC3}"/>
-    <hyperlink ref="D362" r:id="rId221" xr:uid="{EF7B83E6-8263-4F4A-8990-A4FF219972C0}"/>
-    <hyperlink ref="D363" r:id="rId222" xr:uid="{CF0D0627-8DC9-421B-8AB0-E2AA3037676C}"/>
-    <hyperlink ref="D364" r:id="rId223" display="mailto:eliot.chatton@univ-rennes.fr" xr:uid="{AB33B82F-4B5B-4C6B-B2F7-2848C85803C3}"/>
-    <hyperlink ref="D365" r:id="rId224" xr:uid="{85C470E8-693B-4CDB-AC26-2B2F2605F62E}"/>
-    <hyperlink ref="D366" r:id="rId225" xr:uid="{840BC485-374C-4D60-9D91-51253302802B}"/>
-    <hyperlink ref="D367" r:id="rId226" xr:uid="{FA8CBCD0-461C-4B2C-94D5-B26E9BA1ECBE}"/>
-    <hyperlink ref="D368" r:id="rId227" xr:uid="{85F8A557-4F75-4AFF-BD8D-4A369FD13105}"/>
-    <hyperlink ref="D369" r:id="rId228" xr:uid="{66889B16-56CB-402E-A46A-00F6D0BEFB8C}"/>
-    <hyperlink ref="D370" r:id="rId229" xr:uid="{F92D0E57-FA3B-4E3F-9DBA-B1A418EF828A}"/>
-    <hyperlink ref="D371" r:id="rId230" xr:uid="{E8DBB520-B069-457D-A431-3F3CB6A08252}"/>
-    <hyperlink ref="D372" r:id="rId231" xr:uid="{4CE3FB06-FE62-45E8-B523-42BBD4D801FB}"/>
-    <hyperlink ref="D373" r:id="rId232" xr:uid="{A11B4D69-CB33-4549-961B-444440EB4A47}"/>
-    <hyperlink ref="D374" r:id="rId233" display="mailto:didier.jezequel@inrae.fr" xr:uid="{711EC7D6-6F53-4BB8-B6E7-23095EBC9005}"/>
-    <hyperlink ref="D375" r:id="rId234" xr:uid="{7570B12B-7024-4FCF-AA22-E36AF8C1D4CC}"/>
-    <hyperlink ref="D376" r:id="rId235" xr:uid="{61DB90E9-BD67-48D9-B657-89416D2EED69}"/>
-    <hyperlink ref="D377" r:id="rId236" display="mailto:wolfgang.ludwig@univ-perp.fr" xr:uid="{F9C9D1F4-1991-4389-BFE4-9BE7CB7ECED8}"/>
-    <hyperlink ref="D378" r:id="rId237" xr:uid="{5E2B52C1-08B0-43A5-95B4-848A459DB315}"/>
-    <hyperlink ref="D379" r:id="rId238" display="mailto:edouard.metzger@univ-angers.fr" xr:uid="{59E61568-78B5-41C8-85D1-CC43DBA55D0D}"/>
-    <hyperlink ref="D380" r:id="rId239" xr:uid="{0517E78E-5BA6-4C99-95AF-C7D28D0EC215}"/>
-    <hyperlink ref="D381" r:id="rId240" display="mailto:Julien.Nemery@grenoble-inp.fr" xr:uid="{6FDF451D-F42A-43B7-8022-12E0F273F4D3}"/>
-    <hyperlink ref="D382" r:id="rId241" xr:uid="{4178A1DF-1C5B-4C5A-B6DD-D1A40885B42D}"/>
-    <hyperlink ref="D383" r:id="rId242" xr:uid="{E0F33667-16B4-4954-A6A2-B927FEFD3616}"/>
-    <hyperlink ref="D384" r:id="rId243" xr:uid="{399C084D-0179-479B-97B1-866B4936755B}"/>
-    <hyperlink ref="D385" r:id="rId244" xr:uid="{9B1C3AF1-9F70-472A-9B83-1576E6459B24}"/>
-    <hyperlink ref="D386" r:id="rId245" xr:uid="{C2815038-D142-45FB-A194-E2F0C361D416}"/>
-    <hyperlink ref="D387" r:id="rId246" xr:uid="{D7356312-9493-4442-90FB-FFFD508D3B30}"/>
-    <hyperlink ref="D388" r:id="rId247" display="mailto:claire.verin.cv@gmail.com" xr:uid="{4625BDEE-0E44-4607-80E5-6444424D79C9}"/>
-    <hyperlink ref="D389" r:id="rId248" xr:uid="{426011F8-761F-4289-B7E6-842D49598CB2}"/>
-    <hyperlink ref="D390" r:id="rId249" xr:uid="{4B29D626-F502-4D69-B86B-11B91566F18F}"/>
-    <hyperlink ref="D391" r:id="rId250" xr:uid="{54AD00BA-5EA2-4AC8-A903-58568469F719}"/>
-    <hyperlink ref="D392" r:id="rId251" xr:uid="{6E362010-D98B-4E53-9444-2551BC3384F2}"/>
-    <hyperlink ref="D393" r:id="rId252" xr:uid="{CD9F6046-D49C-46C0-B909-143D6A54F0B0}"/>
-    <hyperlink ref="D394" r:id="rId253" xr:uid="{8494696D-F2F6-449A-B6CC-5995FB929EF5}"/>
-    <hyperlink ref="D218" r:id="rId254" xr:uid="{876E6A5F-D6D4-45FF-8233-E0577B77396F}"/>
-    <hyperlink ref="D244" r:id="rId255" xr:uid="{DA3A1AE2-F4FD-41A9-97F8-0072003EA92E}"/>
-    <hyperlink ref="D212" r:id="rId256" xr:uid="{20C18E58-ED58-41E9-945A-471B9F09477D}"/>
-    <hyperlink ref="D304" r:id="rId257" xr:uid="{88B14105-E72E-49AA-B14C-B5EE9252467B}"/>
-    <hyperlink ref="D400" r:id="rId258" xr:uid="{EA39C09B-4B20-4316-8DF4-675B77129A46}"/>
-    <hyperlink ref="D401" r:id="rId259" xr:uid="{1D6715C0-F782-4275-B1A5-935F69FE9808}"/>
-    <hyperlink ref="D402" r:id="rId260" xr:uid="{9310D1D4-AE37-4F8D-B778-E14D476B480F}"/>
-    <hyperlink ref="D355" r:id="rId261" xr:uid="{CA021DE7-E699-4761-B185-897040AD9433}"/>
-    <hyperlink ref="D215" r:id="rId262" xr:uid="{B9A6B7DC-5DF9-4A99-B145-5A3F0D2B7333}"/>
-    <hyperlink ref="D350" r:id="rId263" xr:uid="{B64D5E0B-23AE-4FDD-AA57-B0FBC122B4F1}"/>
-    <hyperlink ref="D99" r:id="rId264" xr:uid="{7089C2BE-4027-4FC6-A1F9-6A1AE4B8725E}"/>
-    <hyperlink ref="D96" r:id="rId265" xr:uid="{71155148-E90E-47B9-8E3F-E19F3F36A0ED}"/>
-    <hyperlink ref="D336" r:id="rId266" xr:uid="{81D62058-B298-48D5-BEA8-2A123AB178FF}"/>
-    <hyperlink ref="D208" r:id="rId267" xr:uid="{78DE2F58-987A-484A-AF89-217D5EAE23C0}"/>
-    <hyperlink ref="D352" r:id="rId268" xr:uid="{4F33A286-1F0E-47CA-9ABD-7D8466C63771}"/>
-    <hyperlink ref="D260" r:id="rId269" xr:uid="{14E47318-C4D0-4AA4-98F9-0DCED3D68A79}"/>
-    <hyperlink ref="D245" r:id="rId270" xr:uid="{D3FF3E83-AA68-4EF8-9F7B-0E2057D0E740}"/>
-    <hyperlink ref="D242" r:id="rId271" xr:uid="{35DDB8DC-C0DF-47BC-9494-B0AFFE3D9CCC}"/>
-    <hyperlink ref="D312" r:id="rId272" xr:uid="{1C3E9AEE-E546-434D-AB91-1B2D579937C2}"/>
-    <hyperlink ref="D308" r:id="rId273" xr:uid="{09E32029-305F-4D3B-9C04-A812A87D30A9}"/>
-    <hyperlink ref="D311" r:id="rId274" xr:uid="{AA668327-E1EC-4D00-B044-D230A1469E10}"/>
-    <hyperlink ref="D204" r:id="rId275" xr:uid="{3425F408-7E94-4C6F-B4CF-B77F836CC73A}"/>
-    <hyperlink ref="D224" r:id="rId276" xr:uid="{BD740CB7-A0EB-4835-AE9A-8EBFB32F0B4D}"/>
-    <hyperlink ref="D397" r:id="rId277" xr:uid="{C2E09F23-E0BB-4D45-AEBC-0EB5BB6A32DF}"/>
-    <hyperlink ref="D398" r:id="rId278" xr:uid="{30E18D0A-4798-4269-87A1-EEC8F7C12AF8}"/>
-    <hyperlink ref="D209" r:id="rId279" xr:uid="{F659B331-2514-4125-B5B6-2746A6C9D815}"/>
-    <hyperlink ref="D252" r:id="rId280" xr:uid="{4B9AA62E-C2E2-43A5-AC7D-A8CB5A45A2E3}"/>
-    <hyperlink ref="D357" r:id="rId281" xr:uid="{3242E85F-FD44-4F58-A8FA-24B267452378}"/>
-    <hyperlink ref="D233" r:id="rId282" xr:uid="{6144C4F1-5BDC-41BC-99EE-CAC11F92DDDB}"/>
-    <hyperlink ref="D281" r:id="rId283" xr:uid="{55ABA163-8EAD-45DA-9926-77A8664D9FF3}"/>
-    <hyperlink ref="D205" r:id="rId284" xr:uid="{2C7377DB-8247-4708-9F7D-137BEB47E5C6}"/>
-    <hyperlink ref="D328" r:id="rId285" xr:uid="{D499EC6E-8184-4657-A8E1-51B90F4674E9}"/>
-    <hyperlink ref="D228" r:id="rId286" xr:uid="{82C4F817-40AF-4213-B681-25FF13B8A33F}"/>
-    <hyperlink ref="D340" r:id="rId287" xr:uid="{FB1612DE-24F1-4A29-A7D3-13B32DC1DFAC}"/>
-    <hyperlink ref="D324" r:id="rId288" xr:uid="{04B99F5E-5F9D-42F5-B7E3-D29F92BA6647}"/>
-    <hyperlink ref="D319" r:id="rId289" xr:uid="{04287E26-EE17-4FE4-BBFB-37390A2DCA8F}"/>
-    <hyperlink ref="D318" r:id="rId290" xr:uid="{B12D5B79-3F7A-41CB-BF81-D8DB501DF44C}"/>
-    <hyperlink ref="D348" r:id="rId291" xr:uid="{81B6701E-8AFC-4836-88E9-9EB0EE7A130C}"/>
-    <hyperlink ref="D248" r:id="rId292" xr:uid="{ACCB4D9F-619A-48F0-B558-838BA15C0088}"/>
-    <hyperlink ref="D210" r:id="rId293" xr:uid="{40664F2A-B511-4392-9307-8DE3EC5EF831}"/>
-    <hyperlink ref="D316" r:id="rId294" xr:uid="{FC88A6A4-3A82-4ACC-A314-4F3E8A70AD04}"/>
-    <hyperlink ref="D240" r:id="rId295" xr:uid="{3C8A276A-0565-4EA6-A659-E4086BBA33EE}"/>
-    <hyperlink ref="D237" r:id="rId296" xr:uid="{C296B55C-EC9A-494D-B196-FE5E88D91A94}"/>
-    <hyperlink ref="D320" r:id="rId297" xr:uid="{BB20E1A2-B3E2-4DCA-A837-D038045B2E0E}"/>
-    <hyperlink ref="D284" r:id="rId298" xr:uid="{C2FB647A-2BEC-4EE7-BE54-858B09F7E66B}"/>
-    <hyperlink ref="D226" r:id="rId299" xr:uid="{15C6E732-4AD7-4051-91CD-2CCA14610CF4}"/>
-    <hyperlink ref="D256" r:id="rId300" xr:uid="{8E1B11C0-AD4C-4C1C-80A0-ECA09FF4ACC4}"/>
-    <hyperlink ref="D280" r:id="rId301" xr:uid="{5BB60BC6-9999-4583-9F90-FFDB1D0368BC}"/>
-    <hyperlink ref="D326" r:id="rId302" xr:uid="{465EB82D-B8E0-48A6-87A3-5A0D60FAFE2D}"/>
-    <hyperlink ref="D335" r:id="rId303" xr:uid="{5B911E15-C04B-4E04-BCB0-DB2CE6977BEB}"/>
-    <hyperlink ref="D207" r:id="rId304" xr:uid="{0E373A37-F42A-47A7-87A0-42C3F6AFFED3}"/>
-    <hyperlink ref="D325" r:id="rId305" xr:uid="{E9E94CEE-1D05-447E-9700-167637BFEFAC}"/>
-    <hyperlink ref="D310" r:id="rId306" xr:uid="{21AFC143-E743-405F-8AA2-F48A8473046A}"/>
-    <hyperlink ref="D358" r:id="rId307" xr:uid="{19542A46-C5EE-4063-A0CD-D52C784EE30A}"/>
-    <hyperlink ref="D235" r:id="rId308" xr:uid="{75038B0D-54FC-46B0-88D5-A63098531A21}"/>
-    <hyperlink ref="D258" r:id="rId309" xr:uid="{0E6C7499-6DFA-4411-A6D4-6FAF0D3B2C66}"/>
-    <hyperlink ref="D291" r:id="rId310" xr:uid="{F3563381-FE64-484C-B8B9-CFC50F829993}"/>
-    <hyperlink ref="D321" r:id="rId311" xr:uid="{F4C44CA3-E7E0-4B31-83CD-B3424FB31911}"/>
-    <hyperlink ref="D342" r:id="rId312" xr:uid="{18A66060-C09C-488E-82E5-812383F3C00B}"/>
-    <hyperlink ref="D341" r:id="rId313" xr:uid="{FE6575E2-21CF-432D-9A1C-C43E51BCAD76}"/>
-    <hyperlink ref="D282" r:id="rId314" xr:uid="{3A3B4A90-9207-4AC0-B366-2757B8D43527}"/>
-    <hyperlink ref="D289" r:id="rId315" xr:uid="{8FC10517-577B-4A05-A510-B89AAE48147D}"/>
-    <hyperlink ref="D221" r:id="rId316" xr:uid="{67248038-E3BC-433A-8EE7-466E967B5D80}"/>
-    <hyperlink ref="D277" r:id="rId317" xr:uid="{DABA2BBA-5AAD-48BB-B895-D3A650C42FAB}"/>
-    <hyperlink ref="D338" r:id="rId318" xr:uid="{D312A4FE-B309-4DDA-8749-BBE8CC5C6609}"/>
-    <hyperlink ref="D344" r:id="rId319" xr:uid="{F0885177-08D1-405C-988F-0C06044636AE}"/>
-    <hyperlink ref="D247" r:id="rId320" xr:uid="{79461B07-5AF4-4FFA-8548-3D897A346C3B}"/>
-    <hyperlink ref="D337" r:id="rId321" xr:uid="{146C6A30-71A1-495D-ABAB-EB888DD5532E}"/>
-    <hyperlink ref="D343" r:id="rId322" xr:uid="{2D3007EC-30F9-4CD4-8C1E-85F9389DEF6F}"/>
-    <hyperlink ref="D353" r:id="rId323" xr:uid="{3A31C012-F064-4452-82BF-698418E19064}"/>
-    <hyperlink ref="D261" r:id="rId324" xr:uid="{87A7465B-A17F-4598-8CD6-572C9F4A5420}"/>
-    <hyperlink ref="D306" r:id="rId325" xr:uid="{3619F9BA-DCC8-41E4-9EF2-0E069F782C57}"/>
-    <hyperlink ref="D262" r:id="rId326" xr:uid="{583DC961-8FCE-44E6-8075-53799FE7F163}"/>
-    <hyperlink ref="D351" r:id="rId327" xr:uid="{D58394C4-67B4-4018-A824-910DA4B3C8B3}"/>
-    <hyperlink ref="D255" r:id="rId328" display="mailto:eric.chaumillon@univ-lr.fr" xr:uid="{5C9A51DC-1566-4EF1-B76D-B827A254060F}"/>
-    <hyperlink ref="D227" r:id="rId329" xr:uid="{D9CF8962-242F-4633-82B0-04CEF8E67E05}"/>
-    <hyperlink ref="D329" r:id="rId330" xr:uid="{0AE47B5B-2112-48D1-9BBF-FE9449A309BE}"/>
-    <hyperlink ref="D257" r:id="rId331" xr:uid="{C5ECA57C-E62C-4DEE-B870-13E194296C2F}"/>
-    <hyperlink ref="D296" r:id="rId332" xr:uid="{DBD8264D-EF4C-4EFB-8E9D-FFB67970E766}"/>
-    <hyperlink ref="D231" r:id="rId333" xr:uid="{8E8CDDB6-984D-4D10-BCDB-8715AD38BC5E}"/>
-    <hyperlink ref="D220" r:id="rId334" xr:uid="{D87D4DC7-A858-464C-A9FC-4CBD519FDF1C}"/>
-    <hyperlink ref="D356" r:id="rId335" xr:uid="{CD2898C2-01BF-4DD7-87A3-2DF871335FC5}"/>
-    <hyperlink ref="D330" r:id="rId336" xr:uid="{DE4A2B41-E351-4FFB-9916-9B5A12D9F826}"/>
-    <hyperlink ref="D278" r:id="rId337" xr:uid="{8ED70CE7-39BA-42D2-8773-FC573EFBF4C3}"/>
-    <hyperlink ref="D331" r:id="rId338" xr:uid="{F9AF74BC-C5BD-4C4C-80E9-B7676EA47DD4}"/>
-    <hyperlink ref="D349" r:id="rId339" xr:uid="{A24A0A03-18C8-4164-9C9C-C6D7E8079A60}"/>
-    <hyperlink ref="D241" r:id="rId340" xr:uid="{3E7272D2-FD11-4455-A18D-8F4152E7C571}"/>
-    <hyperlink ref="D225" r:id="rId341" xr:uid="{8CF31450-9FF6-41B8-B89D-83C1B91BBFED}"/>
-    <hyperlink ref="D290" r:id="rId342" xr:uid="{837E84CE-D2C6-454F-9ABE-6CE8B0C7790A}"/>
-    <hyperlink ref="D230" r:id="rId343" xr:uid="{A18AEC85-42EF-4E96-A88E-939CACB7E8DA}"/>
-    <hyperlink ref="D250" r:id="rId344" xr:uid="{377173B7-75BB-49B3-A644-5B35AE733908}"/>
-    <hyperlink ref="D359" r:id="rId345" xr:uid="{9534021C-50FE-4BB1-98C0-CE7464EBBFF7}"/>
-    <hyperlink ref="D323" r:id="rId346" xr:uid="{0AEACC9D-3DC9-4CD0-83F3-F2B033112830}"/>
-    <hyperlink ref="D276" r:id="rId347" xr:uid="{1671216E-95F7-4F08-8608-2BB33F39DCB9}"/>
-    <hyperlink ref="D206" r:id="rId348" xr:uid="{0B59AB2B-33AB-46D1-AA6F-B867860AE59F}"/>
-    <hyperlink ref="D334" r:id="rId349" xr:uid="{88DB392B-DCA9-416E-A674-4C43805B557D}"/>
-    <hyperlink ref="D249" r:id="rId350" xr:uid="{B4F90C89-EFCB-4817-97BC-06E995AFA609}"/>
-    <hyperlink ref="D254" r:id="rId351" xr:uid="{CC11044E-9CD7-43A8-8FC7-8F4033363256}"/>
-    <hyperlink ref="D279" r:id="rId352" xr:uid="{F084A607-2D86-44C0-9307-F7DBD00E5910}"/>
-    <hyperlink ref="D236" r:id="rId353" display="mailto:Julien.Nemery@grenoble-inp.fr" xr:uid="{0340649A-91E8-4CD6-A93C-F02A3516FBD4}"/>
-    <hyperlink ref="D299" r:id="rId354" xr:uid="{DD5B37F5-6526-40C8-8AF5-F9F118085BD4}"/>
-    <hyperlink ref="D327" r:id="rId355" xr:uid="{1D348DB7-61C1-4B44-B14B-8F272C0AB9C8}"/>
-    <hyperlink ref="D303" r:id="rId356" xr:uid="{092BCB24-DF23-4521-9366-47796D7A1189}"/>
-    <hyperlink ref="D283" r:id="rId357" xr:uid="{D2C18461-0626-41D1-A186-6B586C54C498}"/>
-    <hyperlink ref="D307" r:id="rId358" xr:uid="{6A8E7C01-635E-43A6-8684-5DD44770CE71}"/>
-    <hyperlink ref="D346" r:id="rId359" xr:uid="{0B48683A-8190-49F2-B408-691429B5C75D}"/>
-    <hyperlink ref="D298" r:id="rId360" xr:uid="{E917A3BE-1E99-4042-938B-501DB1125A7F}"/>
-    <hyperlink ref="D300" r:id="rId361" xr:uid="{6DC7C87F-6A4F-4F9D-8B5E-DD7C19AE2C8C}"/>
-    <hyperlink ref="D314" r:id="rId362" xr:uid="{D2E4342A-998D-4C92-817A-1854849A4F5A}"/>
-    <hyperlink ref="D239" r:id="rId363" display="mailto:edouard.metzger@univ-angers.fr" xr:uid="{68A70078-17A2-413F-955D-958F454E2BDD}"/>
-    <hyperlink ref="D253" r:id="rId364" xr:uid="{577CD300-9D35-404A-9BCF-12DEDAFEBE5A}"/>
-    <hyperlink ref="D396" r:id="rId365" xr:uid="{9D25B918-898A-4E55-BA20-F5CF4EB5EF43}"/>
-    <hyperlink ref="D347" r:id="rId366" xr:uid="{D43185F7-C1B9-4DA9-9F31-06BCFB2070BB}"/>
-    <hyperlink ref="D395" r:id="rId367" xr:uid="{6925CD77-67D4-4AA9-8DC4-90DC7FE42CCC}"/>
-    <hyperlink ref="D309" r:id="rId368" xr:uid="{FBF9589E-A068-4C59-B7D3-6DD5F904DCDF}"/>
-    <hyperlink ref="D354" r:id="rId369" xr:uid="{345A319F-E9C5-4319-8CCA-184E77AEE990}"/>
-    <hyperlink ref="D288" r:id="rId370" xr:uid="{95217B08-0875-4396-81C5-BD15C2082B12}"/>
-    <hyperlink ref="D399" r:id="rId371" xr:uid="{7FBE7C64-34EB-486B-BD55-A404857C69F3}"/>
-    <hyperlink ref="D85" r:id="rId372" xr:uid="{8BB6528A-7A82-4EA6-B4E3-59BB570A7940}"/>
-    <hyperlink ref="D104" r:id="rId373" xr:uid="{2FEA2974-9EDC-4C94-B2DF-B67ED2C4DCBB}"/>
-    <hyperlink ref="D219" r:id="rId374" xr:uid="{DA01D55F-3B9A-4FAE-9DD9-321C7F72D7E2}"/>
-    <hyperlink ref="D223" r:id="rId375" xr:uid="{9DA746D1-9366-49F7-BDDE-9D15C844BEE2}"/>
-    <hyperlink ref="D229" r:id="rId376" xr:uid="{CB30AC5E-5A87-41AF-8EF9-B26F875FD98B}"/>
-    <hyperlink ref="D232" r:id="rId377" xr:uid="{A850826F-14DC-4E67-9125-5DE3F036D6C0}"/>
-    <hyperlink ref="D234" r:id="rId378" xr:uid="{442608F8-7C23-4462-B0E5-3525EDD2ED27}"/>
-    <hyperlink ref="D238" r:id="rId379" xr:uid="{E617A275-FA10-4135-84AA-B2C7C8A58606}"/>
-    <hyperlink ref="D259" r:id="rId380" xr:uid="{A66F923C-D0DA-4E05-AD10-8E65B001868D}"/>
-    <hyperlink ref="D287" r:id="rId381" xr:uid="{98CB6401-7831-451C-9BA0-8E0C7FB494BD}"/>
-    <hyperlink ref="D275" r:id="rId382" xr:uid="{0C5F7513-341A-41A8-B847-782409F4099C}"/>
-    <hyperlink ref="D305" r:id="rId383" xr:uid="{25687851-9455-4418-B194-F10132D3FF9A}"/>
-    <hyperlink ref="D313" r:id="rId384" xr:uid="{103A6CE1-24A1-4129-9871-81911FF2A37E}"/>
-    <hyperlink ref="D315" r:id="rId385" xr:uid="{52D97BED-52C9-4312-8FC2-C91EFC6F31BC}"/>
-    <hyperlink ref="D322" r:id="rId386" xr:uid="{99009347-3884-4446-A8B6-CC7D3961074F}"/>
-    <hyperlink ref="D317" r:id="rId387" xr:uid="{B26FBE01-0A47-4D97-9E7E-95A6766AE01F}"/>
-    <hyperlink ref="D332" r:id="rId388" xr:uid="{EB97E93C-00C0-4AD5-A355-1B170395CCAB}"/>
-    <hyperlink ref="D333" r:id="rId389" xr:uid="{CEB884E1-2965-42F8-B096-BE1B6B1A7D2E}"/>
-    <hyperlink ref="D339" r:id="rId390" xr:uid="{346552CA-3DB0-464D-B1EB-BB6924835319}"/>
-    <hyperlink ref="D345" r:id="rId391" xr:uid="{83754732-A552-4928-82C9-6C3DEE7BDBDB}"/>
-    <hyperlink ref="D403" r:id="rId392" xr:uid="{4D5F8E6D-0878-497D-B0B9-B1DDC24BFA44}"/>
-    <hyperlink ref="D404" r:id="rId393" xr:uid="{221312BB-E30C-489C-B404-96A153BA2EF6}"/>
-    <hyperlink ref="D405" r:id="rId394" xr:uid="{36F3B07A-D7AF-4EC0-A1FB-995D18DBF2B3}"/>
-    <hyperlink ref="D406" r:id="rId395" xr:uid="{E3A248A1-605A-473D-AA97-5EF424538A01}"/>
-    <hyperlink ref="D285" r:id="rId396" xr:uid="{5C444050-0B17-4A00-87FB-C84FBD758629}"/>
-    <hyperlink ref="D407" r:id="rId397" xr:uid="{8B165C96-1F8F-4A67-8FC4-65A34E28CDD1}"/>
-    <hyperlink ref="D408" r:id="rId398" xr:uid="{305F290A-787F-428B-8FBC-3BF01E78F765}"/>
-    <hyperlink ref="D409" r:id="rId399" xr:uid="{491E24B7-56D7-48F3-94A5-8D6F75BA65E0}"/>
-    <hyperlink ref="D243" r:id="rId400" xr:uid="{2FC17624-9C68-459D-B98C-AFB693EED57D}"/>
-    <hyperlink ref="D251" r:id="rId401" xr:uid="{BE47F20D-E592-484C-9AFC-2968894359CC}"/>
-    <hyperlink ref="D286" r:id="rId402" xr:uid="{9EC30679-083A-4669-95D1-2BA126C26547}"/>
-    <hyperlink ref="D292" r:id="rId403" xr:uid="{830F9ED0-47CC-4A6C-AB9F-C7489C09FD87}"/>
-    <hyperlink ref="D294" r:id="rId404" xr:uid="{FF924A04-F87C-49BB-9912-00780382B722}"/>
-    <hyperlink ref="D295" r:id="rId405" xr:uid="{0AF25B3D-9D7C-456C-835F-4EFEFC314BEF}"/>
-    <hyperlink ref="D297" r:id="rId406" xr:uid="{08923573-FE1F-4D3A-85FF-C5E20DB195D5}"/>
-    <hyperlink ref="D301" r:id="rId407" xr:uid="{24E77A36-7AEA-434F-9781-11D6712883FD}"/>
-    <hyperlink ref="D302" r:id="rId408" xr:uid="{D46D7396-7329-41E4-8E90-E1CDE1AEF42C}"/>
-    <hyperlink ref="D410" r:id="rId409" xr:uid="{A7416774-29F7-4F4F-924B-792A9D712553}"/>
-    <hyperlink ref="D411" r:id="rId410" xr:uid="{4DE261F8-386C-4ED6-AF66-4AAF82F79CE5}"/>
-    <hyperlink ref="D413" r:id="rId411" xr:uid="{0C18FDD3-2B24-4205-81BA-3995121C96F6}"/>
-    <hyperlink ref="D414" r:id="rId412" xr:uid="{6C4998D7-E946-46E3-8189-6F0802D264CC}"/>
-    <hyperlink ref="D415" r:id="rId413" xr:uid="{529D853F-03FB-4599-A59D-EF805075D34C}"/>
-    <hyperlink ref="D417" r:id="rId414" xr:uid="{F676206E-337D-401B-B572-8209F6FC7689}"/>
-    <hyperlink ref="D418" r:id="rId415" xr:uid="{ED1C34DD-60C6-4B5E-BA8A-27EAA50F2247}"/>
-    <hyperlink ref="D419" r:id="rId416" xr:uid="{F8062A78-E827-4416-9A54-158C783B3932}"/>
-    <hyperlink ref="D420" r:id="rId417" xr:uid="{FF7C78E1-FD78-4893-95F0-5ECC3A18C68D}"/>
-    <hyperlink ref="D421" r:id="rId418" xr:uid="{1951E881-6FE0-45EA-8CF9-D3FAB9FAC8B9}"/>
-    <hyperlink ref="D422" r:id="rId419" xr:uid="{04BFC413-54BE-4617-8D8B-9C72AB166AAF}"/>
-    <hyperlink ref="D423" r:id="rId420" xr:uid="{81FF17D2-2BEB-4A2E-8086-A7339894774C}"/>
-    <hyperlink ref="D424" r:id="rId421" xr:uid="{CEFD15B6-7F4D-4782-9D04-1AC965A6F314}"/>
-    <hyperlink ref="D425" r:id="rId422" xr:uid="{EEA03FD2-AC2B-4961-8A53-F35C0569F7B5}"/>
-    <hyperlink ref="D426" r:id="rId423" xr:uid="{2F018061-F050-4285-8870-635B8A32F29A}"/>
-    <hyperlink ref="D427" r:id="rId424" xr:uid="{1C8B7244-B754-49C0-93A9-52FAF2E59442}"/>
-    <hyperlink ref="D428" r:id="rId425" xr:uid="{42B4EEC4-CC4F-46F0-BA44-432D13DFCAB0}"/>
-    <hyperlink ref="D429" r:id="rId426" xr:uid="{B818ECC1-0D14-4FE0-8D7A-EF3B2949C1F4}"/>
-    <hyperlink ref="D430" r:id="rId427" xr:uid="{7C54CDB8-2E2C-4F85-95D8-9CCF06C57051}"/>
-    <hyperlink ref="D431" r:id="rId428" xr:uid="{72D9903F-4B40-43B9-BF69-86CCE2B0220E}"/>
-    <hyperlink ref="D432" r:id="rId429" xr:uid="{3B0E34B5-9E6F-4FD2-998A-47E5C3F374E1}"/>
-    <hyperlink ref="D433" r:id="rId430" xr:uid="{1780FAF5-8279-44FE-8426-A56AE04C5435}"/>
-    <hyperlink ref="D434" r:id="rId431" xr:uid="{E7E12624-3FA9-4CDE-88E2-3885036864AC}"/>
-    <hyperlink ref="D435" r:id="rId432" xr:uid="{26399E30-9C6A-44E7-BE99-E9FAAA249EB2}"/>
-    <hyperlink ref="D436" r:id="rId433" xr:uid="{43DDE650-A356-4EEB-8A95-BF08588E2601}"/>
-    <hyperlink ref="D437" r:id="rId434" xr:uid="{B5B240FD-5858-4C23-BFF4-405327AB52AE}"/>
-    <hyperlink ref="D438" r:id="rId435" xr:uid="{3F7E3E72-560D-4F4C-B45F-74F76DF4C65A}"/>
-    <hyperlink ref="D439" r:id="rId436" xr:uid="{16EB9642-CB02-4AD9-9E59-E0E9AEEEC6E1}"/>
-    <hyperlink ref="D440" r:id="rId437" xr:uid="{25F01466-BB43-467C-AAA8-870D961BB103}"/>
-    <hyperlink ref="D441" r:id="rId438" xr:uid="{F14BF557-AE02-4E65-9F5F-80AF0F1CADBE}"/>
-    <hyperlink ref="D443" r:id="rId439" xr:uid="{C9DE96B8-B981-4C0E-AED0-D7BFC3FB0C46}"/>
-    <hyperlink ref="D442" r:id="rId440" xr:uid="{066BA859-62BD-4FF8-97FF-A2E77D3A68B9}"/>
-    <hyperlink ref="D444" r:id="rId441" xr:uid="{F07747EA-ACD0-43CD-B097-4032EB770B0C}"/>
-    <hyperlink ref="D445" r:id="rId442" xr:uid="{D76B884C-B3B8-45FB-A7B2-0D9DC4AB9180}"/>
-    <hyperlink ref="D446" r:id="rId443" xr:uid="{5142E7B2-092E-48C4-B763-6C80E4508656}"/>
-    <hyperlink ref="D447" r:id="rId444" xr:uid="{2806A5F7-D0D6-4CBF-8AE7-ED969A65899C}"/>
-    <hyperlink ref="D448" r:id="rId445" xr:uid="{4CBC30FC-EC28-4F92-BAAB-A7D5426DC291}"/>
-    <hyperlink ref="D455" r:id="rId446" xr:uid="{944585FB-6DF5-482E-94C4-4F3002E9C190}"/>
-    <hyperlink ref="D449" r:id="rId447" xr:uid="{301A6C3B-67D8-44F3-9913-8500A6811777}"/>
-    <hyperlink ref="D451" r:id="rId448" xr:uid="{0369DACF-8B99-477C-B3D2-51E99868F5B8}"/>
-    <hyperlink ref="D452" r:id="rId449" xr:uid="{44B3876D-448F-430E-87F7-424D38B98B30}"/>
-    <hyperlink ref="D450" r:id="rId450" xr:uid="{008ACA58-7701-497B-B0A3-519950BBE4CC}"/>
-    <hyperlink ref="D453" r:id="rId451" xr:uid="{F59C6A4C-5BC0-4B69-BC57-701368441DDD}"/>
-    <hyperlink ref="D454" r:id="rId452" xr:uid="{7242D59C-76B9-4F59-B5E8-E7FCFEA6A9B8}"/>
-    <hyperlink ref="D456" r:id="rId453" xr:uid="{977B6D01-7EFC-4495-842A-7F9F55328112}"/>
-    <hyperlink ref="D464" r:id="rId454" xr:uid="{6EBA8B29-8166-4838-AE71-594FE588E88C}"/>
-    <hyperlink ref="D457" r:id="rId455" xr:uid="{FBD81D96-22AD-4141-B9E4-55EEA145BD57}"/>
-    <hyperlink ref="D458" r:id="rId456" xr:uid="{A7BEE7A1-459B-41E9-8610-40E27BE09933}"/>
-    <hyperlink ref="D460" r:id="rId457" xr:uid="{8DC9DBCB-1254-4CC1-B0F5-E70A8A6C79DA}"/>
-    <hyperlink ref="D459" r:id="rId458" xr:uid="{A40CF748-8CB1-4B3C-B4C7-6BE4B4B455C0}"/>
-    <hyperlink ref="D461" r:id="rId459" xr:uid="{F7FB6ADF-AADA-4E38-9500-17B22C6B5C03}"/>
-    <hyperlink ref="D462" r:id="rId460" xr:uid="{D0AB0ABD-86EE-4DAC-90C7-3DA805D7023D}"/>
-    <hyperlink ref="D463" r:id="rId461" xr:uid="{0594FD5F-084F-440C-A3C7-66358ECC43F9}"/>
-    <hyperlink ref="D465" r:id="rId462" xr:uid="{87E44FE2-8212-468A-A66A-CEAB8D9CF125}"/>
-    <hyperlink ref="D466" r:id="rId463" xr:uid="{69B1CC96-8066-45ED-9179-FA1449C0202C}"/>
-    <hyperlink ref="D467" r:id="rId464" xr:uid="{1B3B16CC-DFD9-4085-8296-C2989574E88B}"/>
-    <hyperlink ref="D468" r:id="rId465" xr:uid="{F79321DC-2AF6-4E62-8F3A-A930EA38652B}"/>
-    <hyperlink ref="D469" r:id="rId466" xr:uid="{B8B2F5AE-2D2E-4E32-BA34-BDDEC7C1E847}"/>
-    <hyperlink ref="D470" r:id="rId467" xr:uid="{D830768F-3C92-4000-9E5B-3618C7D57334}"/>
-    <hyperlink ref="D471" r:id="rId468" xr:uid="{C04D2C5A-1965-4933-B470-2E435F1FEB22}"/>
-    <hyperlink ref="D472" r:id="rId469" xr:uid="{3F0C90F5-A494-48DF-91E3-B26F262CE8AA}"/>
-    <hyperlink ref="D473" r:id="rId470" xr:uid="{829A7829-B841-420A-8A5E-521C33C8411B}"/>
-    <hyperlink ref="D474" r:id="rId471" xr:uid="{CF597D61-8B8A-480F-8984-7C9FA7211D37}"/>
-    <hyperlink ref="D475" r:id="rId472" xr:uid="{9976A513-C5C0-447B-A1C7-3EB4558EB98A}"/>
-    <hyperlink ref="D476" r:id="rId473" xr:uid="{707B707C-F0EC-45C1-9A0B-9FE6C2912F76}"/>
-    <hyperlink ref="D477" r:id="rId474" xr:uid="{4D357EAB-8BAC-42A0-B0F5-2CF83E795742}"/>
-    <hyperlink ref="D478" r:id="rId475" xr:uid="{42E6DF94-D998-4634-BD5D-4F25DD4AC797}"/>
-    <hyperlink ref="D479" r:id="rId476" xr:uid="{C74B994B-4C61-486A-9700-43EB53D1CC79}"/>
-    <hyperlink ref="D480" r:id="rId477" xr:uid="{82387677-0E3D-4DE8-81C0-5B8B2219D9EC}"/>
-    <hyperlink ref="D481" r:id="rId478" xr:uid="{AD4EB573-74B0-4AB9-A11A-A180398E3EC5}"/>
-    <hyperlink ref="D482" r:id="rId479" xr:uid="{9E0DF20B-D878-4B6F-8E7C-EBFAB91B239D}"/>
-    <hyperlink ref="D483" r:id="rId480" xr:uid="{E7A48EEF-AE5C-492F-AEC6-62119BA038D3}"/>
-    <hyperlink ref="D484" r:id="rId481" xr:uid="{F8CFE556-D0C9-4745-8166-5B94D1135260}"/>
-    <hyperlink ref="D485" r:id="rId482" xr:uid="{FBA23B10-797D-451F-93F4-5D4ECF58DF18}"/>
-    <hyperlink ref="D486" r:id="rId483" xr:uid="{77CD5E52-13F7-40F8-B7C2-6356F876B868}"/>
-    <hyperlink ref="D487" r:id="rId484" xr:uid="{17DDF098-1759-4D47-8BDD-B66B0EB49FD9}"/>
-    <hyperlink ref="D493" r:id="rId485" xr:uid="{80975341-5200-460B-827B-99751CFC6930}"/>
-    <hyperlink ref="D494" r:id="rId486" xr:uid="{AA58D0B0-EF24-4AC7-8BEB-AC999FFBDF33}"/>
-    <hyperlink ref="D498" r:id="rId487" xr:uid="{133AD072-82C7-4880-9A68-A88FA1CE8863}"/>
-    <hyperlink ref="D515" r:id="rId488" xr:uid="{E2FA476C-A3B8-4177-9E08-97829E6AF772}"/>
-    <hyperlink ref="D516" r:id="rId489" xr:uid="{20FE7417-F51B-4D23-B39D-2F70B920D94D}"/>
-    <hyperlink ref="D517" r:id="rId490" xr:uid="{A6A904AA-9765-4CFF-AF9D-3460FDC5FD5B}"/>
-    <hyperlink ref="D519" r:id="rId491" xr:uid="{20503C73-A4CD-4B0B-8CC6-60D2A6B6F011}"/>
-    <hyperlink ref="D518" r:id="rId492" xr:uid="{7C159450-EF70-4C63-A18C-52EA8AADD36D}"/>
-    <hyperlink ref="D520" r:id="rId493" xr:uid="{304D3556-D71B-420C-82E8-90E3886F4A5E}"/>
-    <hyperlink ref="D521" r:id="rId494" xr:uid="{2C92EED8-6B25-47D2-BF43-61BC35491C20}"/>
-    <hyperlink ref="D522" r:id="rId495" xr:uid="{002660D7-38F8-4E4E-ADFB-017344CF4B51}"/>
-    <hyperlink ref="D416" r:id="rId496" xr:uid="{59677F8D-E486-4D61-86C9-269A2D029F17}"/>
-    <hyperlink ref="D533" r:id="rId497" xr:uid="{1B274682-180A-4F17-A146-1AAAA61C7F81}"/>
+    <hyperlink ref="D81" r:id="rId79" xr:uid="{992A24CC-B9F6-4F6E-A318-5F8018D26303}"/>
+    <hyperlink ref="D82" r:id="rId80" xr:uid="{3308EEBF-3DF3-4730-8880-767B8E2E9EE1}"/>
+    <hyperlink ref="D83" r:id="rId81" xr:uid="{30A97CBD-52C7-418C-B432-13411A97C559}"/>
+    <hyperlink ref="D86" r:id="rId82" xr:uid="{FACFB6D7-D4BB-4B16-98C5-21813B38CD7E}"/>
+    <hyperlink ref="D87" r:id="rId83" xr:uid="{C1010E98-4D8C-4634-B04B-D8D905CD4ACC}"/>
+    <hyperlink ref="D88" r:id="rId84" xr:uid="{6ADC728F-9161-4C8D-84FD-0963CD3266A2}"/>
+    <hyperlink ref="D89" r:id="rId85" xr:uid="{E3EA6B00-463E-4BF8-A48E-4C8F944950B8}"/>
+    <hyperlink ref="D84" r:id="rId86" xr:uid="{FACCC2BC-8378-40D0-9765-1CCD499D7036}"/>
+    <hyperlink ref="D90" r:id="rId87" xr:uid="{341D07D4-F1F4-4067-8DE5-9C093FD0B5AF}"/>
+    <hyperlink ref="D91" r:id="rId88" xr:uid="{B55EFD6D-0920-4D7D-886E-5AF05ECD3BF4}"/>
+    <hyperlink ref="D92" r:id="rId89" xr:uid="{E6635313-99DD-4729-89A6-1248A3D4B669}"/>
+    <hyperlink ref="D95" r:id="rId90" xr:uid="{B3374B68-4D56-4626-8BC8-E705D61B342D}"/>
+    <hyperlink ref="D102" r:id="rId91" xr:uid="{9D681E77-DEDF-41B8-BC1B-D9BB7E0FEEBC}"/>
+    <hyperlink ref="D98" r:id="rId92" xr:uid="{E1BD69CC-AB2E-4F9F-8D30-671496982B5F}"/>
+    <hyperlink ref="D103" r:id="rId93" xr:uid="{91A83172-2BA4-41EB-8DBC-11720ECE2846}"/>
+    <hyperlink ref="D108" r:id="rId94" xr:uid="{8936664B-6231-4629-B487-647C6AF6AD16}"/>
+    <hyperlink ref="D109" r:id="rId95" xr:uid="{2009A43D-6FDD-4652-B575-0FE996527B5B}"/>
+    <hyperlink ref="D110" r:id="rId96" xr:uid="{5BF513EC-08D6-4D76-8E8A-4FA925B137DE}"/>
+    <hyperlink ref="D111" r:id="rId97" xr:uid="{CE03A04B-1DA5-400A-874A-44B88D96D71F}"/>
+    <hyperlink ref="D107" r:id="rId98" xr:uid="{41AC2FFF-26F7-47CE-9C78-B20FDFC986DE}"/>
+    <hyperlink ref="D106" r:id="rId99" xr:uid="{9BA9C628-D43E-4F5A-8545-724D3E41C1C0}"/>
+    <hyperlink ref="D112" r:id="rId100" xr:uid="{FF2D1477-2E14-4762-BE11-4C583FD8A039}"/>
+    <hyperlink ref="D113" r:id="rId101" xr:uid="{F66DC899-8564-4936-BD57-441547CE11A6}"/>
+    <hyperlink ref="D114" r:id="rId102" xr:uid="{DCC85F56-CC4F-44AE-85F8-2207E542E607}"/>
+    <hyperlink ref="D115" r:id="rId103" xr:uid="{C292924A-CF8C-4049-A122-0C4BC247D857}"/>
+    <hyperlink ref="D116" r:id="rId104" xr:uid="{6B44D329-A9E4-4703-8C0E-FA6431859A48}"/>
+    <hyperlink ref="D117" r:id="rId105" xr:uid="{DEACF395-6D5C-40DE-AF5D-059BC1F467F7}"/>
+    <hyperlink ref="D118" r:id="rId106" xr:uid="{45E81D35-884D-4280-8CFB-D8DEC5DE4D34}"/>
+    <hyperlink ref="D119" r:id="rId107" xr:uid="{953131FB-0411-4595-A022-A3D1025AE9B7}"/>
+    <hyperlink ref="D120" r:id="rId108" xr:uid="{4A96FA4B-1254-422D-B697-57CC6BA43402}"/>
+    <hyperlink ref="D121" r:id="rId109" xr:uid="{E6658E27-3F09-4E67-8ED9-0511B04FD557}"/>
+    <hyperlink ref="D122" r:id="rId110" xr:uid="{3830F548-4508-48A9-B871-3D85E397B0D9}"/>
+    <hyperlink ref="D123" r:id="rId111" xr:uid="{EAE04C90-51E8-4B2A-A8D4-6FE15517BEBF}"/>
+    <hyperlink ref="D124" r:id="rId112" xr:uid="{52965897-EDFA-4485-9283-52E8EEC02C82}"/>
+    <hyperlink ref="D125" r:id="rId113" xr:uid="{888C9C36-17CF-48BC-A5B3-F8A917850594}"/>
+    <hyperlink ref="D126" r:id="rId114" xr:uid="{DF7AFFAB-6C45-4807-9B3C-78B3DD012DB3}"/>
+    <hyperlink ref="D127" r:id="rId115" xr:uid="{73FD4728-C8CF-4BEF-8361-F553FA664E98}"/>
+    <hyperlink ref="D128" r:id="rId116" xr:uid="{87096162-8858-4541-826A-DD86B394C052}"/>
+    <hyperlink ref="D129" r:id="rId117" xr:uid="{0911B5E6-13DC-4022-8FAA-5E2541FFBE7E}"/>
+    <hyperlink ref="D130" r:id="rId118" xr:uid="{279020EB-C73D-43FE-9F08-07307C38B7AB}"/>
+    <hyperlink ref="D137" r:id="rId119" xr:uid="{F7C8D236-719F-4EF2-A3CD-C7E4D6E81148}"/>
+    <hyperlink ref="D139" r:id="rId120" xr:uid="{32387BDF-45EC-4E54-B5EB-01E44CE4B52C}"/>
+    <hyperlink ref="D131" r:id="rId121" xr:uid="{026B0701-309C-486A-8F45-8FF84000221B}"/>
+    <hyperlink ref="D132" r:id="rId122" xr:uid="{375AA471-169A-4F9B-8A5D-1341D42A358C}"/>
+    <hyperlink ref="D133" r:id="rId123" xr:uid="{EA34FD32-70E9-4E21-8314-A66726994DD3}"/>
+    <hyperlink ref="D134" r:id="rId124" xr:uid="{94AAF235-6394-4FAD-AB94-D91897A229CD}"/>
+    <hyperlink ref="D135" r:id="rId125" xr:uid="{1A5F3837-7E19-453E-875E-681330D50A52}"/>
+    <hyperlink ref="D136" r:id="rId126" xr:uid="{85E77E4C-84DF-431F-9B7C-37AA63225770}"/>
+    <hyperlink ref="D140" r:id="rId127" xr:uid="{992213FB-B611-4AB7-919C-A9D5033600C0}"/>
+    <hyperlink ref="D141" r:id="rId128" xr:uid="{90F44307-6DBE-4D55-B371-1ACAD08A7D93}"/>
+    <hyperlink ref="D142" r:id="rId129" xr:uid="{C7C5CD5A-8D91-45FD-8249-9D8E4FFA9E18}"/>
+    <hyperlink ref="D143" r:id="rId130" xr:uid="{113742BC-1672-48C9-B351-A71B39E3E2D3}"/>
+    <hyperlink ref="D144" r:id="rId131" xr:uid="{B0348005-72F9-47D8-99DC-5623308FB9B3}"/>
+    <hyperlink ref="D145" r:id="rId132" xr:uid="{3587728B-0FC6-4089-BA43-AAB1AA70C2C1}"/>
+    <hyperlink ref="D146" r:id="rId133" xr:uid="{A2084BEE-38F4-499F-8791-16F60BBAB6CB}"/>
+    <hyperlink ref="D147" r:id="rId134" xr:uid="{AFE3A00F-6634-4F27-8AAA-785588CB3CA9}"/>
+    <hyperlink ref="D148" r:id="rId135" xr:uid="{57822340-657A-407C-8C65-F2566903C26A}"/>
+    <hyperlink ref="D149" r:id="rId136" xr:uid="{D3D81206-3512-4259-95B8-A98FB6503A64}"/>
+    <hyperlink ref="D150" r:id="rId137" xr:uid="{2FD3C88E-397B-4A9C-A08D-BAC9F4752572}"/>
+    <hyperlink ref="D151" r:id="rId138" xr:uid="{B113BBFE-9A26-406F-9805-C86669C65D7D}"/>
+    <hyperlink ref="D138" r:id="rId139" xr:uid="{5FAD256B-CDEB-4828-97AF-67A54E3C8F12}"/>
+    <hyperlink ref="D152" r:id="rId140" xr:uid="{3EAD9A31-3BDF-4B4A-BDA2-D569B59E233B}"/>
+    <hyperlink ref="D153" r:id="rId141" xr:uid="{12C300E0-DCD6-4C5C-9B23-1CB886E317AA}"/>
+    <hyperlink ref="D154" r:id="rId142" xr:uid="{AC653FFA-E170-43DA-A402-DB5AE1B22392}"/>
+    <hyperlink ref="D155" r:id="rId143" xr:uid="{256CB68D-7211-4C8F-B5B6-F29E5D9A3B34}"/>
+    <hyperlink ref="D156" r:id="rId144" xr:uid="{81431275-2CC2-4355-AF6E-BD7C863810D4}"/>
+    <hyperlink ref="D157" r:id="rId145" xr:uid="{BE30EBE2-EF38-481B-B570-4C9AA5DE79CF}"/>
+    <hyperlink ref="D163" r:id="rId146" xr:uid="{74AD4D7A-A665-4D81-9EC1-91ED550AE18A}"/>
+    <hyperlink ref="D164" r:id="rId147" xr:uid="{348CC46B-FA3B-4C67-BA17-586D43B3550A}"/>
+    <hyperlink ref="D161" r:id="rId148" xr:uid="{786E59F5-84C9-49DC-B788-60C7755B4474}"/>
+    <hyperlink ref="D165" r:id="rId149" xr:uid="{840984F6-CBC9-4BC1-927E-978E91FF2872}"/>
+    <hyperlink ref="D162" r:id="rId150" xr:uid="{40895C0A-3A34-46DD-8597-605C620B3396}"/>
+    <hyperlink ref="D166" r:id="rId151" display="mailto:clara.gilloteau@inrae.fr" xr:uid="{D884AD4F-80FF-4AAC-92F1-377C884E887C}"/>
+    <hyperlink ref="D158" r:id="rId152" xr:uid="{BD960D86-DE69-41C7-88A8-3E0A0E4336DD}"/>
+    <hyperlink ref="D159" r:id="rId153" xr:uid="{07AA7898-51AF-4233-B0C8-C926CA5AC508}"/>
+    <hyperlink ref="D160" r:id="rId154" xr:uid="{D1A9CAEC-794E-49B5-919D-49B8F2EE1840}"/>
+    <hyperlink ref="D167" r:id="rId155" xr:uid="{742F2CBF-E925-4643-89B1-A3980A99A80F}"/>
+    <hyperlink ref="D168" r:id="rId156" display="https://listes.cerege.fr/wws/editsubscriber/rhizoseqc?email=adeline.armelin%40cea.fr&amp;previous_action=review" xr:uid="{E113C167-87CA-4D16-A22E-E66EF4A35322}"/>
+    <hyperlink ref="D169" r:id="rId157" xr:uid="{61BE3872-98EA-4558-9CA3-46084F90C3BA}"/>
+    <hyperlink ref="D170" r:id="rId158" xr:uid="{025E4DEF-01E7-4C60-9565-416E471169C6}"/>
+    <hyperlink ref="D171" r:id="rId159" xr:uid="{067B0C9B-6450-4B12-8618-69DC27A86938}"/>
+    <hyperlink ref="D172" r:id="rId160" xr:uid="{EDF1B310-06B3-45EB-80D5-BE2819B91CED}"/>
+    <hyperlink ref="D173" r:id="rId161" xr:uid="{A93B5510-5A64-494B-BD89-1A794306D437}"/>
+    <hyperlink ref="D174" r:id="rId162" xr:uid="{7C115875-394E-4852-961A-341E761221E3}"/>
+    <hyperlink ref="D175" r:id="rId163" xr:uid="{68E3C4CB-86E1-4713-BEF8-E5A1D4E1208D}"/>
+    <hyperlink ref="D176" r:id="rId164" xr:uid="{41FEFCE0-F531-453B-A219-E4E9207E4ABD}"/>
+    <hyperlink ref="D177" r:id="rId165" xr:uid="{C6DA40E3-5386-4F75-8DFD-3F8E4FACE9A3}"/>
+    <hyperlink ref="D178" r:id="rId166" xr:uid="{8DAC9949-C651-4441-9EDE-7C84E9D21D7D}"/>
+    <hyperlink ref="D179" r:id="rId167" xr:uid="{B366F38E-6B8B-4EE3-8198-347988E214E6}"/>
+    <hyperlink ref="D180" r:id="rId168" display="https://listes.cerege.fr/wws/editsubscriber/rhizoseqc?email=dominique.masse%40ird.fr&amp;previous_action=review" xr:uid="{F66AE854-B847-402D-A975-1F12925CB99E}"/>
+    <hyperlink ref="D181" r:id="rId169" xr:uid="{799CDCEA-30ED-49D6-A18A-D3AB1A78291B}"/>
+    <hyperlink ref="D182" r:id="rId170" xr:uid="{922EECB1-18FB-431F-A50D-35BB11B7CAE8}"/>
+    <hyperlink ref="D183" r:id="rId171" xr:uid="{E1891978-EC57-4125-8695-E65007780A6F}"/>
+    <hyperlink ref="D184" r:id="rId172" xr:uid="{5048DDFD-2DAD-4E71-A59C-D099591CAC2D}"/>
+    <hyperlink ref="D185" r:id="rId173" xr:uid="{100CC261-4E92-4071-8B77-AAA4730BE390}"/>
+    <hyperlink ref="D186" r:id="rId174" xr:uid="{E88B3550-2E2E-441D-AE2E-9C341A75B899}"/>
+    <hyperlink ref="D187" r:id="rId175" xr:uid="{A5831976-C50A-4327-871C-3230DB6B56A1}"/>
+    <hyperlink ref="D188" r:id="rId176" xr:uid="{CDF8E337-A608-44BA-A365-87674AD5A4AA}"/>
+    <hyperlink ref="D189" r:id="rId177" xr:uid="{77E15C07-14CF-46A2-A380-3165C7BF71E1}"/>
+    <hyperlink ref="D190" r:id="rId178" xr:uid="{5812CB20-02BB-4D26-A5B0-0882E37403E3}"/>
+    <hyperlink ref="D191" r:id="rId179" xr:uid="{208B13EA-96C7-4352-85BF-3F3953BEFB79}"/>
+    <hyperlink ref="D192" r:id="rId180" xr:uid="{60A3F982-A15F-46D3-A3B2-2A3D1998CD1E}"/>
+    <hyperlink ref="D193" r:id="rId181" xr:uid="{35450EC9-24E8-4AF2-9BC5-6401E69D86C9}"/>
+    <hyperlink ref="D194" r:id="rId182" xr:uid="{EFB1470A-C326-4477-9E36-FE7AD01DE15A}"/>
+    <hyperlink ref="D195" r:id="rId183" xr:uid="{5A92DC38-EE48-485E-9492-3099AA7108D7}"/>
+    <hyperlink ref="D196" r:id="rId184" xr:uid="{A6A30117-6FE9-4B29-B0CB-6985AE8B7D8B}"/>
+    <hyperlink ref="D199" r:id="rId185" xr:uid="{9F93CFD9-FD67-43EB-AAB7-4A13F0ACE8CA}"/>
+    <hyperlink ref="D198" r:id="rId186" xr:uid="{8836D2E1-A1E8-4829-B3A4-F68897928D65}"/>
+    <hyperlink ref="D197" r:id="rId187" xr:uid="{59922D8F-19C3-4792-9D4D-CF3B62CC2889}"/>
+    <hyperlink ref="D200" r:id="rId188" xr:uid="{0983DF29-6698-4EC3-9B26-DF38025F02D9}"/>
+    <hyperlink ref="D202" r:id="rId189" xr:uid="{CFAAA63C-2872-4514-B6BB-C7AB42B01963}"/>
+    <hyperlink ref="D203" r:id="rId190" xr:uid="{ED76EEDE-512A-4868-BF51-62121C15C6A7}"/>
+    <hyperlink ref="D201" r:id="rId191" xr:uid="{DB77F737-D8CB-4475-A20B-21EB1061CF6E}"/>
+    <hyperlink ref="D211" r:id="rId192" xr:uid="{E10E7743-4F8F-4102-B589-0558BB215585}"/>
+    <hyperlink ref="D214" r:id="rId193" xr:uid="{BD93C876-AD84-4057-85DE-C81F4CC6E3D3}"/>
+    <hyperlink ref="D216" r:id="rId194" xr:uid="{E4354BAF-8DD9-4567-9775-D68870CE51D8}"/>
+    <hyperlink ref="D213" r:id="rId195" xr:uid="{C4B20045-BCB6-4110-8A03-9EE1407BFEBD}"/>
+    <hyperlink ref="D217" r:id="rId196" xr:uid="{AA36CB38-3294-4990-A881-B4178B4094EC}"/>
+    <hyperlink ref="D222" r:id="rId197" xr:uid="{26519EBA-A3A9-4425-A2F2-F4A16023238F}"/>
+    <hyperlink ref="D246" r:id="rId198" xr:uid="{328A955D-8038-4C9E-89D0-3DBB7634E2AC}"/>
+    <hyperlink ref="D263" r:id="rId199" xr:uid="{5944CC2D-2912-486D-8B2D-B2F1B803EB4C}"/>
+    <hyperlink ref="D265" r:id="rId200" xr:uid="{FBB02D20-D46A-4265-A382-F42AE2487354}"/>
+    <hyperlink ref="D266" r:id="rId201" xr:uid="{153C9299-725E-4687-AB2F-6AF71AD6D4BA}"/>
+    <hyperlink ref="D273" r:id="rId202" xr:uid="{CF372B3D-95AB-4C0C-AE48-A443E44E2E12}"/>
+    <hyperlink ref="D101" r:id="rId203" xr:uid="{3FEDEAE7-0885-43A2-9EDE-12398C4B1072}"/>
+    <hyperlink ref="D100" r:id="rId204" xr:uid="{4532F07F-C601-4FB1-B580-91AFEED4AB47}"/>
+    <hyperlink ref="D264" r:id="rId205" xr:uid="{D71D8727-99E0-4400-BE64-77DA46FEE4F4}"/>
+    <hyperlink ref="D267" r:id="rId206" xr:uid="{BC0A9543-5B0C-4EC3-89C8-C636A09D30FD}"/>
+    <hyperlink ref="D268" r:id="rId207" xr:uid="{DCC1CA4E-3E71-40EA-95C6-7490C364D8F2}"/>
+    <hyperlink ref="D269" r:id="rId208" xr:uid="{CA5C82F9-AAF5-47CE-BCC2-0DFE57955224}"/>
+    <hyperlink ref="D270" r:id="rId209" xr:uid="{0832F85F-D22A-43B6-875F-7E5CA33EBDBC}"/>
+    <hyperlink ref="D271" r:id="rId210" xr:uid="{330B5F6F-DC3D-46EA-B980-59CC1974BFA2}"/>
+    <hyperlink ref="D272" r:id="rId211" xr:uid="{D6849A02-2B82-43A0-92B0-FDAD2FA552F5}"/>
+    <hyperlink ref="D274" r:id="rId212" xr:uid="{E4477073-177E-4760-AA4F-5B46DFDA14F7}"/>
+    <hyperlink ref="D93" r:id="rId213" xr:uid="{ADE323D7-489E-414A-A0E0-162B849F80A7}"/>
+    <hyperlink ref="D94" r:id="rId214" xr:uid="{2EC6D3CD-FD36-4CAF-AEE2-07761FCB7CCA}"/>
+    <hyperlink ref="D97" r:id="rId215" xr:uid="{F555CB71-12F9-4040-91DB-3FD6F31EF36D}"/>
+    <hyperlink ref="D105" r:id="rId216" xr:uid="{F9AC4976-C48E-4978-A58E-57FBD9B49ECA}"/>
+    <hyperlink ref="D293" r:id="rId217" xr:uid="{86FFA566-E624-4AF7-8514-6C27F4C161C4}"/>
+    <hyperlink ref="D360" r:id="rId218" xr:uid="{FB37F046-3E8C-44B1-965B-C97F9EA82CED}"/>
+    <hyperlink ref="D361" r:id="rId219" xr:uid="{02000C05-C2C4-4CA5-932D-0F19E3E8ADC3}"/>
+    <hyperlink ref="D362" r:id="rId220" xr:uid="{EF7B83E6-8263-4F4A-8990-A4FF219972C0}"/>
+    <hyperlink ref="D363" r:id="rId221" xr:uid="{CF0D0627-8DC9-421B-8AB0-E2AA3037676C}"/>
+    <hyperlink ref="D364" r:id="rId222" display="mailto:eliot.chatton@univ-rennes.fr" xr:uid="{AB33B82F-4B5B-4C6B-B2F7-2848C85803C3}"/>
+    <hyperlink ref="D365" r:id="rId223" xr:uid="{85C470E8-693B-4CDB-AC26-2B2F2605F62E}"/>
+    <hyperlink ref="D366" r:id="rId224" xr:uid="{840BC485-374C-4D60-9D91-51253302802B}"/>
+    <hyperlink ref="D367" r:id="rId225" xr:uid="{FA8CBCD0-461C-4B2C-94D5-B26E9BA1ECBE}"/>
+    <hyperlink ref="D368" r:id="rId226" xr:uid="{85F8A557-4F75-4AFF-BD8D-4A369FD13105}"/>
+    <hyperlink ref="D369" r:id="rId227" xr:uid="{66889B16-56CB-402E-A46A-00F6D0BEFB8C}"/>
+    <hyperlink ref="D370" r:id="rId228" xr:uid="{F92D0E57-FA3B-4E3F-9DBA-B1A418EF828A}"/>
+    <hyperlink ref="D371" r:id="rId229" xr:uid="{E8DBB520-B069-457D-A431-3F3CB6A08252}"/>
+    <hyperlink ref="D372" r:id="rId230" xr:uid="{4CE3FB06-FE62-45E8-B523-42BBD4D801FB}"/>
+    <hyperlink ref="D373" r:id="rId231" xr:uid="{A11B4D69-CB33-4549-961B-444440EB4A47}"/>
+    <hyperlink ref="D374" r:id="rId232" display="mailto:didier.jezequel@inrae.fr" xr:uid="{711EC7D6-6F53-4BB8-B6E7-23095EBC9005}"/>
+    <hyperlink ref="D375" r:id="rId233" xr:uid="{7570B12B-7024-4FCF-AA22-E36AF8C1D4CC}"/>
+    <hyperlink ref="D376" r:id="rId234" xr:uid="{61DB90E9-BD67-48D9-B657-89416D2EED69}"/>
+    <hyperlink ref="D377" r:id="rId235" display="mailto:wolfgang.ludwig@univ-perp.fr" xr:uid="{F9C9D1F4-1991-4389-BFE4-9BE7CB7ECED8}"/>
+    <hyperlink ref="D378" r:id="rId236" xr:uid="{5E2B52C1-08B0-43A5-95B4-848A459DB315}"/>
+    <hyperlink ref="D379" r:id="rId237" display="mailto:edouard.metzger@univ-angers.fr" xr:uid="{59E61568-78B5-41C8-85D1-CC43DBA55D0D}"/>
+    <hyperlink ref="D380" r:id="rId238" xr:uid="{0517E78E-5BA6-4C99-95AF-C7D28D0EC215}"/>
+    <hyperlink ref="D381" r:id="rId239" display="mailto:Julien.Nemery@grenoble-inp.fr" xr:uid="{6FDF451D-F42A-43B7-8022-12E0F273F4D3}"/>
+    <hyperlink ref="D382" r:id="rId240" xr:uid="{4178A1DF-1C5B-4C5A-B6DD-D1A40885B42D}"/>
+    <hyperlink ref="D383" r:id="rId241" xr:uid="{E0F33667-16B4-4954-A6A2-B927FEFD3616}"/>
+    <hyperlink ref="D384" r:id="rId242" xr:uid="{399C084D-0179-479B-97B1-866B4936755B}"/>
+    <hyperlink ref="D385" r:id="rId243" xr:uid="{9B1C3AF1-9F70-472A-9B83-1576E6459B24}"/>
+    <hyperlink ref="D386" r:id="rId244" xr:uid="{C2815038-D142-45FB-A194-E2F0C361D416}"/>
+    <hyperlink ref="D387" r:id="rId245" xr:uid="{D7356312-9493-4442-90FB-FFFD508D3B30}"/>
+    <hyperlink ref="D388" r:id="rId246" display="mailto:claire.verin.cv@gmail.com" xr:uid="{4625BDEE-0E44-4607-80E5-6444424D79C9}"/>
+    <hyperlink ref="D389" r:id="rId247" xr:uid="{426011F8-761F-4289-B7E6-842D49598CB2}"/>
+    <hyperlink ref="D390" r:id="rId248" xr:uid="{4B29D626-F502-4D69-B86B-11B91566F18F}"/>
+    <hyperlink ref="D391" r:id="rId249" xr:uid="{54AD00BA-5EA2-4AC8-A903-58568469F719}"/>
+    <hyperlink ref="D392" r:id="rId250" xr:uid="{6E362010-D98B-4E53-9444-2551BC3384F2}"/>
+    <hyperlink ref="D393" r:id="rId251" xr:uid="{CD9F6046-D49C-46C0-B909-143D6A54F0B0}"/>
+    <hyperlink ref="D394" r:id="rId252" xr:uid="{8494696D-F2F6-449A-B6CC-5995FB929EF5}"/>
+    <hyperlink ref="D218" r:id="rId253" xr:uid="{876E6A5F-D6D4-45FF-8233-E0577B77396F}"/>
+    <hyperlink ref="D244" r:id="rId254" xr:uid="{DA3A1AE2-F4FD-41A9-97F8-0072003EA92E}"/>
+    <hyperlink ref="D212" r:id="rId255" xr:uid="{20C18E58-ED58-41E9-945A-471B9F09477D}"/>
+    <hyperlink ref="D304" r:id="rId256" xr:uid="{88B14105-E72E-49AA-B14C-B5EE9252467B}"/>
+    <hyperlink ref="D400" r:id="rId257" xr:uid="{EA39C09B-4B20-4316-8DF4-675B77129A46}"/>
+    <hyperlink ref="D401" r:id="rId258" xr:uid="{1D6715C0-F782-4275-B1A5-935F69FE9808}"/>
+    <hyperlink ref="D402" r:id="rId259" xr:uid="{9310D1D4-AE37-4F8D-B778-E14D476B480F}"/>
+    <hyperlink ref="D355" r:id="rId260" xr:uid="{CA021DE7-E699-4761-B185-897040AD9433}"/>
+    <hyperlink ref="D215" r:id="rId261" xr:uid="{B9A6B7DC-5DF9-4A99-B145-5A3F0D2B7333}"/>
+    <hyperlink ref="D350" r:id="rId262" xr:uid="{B64D5E0B-23AE-4FDD-AA57-B0FBC122B4F1}"/>
+    <hyperlink ref="D99" r:id="rId263" xr:uid="{7089C2BE-4027-4FC6-A1F9-6A1AE4B8725E}"/>
+    <hyperlink ref="D96" r:id="rId264" xr:uid="{71155148-E90E-47B9-8E3F-E19F3F36A0ED}"/>
+    <hyperlink ref="D336" r:id="rId265" xr:uid="{81D62058-B298-48D5-BEA8-2A123AB178FF}"/>
+    <hyperlink ref="D208" r:id="rId266" xr:uid="{78DE2F58-987A-484A-AF89-217D5EAE23C0}"/>
+    <hyperlink ref="D352" r:id="rId267" xr:uid="{4F33A286-1F0E-47CA-9ABD-7D8466C63771}"/>
+    <hyperlink ref="D260" r:id="rId268" xr:uid="{14E47318-C4D0-4AA4-98F9-0DCED3D68A79}"/>
+    <hyperlink ref="D245" r:id="rId269" xr:uid="{D3FF3E83-AA68-4EF8-9F7B-0E2057D0E740}"/>
+    <hyperlink ref="D242" r:id="rId270" xr:uid="{35DDB8DC-C0DF-47BC-9494-B0AFFE3D9CCC}"/>
+    <hyperlink ref="D312" r:id="rId271" xr:uid="{1C3E9AEE-E546-434D-AB91-1B2D579937C2}"/>
+    <hyperlink ref="D308" r:id="rId272" xr:uid="{09E32029-305F-4D3B-9C04-A812A87D30A9}"/>
+    <hyperlink ref="D311" r:id="rId273" xr:uid="{AA668327-E1EC-4D00-B044-D230A1469E10}"/>
+    <hyperlink ref="D204" r:id="rId274" xr:uid="{3425F408-7E94-4C6F-B4CF-B77F836CC73A}"/>
+    <hyperlink ref="D224" r:id="rId275" xr:uid="{BD740CB7-A0EB-4835-AE9A-8EBFB32F0B4D}"/>
+    <hyperlink ref="D397" r:id="rId276" xr:uid="{C2E09F23-E0BB-4D45-AEBC-0EB5BB6A32DF}"/>
+    <hyperlink ref="D398" r:id="rId277" xr:uid="{30E18D0A-4798-4269-87A1-EEC8F7C12AF8}"/>
+    <hyperlink ref="D209" r:id="rId278" xr:uid="{F659B331-2514-4125-B5B6-2746A6C9D815}"/>
+    <hyperlink ref="D252" r:id="rId279" xr:uid="{4B9AA62E-C2E2-43A5-AC7D-A8CB5A45A2E3}"/>
+    <hyperlink ref="D357" r:id="rId280" xr:uid="{3242E85F-FD44-4F58-A8FA-24B267452378}"/>
+    <hyperlink ref="D233" r:id="rId281" xr:uid="{6144C4F1-5BDC-41BC-99EE-CAC11F92DDDB}"/>
+    <hyperlink ref="D281" r:id="rId282" xr:uid="{55ABA163-8EAD-45DA-9926-77A8664D9FF3}"/>
+    <hyperlink ref="D205" r:id="rId283" xr:uid="{2C7377DB-8247-4708-9F7D-137BEB47E5C6}"/>
+    <hyperlink ref="D328" r:id="rId284" xr:uid="{D499EC6E-8184-4657-A8E1-51B90F4674E9}"/>
+    <hyperlink ref="D228" r:id="rId285" xr:uid="{82C4F817-40AF-4213-B681-25FF13B8A33F}"/>
+    <hyperlink ref="D340" r:id="rId286" xr:uid="{FB1612DE-24F1-4A29-A7D3-13B32DC1DFAC}"/>
+    <hyperlink ref="D324" r:id="rId287" xr:uid="{04B99F5E-5F9D-42F5-B7E3-D29F92BA6647}"/>
+    <hyperlink ref="D319" r:id="rId288" xr:uid="{04287E26-EE17-4FE4-BBFB-37390A2DCA8F}"/>
+    <hyperlink ref="D318" r:id="rId289" xr:uid="{B12D5B79-3F7A-41CB-BF81-D8DB501DF44C}"/>
+    <hyperlink ref="D348" r:id="rId290" xr:uid="{81B6701E-8AFC-4836-88E9-9EB0EE7A130C}"/>
+    <hyperlink ref="D248" r:id="rId291" xr:uid="{ACCB4D9F-619A-48F0-B558-838BA15C0088}"/>
+    <hyperlink ref="D210" r:id="rId292" xr:uid="{40664F2A-B511-4392-9307-8DE3EC5EF831}"/>
+    <hyperlink ref="D316" r:id="rId293" xr:uid="{FC88A6A4-3A82-4ACC-A314-4F3E8A70AD04}"/>
+    <hyperlink ref="D240" r:id="rId294" xr:uid="{3C8A276A-0565-4EA6-A659-E4086BBA33EE}"/>
+    <hyperlink ref="D237" r:id="rId295" xr:uid="{C296B55C-EC9A-494D-B196-FE5E88D91A94}"/>
+    <hyperlink ref="D320" r:id="rId296" xr:uid="{BB20E1A2-B3E2-4DCA-A837-D038045B2E0E}"/>
+    <hyperlink ref="D284" r:id="rId297" xr:uid="{C2FB647A-2BEC-4EE7-BE54-858B09F7E66B}"/>
+    <hyperlink ref="D226" r:id="rId298" xr:uid="{15C6E732-4AD7-4051-91CD-2CCA14610CF4}"/>
+    <hyperlink ref="D256" r:id="rId299" xr:uid="{8E1B11C0-AD4C-4C1C-80A0-ECA09FF4ACC4}"/>
+    <hyperlink ref="D280" r:id="rId300" xr:uid="{5BB60BC6-9999-4583-9F90-FFDB1D0368BC}"/>
+    <hyperlink ref="D326" r:id="rId301" xr:uid="{465EB82D-B8E0-48A6-87A3-5A0D60FAFE2D}"/>
+    <hyperlink ref="D335" r:id="rId302" xr:uid="{5B911E15-C04B-4E04-BCB0-DB2CE6977BEB}"/>
+    <hyperlink ref="D207" r:id="rId303" xr:uid="{0E373A37-F42A-47A7-87A0-42C3F6AFFED3}"/>
+    <hyperlink ref="D325" r:id="rId304" xr:uid="{E9E94CEE-1D05-447E-9700-167637BFEFAC}"/>
+    <hyperlink ref="D310" r:id="rId305" xr:uid="{21AFC143-E743-405F-8AA2-F48A8473046A}"/>
+    <hyperlink ref="D358" r:id="rId306" xr:uid="{19542A46-C5EE-4063-A0CD-D52C784EE30A}"/>
+    <hyperlink ref="D235" r:id="rId307" xr:uid="{75038B0D-54FC-46B0-88D5-A63098531A21}"/>
+    <hyperlink ref="D258" r:id="rId308" xr:uid="{0E6C7499-6DFA-4411-A6D4-6FAF0D3B2C66}"/>
+    <hyperlink ref="D291" r:id="rId309" xr:uid="{F3563381-FE64-484C-B8B9-CFC50F829993}"/>
+    <hyperlink ref="D321" r:id="rId310" xr:uid="{F4C44CA3-E7E0-4B31-83CD-B3424FB31911}"/>
+    <hyperlink ref="D342" r:id="rId311" xr:uid="{18A66060-C09C-488E-82E5-812383F3C00B}"/>
+    <hyperlink ref="D341" r:id="rId312" xr:uid="{FE6575E2-21CF-432D-9A1C-C43E51BCAD76}"/>
+    <hyperlink ref="D282" r:id="rId313" xr:uid="{3A3B4A90-9207-4AC0-B366-2757B8D43527}"/>
+    <hyperlink ref="D289" r:id="rId314" xr:uid="{8FC10517-577B-4A05-A510-B89AAE48147D}"/>
+    <hyperlink ref="D221" r:id="rId315" xr:uid="{67248038-E3BC-433A-8EE7-466E967B5D80}"/>
+    <hyperlink ref="D277" r:id="rId316" xr:uid="{DABA2BBA-5AAD-48BB-B895-D3A650C42FAB}"/>
+    <hyperlink ref="D338" r:id="rId317" xr:uid="{D312A4FE-B309-4DDA-8749-BBE8CC5C6609}"/>
+    <hyperlink ref="D344" r:id="rId318" xr:uid="{F0885177-08D1-405C-988F-0C06044636AE}"/>
+    <hyperlink ref="D247" r:id="rId319" xr:uid="{79461B07-5AF4-4FFA-8548-3D897A346C3B}"/>
+    <hyperlink ref="D337" r:id="rId320" xr:uid="{146C6A30-71A1-495D-ABAB-EB888DD5532E}"/>
+    <hyperlink ref="D343" r:id="rId321" xr:uid="{2D3007EC-30F9-4CD4-8C1E-85F9389DEF6F}"/>
+    <hyperlink ref="D353" r:id="rId322" xr:uid="{3A31C012-F064-4452-82BF-698418E19064}"/>
+    <hyperlink ref="D261" r:id="rId323" xr:uid="{87A7465B-A17F-4598-8CD6-572C9F4A5420}"/>
+    <hyperlink ref="D306" r:id="rId324" xr:uid="{3619F9BA-DCC8-41E4-9EF2-0E069F782C57}"/>
+    <hyperlink ref="D262" r:id="rId325" xr:uid="{583DC961-8FCE-44E6-8075-53799FE7F163}"/>
+    <hyperlink ref="D351" r:id="rId326" xr:uid="{D58394C4-67B4-4018-A824-910DA4B3C8B3}"/>
+    <hyperlink ref="D255" r:id="rId327" display="mailto:eric.chaumillon@univ-lr.fr" xr:uid="{5C9A51DC-1566-4EF1-B76D-B827A254060F}"/>
+    <hyperlink ref="D227" r:id="rId328" xr:uid="{D9CF8962-242F-4633-82B0-04CEF8E67E05}"/>
+    <hyperlink ref="D329" r:id="rId329" xr:uid="{0AE47B5B-2112-48D1-9BBF-FE9449A309BE}"/>
+    <hyperlink ref="D257" r:id="rId330" xr:uid="{C5ECA57C-E62C-4DEE-B870-13E194296C2F}"/>
+    <hyperlink ref="D296" r:id="rId331" xr:uid="{DBD8264D-EF4C-4EFB-8E9D-FFB67970E766}"/>
+    <hyperlink ref="D231" r:id="rId332" xr:uid="{8E8CDDB6-984D-4D10-BCDB-8715AD38BC5E}"/>
+    <hyperlink ref="D220" r:id="rId333" xr:uid="{D87D4DC7-A858-464C-A9FC-4CBD519FDF1C}"/>
+    <hyperlink ref="D356" r:id="rId334" xr:uid="{CD2898C2-01BF-4DD7-87A3-2DF871335FC5}"/>
+    <hyperlink ref="D330" r:id="rId335" xr:uid="{DE4A2B41-E351-4FFB-9916-9B5A12D9F826}"/>
+    <hyperlink ref="D278" r:id="rId336" xr:uid="{8ED70CE7-39BA-42D2-8773-FC573EFBF4C3}"/>
+    <hyperlink ref="D331" r:id="rId337" xr:uid="{F9AF74BC-C5BD-4C4C-80E9-B7676EA47DD4}"/>
+    <hyperlink ref="D349" r:id="rId338" xr:uid="{A24A0A03-18C8-4164-9C9C-C6D7E8079A60}"/>
+    <hyperlink ref="D241" r:id="rId339" xr:uid="{3E7272D2-FD11-4455-A18D-8F4152E7C571}"/>
+    <hyperlink ref="D225" r:id="rId340" xr:uid="{8CF31450-9FF6-41B8-B89D-83C1B91BBFED}"/>
+    <hyperlink ref="D290" r:id="rId341" xr:uid="{837E84CE-D2C6-454F-9ABE-6CE8B0C7790A}"/>
+    <hyperlink ref="D230" r:id="rId342" xr:uid="{A18AEC85-42EF-4E96-A88E-939CACB7E8DA}"/>
+    <hyperlink ref="D250" r:id="rId343" xr:uid="{377173B7-75BB-49B3-A644-5B35AE733908}"/>
+    <hyperlink ref="D359" r:id="rId344" xr:uid="{9534021C-50FE-4BB1-98C0-CE7464EBBFF7}"/>
+    <hyperlink ref="D323" r:id="rId345" xr:uid="{0AEACC9D-3DC9-4CD0-83F3-F2B033112830}"/>
+    <hyperlink ref="D276" r:id="rId346" xr:uid="{1671216E-95F7-4F08-8608-2BB33F39DCB9}"/>
+    <hyperlink ref="D206" r:id="rId347" xr:uid="{0B59AB2B-33AB-46D1-AA6F-B867860AE59F}"/>
+    <hyperlink ref="D334" r:id="rId348" xr:uid="{88DB392B-DCA9-416E-A674-4C43805B557D}"/>
+    <hyperlink ref="D249" r:id="rId349" xr:uid="{B4F90C89-EFCB-4817-97BC-06E995AFA609}"/>
+    <hyperlink ref="D254" r:id="rId350" xr:uid="{CC11044E-9CD7-43A8-8FC7-8F4033363256}"/>
+    <hyperlink ref="D279" r:id="rId351" xr:uid="{F084A607-2D86-44C0-9307-F7DBD00E5910}"/>
+    <hyperlink ref="D236" r:id="rId352" display="mailto:Julien.Nemery@grenoble-inp.fr" xr:uid="{0340649A-91E8-4CD6-A93C-F02A3516FBD4}"/>
+    <hyperlink ref="D299" r:id="rId353" xr:uid="{DD5B37F5-6526-40C8-8AF5-F9F118085BD4}"/>
+    <hyperlink ref="D327" r:id="rId354" xr:uid="{1D348DB7-61C1-4B44-B14B-8F272C0AB9C8}"/>
+    <hyperlink ref="D303" r:id="rId355" xr:uid="{092BCB24-DF23-4521-9366-47796D7A1189}"/>
+    <hyperlink ref="D283" r:id="rId356" xr:uid="{D2C18461-0626-41D1-A186-6B586C54C498}"/>
+    <hyperlink ref="D307" r:id="rId357" xr:uid="{6A8E7C01-635E-43A6-8684-5DD44770CE71}"/>
+    <hyperlink ref="D346" r:id="rId358" xr:uid="{0B48683A-8190-49F2-B408-691429B5C75D}"/>
+    <hyperlink ref="D298" r:id="rId359" xr:uid="{E917A3BE-1E99-4042-938B-501DB1125A7F}"/>
+    <hyperlink ref="D300" r:id="rId360" xr:uid="{6DC7C87F-6A4F-4F9D-8B5E-DD7C19AE2C8C}"/>
+    <hyperlink ref="D314" r:id="rId361" xr:uid="{D2E4342A-998D-4C92-817A-1854849A4F5A}"/>
+    <hyperlink ref="D239" r:id="rId362" display="mailto:edouard.metzger@univ-angers.fr" xr:uid="{68A70078-17A2-413F-955D-958F454E2BDD}"/>
+    <hyperlink ref="D253" r:id="rId363" xr:uid="{577CD300-9D35-404A-9BCF-12DEDAFEBE5A}"/>
+    <hyperlink ref="D396" r:id="rId364" xr:uid="{9D25B918-898A-4E55-BA20-F5CF4EB5EF43}"/>
+    <hyperlink ref="D347" r:id="rId365" xr:uid="{D43185F7-C1B9-4DA9-9F31-06BCFB2070BB}"/>
+    <hyperlink ref="D395" r:id="rId366" xr:uid="{6925CD77-67D4-4AA9-8DC4-90DC7FE42CCC}"/>
+    <hyperlink ref="D309" r:id="rId367" xr:uid="{FBF9589E-A068-4C59-B7D3-6DD5F904DCDF}"/>
+    <hyperlink ref="D354" r:id="rId368" xr:uid="{345A319F-E9C5-4319-8CCA-184E77AEE990}"/>
+    <hyperlink ref="D288" r:id="rId369" xr:uid="{95217B08-0875-4396-81C5-BD15C2082B12}"/>
+    <hyperlink ref="D399" r:id="rId370" xr:uid="{7FBE7C64-34EB-486B-BD55-A404857C69F3}"/>
+    <hyperlink ref="D85" r:id="rId371" xr:uid="{8BB6528A-7A82-4EA6-B4E3-59BB570A7940}"/>
+    <hyperlink ref="D104" r:id="rId372" xr:uid="{2FEA2974-9EDC-4C94-B2DF-B67ED2C4DCBB}"/>
+    <hyperlink ref="D219" r:id="rId373" xr:uid="{DA01D55F-3B9A-4FAE-9DD9-321C7F72D7E2}"/>
+    <hyperlink ref="D223" r:id="rId374" xr:uid="{9DA746D1-9366-49F7-BDDE-9D15C844BEE2}"/>
+    <hyperlink ref="D229" r:id="rId375" xr:uid="{CB30AC5E-5A87-41AF-8EF9-B26F875FD98B}"/>
+    <hyperlink ref="D232" r:id="rId376" xr:uid="{A850826F-14DC-4E67-9125-5DE3F036D6C0}"/>
+    <hyperlink ref="D234" r:id="rId377" xr:uid="{442608F8-7C23-4462-B0E5-3525EDD2ED27}"/>
+    <hyperlink ref="D238" r:id="rId378" xr:uid="{E617A275-FA10-4135-84AA-B2C7C8A58606}"/>
+    <hyperlink ref="D259" r:id="rId379" xr:uid="{A66F923C-D0DA-4E05-AD10-8E65B001868D}"/>
+    <hyperlink ref="D287" r:id="rId380" xr:uid="{98CB6401-7831-451C-9BA0-8E0C7FB494BD}"/>
+    <hyperlink ref="D275" r:id="rId381" xr:uid="{0C5F7513-341A-41A8-B847-782409F4099C}"/>
+    <hyperlink ref="D305" r:id="rId382" xr:uid="{25687851-9455-4418-B194-F10132D3FF9A}"/>
+    <hyperlink ref="D313" r:id="rId383" xr:uid="{103A6CE1-24A1-4129-9871-81911FF2A37E}"/>
+    <hyperlink ref="D315" r:id="rId384" xr:uid="{52D97BED-52C9-4312-8FC2-C91EFC6F31BC}"/>
+    <hyperlink ref="D322" r:id="rId385" xr:uid="{99009347-3884-4446-A8B6-CC7D3961074F}"/>
+    <hyperlink ref="D317" r:id="rId386" xr:uid="{B26FBE01-0A47-4D97-9E7E-95A6766AE01F}"/>
+    <hyperlink ref="D332" r:id="rId387" xr:uid="{EB97E93C-00C0-4AD5-A355-1B170395CCAB}"/>
+    <hyperlink ref="D333" r:id="rId388" xr:uid="{CEB884E1-2965-42F8-B096-BE1B6B1A7D2E}"/>
+    <hyperlink ref="D339" r:id="rId389" xr:uid="{346552CA-3DB0-464D-B1EB-BB6924835319}"/>
+    <hyperlink ref="D345" r:id="rId390" xr:uid="{83754732-A552-4928-82C9-6C3DEE7BDBDB}"/>
+    <hyperlink ref="D403" r:id="rId391" xr:uid="{4D5F8E6D-0878-497D-B0B9-B1DDC24BFA44}"/>
+    <hyperlink ref="D404" r:id="rId392" xr:uid="{221312BB-E30C-489C-B404-96A153BA2EF6}"/>
+    <hyperlink ref="D405" r:id="rId393" xr:uid="{36F3B07A-D7AF-4EC0-A1FB-995D18DBF2B3}"/>
+    <hyperlink ref="D406" r:id="rId394" xr:uid="{E3A248A1-605A-473D-AA97-5EF424538A01}"/>
+    <hyperlink ref="D285" r:id="rId395" xr:uid="{5C444050-0B17-4A00-87FB-C84FBD758629}"/>
+    <hyperlink ref="D407" r:id="rId396" xr:uid="{8B165C96-1F8F-4A67-8FC4-65A34E28CDD1}"/>
+    <hyperlink ref="D408" r:id="rId397" xr:uid="{305F290A-787F-428B-8FBC-3BF01E78F765}"/>
+    <hyperlink ref="D409" r:id="rId398" xr:uid="{491E24B7-56D7-48F3-94A5-8D6F75BA65E0}"/>
+    <hyperlink ref="D243" r:id="rId399" xr:uid="{2FC17624-9C68-459D-B98C-AFB693EED57D}"/>
+    <hyperlink ref="D251" r:id="rId400" xr:uid="{BE47F20D-E592-484C-9AFC-2968894359CC}"/>
+    <hyperlink ref="D286" r:id="rId401" xr:uid="{9EC30679-083A-4669-95D1-2BA126C26547}"/>
+    <hyperlink ref="D292" r:id="rId402" xr:uid="{830F9ED0-47CC-4A6C-AB9F-C7489C09FD87}"/>
+    <hyperlink ref="D294" r:id="rId403" xr:uid="{FF924A04-F87C-49BB-9912-00780382B722}"/>
+    <hyperlink ref="D295" r:id="rId404" xr:uid="{0AF25B3D-9D7C-456C-835F-4EFEFC314BEF}"/>
+    <hyperlink ref="D297" r:id="rId405" xr:uid="{08923573-FE1F-4D3A-85FF-C5E20DB195D5}"/>
+    <hyperlink ref="D301" r:id="rId406" xr:uid="{24E77A36-7AEA-434F-9781-11D6712883FD}"/>
+    <hyperlink ref="D302" r:id="rId407" xr:uid="{D46D7396-7329-41E4-8E90-E1CDE1AEF42C}"/>
+    <hyperlink ref="D410" r:id="rId408" xr:uid="{A7416774-29F7-4F4F-924B-792A9D712553}"/>
+    <hyperlink ref="D411" r:id="rId409" xr:uid="{4DE261F8-386C-4ED6-AF66-4AAF82F79CE5}"/>
+    <hyperlink ref="D413" r:id="rId410" xr:uid="{0C18FDD3-2B24-4205-81BA-3995121C96F6}"/>
+    <hyperlink ref="D414" r:id="rId411" xr:uid="{6C4998D7-E946-46E3-8189-6F0802D264CC}"/>
+    <hyperlink ref="D415" r:id="rId412" xr:uid="{529D853F-03FB-4599-A59D-EF805075D34C}"/>
+    <hyperlink ref="D417" r:id="rId413" xr:uid="{F676206E-337D-401B-B572-8209F6FC7689}"/>
+    <hyperlink ref="D418" r:id="rId414" xr:uid="{ED1C34DD-60C6-4B5E-BA8A-27EAA50F2247}"/>
+    <hyperlink ref="D419" r:id="rId415" xr:uid="{F8062A78-E827-4416-9A54-158C783B3932}"/>
+    <hyperlink ref="D420" r:id="rId416" xr:uid="{FF7C78E1-FD78-4893-95F0-5ECC3A18C68D}"/>
+    <hyperlink ref="D421" r:id="rId417" xr:uid="{1951E881-6FE0-45EA-8CF9-D3FAB9FAC8B9}"/>
+    <hyperlink ref="D422" r:id="rId418" xr:uid="{04BFC413-54BE-4617-8D8B-9C72AB166AAF}"/>
+    <hyperlink ref="D423" r:id="rId419" xr:uid="{81FF17D2-2BEB-4A2E-8086-A7339894774C}"/>
+    <hyperlink ref="D424" r:id="rId420" xr:uid="{CEFD15B6-7F4D-4782-9D04-1AC965A6F314}"/>
+    <hyperlink ref="D425" r:id="rId421" xr:uid="{EEA03FD2-AC2B-4961-8A53-F35C0569F7B5}"/>
+    <hyperlink ref="D426" r:id="rId422" xr:uid="{2F018061-F050-4285-8870-635B8A32F29A}"/>
+    <hyperlink ref="D427" r:id="rId423" xr:uid="{1C8B7244-B754-49C0-93A9-52FAF2E59442}"/>
+    <hyperlink ref="D428" r:id="rId424" xr:uid="{42B4EEC4-CC4F-46F0-BA44-432D13DFCAB0}"/>
+    <hyperlink ref="D429" r:id="rId425" xr:uid="{B818ECC1-0D14-4FE0-8D7A-EF3B2949C1F4}"/>
+    <hyperlink ref="D430" r:id="rId426" xr:uid="{7C54CDB8-2E2C-4F85-95D8-9CCF06C57051}"/>
+    <hyperlink ref="D431" r:id="rId427" xr:uid="{72D9903F-4B40-43B9-BF69-86CCE2B0220E}"/>
+    <hyperlink ref="D432" r:id="rId428" xr:uid="{3B0E34B5-9E6F-4FD2-998A-47E5C3F374E1}"/>
+    <hyperlink ref="D433" r:id="rId429" xr:uid="{1780FAF5-8279-44FE-8426-A56AE04C5435}"/>
+    <hyperlink ref="D434" r:id="rId430" xr:uid="{E7E12624-3FA9-4CDE-88E2-3885036864AC}"/>
+    <hyperlink ref="D435" r:id="rId431" xr:uid="{26399E30-9C6A-44E7-BE99-E9FAAA249EB2}"/>
+    <hyperlink ref="D436" r:id="rId432" xr:uid="{43DDE650-A356-4EEB-8A95-BF08588E2601}"/>
+    <hyperlink ref="D437" r:id="rId433" xr:uid="{B5B240FD-5858-4C23-BFF4-405327AB52AE}"/>
+    <hyperlink ref="D438" r:id="rId434" xr:uid="{3F7E3E72-560D-4F4C-B45F-74F76DF4C65A}"/>
+    <hyperlink ref="D439" r:id="rId435" xr:uid="{16EB9642-CB02-4AD9-9E59-E0E9AEEEC6E1}"/>
+    <hyperlink ref="D440" r:id="rId436" xr:uid="{25F01466-BB43-467C-AAA8-870D961BB103}"/>
+    <hyperlink ref="D441" r:id="rId437" xr:uid="{F14BF557-AE02-4E65-9F5F-80AF0F1CADBE}"/>
+    <hyperlink ref="D443" r:id="rId438" xr:uid="{C9DE96B8-B981-4C0E-AED0-D7BFC3FB0C46}"/>
+    <hyperlink ref="D442" r:id="rId439" xr:uid="{066BA859-62BD-4FF8-97FF-A2E77D3A68B9}"/>
+    <hyperlink ref="D444" r:id="rId440" xr:uid="{F07747EA-ACD0-43CD-B097-4032EB770B0C}"/>
+    <hyperlink ref="D445" r:id="rId441" xr:uid="{D76B884C-B3B8-45FB-A7B2-0D9DC4AB9180}"/>
+    <hyperlink ref="D446" r:id="rId442" xr:uid="{5142E7B2-092E-48C4-B763-6C80E4508656}"/>
+    <hyperlink ref="D447" r:id="rId443" xr:uid="{2806A5F7-D0D6-4CBF-8AE7-ED969A65899C}"/>
+    <hyperlink ref="D448" r:id="rId444" xr:uid="{4CBC30FC-EC28-4F92-BAAB-A7D5426DC291}"/>
+    <hyperlink ref="D455" r:id="rId445" xr:uid="{944585FB-6DF5-482E-94C4-4F3002E9C190}"/>
+    <hyperlink ref="D449" r:id="rId446" xr:uid="{301A6C3B-67D8-44F3-9913-8500A6811777}"/>
+    <hyperlink ref="D451" r:id="rId447" xr:uid="{0369DACF-8B99-477C-B3D2-51E99868F5B8}"/>
+    <hyperlink ref="D452" r:id="rId448" xr:uid="{44B3876D-448F-430E-87F7-424D38B98B30}"/>
+    <hyperlink ref="D450" r:id="rId449" xr:uid="{008ACA58-7701-497B-B0A3-519950BBE4CC}"/>
+    <hyperlink ref="D453" r:id="rId450" xr:uid="{F59C6A4C-5BC0-4B69-BC57-701368441DDD}"/>
+    <hyperlink ref="D454" r:id="rId451" xr:uid="{7242D59C-76B9-4F59-B5E8-E7FCFEA6A9B8}"/>
+    <hyperlink ref="D456" r:id="rId452" xr:uid="{977B6D01-7EFC-4495-842A-7F9F55328112}"/>
+    <hyperlink ref="D464" r:id="rId453" xr:uid="{6EBA8B29-8166-4838-AE71-594FE588E88C}"/>
+    <hyperlink ref="D457" r:id="rId454" xr:uid="{FBD81D96-22AD-4141-B9E4-55EEA145BD57}"/>
+    <hyperlink ref="D458" r:id="rId455" xr:uid="{A7BEE7A1-459B-41E9-8610-40E27BE09933}"/>
+    <hyperlink ref="D460" r:id="rId456" xr:uid="{8DC9DBCB-1254-4CC1-B0F5-E70A8A6C79DA}"/>
+    <hyperlink ref="D459" r:id="rId457" xr:uid="{A40CF748-8CB1-4B3C-B4C7-6BE4B4B455C0}"/>
+    <hyperlink ref="D461" r:id="rId458" xr:uid="{F7FB6ADF-AADA-4E38-9500-17B22C6B5C03}"/>
+    <hyperlink ref="D462" r:id="rId459" xr:uid="{D0AB0ABD-86EE-4DAC-90C7-3DA805D7023D}"/>
+    <hyperlink ref="D463" r:id="rId460" xr:uid="{0594FD5F-084F-440C-A3C7-66358ECC43F9}"/>
+    <hyperlink ref="D465" r:id="rId461" xr:uid="{87E44FE2-8212-468A-A66A-CEAB8D9CF125}"/>
+    <hyperlink ref="D466" r:id="rId462" xr:uid="{69B1CC96-8066-45ED-9179-FA1449C0202C}"/>
+    <hyperlink ref="D467" r:id="rId463" xr:uid="{1B3B16CC-DFD9-4085-8296-C2989574E88B}"/>
+    <hyperlink ref="D468" r:id="rId464" xr:uid="{F79321DC-2AF6-4E62-8F3A-A930EA38652B}"/>
+    <hyperlink ref="D469" r:id="rId465" xr:uid="{B8B2F5AE-2D2E-4E32-BA34-BDDEC7C1E847}"/>
+    <hyperlink ref="D470" r:id="rId466" xr:uid="{D830768F-3C92-4000-9E5B-3618C7D57334}"/>
+    <hyperlink ref="D471" r:id="rId467" xr:uid="{C04D2C5A-1965-4933-B470-2E435F1FEB22}"/>
+    <hyperlink ref="D472" r:id="rId468" xr:uid="{3F0C90F5-A494-48DF-91E3-B26F262CE8AA}"/>
+    <hyperlink ref="D473" r:id="rId469" xr:uid="{829A7829-B841-420A-8A5E-521C33C8411B}"/>
+    <hyperlink ref="D474" r:id="rId470" xr:uid="{CF597D61-8B8A-480F-8984-7C9FA7211D37}"/>
+    <hyperlink ref="D475" r:id="rId471" xr:uid="{9976A513-C5C0-447B-A1C7-3EB4558EB98A}"/>
+    <hyperlink ref="D476" r:id="rId472" xr:uid="{707B707C-F0EC-45C1-9A0B-9FE6C2912F76}"/>
+    <hyperlink ref="D477" r:id="rId473" xr:uid="{4D357EAB-8BAC-42A0-B0F5-2CF83E795742}"/>
+    <hyperlink ref="D478" r:id="rId474" xr:uid="{42E6DF94-D998-4634-BD5D-4F25DD4AC797}"/>
+    <hyperlink ref="D479" r:id="rId475" xr:uid="{C74B994B-4C61-486A-9700-43EB53D1CC79}"/>
+    <hyperlink ref="D480" r:id="rId476" xr:uid="{82387677-0E3D-4DE8-81C0-5B8B2219D9EC}"/>
+    <hyperlink ref="D481" r:id="rId477" xr:uid="{AD4EB573-74B0-4AB9-A11A-A180398E3EC5}"/>
+    <hyperlink ref="D482" r:id="rId478" xr:uid="{9E0DF20B-D878-4B6F-8E7C-EBFAB91B239D}"/>
+    <hyperlink ref="D483" r:id="rId479" xr:uid="{E7A48EEF-AE5C-492F-AEC6-62119BA038D3}"/>
+    <hyperlink ref="D484" r:id="rId480" xr:uid="{F8CFE556-D0C9-4745-8166-5B94D1135260}"/>
+    <hyperlink ref="D485" r:id="rId481" xr:uid="{FBA23B10-797D-451F-93F4-5D4ECF58DF18}"/>
+    <hyperlink ref="D486" r:id="rId482" xr:uid="{77CD5E52-13F7-40F8-B7C2-6356F876B868}"/>
+    <hyperlink ref="D487" r:id="rId483" xr:uid="{17DDF098-1759-4D47-8BDD-B66B0EB49FD9}"/>
+    <hyperlink ref="D493" r:id="rId484" xr:uid="{80975341-5200-460B-827B-99751CFC6930}"/>
+    <hyperlink ref="D494" r:id="rId485" xr:uid="{AA58D0B0-EF24-4AC7-8BEB-AC999FFBDF33}"/>
+    <hyperlink ref="D498" r:id="rId486" xr:uid="{133AD072-82C7-4880-9A68-A88FA1CE8863}"/>
+    <hyperlink ref="D515" r:id="rId487" xr:uid="{E2FA476C-A3B8-4177-9E08-97829E6AF772}"/>
+    <hyperlink ref="D516" r:id="rId488" xr:uid="{20FE7417-F51B-4D23-B39D-2F70B920D94D}"/>
+    <hyperlink ref="D517" r:id="rId489" xr:uid="{A6A904AA-9765-4CFF-AF9D-3460FDC5FD5B}"/>
+    <hyperlink ref="D519" r:id="rId490" xr:uid="{20503C73-A4CD-4B0B-8CC6-60D2A6B6F011}"/>
+    <hyperlink ref="D518" r:id="rId491" xr:uid="{7C159450-EF70-4C63-A18C-52EA8AADD36D}"/>
+    <hyperlink ref="D520" r:id="rId492" xr:uid="{304D3556-D71B-420C-82E8-90E3886F4A5E}"/>
+    <hyperlink ref="D521" r:id="rId493" xr:uid="{2C92EED8-6B25-47D2-BF43-61BC35491C20}"/>
+    <hyperlink ref="D522" r:id="rId494" xr:uid="{002660D7-38F8-4E4E-ADFB-017344CF4B51}"/>
+    <hyperlink ref="D416" r:id="rId495" xr:uid="{59677F8D-E486-4D61-86C9-269A2D029F17}"/>
+    <hyperlink ref="D533" r:id="rId496" xr:uid="{1B274682-180A-4F17-A146-1AAAA61C7F81}"/>
+    <hyperlink ref="D80" r:id="rId497" xr:uid="{FF4D3CF3-B972-4816-93B0-7450E1009BA9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId498"/>
